--- a/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
+++ b/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D803C876-E965-4529-8BED-7102C166DD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02CA20E-20D9-4C1C-95C7-226F380FE415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3510" yWindow="3510" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="239">
   <si>
     <t>Payday Super review: s 18C deadlines and the SG charge estimate</t>
   </si>
@@ -100,6 +100,18 @@
     <t>defined_benefit</t>
   </si>
   <si>
+    <t>Pay_day</t>
+  </si>
+  <si>
+    <t>Remit_day</t>
+  </si>
+  <si>
+    <t>Recv_day</t>
+  </si>
+  <si>
+    <t>Next_day</t>
+  </si>
+  <si>
     <t>Flag_db</t>
   </si>
   <si>
@@ -199,6 +211,9 @@
     <t>Outstanding_to</t>
   </si>
   <si>
+    <t>Accrual_to</t>
+  </si>
+  <si>
     <t>NEC_end</t>
   </si>
   <si>
@@ -568,9 +583,15 @@
     <t>As-at date (notional earnings on unpaid lines run to it)</t>
   </si>
   <si>
+    <t>As-at date used by the register (whole day)</t>
+  </si>
+  <si>
     <t>ATO assessment date (blank if none has issued)</t>
   </si>
   <si>
+    <t>Assessment date used by the register (whole day)</t>
+  </si>
+  <si>
     <t>LCR 2026/1 transition allocation reconciled and confirmed (Y/N)</t>
   </si>
   <si>
@@ -652,7 +673,7 @@
     <t>Lines assessed at a nil SG amount (nothing to assess)</t>
   </si>
   <si>
-    <t>As-at, assessment and coverage dates on Summary are dates</t>
+    <t>As-at, assessment and coverage dates on Summary are real dates</t>
   </si>
   <si>
     <t>No fabricated example line from the shipped sample remains in the register</t>
@@ -827,9 +848,9 @@
     <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
@@ -923,8 +944,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblLines" displayName="tblLines" ref="A1:BH11">
-  <tableColumns count="60">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblLines" displayName="tblLines" ref="A1:BM11">
+  <tableColumns count="65">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="employee_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="payment_date"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="sg_amount"/>
@@ -936,152 +957,167 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="out_of_cycle"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="next_standard_payday"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="defined_benefit"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Flag_db">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Pay_day">
+      <calculatedColumnFormula>IF(tblLines[[#This Row],[payment_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),INT(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Remit_day">
+      <calculatedColumnFormula>IF(tblLines[[#This Row],[remitted_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[remitted_date]]),INT(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Recv_day">
+      <calculatedColumnFormula>IF(tblLines[[#This Row],[fund_received_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),INT(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Next_day">
+      <calculatedColumnFormula>IF(tblLines[[#This Row],[next_standard_payday]]="","",IF(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),INT(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Flag_db">
       <calculatedColumnFormula>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Flag_ooc">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Flag_ooc">
       <calculatedColumnFormula>IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"","0","f","false","n","no"}),0,""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Flag_ftf">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Flag_ftf">
       <calculatedColumnFormula>IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"","0","f","false","n","no"}),0,""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Row_problem">
-      <calculatedColumnFormula>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</calculatedColumnFormula>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Row_problem">
+      <calculatedColumnFormula>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]&gt;DATE(2200,12,31))),"date-not-real ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Pay_day]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[sg_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[remitted_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[matched_amount]],2)=0)),"amount-under-half-a-cent ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[Remit_day]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[matched_amount]],2)),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&lt;ROUND(tblLines[[#This Row],[sg_amount]],2),ISNUMBER(tblLines[[#This Row],[Remit_day]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Remit_day]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Next_day]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]]),ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Next_day]]&lt;=tblLines[[#This Row],[Pay_day]]),"next_standard_payday-not-after-payday ",""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Guard">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Guard">
       <calculatedColumnFormula>IF(OR(_xlfn.ISFORMULA(tblLines[[#This Row],[employee_id]]),_xlfn.ISFORMULA(tblLines[[#This Row],[payment_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[sg_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[matched_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[fund_received_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[first_contribution_to_fund]]),_xlfn.ISFORMULA(tblLines[[#This Row],[out_of_cycle]]),_xlfn.ISFORMULA(tblLines[[#This Row],[next_standard_payday]]),_xlfn.ISFORMULA(tblLines[[#This Row],[defined_benefit]])),1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Cap">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Cap">
       <calculatedColumnFormula>IF(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]],IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]],tblLines[[#This Row],[sg_amount]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Due_ooc">
-      <calculatedColumnFormula>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]])),WORKDAY.INTL(tblLines[[#This Row],[next_standard_payday]],7,1,tblHolidays[date]),"")</calculatedColumnFormula>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Due_ooc">
+      <calculatedColumnFormula>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]])),WORKDAY.INTL(tblLines[[#This Row],[Next_day]],7,1,tblHolidays[date]),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Due_ftf">
-      <calculatedColumnFormula>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</calculatedColumnFormula>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Due_ftf">
+      <calculatedColumnFormula>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],20,1,tblHolidays[date]),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Own_due">
-      <calculatedColumnFormula>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</calculatedColumnFormula>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Own_due">
+      <calculatedColumnFormula>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],7,1,tblHolidays[date])))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Own_pathway">
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Own_pathway">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Earliest_prepay">
-      <calculatedColumnFormula>IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),EDATE(tblLines[[#This Row],[payment_date]]-1,-12)+1,"")</calculatedColumnFormula>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Earliest_prepay">
+      <calculatedColumnFormula>IF(ISNUMBER(tblLines[[#This Row],[Pay_day]]),EDATE(tblLines[[#This Row],[Pay_day]]-1,-12)+1,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Settled">
-      <calculatedColumnFormula>IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[fund_received_date]],"")</calculatedColumnFormula>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Settled">
+      <calculatedColumnFormula>IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Recv_day]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Remit">
-      <calculatedColumnFormula>IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[remitted_date]],"")</calculatedColumnFormula>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Remit">
+      <calculatedColumnFormula>IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Remit_day]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Receipt_credit">
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="Receipt_credit">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[Cap]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Credit">
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Credit">
       <calculatedColumnFormula>IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[remitted_amount]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",ROUND(tblLines[[#This Row],[sg_amount]],2),0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Evidence_own">
-      <calculatedColumnFormula>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</calculatedColumnFormula>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="Evidence_own">
+      <calculatedColumnFormula>IF(OR(tblLines[[#This Row],[Own_due]]=0,ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,tblLines[[#This Row],[Flag_db]]=1,ROUND(tblLines[[#This Row],[Cap]],2)&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),IF(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2,IF(OR(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[Recv_day]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Confirmed_latest">
-      <calculatedColumnFormula array="1">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</calculatedColumnFormula>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="Confirmed_latest">
+      <calculatedColumnFormula array="1">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="Possible_latest">
-      <calculatedColumnFormula array="1">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</calculatedColumnFormula>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="Possible_latest">
+      <calculatedColumnFormula array="1">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Final_due">
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="Final_due">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="Pathway">
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="Pathway">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="Possible_item4">
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="Possible_item4">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Final_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Possible_latest]]),tblLines[[#This Row],[Possible_latest]]&gt;tblLines[[#This Row],[Final_due]]),tblLines[[#This Row],[Possible_latest]],""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="Past_horizon">
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="Past_horizon">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Final_due]]="","",IF((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),1,0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="Branch">
-      <calculatedColumnFormula>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(tblLines[[#This Row],[sg_amount]]&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[payment_date]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"B1",IF(Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</calculatedColumnFormula>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="Branch">
+      <calculatedColumnFormula>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="Verdict">
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="Verdict">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Branch]]="","",INDEX(tblCodes[verdict],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="Unassessable_between">
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="Unassessable_between">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Branch]]="","",T(INDEX(tblCodes[unassessable],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="Exposed">
+    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="Exposed">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[exposed],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="Stale_prepay">
+    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="Stale_prepay">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[stale],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="OTRC">
+    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="OTRC">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[otrc],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))*tblLines[[#This Row],[Receipt_credit]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="Base_shortfall">
+    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="Base_shortfall">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),MAX(ROUND(tblLines[[#This Row],[sg_amount]],2)-tblLines[[#This Row],[OTRC]],0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="Offset_s18D">
-      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$B$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$B$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</calculatedColumnFormula>
+    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="Offset_s18D">
+      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="Final_shortfall">
+    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="Final_shortfall">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),MAX(tblLines[[#This Row],[Base_shortfall]]-tblLines[[#This Row],[Offset_s18D]],0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="Lateness_basis">
-      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</calculatedColumnFormula>
+    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="Lateness_basis">
+      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="Outstanding_to">
-      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[Settled]],Summary!$B$2),"")</calculatedColumnFormula>
+    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="Outstanding_to">
+      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="NEC_end">
-      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),MIN(IF(Summary!$B$3="",DATE(2030,12,31),Summary!$B$3-1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$B$2)),"")</calculatedColumnFormula>
+    <tableColumn id="49" xr3:uid="{00000000-0010-0000-0000-000031000000}" name="Accrual_to">
+      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="Days_late">
+    <tableColumn id="50" xr3:uid="{00000000-0010-0000-0000-000032000000}" name="NEC_end">
+      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(Summary!$D$3="",tblLines[[#This Row],[Accrual_to]],MIN(Summary!$D$3-1,tblLines[[#This Row],[Accrual_to]])),"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="51" xr3:uid="{00000000-0010-0000-0000-000033000000}" name="Days_late">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="NEC">
+    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" name="NEC">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="GIC_estimated">
+    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" name="GIC_estimated">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="49" xr3:uid="{00000000-0010-0000-0000-000031000000}" name="Shortfall_r">
+    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" name="Shortfall_r">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="50" xr3:uid="{00000000-0010-0000-0000-000032000000}" name="NEC_r">
+    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" name="NEC_r">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="51" xr3:uid="{00000000-0010-0000-0000-000033000000}" name="Uplift_best">
+    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" name="Uplift_best">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" name="Uplift_worst">
+    <tableColumn id="57" xr3:uid="{00000000-0010-0000-0000-000039000000}" name="Uplift_worst">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" name="SGC_low">
+    <tableColumn id="58" xr3:uid="{00000000-0010-0000-0000-00003A000000}" name="SGC_low">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" name="SGC_high">
+    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0000-00003B000000}" name="SGC_high">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" name="Transition_row">
-      <calculatedColumnFormula>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0,tblLines[[#This Row],[Cap]]&gt;0,OR(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]])),IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]],tblLines[[#This Row],[remitted_date]])&lt;=DATE(2026,7,28)),1,0)</calculatedColumnFormula>
+    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0000-00003C000000}" name="Transition_row">
+      <calculatedColumnFormula>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0,ROUND(tblLines[[#This Row],[Cap]],2)&gt;0,OR(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]])),IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]],tblLines[[#This Row],[Remit_day]])&lt;=DATE(2026,7,28)),1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" name="Receipt_established">
+    <tableColumn id="61" xr3:uid="{00000000-0010-0000-0000-00003D000000}" name="Receipt_established">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="57" xr3:uid="{00000000-0010-0000-0000-000039000000}" name="Assessable">
-      <calculatedColumnFormula>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0),1,0)</calculatedColumnFormula>
+    <tableColumn id="62" xr3:uid="{00000000-0010-0000-0000-00003E000000}" name="Assessable">
+      <calculatedColumnFormula>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0),1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="58" xr3:uid="{00000000-0010-0000-0000-00003A000000}" name="Duplicate">
-      <calculatedColumnFormula>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</calculatedColumnFormula>
+    <tableColumn id="63" xr3:uid="{00000000-0010-0000-0000-00003F000000}" name="Duplicate">
+      <calculatedColumnFormula>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[Pay_day]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[Remit_day]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[Recv_day]]&amp;"")&gt;1,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0000-00003B000000}" name="Case_variant">
+    <tableColumn id="64" xr3:uid="{00000000-0010-0000-0000-000040000000}" name="Case_variant">
       <calculatedColumnFormula array="1">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0000-00003C000000}" name="Sample_row">
-      <calculatedColumnFormula>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</calculatedColumnFormula>
+    <tableColumn id="65" xr3:uid="{00000000-0010-0000-0000-000041000000}" name="Sample_row">
+      <calculatedColumnFormula>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[Pay_day]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1114,7 +1150,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tblGic" displayName="tblGic" ref="A1:F8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tblGic" displayName="tblGic" ref="A1:F178">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="from"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="to"/>
@@ -1487,19 +1523,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BH11"/>
+  <dimension ref="A1:BM11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="30" customWidth="1"/>
-    <col min="16" max="35" width="13" customWidth="1"/>
-    <col min="36" max="36" width="22" customWidth="1"/>
-    <col min="37" max="42" width="13" customWidth="1"/>
-    <col min="43" max="43" width="34" customWidth="1"/>
-    <col min="44" max="60" width="13" customWidth="1"/>
+    <col min="1" max="18" width="13" customWidth="1"/>
+    <col min="19" max="19" width="30" customWidth="1"/>
+    <col min="20" max="39" width="13" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="34" customWidth="1"/>
+    <col min="48" max="65" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
@@ -1680,10 +1716,25 @@
       <c r="BH1" s="5" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="2" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="BI1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="BK1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="BL1" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="BM1" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B2" s="7">
         <v>46212</v>
@@ -1700,215 +1751,235 @@
         <v>46219</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J2" s="7"/>
       <c r="K2" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L2" s="9">
+        <f>IF(tblLines[[#This Row],[payment_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),INT(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]))</f>
+        <v>46212</v>
+      </c>
+      <c r="M2" s="9">
+        <f>IF(tblLines[[#This Row],[remitted_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[remitted_date]]),INT(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]))</f>
+        <v>46217</v>
+      </c>
+      <c r="N2" s="9">
+        <f>IF(tblLines[[#This Row],[fund_received_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),INT(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]))</f>
+        <v>46219</v>
+      </c>
+      <c r="O2" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[next_standard_payday]]="","",IF(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),INT(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]))</f>
+        <v/>
+      </c>
+      <c r="P2" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="M2" s="9">
+      <c r="Q2" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="N2" s="9">
+      <c r="R2" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="O2" s="9" t="str">
-        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
-        <v/>
-      </c>
-      <c r="P2" s="9">
+      <c r="S2" s="10" t="str">
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]&gt;DATE(2200,12,31))),"date-not-real ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Pay_day]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[sg_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[remitted_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[matched_amount]],2)=0)),"amount-under-half-a-cent ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[Remit_day]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[matched_amount]],2)),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&lt;ROUND(tblLines[[#This Row],[sg_amount]],2),ISNUMBER(tblLines[[#This Row],[Remit_day]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Remit_day]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Next_day]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]]),ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Next_day]]&lt;=tblLines[[#This Row],[Pay_day]]),"next_standard_payday-not-after-payday ",""))</f>
+        <v/>
+      </c>
+      <c r="T2" s="10">
         <f>IF(OR(_xlfn.ISFORMULA(tblLines[[#This Row],[employee_id]]),_xlfn.ISFORMULA(tblLines[[#This Row],[payment_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[sg_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[matched_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[fund_received_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[first_contribution_to_fund]]),_xlfn.ISFORMULA(tblLines[[#This Row],[out_of_cycle]]),_xlfn.ISFORMULA(tblLines[[#This Row],[next_standard_payday]]),_xlfn.ISFORMULA(tblLines[[#This Row],[defined_benefit]])),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="U2" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]],IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]],tblLines[[#This Row],[sg_amount]]))</f>
         <v>612</v>
       </c>
-      <c r="R2" s="11" t="str">
-        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]])),WORKDAY.INTL(tblLines[[#This Row],[next_standard_payday]],7,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="S2" s="11" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="T2" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+      <c r="V2" s="9" t="str">
+        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]])),WORKDAY.INTL(tblLines[[#This Row],[Next_day]],7,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="W2" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],20,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="X2" s="9">
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],7,1,tblHolidays[date])))</f>
         <v>46223</v>
       </c>
-      <c r="U2" s="9" t="str">
+      <c r="Y2" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="V2" s="11">
-        <f>IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),EDATE(tblLines[[#This Row],[payment_date]]-1,-12)+1,"")</f>
+      <c r="Z2" s="9">
+        <f>IF(ISNUMBER(tblLines[[#This Row],[Pay_day]]),EDATE(tblLines[[#This Row],[Pay_day]]-1,-12)+1,"")</f>
         <v>45847</v>
       </c>
-      <c r="W2" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[fund_received_date]],"")</f>
+      <c r="AA2" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Recv_day]],"")</f>
         <v>46219</v>
       </c>
-      <c r="X2" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[remitted_date]],"")</f>
+      <c r="AB2" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Remit_day]],"")</f>
         <v>46217</v>
       </c>
-      <c r="Y2" s="10">
+      <c r="AC2" s="11">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[Cap]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0)</f>
         <v>612</v>
       </c>
-      <c r="Z2" s="10">
+      <c r="AD2" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[remitted_amount]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",ROUND(tblLines[[#This Row],[sg_amount]],2),0))</f>
         <v>612</v>
       </c>
-      <c r="AA2" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+      <c r="AE2" s="10" t="str">
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,tblLines[[#This Row],[Flag_db]]=1,ROUND(tblLines[[#This Row],[Cap]],2)&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),IF(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2,IF(OR(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[Recv_day]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>confirmed</v>
       </c>
-      <c r="AB2" s="11">
-        <f t="array" ref="AB2">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AC2" s="11">
-        <f t="array" ref="AC2">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AD2" s="11">
+      <c r="AF2" s="9">
+        <f t="array" ref="AF2">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AG2" s="9">
+        <f t="array" ref="AG2">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AH2" s="9">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46223</v>
       </c>
-      <c r="AE2" s="9" t="str">
+      <c r="AI2" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="AF2" s="11" t="str">
+      <c r="AJ2" s="9" t="str">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Possible_latest]]),tblLines[[#This Row],[Possible_latest]]&gt;tblLines[[#This Row],[Final_due]]),tblLines[[#This Row],[Possible_latest]],""))</f>
         <v/>
       </c>
-      <c r="AG2" s="9">
+      <c r="AK2" s="10">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),1,0))</f>
         <v>0</v>
       </c>
-      <c r="AH2" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(tblLines[[#This Row],[sg_amount]]&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[payment_date]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"B1",IF(Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+      <c r="AL2" s="10" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>D1</v>
       </c>
-      <c r="AI2" s="9" t="str">
+      <c r="AM2" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",INDEX(tblCodes[verdict],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>ON_TIME</v>
       </c>
-      <c r="AJ2" s="9" t="str">
+      <c r="AN2" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",T(INDEX(tblCodes[unassessable],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))))</f>
         <v/>
       </c>
-      <c r="AK2" s="9">
+      <c r="AO2" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[exposed],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AL2" s="9">
+      <c r="AP2" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[stale],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AM2" s="10">
+      <c r="AQ2" s="11">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[otrc],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))*tblLines[[#This Row],[Receipt_credit]])</f>
         <v>612</v>
       </c>
-      <c r="AN2" s="10" t="str">
+      <c r="AR2" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(ROUND(tblLines[[#This Row],[sg_amount]],2)-tblLines[[#This Row],[OTRC]],0),"")</f>
         <v/>
       </c>
-      <c r="AO2" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$B$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$B$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
-        <v/>
-      </c>
-      <c r="AP2" s="10" t="str">
+      <c r="AS2" s="11" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="AT2" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(tblLines[[#This Row],[Base_shortfall]]-tblLines[[#This Row],[Offset_s18D]],0),"")</f>
         <v/>
       </c>
-      <c r="AQ2" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
-        <v/>
-      </c>
-      <c r="AR2" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[Settled]],Summary!$B$2),"")</f>
-        <v/>
-      </c>
-      <c r="AS2" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),MIN(IF(Summary!$B$3="",DATE(2030,12,31),Summary!$B$3-1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$B$2)),"")</f>
-        <v/>
-      </c>
-      <c r="AT2" s="9" t="str">
+      <c r="AU2" s="10" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <v/>
+      </c>
+      <c r="AV2" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AW2" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AX2" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(Summary!$D$3="",tblLines[[#This Row],[Accrual_to]],MIN(Summary!$D$3-1,tblLines[[#This Row],[Accrual_to]])),"")</f>
+        <v/>
+      </c>
+      <c r="AY2" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v/>
       </c>
-      <c r="AU2" s="10" t="str">
+      <c r="AZ2" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
         <v/>
       </c>
-      <c r="AV2" s="9" t="str">
+      <c r="BA2" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
         <v/>
       </c>
-      <c r="AW2" s="10" t="str">
+      <c r="BB2" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</f>
         <v/>
       </c>
-      <c r="AX2" s="10" t="str">
+      <c r="BC2" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
         <v/>
       </c>
-      <c r="AY2" s="10" t="str">
+      <c r="BD2" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
         <v/>
       </c>
-      <c r="AZ2" s="10" t="str">
+      <c r="BE2" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
         <v/>
       </c>
-      <c r="BA2" s="10" t="str">
+      <c r="BF2" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
         <v/>
       </c>
-      <c r="BB2" s="10" t="str">
+      <c r="BG2" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
         <v/>
       </c>
-      <c r="BC2" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0,tblLines[[#This Row],[Cap]]&gt;0,OR(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]])),IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]],tblLines[[#This Row],[remitted_date]])&lt;=DATE(2026,7,28)),1,0)</f>
+      <c r="BH2" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0,ROUND(tblLines[[#This Row],[Cap]],2)&gt;0,OR(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]])),IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]],tblLines[[#This Row],[Remit_day]])&lt;=DATE(2026,7,28)),1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD2" s="9">
+      <c r="BI2" s="10">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE2" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0),1,0)</f>
+      <c r="BJ2" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF2" s="9">
-        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BG2" s="9">
-        <f t="array" ref="BG2">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH2" s="9">
-        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+      <c r="BK2" s="10">
+        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[Pay_day]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[Remit_day]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[Recv_day]]&amp;"")&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL2" s="10">
+        <f t="array" ref="BL2">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM2" s="10">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[Pay_day]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B3" s="7">
         <v>46212</v>
@@ -1925,215 +1996,235 @@
         <v>46238</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J3" s="7"/>
       <c r="K3" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L3" s="9">
+        <f>IF(tblLines[[#This Row],[payment_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),INT(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]))</f>
+        <v>46212</v>
+      </c>
+      <c r="M3" s="9">
+        <f>IF(tblLines[[#This Row],[remitted_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[remitted_date]]),INT(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]))</f>
+        <v>46233</v>
+      </c>
+      <c r="N3" s="9">
+        <f>IF(tblLines[[#This Row],[fund_received_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),INT(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]))</f>
+        <v>46238</v>
+      </c>
+      <c r="O3" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[next_standard_payday]]="","",IF(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),INT(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]))</f>
+        <v/>
+      </c>
+      <c r="P3" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="M3" s="9">
+      <c r="Q3" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="N3" s="9">
+      <c r="R3" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="O3" s="9" t="str">
-        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
-        <v/>
-      </c>
-      <c r="P3" s="9">
+      <c r="S3" s="10" t="str">
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]&gt;DATE(2200,12,31))),"date-not-real ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Pay_day]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[sg_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[remitted_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[matched_amount]],2)=0)),"amount-under-half-a-cent ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[Remit_day]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[matched_amount]],2)),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&lt;ROUND(tblLines[[#This Row],[sg_amount]],2),ISNUMBER(tblLines[[#This Row],[Remit_day]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Remit_day]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Next_day]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]]),ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Next_day]]&lt;=tblLines[[#This Row],[Pay_day]]),"next_standard_payday-not-after-payday ",""))</f>
+        <v/>
+      </c>
+      <c r="T3" s="10">
         <f>IF(OR(_xlfn.ISFORMULA(tblLines[[#This Row],[employee_id]]),_xlfn.ISFORMULA(tblLines[[#This Row],[payment_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[sg_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[matched_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[fund_received_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[first_contribution_to_fund]]),_xlfn.ISFORMULA(tblLines[[#This Row],[out_of_cycle]]),_xlfn.ISFORMULA(tblLines[[#This Row],[next_standard_payday]]),_xlfn.ISFORMULA(tblLines[[#This Row],[defined_benefit]])),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="10">
+      <c r="U3" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]],IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]],tblLines[[#This Row],[sg_amount]]))</f>
         <v>540</v>
       </c>
-      <c r="R3" s="11" t="str">
-        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]])),WORKDAY.INTL(tblLines[[#This Row],[next_standard_payday]],7,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="S3" s="11" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="T3" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+      <c r="V3" s="9" t="str">
+        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]])),WORKDAY.INTL(tblLines[[#This Row],[Next_day]],7,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="W3" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],20,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="X3" s="9">
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],7,1,tblHolidays[date])))</f>
         <v>46223</v>
       </c>
-      <c r="U3" s="9" t="str">
+      <c r="Y3" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="V3" s="11">
-        <f>IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),EDATE(tblLines[[#This Row],[payment_date]]-1,-12)+1,"")</f>
+      <c r="Z3" s="9">
+        <f>IF(ISNUMBER(tblLines[[#This Row],[Pay_day]]),EDATE(tblLines[[#This Row],[Pay_day]]-1,-12)+1,"")</f>
         <v>45847</v>
       </c>
-      <c r="W3" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[fund_received_date]],"")</f>
+      <c r="AA3" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Recv_day]],"")</f>
         <v>46238</v>
       </c>
-      <c r="X3" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[remitted_date]],"")</f>
+      <c r="AB3" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Remit_day]],"")</f>
         <v>46233</v>
       </c>
-      <c r="Y3" s="10">
+      <c r="AC3" s="11">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[Cap]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0)</f>
         <v>540</v>
       </c>
-      <c r="Z3" s="10">
+      <c r="AD3" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[remitted_amount]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",ROUND(tblLines[[#This Row],[sg_amount]],2),0))</f>
         <v>540</v>
       </c>
-      <c r="AA3" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+      <c r="AE3" s="10" t="str">
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,tblLines[[#This Row],[Flag_db]]=1,ROUND(tblLines[[#This Row],[Cap]],2)&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),IF(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2,IF(OR(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[Recv_day]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>impossible</v>
       </c>
-      <c r="AB3" s="11">
-        <f t="array" ref="AB3">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AC3" s="11">
-        <f t="array" ref="AC3">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AD3" s="11">
+      <c r="AF3" s="9">
+        <f t="array" ref="AF3">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AG3" s="9">
+        <f t="array" ref="AG3">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AH3" s="9">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46223</v>
       </c>
-      <c r="AE3" s="9" t="str">
+      <c r="AI3" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="AF3" s="11" t="str">
+      <c r="AJ3" s="9" t="str">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Possible_latest]]),tblLines[[#This Row],[Possible_latest]]&gt;tblLines[[#This Row],[Final_due]]),tblLines[[#This Row],[Possible_latest]],""))</f>
         <v/>
       </c>
-      <c r="AG3" s="9">
+      <c r="AK3" s="10">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),1,0))</f>
         <v>0</v>
       </c>
-      <c r="AH3" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(tblLines[[#This Row],[sg_amount]]&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[payment_date]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"B1",IF(Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+      <c r="AL3" s="10" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>E</v>
       </c>
-      <c r="AI3" s="9" t="str">
+      <c r="AM3" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",INDEX(tblCodes[verdict],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>LATE</v>
       </c>
-      <c r="AJ3" s="9" t="str">
+      <c r="AN3" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",T(INDEX(tblCodes[unassessable],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))))</f>
         <v/>
       </c>
-      <c r="AK3" s="9">
+      <c r="AO3" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[exposed],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>1</v>
       </c>
-      <c r="AL3" s="9">
+      <c r="AP3" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[stale],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AM3" s="10">
+      <c r="AQ3" s="11">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[otrc],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))*tblLines[[#This Row],[Receipt_credit]])</f>
         <v>0</v>
       </c>
-      <c r="AN3" s="10">
+      <c r="AR3" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(ROUND(tblLines[[#This Row],[sg_amount]],2)-tblLines[[#This Row],[OTRC]],0),"")</f>
         <v>540</v>
       </c>
-      <c r="AO3" s="10">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$B$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$B$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+      <c r="AS3" s="11">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
         <v>540</v>
       </c>
-      <c r="AP3" s="10">
+      <c r="AT3" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(tblLines[[#This Row],[Base_shortfall]]-tblLines[[#This Row],[Offset_s18D]],0),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ3" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+      <c r="AU3" s="10" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
         <v>fund receipt</v>
       </c>
-      <c r="AR3" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[Settled]],Summary!$B$2),"")</f>
+      <c r="AV3" s="9">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v>46238</v>
       </c>
-      <c r="AS3" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),MIN(IF(Summary!$B$3="",DATE(2030,12,31),Summary!$B$3-1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$B$2)),"")</f>
+      <c r="AW3" s="9">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v>46238</v>
       </c>
-      <c r="AT3" s="9">
+      <c r="AX3" s="9">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(Summary!$D$3="",tblLines[[#This Row],[Accrual_to]],MIN(Summary!$D$3-1,tblLines[[#This Row],[Accrual_to]])),"")</f>
+        <v>46238</v>
+      </c>
+      <c r="AY3" s="10">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v>15</v>
       </c>
-      <c r="AU3" s="10">
+      <c r="AZ3" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
         <v>2.5420882921707211</v>
       </c>
-      <c r="AV3" s="9">
+      <c r="BA3" s="10">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
         <v>0</v>
       </c>
-      <c r="AW3" s="10">
+      <c r="BB3" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</f>
         <v>0</v>
       </c>
-      <c r="AX3" s="10">
+      <c r="BC3" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
         <v>2.54</v>
       </c>
-      <c r="AY3" s="10">
+      <c r="BD3" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
         <v>0</v>
       </c>
-      <c r="AZ3" s="10">
+      <c r="BE3" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
         <v>1.53</v>
       </c>
-      <c r="BA3" s="10">
+      <c r="BF3" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
         <v>2.54</v>
       </c>
-      <c r="BB3" s="10">
+      <c r="BG3" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
         <v>4.07</v>
       </c>
-      <c r="BC3" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0,tblLines[[#This Row],[Cap]]&gt;0,OR(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]])),IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]],tblLines[[#This Row],[remitted_date]])&lt;=DATE(2026,7,28)),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BD3" s="9">
+      <c r="BH3" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0,ROUND(tblLines[[#This Row],[Cap]],2)&gt;0,OR(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]])),IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]],tblLines[[#This Row],[Remit_day]])&lt;=DATE(2026,7,28)),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI3" s="10">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE3" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0),1,0)</f>
+      <c r="BJ3" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF3" s="9">
-        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BG3" s="9">
-        <f t="array" ref="BG3">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH3" s="9">
-        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+      <c r="BK3" s="10">
+        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[Pay_day]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[Remit_day]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[Recv_day]]&amp;"")&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL3" s="10">
+        <f t="array" ref="BL3">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM3" s="10">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[Pay_day]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B4" s="7">
         <v>46212</v>
@@ -2148,215 +2239,235 @@
       <c r="F4" s="8"/>
       <c r="G4" s="7"/>
       <c r="H4" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J4" s="7"/>
       <c r="K4" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L4" s="9">
+        <f>IF(tblLines[[#This Row],[payment_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),INT(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]))</f>
+        <v>46212</v>
+      </c>
+      <c r="M4" s="9">
+        <f>IF(tblLines[[#This Row],[remitted_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[remitted_date]]),INT(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]))</f>
+        <v>46218</v>
+      </c>
+      <c r="N4" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[fund_received_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),INT(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]))</f>
+        <v/>
+      </c>
+      <c r="O4" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[next_standard_payday]]="","",IF(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),INT(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]))</f>
+        <v/>
+      </c>
+      <c r="P4" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="M4" s="9">
+      <c r="Q4" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="N4" s="9">
+      <c r="R4" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="O4" s="9" t="str">
-        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
-        <v/>
-      </c>
-      <c r="P4" s="9">
+      <c r="S4" s="10" t="str">
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]&gt;DATE(2200,12,31))),"date-not-real ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Pay_day]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[sg_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[remitted_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[matched_amount]],2)=0)),"amount-under-half-a-cent ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[Remit_day]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[matched_amount]],2)),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&lt;ROUND(tblLines[[#This Row],[sg_amount]],2),ISNUMBER(tblLines[[#This Row],[Remit_day]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Remit_day]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Next_day]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]]),ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Next_day]]&lt;=tblLines[[#This Row],[Pay_day]]),"next_standard_payday-not-after-payday ",""))</f>
+        <v/>
+      </c>
+      <c r="T4" s="10">
         <f>IF(OR(_xlfn.ISFORMULA(tblLines[[#This Row],[employee_id]]),_xlfn.ISFORMULA(tblLines[[#This Row],[payment_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[sg_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[matched_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[fund_received_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[first_contribution_to_fund]]),_xlfn.ISFORMULA(tblLines[[#This Row],[out_of_cycle]]),_xlfn.ISFORMULA(tblLines[[#This Row],[next_standard_payday]]),_xlfn.ISFORMULA(tblLines[[#This Row],[defined_benefit]])),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="10">
+      <c r="U4" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]],IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]],tblLines[[#This Row],[sg_amount]]))</f>
         <v>318</v>
       </c>
-      <c r="R4" s="11" t="str">
-        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]])),WORKDAY.INTL(tblLines[[#This Row],[next_standard_payday]],7,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="S4" s="11" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="T4" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+      <c r="V4" s="9" t="str">
+        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]])),WORKDAY.INTL(tblLines[[#This Row],[Next_day]],7,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="W4" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],20,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="X4" s="9">
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],7,1,tblHolidays[date])))</f>
         <v>46223</v>
       </c>
-      <c r="U4" s="9" t="str">
+      <c r="Y4" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="V4" s="11">
-        <f>IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),EDATE(tblLines[[#This Row],[payment_date]]-1,-12)+1,"")</f>
+      <c r="Z4" s="9">
+        <f>IF(ISNUMBER(tblLines[[#This Row],[Pay_day]]),EDATE(tblLines[[#This Row],[Pay_day]]-1,-12)+1,"")</f>
         <v>45847</v>
       </c>
-      <c r="W4" s="11" t="str">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[fund_received_date]],"")</f>
-        <v/>
-      </c>
-      <c r="X4" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[remitted_date]],"")</f>
+      <c r="AA4" s="9" t="str">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Recv_day]],"")</f>
+        <v/>
+      </c>
+      <c r="AB4" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Remit_day]],"")</f>
         <v>46218</v>
       </c>
-      <c r="Y4" s="10">
+      <c r="AC4" s="11">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[Cap]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0)</f>
         <v>0</v>
       </c>
-      <c r="Z4" s="10">
+      <c r="AD4" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[remitted_amount]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",ROUND(tblLines[[#This Row],[sg_amount]],2),0))</f>
         <v>318</v>
       </c>
-      <c r="AA4" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+      <c r="AE4" s="10" t="str">
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,tblLines[[#This Row],[Flag_db]]=1,ROUND(tblLines[[#This Row],[Cap]],2)&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),IF(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2,IF(OR(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[Recv_day]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>possible</v>
       </c>
-      <c r="AB4" s="11">
-        <f t="array" ref="AB4">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AC4" s="11">
-        <f t="array" ref="AC4">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AD4" s="11">
+      <c r="AF4" s="9">
+        <f t="array" ref="AF4">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AG4" s="9">
+        <f t="array" ref="AG4">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AH4" s="9">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46223</v>
       </c>
-      <c r="AE4" s="9" t="str">
+      <c r="AI4" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="AF4" s="11" t="str">
+      <c r="AJ4" s="9" t="str">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Possible_latest]]),tblLines[[#This Row],[Possible_latest]]&gt;tblLines[[#This Row],[Final_due]]),tblLines[[#This Row],[Possible_latest]],""))</f>
         <v/>
       </c>
-      <c r="AG4" s="9">
+      <c r="AK4" s="10">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),1,0))</f>
         <v>0</v>
       </c>
-      <c r="AH4" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(tblLines[[#This Row],[sg_amount]]&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[payment_date]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"B1",IF(Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+      <c r="AL4" s="10" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>R3</v>
       </c>
-      <c r="AI4" s="9" t="str">
+      <c r="AM4" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",INDEX(tblCodes[verdict],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>AT_RISK</v>
       </c>
-      <c r="AJ4" s="9" t="str">
+      <c r="AN4" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",T(INDEX(tblCodes[unassessable],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))))</f>
         <v/>
       </c>
-      <c r="AK4" s="9">
+      <c r="AO4" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[exposed],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AL4" s="9">
+      <c r="AP4" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[stale],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AM4" s="10">
+      <c r="AQ4" s="11">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[otrc],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))*tblLines[[#This Row],[Receipt_credit]])</f>
         <v>0</v>
       </c>
-      <c r="AN4" s="10" t="str">
+      <c r="AR4" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(ROUND(tblLines[[#This Row],[sg_amount]],2)-tblLines[[#This Row],[OTRC]],0),"")</f>
         <v/>
       </c>
-      <c r="AO4" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$B$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$B$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
-        <v/>
-      </c>
-      <c r="AP4" s="10" t="str">
+      <c r="AS4" s="11" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="AT4" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(tblLines[[#This Row],[Base_shortfall]]-tblLines[[#This Row],[Offset_s18D]],0),"")</f>
         <v/>
       </c>
-      <c r="AQ4" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
-        <v/>
-      </c>
-      <c r="AR4" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[Settled]],Summary!$B$2),"")</f>
-        <v/>
-      </c>
-      <c r="AS4" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),MIN(IF(Summary!$B$3="",DATE(2030,12,31),Summary!$B$3-1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$B$2)),"")</f>
-        <v/>
-      </c>
-      <c r="AT4" s="9" t="str">
+      <c r="AU4" s="10" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <v/>
+      </c>
+      <c r="AV4" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AW4" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AX4" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(Summary!$D$3="",tblLines[[#This Row],[Accrual_to]],MIN(Summary!$D$3-1,tblLines[[#This Row],[Accrual_to]])),"")</f>
+        <v/>
+      </c>
+      <c r="AY4" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v/>
       </c>
-      <c r="AU4" s="10" t="str">
+      <c r="AZ4" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
         <v/>
       </c>
-      <c r="AV4" s="9" t="str">
+      <c r="BA4" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
         <v/>
       </c>
-      <c r="AW4" s="10" t="str">
+      <c r="BB4" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</f>
         <v/>
       </c>
-      <c r="AX4" s="10" t="str">
+      <c r="BC4" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
         <v/>
       </c>
-      <c r="AY4" s="10" t="str">
+      <c r="BD4" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
         <v/>
       </c>
-      <c r="AZ4" s="10" t="str">
+      <c r="BE4" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
         <v/>
       </c>
-      <c r="BA4" s="10" t="str">
+      <c r="BF4" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
         <v/>
       </c>
-      <c r="BB4" s="10" t="str">
+      <c r="BG4" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
         <v/>
       </c>
-      <c r="BC4" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0,tblLines[[#This Row],[Cap]]&gt;0,OR(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]])),IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]],tblLines[[#This Row],[remitted_date]])&lt;=DATE(2026,7,28)),1,0)</f>
+      <c r="BH4" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0,ROUND(tblLines[[#This Row],[Cap]],2)&gt;0,OR(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]])),IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]],tblLines[[#This Row],[Remit_day]])&lt;=DATE(2026,7,28)),1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD4" s="9">
+      <c r="BI4" s="10">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",1,0)</f>
         <v>0</v>
       </c>
-      <c r="BE4" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0),1,0)</f>
+      <c r="BJ4" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF4" s="9">
-        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BG4" s="9">
-        <f t="array" ref="BG4">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH4" s="9">
-        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+      <c r="BK4" s="10">
+        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[Pay_day]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[Remit_day]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[Recv_day]]&amp;"")&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL4" s="10">
+        <f t="array" ref="BL4">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM4" s="10">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[Pay_day]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B5" s="7">
         <v>46212</v>
@@ -2369,215 +2480,235 @@
       <c r="F5" s="8"/>
       <c r="G5" s="7"/>
       <c r="H5" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J5" s="7"/>
       <c r="K5" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L5" s="9">
+        <f>IF(tblLines[[#This Row],[payment_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),INT(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]))</f>
+        <v>46212</v>
+      </c>
+      <c r="M5" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[remitted_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[remitted_date]]),INT(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]))</f>
+        <v/>
+      </c>
+      <c r="N5" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[fund_received_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),INT(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]))</f>
+        <v/>
+      </c>
+      <c r="O5" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[next_standard_payday]]="","",IF(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),INT(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]))</f>
+        <v/>
+      </c>
+      <c r="P5" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="M5" s="9">
+      <c r="Q5" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="N5" s="9">
+      <c r="R5" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="O5" s="9" t="str">
-        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
-        <v/>
-      </c>
-      <c r="P5" s="9">
+      <c r="S5" s="10" t="str">
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]&gt;DATE(2200,12,31))),"date-not-real ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Pay_day]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[sg_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[remitted_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[matched_amount]],2)=0)),"amount-under-half-a-cent ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[Remit_day]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[matched_amount]],2)),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&lt;ROUND(tblLines[[#This Row],[sg_amount]],2),ISNUMBER(tblLines[[#This Row],[Remit_day]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Remit_day]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Next_day]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]]),ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Next_day]]&lt;=tblLines[[#This Row],[Pay_day]]),"next_standard_payday-not-after-payday ",""))</f>
+        <v/>
+      </c>
+      <c r="T5" s="10">
         <f>IF(OR(_xlfn.ISFORMULA(tblLines[[#This Row],[employee_id]]),_xlfn.ISFORMULA(tblLines[[#This Row],[payment_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[sg_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[matched_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[fund_received_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[first_contribution_to_fund]]),_xlfn.ISFORMULA(tblLines[[#This Row],[out_of_cycle]]),_xlfn.ISFORMULA(tblLines[[#This Row],[next_standard_payday]]),_xlfn.ISFORMULA(tblLines[[#This Row],[defined_benefit]])),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="10">
+      <c r="U5" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]],IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]],tblLines[[#This Row],[sg_amount]]))</f>
         <v>780</v>
       </c>
-      <c r="R5" s="11" t="str">
-        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]])),WORKDAY.INTL(tblLines[[#This Row],[next_standard_payday]],7,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="S5" s="11" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="T5" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+      <c r="V5" s="9" t="str">
+        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]])),WORKDAY.INTL(tblLines[[#This Row],[Next_day]],7,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="W5" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],20,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="X5" s="9">
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],7,1,tblHolidays[date])))</f>
         <v>46223</v>
       </c>
-      <c r="U5" s="9" t="str">
+      <c r="Y5" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="V5" s="11">
-        <f>IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),EDATE(tblLines[[#This Row],[payment_date]]-1,-12)+1,"")</f>
+      <c r="Z5" s="9">
+        <f>IF(ISNUMBER(tblLines[[#This Row],[Pay_day]]),EDATE(tblLines[[#This Row],[Pay_day]]-1,-12)+1,"")</f>
         <v>45847</v>
       </c>
-      <c r="W5" s="11" t="str">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[fund_received_date]],"")</f>
-        <v/>
-      </c>
-      <c r="X5" s="11" t="str">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[remitted_date]],"")</f>
-        <v/>
-      </c>
-      <c r="Y5" s="10">
+      <c r="AA5" s="9" t="str">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Recv_day]],"")</f>
+        <v/>
+      </c>
+      <c r="AB5" s="9" t="str">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Remit_day]],"")</f>
+        <v/>
+      </c>
+      <c r="AC5" s="11">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[Cap]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0)</f>
         <v>0</v>
       </c>
-      <c r="Z5" s="10">
+      <c r="AD5" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[remitted_amount]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",ROUND(tblLines[[#This Row],[sg_amount]],2),0))</f>
         <v>0</v>
       </c>
-      <c r="AA5" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+      <c r="AE5" s="10" t="str">
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,tblLines[[#This Row],[Flag_db]]=1,ROUND(tblLines[[#This Row],[Cap]],2)&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),IF(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2,IF(OR(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[Recv_day]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>possible</v>
       </c>
-      <c r="AB5" s="11">
-        <f t="array" ref="AB5">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AC5" s="11">
-        <f t="array" ref="AC5">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AD5" s="11">
+      <c r="AF5" s="9">
+        <f t="array" ref="AF5">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AG5" s="9">
+        <f t="array" ref="AG5">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AH5" s="9">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46223</v>
       </c>
-      <c r="AE5" s="9" t="str">
+      <c r="AI5" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="AF5" s="11" t="str">
+      <c r="AJ5" s="9" t="str">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Possible_latest]]),tblLines[[#This Row],[Possible_latest]]&gt;tblLines[[#This Row],[Final_due]]),tblLines[[#This Row],[Possible_latest]],""))</f>
         <v/>
       </c>
-      <c r="AG5" s="9">
+      <c r="AK5" s="10">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),1,0))</f>
         <v>0</v>
       </c>
-      <c r="AH5" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(tblLines[[#This Row],[sg_amount]]&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[payment_date]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"B1",IF(Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+      <c r="AL5" s="10" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>N2</v>
       </c>
-      <c r="AI5" s="9" t="str">
+      <c r="AM5" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",INDEX(tblCodes[verdict],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>UNPAID</v>
       </c>
-      <c r="AJ5" s="9" t="str">
+      <c r="AN5" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",T(INDEX(tblCodes[unassessable],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))))</f>
         <v/>
       </c>
-      <c r="AK5" s="9">
+      <c r="AO5" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[exposed],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>1</v>
       </c>
-      <c r="AL5" s="9">
+      <c r="AP5" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[stale],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AM5" s="10">
+      <c r="AQ5" s="11">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[otrc],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))*tblLines[[#This Row],[Receipt_credit]])</f>
         <v>0</v>
       </c>
-      <c r="AN5" s="10">
+      <c r="AR5" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(ROUND(tblLines[[#This Row],[sg_amount]],2)-tblLines[[#This Row],[OTRC]],0),"")</f>
         <v>780</v>
       </c>
-      <c r="AO5" s="10">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$B$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$B$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
-        <v>0</v>
-      </c>
-      <c r="AP5" s="10">
+      <c r="AS5" s="11">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="AT5" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(tblLines[[#This Row],[Base_shortfall]]-tblLines[[#This Row],[Offset_s18D]],0),"")</f>
         <v>780</v>
       </c>
-      <c r="AQ5" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+      <c r="AU5" s="10" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
         <v>as-at date (nothing applied to this payday)</v>
       </c>
-      <c r="AR5" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[Settled]],Summary!$B$2),"")</f>
+      <c r="AV5" s="9">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v>46244</v>
       </c>
-      <c r="AS5" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),MIN(IF(Summary!$B$3="",DATE(2030,12,31),Summary!$B$3-1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$B$2)),"")</f>
+      <c r="AW5" s="9">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v>46244</v>
       </c>
-      <c r="AT5" s="9">
+      <c r="AX5" s="9">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(Summary!$D$3="",tblLines[[#This Row],[Accrual_to]],MIN(Summary!$D$3-1,tblLines[[#This Row],[Accrual_to]])),"")</f>
+        <v>46244</v>
+      </c>
+      <c r="AY5" s="10">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v>21</v>
       </c>
-      <c r="AU5" s="10">
+      <c r="AZ5" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
         <v>5.1455028981957529</v>
       </c>
-      <c r="AV5" s="9">
+      <c r="BA5" s="10">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
         <v>0</v>
       </c>
-      <c r="AW5" s="10">
+      <c r="BB5" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</f>
         <v>780</v>
       </c>
-      <c r="AX5" s="10">
+      <c r="BC5" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
         <v>5.15</v>
       </c>
-      <c r="AY5" s="10">
+      <c r="BD5" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
         <v>0</v>
       </c>
-      <c r="AZ5" s="10">
+      <c r="BE5" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
         <v>471.09</v>
       </c>
-      <c r="BA5" s="10">
+      <c r="BF5" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
         <v>785.15</v>
       </c>
-      <c r="BB5" s="10">
+      <c r="BG5" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
         <v>1256.24</v>
       </c>
-      <c r="BC5" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0,tblLines[[#This Row],[Cap]]&gt;0,OR(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]])),IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]],tblLines[[#This Row],[remitted_date]])&lt;=DATE(2026,7,28)),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BD5" s="9">
+      <c r="BH5" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0,ROUND(tblLines[[#This Row],[Cap]],2)&gt;0,OR(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]])),IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]],tblLines[[#This Row],[Remit_day]])&lt;=DATE(2026,7,28)),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI5" s="10">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",1,0)</f>
         <v>0</v>
       </c>
-      <c r="BE5" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0),1,0)</f>
+      <c r="BJ5" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF5" s="9">
-        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BG5" s="9">
-        <f t="array" ref="BG5">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH5" s="9">
-        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+      <c r="BK5" s="10">
+        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[Pay_day]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[Remit_day]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[Recv_day]]&amp;"")&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL5" s="10">
+        <f t="array" ref="BL5">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM5" s="10">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[Pay_day]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B6" s="7">
         <v>46212</v>
@@ -2594,215 +2725,235 @@
         <v>46239</v>
       </c>
       <c r="H6" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L6" s="9">
+        <f>IF(tblLines[[#This Row],[payment_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),INT(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]))</f>
+        <v>46212</v>
+      </c>
+      <c r="M6" s="9">
+        <f>IF(tblLines[[#This Row],[remitted_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[remitted_date]]),INT(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]))</f>
+        <v>46237</v>
+      </c>
+      <c r="N6" s="9">
+        <f>IF(tblLines[[#This Row],[fund_received_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),INT(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]))</f>
+        <v>46239</v>
+      </c>
+      <c r="O6" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[next_standard_payday]]="","",IF(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),INT(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]))</f>
+        <v/>
+      </c>
+      <c r="P6" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="M6" s="9">
+      <c r="Q6" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="N6" s="9">
+      <c r="R6" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>1</v>
       </c>
-      <c r="O6" s="9" t="str">
-        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
-        <v/>
-      </c>
-      <c r="P6" s="9">
+      <c r="S6" s="10" t="str">
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]&gt;DATE(2200,12,31))),"date-not-real ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Pay_day]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[sg_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[remitted_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[matched_amount]],2)=0)),"amount-under-half-a-cent ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[Remit_day]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[matched_amount]],2)),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&lt;ROUND(tblLines[[#This Row],[sg_amount]],2),ISNUMBER(tblLines[[#This Row],[Remit_day]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Remit_day]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Next_day]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]]),ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Next_day]]&lt;=tblLines[[#This Row],[Pay_day]]),"next_standard_payday-not-after-payday ",""))</f>
+        <v/>
+      </c>
+      <c r="T6" s="10">
         <f>IF(OR(_xlfn.ISFORMULA(tblLines[[#This Row],[employee_id]]),_xlfn.ISFORMULA(tblLines[[#This Row],[payment_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[sg_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[matched_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[fund_received_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[first_contribution_to_fund]]),_xlfn.ISFORMULA(tblLines[[#This Row],[out_of_cycle]]),_xlfn.ISFORMULA(tblLines[[#This Row],[next_standard_payday]]),_xlfn.ISFORMULA(tblLines[[#This Row],[defined_benefit]])),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="10">
+      <c r="U6" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]],IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]],tblLines[[#This Row],[sg_amount]]))</f>
         <v>450</v>
       </c>
-      <c r="R6" s="11" t="str">
-        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]])),WORKDAY.INTL(tblLines[[#This Row],[next_standard_payday]],7,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="S6" s="11">
-        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</f>
+      <c r="V6" s="9" t="str">
+        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]])),WORKDAY.INTL(tblLines[[#This Row],[Next_day]],7,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="W6" s="9">
+        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],20,1,tblHolidays[date]),"")</f>
         <v>46241</v>
       </c>
-      <c r="T6" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+      <c r="X6" s="9">
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],7,1,tblHolidays[date])))</f>
         <v>46241</v>
       </c>
-      <c r="U6" s="9" t="str">
+      <c r="Y6" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</f>
         <v>EXTENDED_20BD</v>
       </c>
-      <c r="V6" s="11">
-        <f>IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),EDATE(tblLines[[#This Row],[payment_date]]-1,-12)+1,"")</f>
+      <c r="Z6" s="9">
+        <f>IF(ISNUMBER(tblLines[[#This Row],[Pay_day]]),EDATE(tblLines[[#This Row],[Pay_day]]-1,-12)+1,"")</f>
         <v>45847</v>
       </c>
-      <c r="W6" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[fund_received_date]],"")</f>
+      <c r="AA6" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Recv_day]],"")</f>
         <v>46239</v>
       </c>
-      <c r="X6" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[remitted_date]],"")</f>
+      <c r="AB6" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Remit_day]],"")</f>
         <v>46237</v>
       </c>
-      <c r="Y6" s="10">
+      <c r="AC6" s="11">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[Cap]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0)</f>
         <v>450</v>
       </c>
-      <c r="Z6" s="10">
+      <c r="AD6" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[remitted_amount]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",ROUND(tblLines[[#This Row],[sg_amount]],2),0))</f>
         <v>450</v>
       </c>
-      <c r="AA6" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+      <c r="AE6" s="10" t="str">
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,tblLines[[#This Row],[Flag_db]]=1,ROUND(tblLines[[#This Row],[Cap]],2)&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),IF(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2,IF(OR(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[Recv_day]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>confirmed</v>
       </c>
-      <c r="AB6" s="11">
-        <f t="array" ref="AB6">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AC6" s="11">
-        <f t="array" ref="AC6">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AD6" s="11">
+      <c r="AF6" s="9">
+        <f t="array" ref="AF6">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AG6" s="9">
+        <f t="array" ref="AG6">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AH6" s="9">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46241</v>
       </c>
-      <c r="AE6" s="9" t="str">
+      <c r="AI6" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>EXTENDED_20BD</v>
       </c>
-      <c r="AF6" s="11" t="str">
+      <c r="AJ6" s="9" t="str">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Possible_latest]]),tblLines[[#This Row],[Possible_latest]]&gt;tblLines[[#This Row],[Final_due]]),tblLines[[#This Row],[Possible_latest]],""))</f>
         <v/>
       </c>
-      <c r="AG6" s="9">
+      <c r="AK6" s="10">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),1,0))</f>
         <v>0</v>
       </c>
-      <c r="AH6" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(tblLines[[#This Row],[sg_amount]]&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[payment_date]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"B1",IF(Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+      <c r="AL6" s="10" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>D1</v>
       </c>
-      <c r="AI6" s="9" t="str">
+      <c r="AM6" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",INDEX(tblCodes[verdict],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>ON_TIME</v>
       </c>
-      <c r="AJ6" s="9" t="str">
+      <c r="AN6" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",T(INDEX(tblCodes[unassessable],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))))</f>
         <v/>
       </c>
-      <c r="AK6" s="9">
+      <c r="AO6" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[exposed],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AL6" s="9">
+      <c r="AP6" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[stale],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AM6" s="10">
+      <c r="AQ6" s="11">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[otrc],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))*tblLines[[#This Row],[Receipt_credit]])</f>
         <v>450</v>
       </c>
-      <c r="AN6" s="10" t="str">
+      <c r="AR6" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(ROUND(tblLines[[#This Row],[sg_amount]],2)-tblLines[[#This Row],[OTRC]],0),"")</f>
         <v/>
       </c>
-      <c r="AO6" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$B$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$B$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
-        <v/>
-      </c>
-      <c r="AP6" s="10" t="str">
+      <c r="AS6" s="11" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="AT6" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(tblLines[[#This Row],[Base_shortfall]]-tblLines[[#This Row],[Offset_s18D]],0),"")</f>
         <v/>
       </c>
-      <c r="AQ6" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
-        <v/>
-      </c>
-      <c r="AR6" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[Settled]],Summary!$B$2),"")</f>
-        <v/>
-      </c>
-      <c r="AS6" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),MIN(IF(Summary!$B$3="",DATE(2030,12,31),Summary!$B$3-1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$B$2)),"")</f>
-        <v/>
-      </c>
-      <c r="AT6" s="9" t="str">
+      <c r="AU6" s="10" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <v/>
+      </c>
+      <c r="AV6" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AW6" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AX6" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(Summary!$D$3="",tblLines[[#This Row],[Accrual_to]],MIN(Summary!$D$3-1,tblLines[[#This Row],[Accrual_to]])),"")</f>
+        <v/>
+      </c>
+      <c r="AY6" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v/>
       </c>
-      <c r="AU6" s="10" t="str">
+      <c r="AZ6" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
         <v/>
       </c>
-      <c r="AV6" s="9" t="str">
+      <c r="BA6" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
         <v/>
       </c>
-      <c r="AW6" s="10" t="str">
+      <c r="BB6" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</f>
         <v/>
       </c>
-      <c r="AX6" s="10" t="str">
+      <c r="BC6" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
         <v/>
       </c>
-      <c r="AY6" s="10" t="str">
+      <c r="BD6" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
         <v/>
       </c>
-      <c r="AZ6" s="10" t="str">
+      <c r="BE6" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
         <v/>
       </c>
-      <c r="BA6" s="10" t="str">
+      <c r="BF6" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
         <v/>
       </c>
-      <c r="BB6" s="10" t="str">
+      <c r="BG6" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
         <v/>
       </c>
-      <c r="BC6" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0,tblLines[[#This Row],[Cap]]&gt;0,OR(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]])),IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]],tblLines[[#This Row],[remitted_date]])&lt;=DATE(2026,7,28)),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BD6" s="9">
+      <c r="BH6" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0,ROUND(tblLines[[#This Row],[Cap]],2)&gt;0,OR(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]])),IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]],tblLines[[#This Row],[Remit_day]])&lt;=DATE(2026,7,28)),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI6" s="10">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE6" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0),1,0)</f>
+      <c r="BJ6" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF6" s="9">
-        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BG6" s="9">
-        <f t="array" ref="BG6">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH6" s="9">
-        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+      <c r="BK6" s="10">
+        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[Pay_day]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[Remit_day]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[Recv_day]]&amp;"")&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL6" s="10">
+        <f t="array" ref="BL6">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM6" s="10">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[Pay_day]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B7" s="7">
         <v>46218</v>
@@ -2819,217 +2970,237 @@
         <v>46234</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J7" s="7">
         <v>46226</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L7" s="9">
+        <f>IF(tblLines[[#This Row],[payment_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),INT(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]))</f>
+        <v>46218</v>
+      </c>
+      <c r="M7" s="9">
+        <f>IF(tblLines[[#This Row],[remitted_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[remitted_date]]),INT(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]))</f>
+        <v>46233</v>
+      </c>
+      <c r="N7" s="9">
+        <f>IF(tblLines[[#This Row],[fund_received_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),INT(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]))</f>
+        <v>46234</v>
+      </c>
+      <c r="O7" s="9">
+        <f>IF(tblLines[[#This Row],[next_standard_payday]]="","",IF(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),INT(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]))</f>
+        <v>46226</v>
+      </c>
+      <c r="P7" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="M7" s="9">
+      <c r="Q7" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>1</v>
       </c>
-      <c r="N7" s="9">
+      <c r="R7" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="O7" s="9" t="str">
-        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
-        <v/>
-      </c>
-      <c r="P7" s="9">
+      <c r="S7" s="10" t="str">
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]&gt;DATE(2200,12,31))),"date-not-real ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Pay_day]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[sg_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[remitted_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[matched_amount]],2)=0)),"amount-under-half-a-cent ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[Remit_day]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[matched_amount]],2)),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&lt;ROUND(tblLines[[#This Row],[sg_amount]],2),ISNUMBER(tblLines[[#This Row],[Remit_day]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Remit_day]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Next_day]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]]),ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Next_day]]&lt;=tblLines[[#This Row],[Pay_day]]),"next_standard_payday-not-after-payday ",""))</f>
+        <v/>
+      </c>
+      <c r="T7" s="10">
         <f>IF(OR(_xlfn.ISFORMULA(tblLines[[#This Row],[employee_id]]),_xlfn.ISFORMULA(tblLines[[#This Row],[payment_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[sg_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[matched_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[fund_received_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[first_contribution_to_fund]]),_xlfn.ISFORMULA(tblLines[[#This Row],[out_of_cycle]]),_xlfn.ISFORMULA(tblLines[[#This Row],[next_standard_payday]]),_xlfn.ISFORMULA(tblLines[[#This Row],[defined_benefit]])),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="10">
+      <c r="U7" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]],IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]],tblLines[[#This Row],[sg_amount]]))</f>
         <v>120</v>
       </c>
-      <c r="R7" s="11">
-        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]])),WORKDAY.INTL(tblLines[[#This Row],[next_standard_payday]],7,1,tblHolidays[date]),"")</f>
+      <c r="V7" s="9">
+        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]])),WORKDAY.INTL(tblLines[[#This Row],[Next_day]],7,1,tblHolidays[date]),"")</f>
         <v>46238</v>
       </c>
-      <c r="S7" s="11" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="T7" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+      <c r="W7" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],20,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="X7" s="9">
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],7,1,tblHolidays[date])))</f>
         <v>46238</v>
       </c>
-      <c r="U7" s="9" t="str">
+      <c r="Y7" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</f>
         <v>OUT_OF_CYCLE</v>
       </c>
-      <c r="V7" s="11">
-        <f>IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),EDATE(tblLines[[#This Row],[payment_date]]-1,-12)+1,"")</f>
+      <c r="Z7" s="9">
+        <f>IF(ISNUMBER(tblLines[[#This Row],[Pay_day]]),EDATE(tblLines[[#This Row],[Pay_day]]-1,-12)+1,"")</f>
         <v>45853</v>
       </c>
-      <c r="W7" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[fund_received_date]],"")</f>
+      <c r="AA7" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Recv_day]],"")</f>
         <v>46234</v>
       </c>
-      <c r="X7" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[remitted_date]],"")</f>
+      <c r="AB7" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Remit_day]],"")</f>
         <v>46233</v>
       </c>
-      <c r="Y7" s="10">
+      <c r="AC7" s="11">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[Cap]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0)</f>
         <v>120</v>
       </c>
-      <c r="Z7" s="10">
+      <c r="AD7" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[remitted_amount]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",ROUND(tblLines[[#This Row],[sg_amount]],2),0))</f>
         <v>120</v>
       </c>
-      <c r="AA7" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+      <c r="AE7" s="10" t="str">
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,tblLines[[#This Row],[Flag_db]]=1,ROUND(tblLines[[#This Row],[Cap]],2)&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),IF(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2,IF(OR(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[Recv_day]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>confirmed</v>
       </c>
-      <c r="AB7" s="11">
-        <f t="array" ref="AB7">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AC7" s="11">
-        <f t="array" ref="AC7">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AD7" s="11">
+      <c r="AF7" s="9">
+        <f t="array" ref="AF7">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AG7" s="9">
+        <f t="array" ref="AG7">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AH7" s="9">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46238</v>
       </c>
-      <c r="AE7" s="9" t="str">
+      <c r="AI7" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>OUT_OF_CYCLE</v>
       </c>
-      <c r="AF7" s="11" t="str">
+      <c r="AJ7" s="9" t="str">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Possible_latest]]),tblLines[[#This Row],[Possible_latest]]&gt;tblLines[[#This Row],[Final_due]]),tblLines[[#This Row],[Possible_latest]],""))</f>
         <v/>
       </c>
-      <c r="AG7" s="9">
+      <c r="AK7" s="10">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),1,0))</f>
         <v>0</v>
       </c>
-      <c r="AH7" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(tblLines[[#This Row],[sg_amount]]&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[payment_date]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"B1",IF(Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+      <c r="AL7" s="10" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>D1</v>
       </c>
-      <c r="AI7" s="9" t="str">
+      <c r="AM7" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",INDEX(tblCodes[verdict],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>ON_TIME</v>
       </c>
-      <c r="AJ7" s="9" t="str">
+      <c r="AN7" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",T(INDEX(tblCodes[unassessable],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))))</f>
         <v/>
       </c>
-      <c r="AK7" s="9">
+      <c r="AO7" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[exposed],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AL7" s="9">
+      <c r="AP7" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[stale],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AM7" s="10">
+      <c r="AQ7" s="11">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[otrc],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))*tblLines[[#This Row],[Receipt_credit]])</f>
         <v>120</v>
       </c>
-      <c r="AN7" s="10" t="str">
+      <c r="AR7" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(ROUND(tblLines[[#This Row],[sg_amount]],2)-tblLines[[#This Row],[OTRC]],0),"")</f>
         <v/>
       </c>
-      <c r="AO7" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$B$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$B$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
-        <v/>
-      </c>
-      <c r="AP7" s="10" t="str">
+      <c r="AS7" s="11" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="AT7" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(tblLines[[#This Row],[Base_shortfall]]-tblLines[[#This Row],[Offset_s18D]],0),"")</f>
         <v/>
       </c>
-      <c r="AQ7" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
-        <v/>
-      </c>
-      <c r="AR7" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[Settled]],Summary!$B$2),"")</f>
-        <v/>
-      </c>
-      <c r="AS7" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),MIN(IF(Summary!$B$3="",DATE(2030,12,31),Summary!$B$3-1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$B$2)),"")</f>
-        <v/>
-      </c>
-      <c r="AT7" s="9" t="str">
+      <c r="AU7" s="10" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <v/>
+      </c>
+      <c r="AV7" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AW7" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AX7" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(Summary!$D$3="",tblLines[[#This Row],[Accrual_to]],MIN(Summary!$D$3-1,tblLines[[#This Row],[Accrual_to]])),"")</f>
+        <v/>
+      </c>
+      <c r="AY7" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v/>
       </c>
-      <c r="AU7" s="10" t="str">
+      <c r="AZ7" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
         <v/>
       </c>
-      <c r="AV7" s="9" t="str">
+      <c r="BA7" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
         <v/>
       </c>
-      <c r="AW7" s="10" t="str">
+      <c r="BB7" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</f>
         <v/>
       </c>
-      <c r="AX7" s="10" t="str">
+      <c r="BC7" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
         <v/>
       </c>
-      <c r="AY7" s="10" t="str">
+      <c r="BD7" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
         <v/>
       </c>
-      <c r="AZ7" s="10" t="str">
+      <c r="BE7" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
         <v/>
       </c>
-      <c r="BA7" s="10" t="str">
+      <c r="BF7" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
         <v/>
       </c>
-      <c r="BB7" s="10" t="str">
+      <c r="BG7" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
         <v/>
       </c>
-      <c r="BC7" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0,tblLines[[#This Row],[Cap]]&gt;0,OR(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]])),IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]],tblLines[[#This Row],[remitted_date]])&lt;=DATE(2026,7,28)),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BD7" s="9">
+      <c r="BH7" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0,ROUND(tblLines[[#This Row],[Cap]],2)&gt;0,OR(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]])),IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]],tblLines[[#This Row],[Remit_day]])&lt;=DATE(2026,7,28)),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI7" s="10">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE7" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0),1,0)</f>
+      <c r="BJ7" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF7" s="9">
-        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BG7" s="9">
-        <f t="array" ref="BG7">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH7" s="9">
-        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+      <c r="BK7" s="10">
+        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[Pay_day]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[Remit_day]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[Recv_day]]&amp;"")&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL7" s="10">
+        <f t="array" ref="BL7">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM7" s="10">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[Pay_day]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B8" s="7">
         <v>46212</v>
@@ -3046,215 +3217,235 @@
         <v>46216</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L8" s="9">
+        <f>IF(tblLines[[#This Row],[payment_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),INT(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]))</f>
+        <v>46212</v>
+      </c>
+      <c r="M8" s="9">
+        <f>IF(tblLines[[#This Row],[remitted_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[remitted_date]]),INT(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]))</f>
+        <v>46216</v>
+      </c>
+      <c r="N8" s="9">
+        <f>IF(tblLines[[#This Row],[fund_received_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),INT(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]))</f>
+        <v>46216</v>
+      </c>
+      <c r="O8" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[next_standard_payday]]="","",IF(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),INT(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]))</f>
+        <v/>
+      </c>
+      <c r="P8" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>1</v>
       </c>
-      <c r="M8" s="9">
+      <c r="Q8" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="N8" s="9">
+      <c r="R8" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="O8" s="9" t="str">
-        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
-        <v/>
-      </c>
-      <c r="P8" s="9">
+      <c r="S8" s="10" t="str">
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]&gt;DATE(2200,12,31))),"date-not-real ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Pay_day]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[sg_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[remitted_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[matched_amount]],2)=0)),"amount-under-half-a-cent ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[Remit_day]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[matched_amount]],2)),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&lt;ROUND(tblLines[[#This Row],[sg_amount]],2),ISNUMBER(tblLines[[#This Row],[Remit_day]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Remit_day]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Next_day]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]]),ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Next_day]]&lt;=tblLines[[#This Row],[Pay_day]]),"next_standard_payday-not-after-payday ",""))</f>
+        <v/>
+      </c>
+      <c r="T8" s="10">
         <f>IF(OR(_xlfn.ISFORMULA(tblLines[[#This Row],[employee_id]]),_xlfn.ISFORMULA(tblLines[[#This Row],[payment_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[sg_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[matched_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[fund_received_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[first_contribution_to_fund]]),_xlfn.ISFORMULA(tblLines[[#This Row],[out_of_cycle]]),_xlfn.ISFORMULA(tblLines[[#This Row],[next_standard_payday]]),_xlfn.ISFORMULA(tblLines[[#This Row],[defined_benefit]])),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="10">
+      <c r="U8" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]],IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]],tblLines[[#This Row],[sg_amount]]))</f>
         <v>900</v>
       </c>
-      <c r="R8" s="11" t="str">
-        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]])),WORKDAY.INTL(tblLines[[#This Row],[next_standard_payday]],7,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="S8" s="11" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="T8" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
-        <v>0</v>
-      </c>
-      <c r="U8" s="9" t="str">
+      <c r="V8" s="9" t="str">
+        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]])),WORKDAY.INTL(tblLines[[#This Row],[Next_day]],7,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="W8" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],20,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="X8" s="9">
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],7,1,tblHolidays[date])))</f>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</f>
         <v>SKIP_DB</v>
       </c>
-      <c r="V8" s="11">
-        <f>IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),EDATE(tblLines[[#This Row],[payment_date]]-1,-12)+1,"")</f>
+      <c r="Z8" s="9">
+        <f>IF(ISNUMBER(tblLines[[#This Row],[Pay_day]]),EDATE(tblLines[[#This Row],[Pay_day]]-1,-12)+1,"")</f>
         <v>45847</v>
       </c>
-      <c r="W8" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[fund_received_date]],"")</f>
+      <c r="AA8" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Recv_day]],"")</f>
         <v>46216</v>
       </c>
-      <c r="X8" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[remitted_date]],"")</f>
+      <c r="AB8" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Remit_day]],"")</f>
         <v>46216</v>
       </c>
-      <c r="Y8" s="10">
+      <c r="AC8" s="11">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[Cap]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0)</f>
         <v>900</v>
       </c>
-      <c r="Z8" s="10">
+      <c r="AD8" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[remitted_amount]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",ROUND(tblLines[[#This Row],[sg_amount]],2),0))</f>
         <v>900</v>
       </c>
-      <c r="AA8" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+      <c r="AE8" s="10" t="str">
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,tblLines[[#This Row],[Flag_db]]=1,ROUND(tblLines[[#This Row],[Cap]],2)&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),IF(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2,IF(OR(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[Recv_day]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>impossible</v>
       </c>
-      <c r="AB8" s="11" t="str">
-        <f t="array" ref="AB8">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
-        <v/>
-      </c>
-      <c r="AC8" s="11" t="str">
-        <f t="array" ref="AC8">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
-        <v/>
-      </c>
-      <c r="AD8" s="11" t="str">
+      <c r="AF8" s="9" t="str">
+        <f t="array" ref="AF8">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
+        <v/>
+      </c>
+      <c r="AG8" s="9" t="str">
+        <f t="array" ref="AG8">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
+        <v/>
+      </c>
+      <c r="AH8" s="9" t="str">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v/>
       </c>
-      <c r="AE8" s="9" t="str">
+      <c r="AI8" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>SKIP_DB</v>
       </c>
-      <c r="AF8" s="11" t="str">
+      <c r="AJ8" s="9" t="str">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Possible_latest]]),tblLines[[#This Row],[Possible_latest]]&gt;tblLines[[#This Row],[Final_due]]),tblLines[[#This Row],[Possible_latest]],""))</f>
         <v/>
       </c>
-      <c r="AG8" s="9" t="str">
+      <c r="AK8" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),1,0))</f>
         <v/>
       </c>
-      <c r="AH8" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(tblLines[[#This Row],[sg_amount]]&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[payment_date]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"B1",IF(Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+      <c r="AL8" s="10" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>DB</v>
       </c>
-      <c r="AI8" s="9" t="str">
+      <c r="AM8" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",INDEX(tblCodes[verdict],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>SKIPPED</v>
       </c>
-      <c r="AJ8" s="9" t="str">
+      <c r="AN8" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",T(INDEX(tblCodes[unassessable],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))))</f>
         <v/>
       </c>
-      <c r="AK8" s="9">
+      <c r="AO8" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[exposed],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AL8" s="9">
+      <c r="AP8" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[stale],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AM8" s="10">
+      <c r="AQ8" s="11">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[otrc],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))*tblLines[[#This Row],[Receipt_credit]])</f>
         <v>0</v>
       </c>
-      <c r="AN8" s="10" t="str">
+      <c r="AR8" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(ROUND(tblLines[[#This Row],[sg_amount]],2)-tblLines[[#This Row],[OTRC]],0),"")</f>
         <v/>
       </c>
-      <c r="AO8" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$B$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$B$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
-        <v/>
-      </c>
-      <c r="AP8" s="10" t="str">
+      <c r="AS8" s="11" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="AT8" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(tblLines[[#This Row],[Base_shortfall]]-tblLines[[#This Row],[Offset_s18D]],0),"")</f>
         <v/>
       </c>
-      <c r="AQ8" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
-        <v/>
-      </c>
-      <c r="AR8" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[Settled]],Summary!$B$2),"")</f>
-        <v/>
-      </c>
-      <c r="AS8" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),MIN(IF(Summary!$B$3="",DATE(2030,12,31),Summary!$B$3-1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$B$2)),"")</f>
-        <v/>
-      </c>
-      <c r="AT8" s="9" t="str">
+      <c r="AU8" s="10" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <v/>
+      </c>
+      <c r="AV8" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AW8" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AX8" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(Summary!$D$3="",tblLines[[#This Row],[Accrual_to]],MIN(Summary!$D$3-1,tblLines[[#This Row],[Accrual_to]])),"")</f>
+        <v/>
+      </c>
+      <c r="AY8" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v/>
       </c>
-      <c r="AU8" s="10" t="str">
+      <c r="AZ8" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
         <v/>
       </c>
-      <c r="AV8" s="9" t="str">
+      <c r="BA8" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
         <v/>
       </c>
-      <c r="AW8" s="10" t="str">
+      <c r="BB8" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</f>
         <v/>
       </c>
-      <c r="AX8" s="10" t="str">
+      <c r="BC8" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
         <v/>
       </c>
-      <c r="AY8" s="10" t="str">
+      <c r="BD8" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
         <v/>
       </c>
-      <c r="AZ8" s="10" t="str">
+      <c r="BE8" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
         <v/>
       </c>
-      <c r="BA8" s="10" t="str">
+      <c r="BF8" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
         <v/>
       </c>
-      <c r="BB8" s="10" t="str">
+      <c r="BG8" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
         <v/>
       </c>
-      <c r="BC8" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0,tblLines[[#This Row],[Cap]]&gt;0,OR(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]])),IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]],tblLines[[#This Row],[remitted_date]])&lt;=DATE(2026,7,28)),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BD8" s="9">
+      <c r="BH8" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0,ROUND(tblLines[[#This Row],[Cap]],2)&gt;0,OR(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]])),IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]],tblLines[[#This Row],[Remit_day]])&lt;=DATE(2026,7,28)),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI8" s="10">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE8" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BF8" s="9">
-        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BG8" s="9">
-        <f t="array" ref="BG8">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH8" s="9">
-        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+      <c r="BJ8" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK8" s="10">
+        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[Pay_day]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[Remit_day]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[Recv_day]]&amp;"")&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL8" s="10">
+        <f t="array" ref="BL8">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM8" s="10">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[Pay_day]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B9" s="7">
         <v>46226</v>
@@ -3271,215 +3462,235 @@
         <v>46240</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J9" s="7"/>
       <c r="K9" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L9" s="9">
+        <f>IF(tblLines[[#This Row],[payment_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),INT(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]))</f>
+        <v>46226</v>
+      </c>
+      <c r="M9" s="9">
+        <f>IF(tblLines[[#This Row],[remitted_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[remitted_date]]),INT(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]))</f>
+        <v>46239</v>
+      </c>
+      <c r="N9" s="9">
+        <f>IF(tblLines[[#This Row],[fund_received_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),INT(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]))</f>
+        <v>46240</v>
+      </c>
+      <c r="O9" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[next_standard_payday]]="","",IF(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),INT(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]))</f>
+        <v/>
+      </c>
+      <c r="P9" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="M9" s="9">
+      <c r="Q9" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="N9" s="9">
+      <c r="R9" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="O9" s="9" t="str">
-        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
-        <v/>
-      </c>
-      <c r="P9" s="9">
+      <c r="S9" s="10" t="str">
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]&gt;DATE(2200,12,31))),"date-not-real ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Pay_day]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[sg_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[remitted_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[matched_amount]],2)=0)),"amount-under-half-a-cent ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[Remit_day]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[matched_amount]],2)),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&lt;ROUND(tblLines[[#This Row],[sg_amount]],2),ISNUMBER(tblLines[[#This Row],[Remit_day]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Remit_day]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Next_day]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]]),ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Next_day]]&lt;=tblLines[[#This Row],[Pay_day]]),"next_standard_payday-not-after-payday ",""))</f>
+        <v/>
+      </c>
+      <c r="T9" s="10">
         <f>IF(OR(_xlfn.ISFORMULA(tblLines[[#This Row],[employee_id]]),_xlfn.ISFORMULA(tblLines[[#This Row],[payment_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[sg_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[matched_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[fund_received_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[first_contribution_to_fund]]),_xlfn.ISFORMULA(tblLines[[#This Row],[out_of_cycle]]),_xlfn.ISFORMULA(tblLines[[#This Row],[next_standard_payday]]),_xlfn.ISFORMULA(tblLines[[#This Row],[defined_benefit]])),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="10">
+      <c r="U9" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]],IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]],tblLines[[#This Row],[sg_amount]]))</f>
         <v>612</v>
       </c>
-      <c r="R9" s="11" t="str">
-        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]])),WORKDAY.INTL(tblLines[[#This Row],[next_standard_payday]],7,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="S9" s="11" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="T9" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+      <c r="V9" s="9" t="str">
+        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]])),WORKDAY.INTL(tblLines[[#This Row],[Next_day]],7,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="W9" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],20,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="X9" s="9">
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],7,1,tblHolidays[date])))</f>
         <v>46238</v>
       </c>
-      <c r="U9" s="9" t="str">
+      <c r="Y9" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="V9" s="11">
-        <f>IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),EDATE(tblLines[[#This Row],[payment_date]]-1,-12)+1,"")</f>
+      <c r="Z9" s="9">
+        <f>IF(ISNUMBER(tblLines[[#This Row],[Pay_day]]),EDATE(tblLines[[#This Row],[Pay_day]]-1,-12)+1,"")</f>
         <v>45861</v>
       </c>
-      <c r="W9" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[fund_received_date]],"")</f>
+      <c r="AA9" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Recv_day]],"")</f>
         <v>46240</v>
       </c>
-      <c r="X9" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[remitted_date]],"")</f>
+      <c r="AB9" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Remit_day]],"")</f>
         <v>46239</v>
       </c>
-      <c r="Y9" s="10">
+      <c r="AC9" s="11">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[Cap]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0)</f>
         <v>612</v>
       </c>
-      <c r="Z9" s="10">
+      <c r="AD9" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[remitted_amount]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",ROUND(tblLines[[#This Row],[sg_amount]],2),0))</f>
         <v>612</v>
       </c>
-      <c r="AA9" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+      <c r="AE9" s="10" t="str">
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,tblLines[[#This Row],[Flag_db]]=1,ROUND(tblLines[[#This Row],[Cap]],2)&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),IF(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2,IF(OR(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[Recv_day]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>impossible</v>
       </c>
-      <c r="AB9" s="11">
-        <f t="array" ref="AB9">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
+      <c r="AF9" s="9">
+        <f t="array" ref="AF9">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
         <v>46223</v>
       </c>
-      <c r="AC9" s="11">
-        <f t="array" ref="AC9">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
+      <c r="AG9" s="9">
+        <f t="array" ref="AG9">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
         <v>46223</v>
       </c>
-      <c r="AD9" s="11">
+      <c r="AH9" s="9">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46238</v>
       </c>
-      <c r="AE9" s="9" t="str">
+      <c r="AI9" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="AF9" s="11" t="str">
+      <c r="AJ9" s="9" t="str">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Possible_latest]]),tblLines[[#This Row],[Possible_latest]]&gt;tblLines[[#This Row],[Final_due]]),tblLines[[#This Row],[Possible_latest]],""))</f>
         <v/>
       </c>
-      <c r="AG9" s="9">
+      <c r="AK9" s="10">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),1,0))</f>
         <v>0</v>
       </c>
-      <c r="AH9" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(tblLines[[#This Row],[sg_amount]]&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[payment_date]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"B1",IF(Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+      <c r="AL9" s="10" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>E</v>
       </c>
-      <c r="AI9" s="9" t="str">
+      <c r="AM9" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",INDEX(tblCodes[verdict],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>LATE</v>
       </c>
-      <c r="AJ9" s="9" t="str">
+      <c r="AN9" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",T(INDEX(tblCodes[unassessable],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))))</f>
         <v/>
       </c>
-      <c r="AK9" s="9">
+      <c r="AO9" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[exposed],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>1</v>
       </c>
-      <c r="AL9" s="9">
+      <c r="AP9" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[stale],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AM9" s="10">
+      <c r="AQ9" s="11">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[otrc],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))*tblLines[[#This Row],[Receipt_credit]])</f>
         <v>0</v>
       </c>
-      <c r="AN9" s="10">
+      <c r="AR9" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(ROUND(tblLines[[#This Row],[sg_amount]],2)-tblLines[[#This Row],[OTRC]],0),"")</f>
         <v>612</v>
       </c>
-      <c r="AO9" s="10">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$B$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$B$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+      <c r="AS9" s="11">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
         <v>612</v>
       </c>
-      <c r="AP9" s="10">
+      <c r="AT9" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(tblLines[[#This Row],[Base_shortfall]]-tblLines[[#This Row],[Offset_s18D]],0),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ9" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+      <c r="AU9" s="10" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
         <v>fund receipt</v>
       </c>
-      <c r="AR9" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[Settled]],Summary!$B$2),"")</f>
+      <c r="AV9" s="9">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v>46240</v>
       </c>
-      <c r="AS9" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),MIN(IF(Summary!$B$3="",DATE(2030,12,31),Summary!$B$3-1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$B$2)),"")</f>
+      <c r="AW9" s="9">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v>46240</v>
       </c>
-      <c r="AT9" s="9">
+      <c r="AX9" s="9">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(Summary!$D$3="",tblLines[[#This Row],[Accrual_to]],MIN(Summary!$D$3-1,tblLines[[#This Row],[Accrual_to]])),"")</f>
+        <v>46240</v>
+      </c>
+      <c r="AY9" s="10">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v>2</v>
       </c>
-      <c r="AU9" s="10">
+      <c r="AZ9" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
         <v>0.38335645312715005</v>
       </c>
-      <c r="AV9" s="9">
+      <c r="BA9" s="10">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
         <v>0</v>
       </c>
-      <c r="AW9" s="10">
+      <c r="BB9" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</f>
         <v>0</v>
       </c>
-      <c r="AX9" s="10">
+      <c r="BC9" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
         <v>0.38</v>
       </c>
-      <c r="AY9" s="10">
+      <c r="BD9" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
         <v>0</v>
       </c>
-      <c r="AZ9" s="10">
+      <c r="BE9" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
         <v>0.23</v>
       </c>
-      <c r="BA9" s="10">
+      <c r="BF9" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
         <v>0.38</v>
       </c>
-      <c r="BB9" s="10">
+      <c r="BG9" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
         <v>0.61</v>
       </c>
-      <c r="BC9" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0,tblLines[[#This Row],[Cap]]&gt;0,OR(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]])),IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]],tblLines[[#This Row],[remitted_date]])&lt;=DATE(2026,7,28)),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BD9" s="9">
+      <c r="BH9" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0,ROUND(tblLines[[#This Row],[Cap]],2)&gt;0,OR(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]])),IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]],tblLines[[#This Row],[Remit_day]])&lt;=DATE(2026,7,28)),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI9" s="10">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE9" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0),1,0)</f>
+      <c r="BJ9" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF9" s="9">
-        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BG9" s="9">
-        <f t="array" ref="BG9">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH9" s="9">
-        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+      <c r="BK9" s="10">
+        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[Pay_day]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[Remit_day]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[Recv_day]]&amp;"")&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL9" s="10">
+        <f t="array" ref="BL9">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM9" s="10">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[Pay_day]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B10" s="7">
         <v>46226</v>
@@ -3496,215 +3707,235 @@
         <v>46233</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J10" s="7"/>
       <c r="K10" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L10" s="9">
+        <f>IF(tblLines[[#This Row],[payment_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),INT(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]))</f>
+        <v>46226</v>
+      </c>
+      <c r="M10" s="9">
+        <f>IF(tblLines[[#This Row],[remitted_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[remitted_date]]),INT(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]))</f>
+        <v>46231</v>
+      </c>
+      <c r="N10" s="9">
+        <f>IF(tblLines[[#This Row],[fund_received_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),INT(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]))</f>
+        <v>46233</v>
+      </c>
+      <c r="O10" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[next_standard_payday]]="","",IF(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),INT(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]))</f>
+        <v/>
+      </c>
+      <c r="P10" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="M10" s="9">
+      <c r="Q10" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="N10" s="9">
+      <c r="R10" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="O10" s="9" t="str">
-        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
-        <v/>
-      </c>
-      <c r="P10" s="9">
+      <c r="S10" s="10" t="str">
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]&gt;DATE(2200,12,31))),"date-not-real ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Pay_day]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[sg_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[remitted_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[matched_amount]],2)=0)),"amount-under-half-a-cent ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[Remit_day]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[matched_amount]],2)),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&lt;ROUND(tblLines[[#This Row],[sg_amount]],2),ISNUMBER(tblLines[[#This Row],[Remit_day]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Remit_day]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Next_day]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]]),ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Next_day]]&lt;=tblLines[[#This Row],[Pay_day]]),"next_standard_payday-not-after-payday ",""))</f>
+        <v/>
+      </c>
+      <c r="T10" s="10">
         <f>IF(OR(_xlfn.ISFORMULA(tblLines[[#This Row],[employee_id]]),_xlfn.ISFORMULA(tblLines[[#This Row],[payment_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[sg_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[matched_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[fund_received_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[first_contribution_to_fund]]),_xlfn.ISFORMULA(tblLines[[#This Row],[out_of_cycle]]),_xlfn.ISFORMULA(tblLines[[#This Row],[next_standard_payday]]),_xlfn.ISFORMULA(tblLines[[#This Row],[defined_benefit]])),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="10">
+      <c r="U10" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]],IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]],tblLines[[#This Row],[sg_amount]]))</f>
         <v>540</v>
       </c>
-      <c r="R10" s="11" t="str">
-        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]])),WORKDAY.INTL(tblLines[[#This Row],[next_standard_payday]],7,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="S10" s="11" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="T10" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+      <c r="V10" s="9" t="str">
+        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]])),WORKDAY.INTL(tblLines[[#This Row],[Next_day]],7,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="W10" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],20,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="X10" s="9">
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],7,1,tblHolidays[date])))</f>
         <v>46238</v>
       </c>
-      <c r="U10" s="9" t="str">
+      <c r="Y10" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="V10" s="11">
-        <f>IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),EDATE(tblLines[[#This Row],[payment_date]]-1,-12)+1,"")</f>
+      <c r="Z10" s="9">
+        <f>IF(ISNUMBER(tblLines[[#This Row],[Pay_day]]),EDATE(tblLines[[#This Row],[Pay_day]]-1,-12)+1,"")</f>
         <v>45861</v>
       </c>
-      <c r="W10" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[fund_received_date]],"")</f>
+      <c r="AA10" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Recv_day]],"")</f>
         <v>46233</v>
       </c>
-      <c r="X10" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[remitted_date]],"")</f>
+      <c r="AB10" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Remit_day]],"")</f>
         <v>46231</v>
       </c>
-      <c r="Y10" s="10">
+      <c r="AC10" s="11">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[Cap]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0)</f>
         <v>540</v>
       </c>
-      <c r="Z10" s="10">
+      <c r="AD10" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[remitted_amount]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",ROUND(tblLines[[#This Row],[sg_amount]],2),0))</f>
         <v>540</v>
       </c>
-      <c r="AA10" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+      <c r="AE10" s="10" t="str">
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,tblLines[[#This Row],[Flag_db]]=1,ROUND(tblLines[[#This Row],[Cap]],2)&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),IF(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2,IF(OR(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[Recv_day]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>confirmed</v>
       </c>
-      <c r="AB10" s="11">
-        <f t="array" ref="AB10">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AC10" s="11">
-        <f t="array" ref="AC10">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AD10" s="11">
+      <c r="AF10" s="9">
+        <f t="array" ref="AF10">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AG10" s="9">
+        <f t="array" ref="AG10">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AH10" s="9">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46238</v>
       </c>
-      <c r="AE10" s="9" t="str">
+      <c r="AI10" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="AF10" s="11" t="str">
+      <c r="AJ10" s="9" t="str">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Possible_latest]]),tblLines[[#This Row],[Possible_latest]]&gt;tblLines[[#This Row],[Final_due]]),tblLines[[#This Row],[Possible_latest]],""))</f>
         <v/>
       </c>
-      <c r="AG10" s="9">
+      <c r="AK10" s="10">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),1,0))</f>
         <v>0</v>
       </c>
-      <c r="AH10" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(tblLines[[#This Row],[sg_amount]]&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[payment_date]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"B1",IF(Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+      <c r="AL10" s="10" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>D1</v>
       </c>
-      <c r="AI10" s="9" t="str">
+      <c r="AM10" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",INDEX(tblCodes[verdict],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>ON_TIME</v>
       </c>
-      <c r="AJ10" s="9" t="str">
+      <c r="AN10" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",T(INDEX(tblCodes[unassessable],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))))</f>
         <v/>
       </c>
-      <c r="AK10" s="9">
+      <c r="AO10" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[exposed],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AL10" s="9">
+      <c r="AP10" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[stale],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AM10" s="10">
+      <c r="AQ10" s="11">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[otrc],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))*tblLines[[#This Row],[Receipt_credit]])</f>
         <v>540</v>
       </c>
-      <c r="AN10" s="10" t="str">
+      <c r="AR10" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(ROUND(tblLines[[#This Row],[sg_amount]],2)-tblLines[[#This Row],[OTRC]],0),"")</f>
         <v/>
       </c>
-      <c r="AO10" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$B$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$B$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
-        <v/>
-      </c>
-      <c r="AP10" s="10" t="str">
+      <c r="AS10" s="11" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="AT10" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(tblLines[[#This Row],[Base_shortfall]]-tblLines[[#This Row],[Offset_s18D]],0),"")</f>
         <v/>
       </c>
-      <c r="AQ10" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
-        <v/>
-      </c>
-      <c r="AR10" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[Settled]],Summary!$B$2),"")</f>
-        <v/>
-      </c>
-      <c r="AS10" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),MIN(IF(Summary!$B$3="",DATE(2030,12,31),Summary!$B$3-1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$B$2)),"")</f>
-        <v/>
-      </c>
-      <c r="AT10" s="9" t="str">
+      <c r="AU10" s="10" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <v/>
+      </c>
+      <c r="AV10" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AW10" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AX10" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(Summary!$D$3="",tblLines[[#This Row],[Accrual_to]],MIN(Summary!$D$3-1,tblLines[[#This Row],[Accrual_to]])),"")</f>
+        <v/>
+      </c>
+      <c r="AY10" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v/>
       </c>
-      <c r="AU10" s="10" t="str">
+      <c r="AZ10" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
         <v/>
       </c>
-      <c r="AV10" s="9" t="str">
+      <c r="BA10" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
         <v/>
       </c>
-      <c r="AW10" s="10" t="str">
+      <c r="BB10" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</f>
         <v/>
       </c>
-      <c r="AX10" s="10" t="str">
+      <c r="BC10" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
         <v/>
       </c>
-      <c r="AY10" s="10" t="str">
+      <c r="BD10" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
         <v/>
       </c>
-      <c r="AZ10" s="10" t="str">
+      <c r="BE10" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
         <v/>
       </c>
-      <c r="BA10" s="10" t="str">
+      <c r="BF10" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
         <v/>
       </c>
-      <c r="BB10" s="10" t="str">
+      <c r="BG10" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
         <v/>
       </c>
-      <c r="BC10" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0,tblLines[[#This Row],[Cap]]&gt;0,OR(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]])),IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]],tblLines[[#This Row],[remitted_date]])&lt;=DATE(2026,7,28)),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BD10" s="9">
+      <c r="BH10" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0,ROUND(tblLines[[#This Row],[Cap]],2)&gt;0,OR(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]])),IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]],tblLines[[#This Row],[Remit_day]])&lt;=DATE(2026,7,28)),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI10" s="10">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE10" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0),1,0)</f>
+      <c r="BJ10" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF10" s="9">
-        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BG10" s="9">
-        <f t="array" ref="BG10">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH10" s="9">
-        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+      <c r="BK10" s="10">
+        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[Pay_day]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[Remit_day]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[Recv_day]]&amp;"")&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL10" s="10">
+        <f t="array" ref="BL10">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM10" s="10">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[Pay_day]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B11" s="7">
         <v>46226</v>
@@ -3721,209 +3952,229 @@
         <v>46240</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L11" s="9">
+        <f>IF(tblLines[[#This Row],[payment_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),INT(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]))</f>
+        <v>46226</v>
+      </c>
+      <c r="M11" s="9">
+        <f>IF(tblLines[[#This Row],[remitted_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[remitted_date]]),INT(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]))</f>
+        <v>46239</v>
+      </c>
+      <c r="N11" s="9">
+        <f>IF(tblLines[[#This Row],[fund_received_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),INT(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]))</f>
+        <v>46240</v>
+      </c>
+      <c r="O11" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[next_standard_payday]]="","",IF(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),INT(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]))</f>
+        <v/>
+      </c>
+      <c r="P11" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="M11" s="9">
+      <c r="Q11" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="N11" s="9">
+      <c r="R11" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="O11" s="9" t="str">
-        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
-        <v/>
-      </c>
-      <c r="P11" s="9">
+      <c r="S11" s="10" t="str">
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]&gt;DATE(2200,12,31))),"date-not-real ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Pay_day]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[sg_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[remitted_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[matched_amount]],2)=0)),"amount-under-half-a-cent ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[Remit_day]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[matched_amount]],2)),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&lt;ROUND(tblLines[[#This Row],[sg_amount]],2),ISNUMBER(tblLines[[#This Row],[Remit_day]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Remit_day]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Next_day]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]]),ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Next_day]]&lt;=tblLines[[#This Row],[Pay_day]]),"next_standard_payday-not-after-payday ",""))</f>
+        <v/>
+      </c>
+      <c r="T11" s="10">
         <f>IF(OR(_xlfn.ISFORMULA(tblLines[[#This Row],[employee_id]]),_xlfn.ISFORMULA(tblLines[[#This Row],[payment_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[sg_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[matched_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[fund_received_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[first_contribution_to_fund]]),_xlfn.ISFORMULA(tblLines[[#This Row],[out_of_cycle]]),_xlfn.ISFORMULA(tblLines[[#This Row],[next_standard_payday]]),_xlfn.ISFORMULA(tblLines[[#This Row],[defined_benefit]])),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="10">
+      <c r="U11" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]],IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]],tblLines[[#This Row],[sg_amount]]))</f>
         <v>450</v>
       </c>
-      <c r="R11" s="11" t="str">
-        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]])),WORKDAY.INTL(tblLines[[#This Row],[next_standard_payday]],7,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="S11" s="11" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="T11" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+      <c r="V11" s="9" t="str">
+        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]])),WORKDAY.INTL(tblLines[[#This Row],[Next_day]],7,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="W11" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],20,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="X11" s="9">
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],7,1,tblHolidays[date])))</f>
         <v>46238</v>
       </c>
-      <c r="U11" s="9" t="str">
+      <c r="Y11" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="V11" s="11">
-        <f>IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),EDATE(tblLines[[#This Row],[payment_date]]-1,-12)+1,"")</f>
+      <c r="Z11" s="9">
+        <f>IF(ISNUMBER(tblLines[[#This Row],[Pay_day]]),EDATE(tblLines[[#This Row],[Pay_day]]-1,-12)+1,"")</f>
         <v>45861</v>
       </c>
-      <c r="W11" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[fund_received_date]],"")</f>
+      <c r="AA11" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Recv_day]],"")</f>
         <v>46240</v>
       </c>
-      <c r="X11" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[remitted_date]],"")</f>
+      <c r="AB11" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Remit_day]],"")</f>
         <v>46239</v>
       </c>
-      <c r="Y11" s="10">
+      <c r="AC11" s="11">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[Cap]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0)</f>
         <v>450</v>
       </c>
-      <c r="Z11" s="10">
+      <c r="AD11" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[remitted_amount]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",ROUND(tblLines[[#This Row],[sg_amount]],2),0))</f>
         <v>450</v>
       </c>
-      <c r="AA11" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+      <c r="AE11" s="10" t="str">
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,tblLines[[#This Row],[Flag_db]]=1,ROUND(tblLines[[#This Row],[Cap]],2)&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),IF(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2,IF(OR(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[Recv_day]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>impossible</v>
       </c>
-      <c r="AB11" s="11">
-        <f t="array" ref="AB11">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
+      <c r="AF11" s="9">
+        <f t="array" ref="AF11">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
         <v>46241</v>
       </c>
-      <c r="AC11" s="11">
-        <f t="array" ref="AC11">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
+      <c r="AG11" s="9">
+        <f t="array" ref="AG11">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
         <v>46241</v>
       </c>
-      <c r="AD11" s="11">
+      <c r="AH11" s="9">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46241</v>
       </c>
-      <c r="AE11" s="9" t="str">
+      <c r="AI11" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>ITEM4_ALIGNED</v>
       </c>
-      <c r="AF11" s="11" t="str">
+      <c r="AJ11" s="9" t="str">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Possible_latest]]),tblLines[[#This Row],[Possible_latest]]&gt;tblLines[[#This Row],[Final_due]]),tblLines[[#This Row],[Possible_latest]],""))</f>
         <v/>
       </c>
-      <c r="AG11" s="9">
+      <c r="AK11" s="10">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),1,0))</f>
         <v>0</v>
       </c>
-      <c r="AH11" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(tblLines[[#This Row],[sg_amount]]&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[payment_date]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"B1",IF(Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+      <c r="AL11" s="10" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>D1</v>
       </c>
-      <c r="AI11" s="9" t="str">
+      <c r="AM11" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",INDEX(tblCodes[verdict],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>ON_TIME</v>
       </c>
-      <c r="AJ11" s="9" t="str">
+      <c r="AN11" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",T(INDEX(tblCodes[unassessable],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))))</f>
         <v/>
       </c>
-      <c r="AK11" s="9">
+      <c r="AO11" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[exposed],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AL11" s="9">
+      <c r="AP11" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[stale],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AM11" s="10">
+      <c r="AQ11" s="11">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[otrc],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))*tblLines[[#This Row],[Receipt_credit]])</f>
         <v>450</v>
       </c>
-      <c r="AN11" s="10" t="str">
+      <c r="AR11" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(ROUND(tblLines[[#This Row],[sg_amount]],2)-tblLines[[#This Row],[OTRC]],0),"")</f>
         <v/>
       </c>
-      <c r="AO11" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$B$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$B$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
-        <v/>
-      </c>
-      <c r="AP11" s="10" t="str">
+      <c r="AS11" s="11" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="AT11" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(tblLines[[#This Row],[Base_shortfall]]-tblLines[[#This Row],[Offset_s18D]],0),"")</f>
         <v/>
       </c>
-      <c r="AQ11" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
-        <v/>
-      </c>
-      <c r="AR11" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[Settled]],Summary!$B$2),"")</f>
-        <v/>
-      </c>
-      <c r="AS11" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),MIN(IF(Summary!$B$3="",DATE(2030,12,31),Summary!$B$3-1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$B$2)),"")</f>
-        <v/>
-      </c>
-      <c r="AT11" s="9" t="str">
+      <c r="AU11" s="10" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <v/>
+      </c>
+      <c r="AV11" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AW11" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AX11" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(Summary!$D$3="",tblLines[[#This Row],[Accrual_to]],MIN(Summary!$D$3-1,tblLines[[#This Row],[Accrual_to]])),"")</f>
+        <v/>
+      </c>
+      <c r="AY11" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v/>
       </c>
-      <c r="AU11" s="10" t="str">
+      <c r="AZ11" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
         <v/>
       </c>
-      <c r="AV11" s="9" t="str">
+      <c r="BA11" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
         <v/>
       </c>
-      <c r="AW11" s="10" t="str">
+      <c r="BB11" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</f>
         <v/>
       </c>
-      <c r="AX11" s="10" t="str">
+      <c r="BC11" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
         <v/>
       </c>
-      <c r="AY11" s="10" t="str">
+      <c r="BD11" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
         <v/>
       </c>
-      <c r="AZ11" s="10" t="str">
+      <c r="BE11" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
         <v/>
       </c>
-      <c r="BA11" s="10" t="str">
+      <c r="BF11" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
         <v/>
       </c>
-      <c r="BB11" s="10" t="str">
+      <c r="BG11" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
         <v/>
       </c>
-      <c r="BC11" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0,tblLines[[#This Row],[Cap]]&gt;0,OR(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]])),IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]],tblLines[[#This Row],[remitted_date]])&lt;=DATE(2026,7,28)),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BD11" s="9">
+      <c r="BH11" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0,ROUND(tblLines[[#This Row],[Cap]],2)&gt;0,OR(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]])),IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]],tblLines[[#This Row],[Remit_day]])&lt;=DATE(2026,7,28)),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI11" s="10">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE11" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0),1,0)</f>
+      <c r="BJ11" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF11" s="9">
-        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BG11" s="9">
-        <f t="array" ref="BG11">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH11" s="9">
-        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+      <c r="BK11" s="10">
+        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[Pay_day]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[Remit_day]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[Recv_day]]&amp;"")&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL11" s="10">
+        <f t="array" ref="BL11">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM11" s="10">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[Pay_day]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
         <v>1</v>
       </c>
     </row>
@@ -3950,30 +4201,30 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -3987,10 +4238,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -4004,10 +4255,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -4021,10 +4272,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -4038,13 +4289,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -4058,10 +4309,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -4075,10 +4326,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -4092,13 +4343,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -4112,10 +4363,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B10" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -4129,13 +4380,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -4149,13 +4400,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" t="s">
         <v>102</v>
-      </c>
-      <c r="B12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" t="s">
-        <v>97</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -4169,13 +4420,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -4189,13 +4440,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -4209,13 +4460,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -4229,10 +4480,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -4246,13 +4497,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -4266,10 +4517,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -4283,10 +4534,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -4300,10 +4551,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -4317,13 +4568,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -4337,13 +4588,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -4357,10 +4608,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B23" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -4374,10 +4625,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -4391,13 +4642,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -4411,10 +4662,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -4428,10 +4679,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -4463,13 +4714,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4477,10 +4728,10 @@
         <v>46023</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4488,10 +4739,10 @@
         <v>46048</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -4499,10 +4750,10 @@
         <v>46083</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4510,10 +4761,10 @@
         <v>46090</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -4521,10 +4772,10 @@
         <v>46115</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -4532,10 +4783,10 @@
         <v>46116</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -4543,10 +4794,10 @@
         <v>46117</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -4554,10 +4805,10 @@
         <v>46118</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -4565,10 +4816,10 @@
         <v>46137</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -4576,10 +4827,10 @@
         <v>46139</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -4587,10 +4838,10 @@
         <v>46146</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -4598,10 +4849,10 @@
         <v>46174</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -4609,10 +4860,10 @@
         <v>46181</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -4620,10 +4871,10 @@
         <v>46237</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -4631,10 +4882,10 @@
         <v>46290</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -4642,10 +4893,10 @@
         <v>46300</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -4653,10 +4904,10 @@
         <v>46381</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -4664,10 +4915,10 @@
         <v>46382</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -4675,10 +4926,10 @@
         <v>46384</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -4686,10 +4937,10 @@
         <v>46388</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -4697,10 +4948,10 @@
         <v>46413</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -4708,10 +4959,10 @@
         <v>46447</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -4719,10 +4970,10 @@
         <v>46454</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -4730,10 +4981,10 @@
         <v>46472</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -4741,10 +4992,10 @@
         <v>46473</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -4752,10 +5003,10 @@
         <v>46474</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -4763,10 +5014,10 @@
         <v>46475</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -4774,10 +5025,10 @@
         <v>46502</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -4785,10 +5036,10 @@
         <v>46503</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -4796,10 +5047,10 @@
         <v>46510</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -4807,10 +5058,10 @@
         <v>46538</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -4818,10 +5069,10 @@
         <v>46545</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -4829,10 +5080,10 @@
         <v>46552</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -4840,10 +5091,10 @@
         <v>46601</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -4851,10 +5102,10 @@
         <v>46664</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -4862,10 +5113,10 @@
         <v>46746</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -4873,10 +5124,10 @@
         <v>46747</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -4884,10 +5135,10 @@
         <v>46748</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -4895,20 +5146,20 @@
         <v>46749</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -4921,7 +5172,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F181"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="14" customWidth="1"/>
@@ -4929,22 +5180,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -4961,10 +5212,10 @@
         <v>365</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -4981,10 +5232,10 @@
         <v>365</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -5001,7 +5252,7 @@
         <v>365</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F4" s="12"/>
     </row>
@@ -5019,7 +5270,7 @@
         <v>365</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F5" s="12"/>
     </row>
@@ -5037,7 +5288,7 @@
         <v>366</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F6" s="12"/>
     </row>
@@ -5055,7 +5306,7 @@
         <v>365</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F7" s="12"/>
     </row>
@@ -5073,13 +5324,3073 @@
         <v>365</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F8" s="12"/>
     </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>47849</v>
+      </c>
+      <c r="B9" s="7">
+        <v>48213</v>
+      </c>
+      <c r="C9" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D9" s="12">
+        <v>365</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F9" s="12"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
+        <v>48214</v>
+      </c>
+      <c r="B10" s="7">
+        <v>48579</v>
+      </c>
+      <c r="C10" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D10" s="12">
+        <v>366</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F10" s="12"/>
+    </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>173</v>
+      <c r="A11" s="7">
+        <v>48580</v>
+      </c>
+      <c r="B11" s="7">
+        <v>48944</v>
+      </c>
+      <c r="C11" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D11" s="12">
+        <v>365</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F11" s="12"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
+        <v>48945</v>
+      </c>
+      <c r="B12" s="7">
+        <v>49309</v>
+      </c>
+      <c r="C12" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D12" s="12">
+        <v>365</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F12" s="12"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
+        <v>49310</v>
+      </c>
+      <c r="B13" s="7">
+        <v>49674</v>
+      </c>
+      <c r="C13" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D13" s="12">
+        <v>365</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F13" s="12"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="7">
+        <v>49675</v>
+      </c>
+      <c r="B14" s="7">
+        <v>50040</v>
+      </c>
+      <c r="C14" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D14" s="12">
+        <v>366</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F14" s="12"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="7">
+        <v>50041</v>
+      </c>
+      <c r="B15" s="7">
+        <v>50405</v>
+      </c>
+      <c r="C15" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D15" s="12">
+        <v>365</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F15" s="12"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
+        <v>50406</v>
+      </c>
+      <c r="B16" s="7">
+        <v>50770</v>
+      </c>
+      <c r="C16" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D16" s="12">
+        <v>365</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F16" s="12"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
+        <v>50771</v>
+      </c>
+      <c r="B17" s="7">
+        <v>51135</v>
+      </c>
+      <c r="C17" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D17" s="12">
+        <v>365</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F17" s="12"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>51136</v>
+      </c>
+      <c r="B18" s="7">
+        <v>51501</v>
+      </c>
+      <c r="C18" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D18" s="12">
+        <v>366</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F18" s="12"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
+        <v>51502</v>
+      </c>
+      <c r="B19" s="7">
+        <v>51866</v>
+      </c>
+      <c r="C19" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D19" s="12">
+        <v>365</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F19" s="12"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="7">
+        <v>51867</v>
+      </c>
+      <c r="B20" s="7">
+        <v>52231</v>
+      </c>
+      <c r="C20" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D20" s="12">
+        <v>365</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F20" s="12"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
+        <v>52232</v>
+      </c>
+      <c r="B21" s="7">
+        <v>52596</v>
+      </c>
+      <c r="C21" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D21" s="12">
+        <v>365</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F21" s="12"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
+        <v>52597</v>
+      </c>
+      <c r="B22" s="7">
+        <v>52962</v>
+      </c>
+      <c r="C22" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D22" s="12">
+        <v>366</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F22" s="12"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>52963</v>
+      </c>
+      <c r="B23" s="7">
+        <v>53327</v>
+      </c>
+      <c r="C23" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D23" s="12">
+        <v>365</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F23" s="12"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
+        <v>53328</v>
+      </c>
+      <c r="B24" s="7">
+        <v>53692</v>
+      </c>
+      <c r="C24" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D24" s="12">
+        <v>365</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F24" s="12"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
+        <v>53693</v>
+      </c>
+      <c r="B25" s="7">
+        <v>54057</v>
+      </c>
+      <c r="C25" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D25" s="12">
+        <v>365</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F25" s="12"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <v>54058</v>
+      </c>
+      <c r="B26" s="7">
+        <v>54423</v>
+      </c>
+      <c r="C26" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D26" s="12">
+        <v>366</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F26" s="12"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="7">
+        <v>54424</v>
+      </c>
+      <c r="B27" s="7">
+        <v>54788</v>
+      </c>
+      <c r="C27" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D27" s="12">
+        <v>365</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F27" s="12"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
+        <v>54789</v>
+      </c>
+      <c r="B28" s="7">
+        <v>55153</v>
+      </c>
+      <c r="C28" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D28" s="12">
+        <v>365</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F28" s="12"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>55154</v>
+      </c>
+      <c r="B29" s="7">
+        <v>55518</v>
+      </c>
+      <c r="C29" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D29" s="12">
+        <v>365</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F29" s="12"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <v>55519</v>
+      </c>
+      <c r="B30" s="7">
+        <v>55884</v>
+      </c>
+      <c r="C30" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D30" s="12">
+        <v>366</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F30" s="12"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
+        <v>55885</v>
+      </c>
+      <c r="B31" s="7">
+        <v>56249</v>
+      </c>
+      <c r="C31" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D31" s="12">
+        <v>365</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F31" s="12"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="7">
+        <v>56250</v>
+      </c>
+      <c r="B32" s="7">
+        <v>56614</v>
+      </c>
+      <c r="C32" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D32" s="12">
+        <v>365</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F32" s="12"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="7">
+        <v>56615</v>
+      </c>
+      <c r="B33" s="7">
+        <v>56979</v>
+      </c>
+      <c r="C33" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D33" s="12">
+        <v>365</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F33" s="12"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
+        <v>56980</v>
+      </c>
+      <c r="B34" s="7">
+        <v>57345</v>
+      </c>
+      <c r="C34" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D34" s="12">
+        <v>366</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F34" s="12"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="7">
+        <v>57346</v>
+      </c>
+      <c r="B35" s="7">
+        <v>57710</v>
+      </c>
+      <c r="C35" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D35" s="12">
+        <v>365</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F35" s="12"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="7">
+        <v>57711</v>
+      </c>
+      <c r="B36" s="7">
+        <v>58075</v>
+      </c>
+      <c r="C36" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D36" s="12">
+        <v>365</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F36" s="12"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="7">
+        <v>58076</v>
+      </c>
+      <c r="B37" s="7">
+        <v>58440</v>
+      </c>
+      <c r="C37" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D37" s="12">
+        <v>365</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F37" s="12"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="7">
+        <v>58441</v>
+      </c>
+      <c r="B38" s="7">
+        <v>58806</v>
+      </c>
+      <c r="C38" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D38" s="12">
+        <v>366</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F38" s="12"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="7">
+        <v>58807</v>
+      </c>
+      <c r="B39" s="7">
+        <v>59171</v>
+      </c>
+      <c r="C39" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D39" s="12">
+        <v>365</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F39" s="12"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="7">
+        <v>59172</v>
+      </c>
+      <c r="B40" s="7">
+        <v>59536</v>
+      </c>
+      <c r="C40" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D40" s="12">
+        <v>365</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F40" s="12"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="7">
+        <v>59537</v>
+      </c>
+      <c r="B41" s="7">
+        <v>59901</v>
+      </c>
+      <c r="C41" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D41" s="12">
+        <v>365</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F41" s="12"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="7">
+        <v>59902</v>
+      </c>
+      <c r="B42" s="7">
+        <v>60267</v>
+      </c>
+      <c r="C42" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D42" s="12">
+        <v>366</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F42" s="12"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="7">
+        <v>60268</v>
+      </c>
+      <c r="B43" s="7">
+        <v>60632</v>
+      </c>
+      <c r="C43" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D43" s="12">
+        <v>365</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F43" s="12"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
+        <v>60633</v>
+      </c>
+      <c r="B44" s="7">
+        <v>60997</v>
+      </c>
+      <c r="C44" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D44" s="12">
+        <v>365</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F44" s="12"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="7">
+        <v>60998</v>
+      </c>
+      <c r="B45" s="7">
+        <v>61362</v>
+      </c>
+      <c r="C45" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D45" s="12">
+        <v>365</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F45" s="12"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="7">
+        <v>61363</v>
+      </c>
+      <c r="B46" s="7">
+        <v>61728</v>
+      </c>
+      <c r="C46" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D46" s="12">
+        <v>366</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F46" s="12"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="7">
+        <v>61729</v>
+      </c>
+      <c r="B47" s="7">
+        <v>62093</v>
+      </c>
+      <c r="C47" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D47" s="12">
+        <v>365</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F47" s="12"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="7">
+        <v>62094</v>
+      </c>
+      <c r="B48" s="7">
+        <v>62458</v>
+      </c>
+      <c r="C48" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D48" s="12">
+        <v>365</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F48" s="12"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="7">
+        <v>62459</v>
+      </c>
+      <c r="B49" s="7">
+        <v>62823</v>
+      </c>
+      <c r="C49" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D49" s="12">
+        <v>365</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F49" s="12"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="7">
+        <v>62824</v>
+      </c>
+      <c r="B50" s="7">
+        <v>63189</v>
+      </c>
+      <c r="C50" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D50" s="12">
+        <v>366</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F50" s="12"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="7">
+        <v>63190</v>
+      </c>
+      <c r="B51" s="7">
+        <v>63554</v>
+      </c>
+      <c r="C51" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D51" s="12">
+        <v>365</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F51" s="12"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="7">
+        <v>63555</v>
+      </c>
+      <c r="B52" s="7">
+        <v>63919</v>
+      </c>
+      <c r="C52" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D52" s="12">
+        <v>365</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F52" s="12"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="7">
+        <v>63920</v>
+      </c>
+      <c r="B53" s="7">
+        <v>64284</v>
+      </c>
+      <c r="C53" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D53" s="12">
+        <v>365</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F53" s="12"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="7">
+        <v>64285</v>
+      </c>
+      <c r="B54" s="7">
+        <v>64650</v>
+      </c>
+      <c r="C54" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D54" s="12">
+        <v>366</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F54" s="12"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="7">
+        <v>64651</v>
+      </c>
+      <c r="B55" s="7">
+        <v>65015</v>
+      </c>
+      <c r="C55" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D55" s="12">
+        <v>365</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F55" s="12"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="7">
+        <v>65016</v>
+      </c>
+      <c r="B56" s="7">
+        <v>65380</v>
+      </c>
+      <c r="C56" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D56" s="12">
+        <v>365</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F56" s="12"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="7">
+        <v>65381</v>
+      </c>
+      <c r="B57" s="7">
+        <v>65745</v>
+      </c>
+      <c r="C57" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D57" s="12">
+        <v>365</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F57" s="12"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="7">
+        <v>65746</v>
+      </c>
+      <c r="B58" s="7">
+        <v>66111</v>
+      </c>
+      <c r="C58" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D58" s="12">
+        <v>366</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F58" s="12"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="7">
+        <v>66112</v>
+      </c>
+      <c r="B59" s="7">
+        <v>66476</v>
+      </c>
+      <c r="C59" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D59" s="12">
+        <v>365</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F59" s="12"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="7">
+        <v>66477</v>
+      </c>
+      <c r="B60" s="7">
+        <v>66841</v>
+      </c>
+      <c r="C60" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D60" s="12">
+        <v>365</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F60" s="12"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="7">
+        <v>66842</v>
+      </c>
+      <c r="B61" s="7">
+        <v>67206</v>
+      </c>
+      <c r="C61" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D61" s="12">
+        <v>365</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F61" s="12"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="7">
+        <v>67207</v>
+      </c>
+      <c r="B62" s="7">
+        <v>67572</v>
+      </c>
+      <c r="C62" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D62" s="12">
+        <v>366</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F62" s="12"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="7">
+        <v>67573</v>
+      </c>
+      <c r="B63" s="7">
+        <v>67937</v>
+      </c>
+      <c r="C63" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D63" s="12">
+        <v>365</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F63" s="12"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="7">
+        <v>67938</v>
+      </c>
+      <c r="B64" s="7">
+        <v>68302</v>
+      </c>
+      <c r="C64" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D64" s="12">
+        <v>365</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F64" s="12"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="7">
+        <v>68303</v>
+      </c>
+      <c r="B65" s="7">
+        <v>68667</v>
+      </c>
+      <c r="C65" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D65" s="12">
+        <v>365</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F65" s="12"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="7">
+        <v>68668</v>
+      </c>
+      <c r="B66" s="7">
+        <v>69033</v>
+      </c>
+      <c r="C66" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D66" s="12">
+        <v>366</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F66" s="12"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="7">
+        <v>69034</v>
+      </c>
+      <c r="B67" s="7">
+        <v>69398</v>
+      </c>
+      <c r="C67" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D67" s="12">
+        <v>365</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F67" s="12"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="7">
+        <v>69399</v>
+      </c>
+      <c r="B68" s="7">
+        <v>69763</v>
+      </c>
+      <c r="C68" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D68" s="12">
+        <v>365</v>
+      </c>
+      <c r="E68" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F68" s="12"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="7">
+        <v>69764</v>
+      </c>
+      <c r="B69" s="7">
+        <v>70128</v>
+      </c>
+      <c r="C69" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D69" s="12">
+        <v>365</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F69" s="12"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="7">
+        <v>70129</v>
+      </c>
+      <c r="B70" s="7">
+        <v>70494</v>
+      </c>
+      <c r="C70" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D70" s="12">
+        <v>366</v>
+      </c>
+      <c r="E70" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F70" s="12"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="7">
+        <v>70495</v>
+      </c>
+      <c r="B71" s="7">
+        <v>70859</v>
+      </c>
+      <c r="C71" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D71" s="12">
+        <v>365</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F71" s="12"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="7">
+        <v>70860</v>
+      </c>
+      <c r="B72" s="7">
+        <v>71224</v>
+      </c>
+      <c r="C72" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D72" s="12">
+        <v>365</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F72" s="12"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="7">
+        <v>71225</v>
+      </c>
+      <c r="B73" s="7">
+        <v>71589</v>
+      </c>
+      <c r="C73" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D73" s="12">
+        <v>365</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F73" s="12"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="7">
+        <v>71590</v>
+      </c>
+      <c r="B74" s="7">
+        <v>71955</v>
+      </c>
+      <c r="C74" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D74" s="12">
+        <v>366</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F74" s="12"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="7">
+        <v>71956</v>
+      </c>
+      <c r="B75" s="7">
+        <v>72320</v>
+      </c>
+      <c r="C75" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D75" s="12">
+        <v>365</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F75" s="12"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="7">
+        <v>72321</v>
+      </c>
+      <c r="B76" s="7">
+        <v>72685</v>
+      </c>
+      <c r="C76" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D76" s="12">
+        <v>365</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F76" s="12"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="7">
+        <v>72686</v>
+      </c>
+      <c r="B77" s="7">
+        <v>73050</v>
+      </c>
+      <c r="C77" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D77" s="12">
+        <v>365</v>
+      </c>
+      <c r="E77" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F77" s="12"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="7">
+        <v>73051</v>
+      </c>
+      <c r="B78" s="7">
+        <v>73415</v>
+      </c>
+      <c r="C78" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D78" s="12">
+        <v>365</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F78" s="12"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="7">
+        <v>73416</v>
+      </c>
+      <c r="B79" s="7">
+        <v>73780</v>
+      </c>
+      <c r="C79" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D79" s="12">
+        <v>365</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F79" s="12"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="7">
+        <v>73781</v>
+      </c>
+      <c r="B80" s="7">
+        <v>74145</v>
+      </c>
+      <c r="C80" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D80" s="12">
+        <v>365</v>
+      </c>
+      <c r="E80" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F80" s="12"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="7">
+        <v>74146</v>
+      </c>
+      <c r="B81" s="7">
+        <v>74510</v>
+      </c>
+      <c r="C81" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D81" s="12">
+        <v>365</v>
+      </c>
+      <c r="E81" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F81" s="12"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="7">
+        <v>74511</v>
+      </c>
+      <c r="B82" s="7">
+        <v>74876</v>
+      </c>
+      <c r="C82" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D82" s="12">
+        <v>366</v>
+      </c>
+      <c r="E82" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F82" s="12"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="7">
+        <v>74877</v>
+      </c>
+      <c r="B83" s="7">
+        <v>75241</v>
+      </c>
+      <c r="C83" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D83" s="12">
+        <v>365</v>
+      </c>
+      <c r="E83" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F83" s="12"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="7">
+        <v>75242</v>
+      </c>
+      <c r="B84" s="7">
+        <v>75606</v>
+      </c>
+      <c r="C84" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D84" s="12">
+        <v>365</v>
+      </c>
+      <c r="E84" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F84" s="12"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="7">
+        <v>75607</v>
+      </c>
+      <c r="B85" s="7">
+        <v>75971</v>
+      </c>
+      <c r="C85" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D85" s="12">
+        <v>365</v>
+      </c>
+      <c r="E85" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F85" s="12"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="7">
+        <v>75972</v>
+      </c>
+      <c r="B86" s="7">
+        <v>76337</v>
+      </c>
+      <c r="C86" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D86" s="12">
+        <v>366</v>
+      </c>
+      <c r="E86" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F86" s="12"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="7">
+        <v>76338</v>
+      </c>
+      <c r="B87" s="7">
+        <v>76702</v>
+      </c>
+      <c r="C87" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D87" s="12">
+        <v>365</v>
+      </c>
+      <c r="E87" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F87" s="12"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="7">
+        <v>76703</v>
+      </c>
+      <c r="B88" s="7">
+        <v>77067</v>
+      </c>
+      <c r="C88" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D88" s="12">
+        <v>365</v>
+      </c>
+      <c r="E88" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F88" s="12"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="7">
+        <v>77068</v>
+      </c>
+      <c r="B89" s="7">
+        <v>77432</v>
+      </c>
+      <c r="C89" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D89" s="12">
+        <v>365</v>
+      </c>
+      <c r="E89" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F89" s="12"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="7">
+        <v>77433</v>
+      </c>
+      <c r="B90" s="7">
+        <v>77798</v>
+      </c>
+      <c r="C90" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D90" s="12">
+        <v>366</v>
+      </c>
+      <c r="E90" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F90" s="12"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="7">
+        <v>77799</v>
+      </c>
+      <c r="B91" s="7">
+        <v>78163</v>
+      </c>
+      <c r="C91" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D91" s="12">
+        <v>365</v>
+      </c>
+      <c r="E91" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F91" s="12"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="7">
+        <v>78164</v>
+      </c>
+      <c r="B92" s="7">
+        <v>78528</v>
+      </c>
+      <c r="C92" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D92" s="12">
+        <v>365</v>
+      </c>
+      <c r="E92" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F92" s="12"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="7">
+        <v>78529</v>
+      </c>
+      <c r="B93" s="7">
+        <v>78893</v>
+      </c>
+      <c r="C93" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D93" s="12">
+        <v>365</v>
+      </c>
+      <c r="E93" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F93" s="12"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="7">
+        <v>78894</v>
+      </c>
+      <c r="B94" s="7">
+        <v>79259</v>
+      </c>
+      <c r="C94" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D94" s="12">
+        <v>366</v>
+      </c>
+      <c r="E94" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F94" s="12"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="7">
+        <v>79260</v>
+      </c>
+      <c r="B95" s="7">
+        <v>79624</v>
+      </c>
+      <c r="C95" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D95" s="12">
+        <v>365</v>
+      </c>
+      <c r="E95" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F95" s="12"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="7">
+        <v>79625</v>
+      </c>
+      <c r="B96" s="7">
+        <v>79989</v>
+      </c>
+      <c r="C96" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D96" s="12">
+        <v>365</v>
+      </c>
+      <c r="E96" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F96" s="12"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="7">
+        <v>79990</v>
+      </c>
+      <c r="B97" s="7">
+        <v>80354</v>
+      </c>
+      <c r="C97" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D97" s="12">
+        <v>365</v>
+      </c>
+      <c r="E97" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F97" s="12"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="7">
+        <v>80355</v>
+      </c>
+      <c r="B98" s="7">
+        <v>80720</v>
+      </c>
+      <c r="C98" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D98" s="12">
+        <v>366</v>
+      </c>
+      <c r="E98" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F98" s="12"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="7">
+        <v>80721</v>
+      </c>
+      <c r="B99" s="7">
+        <v>81085</v>
+      </c>
+      <c r="C99" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D99" s="12">
+        <v>365</v>
+      </c>
+      <c r="E99" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F99" s="12"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="7">
+        <v>81086</v>
+      </c>
+      <c r="B100" s="7">
+        <v>81450</v>
+      </c>
+      <c r="C100" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D100" s="12">
+        <v>365</v>
+      </c>
+      <c r="E100" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F100" s="12"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="7">
+        <v>81451</v>
+      </c>
+      <c r="B101" s="7">
+        <v>81815</v>
+      </c>
+      <c r="C101" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D101" s="12">
+        <v>365</v>
+      </c>
+      <c r="E101" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F101" s="12"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="7">
+        <v>81816</v>
+      </c>
+      <c r="B102" s="7">
+        <v>82181</v>
+      </c>
+      <c r="C102" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D102" s="12">
+        <v>366</v>
+      </c>
+      <c r="E102" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F102" s="12"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="7">
+        <v>82182</v>
+      </c>
+      <c r="B103" s="7">
+        <v>82546</v>
+      </c>
+      <c r="C103" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D103" s="12">
+        <v>365</v>
+      </c>
+      <c r="E103" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F103" s="12"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="7">
+        <v>82547</v>
+      </c>
+      <c r="B104" s="7">
+        <v>82911</v>
+      </c>
+      <c r="C104" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D104" s="12">
+        <v>365</v>
+      </c>
+      <c r="E104" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F104" s="12"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="7">
+        <v>82912</v>
+      </c>
+      <c r="B105" s="7">
+        <v>83276</v>
+      </c>
+      <c r="C105" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D105" s="12">
+        <v>365</v>
+      </c>
+      <c r="E105" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F105" s="12"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="7">
+        <v>83277</v>
+      </c>
+      <c r="B106" s="7">
+        <v>83642</v>
+      </c>
+      <c r="C106" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D106" s="12">
+        <v>366</v>
+      </c>
+      <c r="E106" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F106" s="12"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="7">
+        <v>83643</v>
+      </c>
+      <c r="B107" s="7">
+        <v>84007</v>
+      </c>
+      <c r="C107" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D107" s="12">
+        <v>365</v>
+      </c>
+      <c r="E107" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F107" s="12"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="7">
+        <v>84008</v>
+      </c>
+      <c r="B108" s="7">
+        <v>84372</v>
+      </c>
+      <c r="C108" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D108" s="12">
+        <v>365</v>
+      </c>
+      <c r="E108" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F108" s="12"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="7">
+        <v>84373</v>
+      </c>
+      <c r="B109" s="7">
+        <v>84737</v>
+      </c>
+      <c r="C109" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D109" s="12">
+        <v>365</v>
+      </c>
+      <c r="E109" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F109" s="12"/>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="7">
+        <v>84738</v>
+      </c>
+      <c r="B110" s="7">
+        <v>85103</v>
+      </c>
+      <c r="C110" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D110" s="12">
+        <v>366</v>
+      </c>
+      <c r="E110" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F110" s="12"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="7">
+        <v>85104</v>
+      </c>
+      <c r="B111" s="7">
+        <v>85468</v>
+      </c>
+      <c r="C111" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D111" s="12">
+        <v>365</v>
+      </c>
+      <c r="E111" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F111" s="12"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="7">
+        <v>85469</v>
+      </c>
+      <c r="B112" s="7">
+        <v>85833</v>
+      </c>
+      <c r="C112" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D112" s="12">
+        <v>365</v>
+      </c>
+      <c r="E112" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F112" s="12"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="7">
+        <v>85834</v>
+      </c>
+      <c r="B113" s="7">
+        <v>86198</v>
+      </c>
+      <c r="C113" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D113" s="12">
+        <v>365</v>
+      </c>
+      <c r="E113" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F113" s="12"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="7">
+        <v>86199</v>
+      </c>
+      <c r="B114" s="7">
+        <v>86564</v>
+      </c>
+      <c r="C114" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D114" s="12">
+        <v>366</v>
+      </c>
+      <c r="E114" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F114" s="12"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="7">
+        <v>86565</v>
+      </c>
+      <c r="B115" s="7">
+        <v>86929</v>
+      </c>
+      <c r="C115" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D115" s="12">
+        <v>365</v>
+      </c>
+      <c r="E115" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F115" s="12"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="7">
+        <v>86930</v>
+      </c>
+      <c r="B116" s="7">
+        <v>87294</v>
+      </c>
+      <c r="C116" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D116" s="12">
+        <v>365</v>
+      </c>
+      <c r="E116" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F116" s="12"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="7">
+        <v>87295</v>
+      </c>
+      <c r="B117" s="7">
+        <v>87659</v>
+      </c>
+      <c r="C117" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D117" s="12">
+        <v>365</v>
+      </c>
+      <c r="E117" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F117" s="12"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="7">
+        <v>87660</v>
+      </c>
+      <c r="B118" s="7">
+        <v>88025</v>
+      </c>
+      <c r="C118" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D118" s="12">
+        <v>366</v>
+      </c>
+      <c r="E118" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F118" s="12"/>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="7">
+        <v>88026</v>
+      </c>
+      <c r="B119" s="7">
+        <v>88390</v>
+      </c>
+      <c r="C119" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D119" s="12">
+        <v>365</v>
+      </c>
+      <c r="E119" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F119" s="12"/>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="7">
+        <v>88391</v>
+      </c>
+      <c r="B120" s="7">
+        <v>88755</v>
+      </c>
+      <c r="C120" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D120" s="12">
+        <v>365</v>
+      </c>
+      <c r="E120" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F120" s="12"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="7">
+        <v>88756</v>
+      </c>
+      <c r="B121" s="7">
+        <v>89120</v>
+      </c>
+      <c r="C121" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D121" s="12">
+        <v>365</v>
+      </c>
+      <c r="E121" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F121" s="12"/>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="7">
+        <v>89121</v>
+      </c>
+      <c r="B122" s="7">
+        <v>89486</v>
+      </c>
+      <c r="C122" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D122" s="12">
+        <v>366</v>
+      </c>
+      <c r="E122" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F122" s="12"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="7">
+        <v>89487</v>
+      </c>
+      <c r="B123" s="7">
+        <v>89851</v>
+      </c>
+      <c r="C123" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D123" s="12">
+        <v>365</v>
+      </c>
+      <c r="E123" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F123" s="12"/>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="7">
+        <v>89852</v>
+      </c>
+      <c r="B124" s="7">
+        <v>90216</v>
+      </c>
+      <c r="C124" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D124" s="12">
+        <v>365</v>
+      </c>
+      <c r="E124" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F124" s="12"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="7">
+        <v>90217</v>
+      </c>
+      <c r="B125" s="7">
+        <v>90581</v>
+      </c>
+      <c r="C125" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D125" s="12">
+        <v>365</v>
+      </c>
+      <c r="E125" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F125" s="12"/>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="7">
+        <v>90582</v>
+      </c>
+      <c r="B126" s="7">
+        <v>90947</v>
+      </c>
+      <c r="C126" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D126" s="12">
+        <v>366</v>
+      </c>
+      <c r="E126" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F126" s="12"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="7">
+        <v>90948</v>
+      </c>
+      <c r="B127" s="7">
+        <v>91312</v>
+      </c>
+      <c r="C127" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D127" s="12">
+        <v>365</v>
+      </c>
+      <c r="E127" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F127" s="12"/>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="7">
+        <v>91313</v>
+      </c>
+      <c r="B128" s="7">
+        <v>91677</v>
+      </c>
+      <c r="C128" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D128" s="12">
+        <v>365</v>
+      </c>
+      <c r="E128" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F128" s="12"/>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="7">
+        <v>91678</v>
+      </c>
+      <c r="B129" s="7">
+        <v>92042</v>
+      </c>
+      <c r="C129" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D129" s="12">
+        <v>365</v>
+      </c>
+      <c r="E129" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F129" s="12"/>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="7">
+        <v>92043</v>
+      </c>
+      <c r="B130" s="7">
+        <v>92408</v>
+      </c>
+      <c r="C130" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D130" s="12">
+        <v>366</v>
+      </c>
+      <c r="E130" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F130" s="12"/>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="7">
+        <v>92409</v>
+      </c>
+      <c r="B131" s="7">
+        <v>92773</v>
+      </c>
+      <c r="C131" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D131" s="12">
+        <v>365</v>
+      </c>
+      <c r="E131" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F131" s="12"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="7">
+        <v>92774</v>
+      </c>
+      <c r="B132" s="7">
+        <v>93138</v>
+      </c>
+      <c r="C132" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D132" s="12">
+        <v>365</v>
+      </c>
+      <c r="E132" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F132" s="12"/>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" s="7">
+        <v>93139</v>
+      </c>
+      <c r="B133" s="7">
+        <v>93503</v>
+      </c>
+      <c r="C133" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D133" s="12">
+        <v>365</v>
+      </c>
+      <c r="E133" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F133" s="12"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="7">
+        <v>93504</v>
+      </c>
+      <c r="B134" s="7">
+        <v>93869</v>
+      </c>
+      <c r="C134" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D134" s="12">
+        <v>366</v>
+      </c>
+      <c r="E134" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F134" s="12"/>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="7">
+        <v>93870</v>
+      </c>
+      <c r="B135" s="7">
+        <v>94234</v>
+      </c>
+      <c r="C135" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D135" s="12">
+        <v>365</v>
+      </c>
+      <c r="E135" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F135" s="12"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="7">
+        <v>94235</v>
+      </c>
+      <c r="B136" s="7">
+        <v>94599</v>
+      </c>
+      <c r="C136" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D136" s="12">
+        <v>365</v>
+      </c>
+      <c r="E136" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F136" s="12"/>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="7">
+        <v>94600</v>
+      </c>
+      <c r="B137" s="7">
+        <v>94964</v>
+      </c>
+      <c r="C137" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D137" s="12">
+        <v>365</v>
+      </c>
+      <c r="E137" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F137" s="12"/>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="7">
+        <v>94965</v>
+      </c>
+      <c r="B138" s="7">
+        <v>95330</v>
+      </c>
+      <c r="C138" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D138" s="12">
+        <v>366</v>
+      </c>
+      <c r="E138" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F138" s="12"/>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="7">
+        <v>95331</v>
+      </c>
+      <c r="B139" s="7">
+        <v>95695</v>
+      </c>
+      <c r="C139" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D139" s="12">
+        <v>365</v>
+      </c>
+      <c r="E139" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F139" s="12"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="7">
+        <v>95696</v>
+      </c>
+      <c r="B140" s="7">
+        <v>96060</v>
+      </c>
+      <c r="C140" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D140" s="12">
+        <v>365</v>
+      </c>
+      <c r="E140" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F140" s="12"/>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="7">
+        <v>96061</v>
+      </c>
+      <c r="B141" s="7">
+        <v>96425</v>
+      </c>
+      <c r="C141" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D141" s="12">
+        <v>365</v>
+      </c>
+      <c r="E141" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F141" s="12"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="7">
+        <v>96426</v>
+      </c>
+      <c r="B142" s="7">
+        <v>96791</v>
+      </c>
+      <c r="C142" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D142" s="12">
+        <v>366</v>
+      </c>
+      <c r="E142" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F142" s="12"/>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="7">
+        <v>96792</v>
+      </c>
+      <c r="B143" s="7">
+        <v>97156</v>
+      </c>
+      <c r="C143" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D143" s="12">
+        <v>365</v>
+      </c>
+      <c r="E143" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F143" s="12"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="7">
+        <v>97157</v>
+      </c>
+      <c r="B144" s="7">
+        <v>97521</v>
+      </c>
+      <c r="C144" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D144" s="12">
+        <v>365</v>
+      </c>
+      <c r="E144" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F144" s="12"/>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="7">
+        <v>97522</v>
+      </c>
+      <c r="B145" s="7">
+        <v>97886</v>
+      </c>
+      <c r="C145" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D145" s="12">
+        <v>365</v>
+      </c>
+      <c r="E145" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F145" s="12"/>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" s="7">
+        <v>97887</v>
+      </c>
+      <c r="B146" s="7">
+        <v>98252</v>
+      </c>
+      <c r="C146" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D146" s="12">
+        <v>366</v>
+      </c>
+      <c r="E146" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F146" s="12"/>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" s="7">
+        <v>98253</v>
+      </c>
+      <c r="B147" s="7">
+        <v>98617</v>
+      </c>
+      <c r="C147" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D147" s="12">
+        <v>365</v>
+      </c>
+      <c r="E147" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F147" s="12"/>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" s="7">
+        <v>98618</v>
+      </c>
+      <c r="B148" s="7">
+        <v>98982</v>
+      </c>
+      <c r="C148" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D148" s="12">
+        <v>365</v>
+      </c>
+      <c r="E148" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F148" s="12"/>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" s="7">
+        <v>98983</v>
+      </c>
+      <c r="B149" s="7">
+        <v>99347</v>
+      </c>
+      <c r="C149" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D149" s="12">
+        <v>365</v>
+      </c>
+      <c r="E149" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F149" s="12"/>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" s="7">
+        <v>99348</v>
+      </c>
+      <c r="B150" s="7">
+        <v>99713</v>
+      </c>
+      <c r="C150" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D150" s="12">
+        <v>366</v>
+      </c>
+      <c r="E150" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F150" s="12"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" s="7">
+        <v>99714</v>
+      </c>
+      <c r="B151" s="7">
+        <v>100078</v>
+      </c>
+      <c r="C151" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D151" s="12">
+        <v>365</v>
+      </c>
+      <c r="E151" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F151" s="12"/>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="7">
+        <v>100079</v>
+      </c>
+      <c r="B152" s="7">
+        <v>100443</v>
+      </c>
+      <c r="C152" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D152" s="12">
+        <v>365</v>
+      </c>
+      <c r="E152" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F152" s="12"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" s="7">
+        <v>100444</v>
+      </c>
+      <c r="B153" s="7">
+        <v>100808</v>
+      </c>
+      <c r="C153" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D153" s="12">
+        <v>365</v>
+      </c>
+      <c r="E153" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F153" s="12"/>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" s="7">
+        <v>100809</v>
+      </c>
+      <c r="B154" s="7">
+        <v>101174</v>
+      </c>
+      <c r="C154" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D154" s="12">
+        <v>366</v>
+      </c>
+      <c r="E154" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F154" s="12"/>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" s="7">
+        <v>101175</v>
+      </c>
+      <c r="B155" s="7">
+        <v>101539</v>
+      </c>
+      <c r="C155" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D155" s="12">
+        <v>365</v>
+      </c>
+      <c r="E155" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F155" s="12"/>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" s="7">
+        <v>101540</v>
+      </c>
+      <c r="B156" s="7">
+        <v>101904</v>
+      </c>
+      <c r="C156" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D156" s="12">
+        <v>365</v>
+      </c>
+      <c r="E156" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F156" s="12"/>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" s="7">
+        <v>101905</v>
+      </c>
+      <c r="B157" s="7">
+        <v>102269</v>
+      </c>
+      <c r="C157" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D157" s="12">
+        <v>365</v>
+      </c>
+      <c r="E157" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F157" s="12"/>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" s="7">
+        <v>102270</v>
+      </c>
+      <c r="B158" s="7">
+        <v>102635</v>
+      </c>
+      <c r="C158" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D158" s="12">
+        <v>366</v>
+      </c>
+      <c r="E158" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F158" s="12"/>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" s="7">
+        <v>102636</v>
+      </c>
+      <c r="B159" s="7">
+        <v>103000</v>
+      </c>
+      <c r="C159" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D159" s="12">
+        <v>365</v>
+      </c>
+      <c r="E159" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F159" s="12"/>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" s="7">
+        <v>103001</v>
+      </c>
+      <c r="B160" s="7">
+        <v>103365</v>
+      </c>
+      <c r="C160" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D160" s="12">
+        <v>365</v>
+      </c>
+      <c r="E160" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F160" s="12"/>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" s="7">
+        <v>103366</v>
+      </c>
+      <c r="B161" s="7">
+        <v>103730</v>
+      </c>
+      <c r="C161" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D161" s="12">
+        <v>365</v>
+      </c>
+      <c r="E161" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F161" s="12"/>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" s="7">
+        <v>103731</v>
+      </c>
+      <c r="B162" s="7">
+        <v>104096</v>
+      </c>
+      <c r="C162" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D162" s="12">
+        <v>366</v>
+      </c>
+      <c r="E162" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F162" s="12"/>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" s="7">
+        <v>104097</v>
+      </c>
+      <c r="B163" s="7">
+        <v>104461</v>
+      </c>
+      <c r="C163" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D163" s="12">
+        <v>365</v>
+      </c>
+      <c r="E163" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F163" s="12"/>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" s="7">
+        <v>104462</v>
+      </c>
+      <c r="B164" s="7">
+        <v>104826</v>
+      </c>
+      <c r="C164" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D164" s="12">
+        <v>365</v>
+      </c>
+      <c r="E164" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F164" s="12"/>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" s="7">
+        <v>104827</v>
+      </c>
+      <c r="B165" s="7">
+        <v>105191</v>
+      </c>
+      <c r="C165" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D165" s="12">
+        <v>365</v>
+      </c>
+      <c r="E165" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F165" s="12"/>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" s="7">
+        <v>105192</v>
+      </c>
+      <c r="B166" s="7">
+        <v>105557</v>
+      </c>
+      <c r="C166" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D166" s="12">
+        <v>366</v>
+      </c>
+      <c r="E166" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F166" s="12"/>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" s="7">
+        <v>105558</v>
+      </c>
+      <c r="B167" s="7">
+        <v>105922</v>
+      </c>
+      <c r="C167" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D167" s="12">
+        <v>365</v>
+      </c>
+      <c r="E167" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F167" s="12"/>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" s="7">
+        <v>105923</v>
+      </c>
+      <c r="B168" s="7">
+        <v>106287</v>
+      </c>
+      <c r="C168" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D168" s="12">
+        <v>365</v>
+      </c>
+      <c r="E168" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F168" s="12"/>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" s="7">
+        <v>106288</v>
+      </c>
+      <c r="B169" s="7">
+        <v>106652</v>
+      </c>
+      <c r="C169" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D169" s="12">
+        <v>365</v>
+      </c>
+      <c r="E169" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F169" s="12"/>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" s="7">
+        <v>106653</v>
+      </c>
+      <c r="B170" s="7">
+        <v>107018</v>
+      </c>
+      <c r="C170" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D170" s="12">
+        <v>366</v>
+      </c>
+      <c r="E170" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F170" s="12"/>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" s="7">
+        <v>107019</v>
+      </c>
+      <c r="B171" s="7">
+        <v>107383</v>
+      </c>
+      <c r="C171" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D171" s="12">
+        <v>365</v>
+      </c>
+      <c r="E171" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F171" s="12"/>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" s="7">
+        <v>107384</v>
+      </c>
+      <c r="B172" s="7">
+        <v>107748</v>
+      </c>
+      <c r="C172" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D172" s="12">
+        <v>365</v>
+      </c>
+      <c r="E172" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F172" s="12"/>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" s="7">
+        <v>107749</v>
+      </c>
+      <c r="B173" s="7">
+        <v>108113</v>
+      </c>
+      <c r="C173" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D173" s="12">
+        <v>365</v>
+      </c>
+      <c r="E173" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F173" s="12"/>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" s="7">
+        <v>108114</v>
+      </c>
+      <c r="B174" s="7">
+        <v>108479</v>
+      </c>
+      <c r="C174" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D174" s="12">
+        <v>366</v>
+      </c>
+      <c r="E174" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F174" s="12"/>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" s="7">
+        <v>108480</v>
+      </c>
+      <c r="B175" s="7">
+        <v>108844</v>
+      </c>
+      <c r="C175" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D175" s="12">
+        <v>365</v>
+      </c>
+      <c r="E175" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F175" s="12"/>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176" s="7">
+        <v>108845</v>
+      </c>
+      <c r="B176" s="7">
+        <v>109209</v>
+      </c>
+      <c r="C176" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D176" s="12">
+        <v>365</v>
+      </c>
+      <c r="E176" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F176" s="12"/>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" s="7">
+        <v>109210</v>
+      </c>
+      <c r="B177" s="7">
+        <v>109574</v>
+      </c>
+      <c r="C177" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D177" s="12">
+        <v>365</v>
+      </c>
+      <c r="E177" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F177" s="12"/>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" s="7">
+        <v>109575</v>
+      </c>
+      <c r="B178" s="7">
+        <v>109939</v>
+      </c>
+      <c r="C178" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D178" s="12">
+        <v>365</v>
+      </c>
+      <c r="E178" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F178" s="12"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -5092,185 +8403,199 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="64" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B1" s="5"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B2" s="13">
         <v>46244</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2" s="9">
+        <f>IF(Summary!$B$2="","",IF(ISNUMBER(Summary!$B$2),INT(Summary!$B$2),Summary!$B$2))</f>
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B3" s="13"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D3" s="9" t="str">
+        <f>IF(Summary!$B$3="","",IF(ISNUMBER(Summary!$B$3),INT(Summary!$B$3),Summary!$B$3))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="B6" s="13">
         <v>46630</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>181</v>
-      </c>
-      <c r="B7" s="11">
+        <v>188</v>
+      </c>
+      <c r="B7" s="9">
         <f>_xlfn.MAXIFS(tblGic[to],tblGic[basis],"known")</f>
         <v>46295</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B9" s="5"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>89</v>
-      </c>
-      <c r="B10" s="9">
+        <v>94</v>
+      </c>
+      <c r="B10" s="10">
         <f>COUNTIF(tblLines[Verdict],"ON_TIME")</f>
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B11" s="9">
+        <v>121</v>
+      </c>
+      <c r="B11" s="10">
         <f>COUNTIF(tblLines[Verdict],"AT_RISK")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>99</v>
-      </c>
-      <c r="B12" s="9">
+        <v>104</v>
+      </c>
+      <c r="B12" s="10">
         <f>COUNTIF(tblLines[Verdict],"LATE")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>94</v>
-      </c>
-      <c r="B13" s="9">
+        <v>99</v>
+      </c>
+      <c r="B13" s="10">
         <f>COUNTIF(tblLines[Verdict],"UNPAID")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>87</v>
-      </c>
-      <c r="B14" s="9">
+        <v>92</v>
+      </c>
+      <c r="B14" s="10">
         <f>COUNTIF(tblLines[Verdict],"UNKNOWN")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>85</v>
-      </c>
-      <c r="B15" s="9">
+        <v>90</v>
+      </c>
+      <c r="B15" s="10">
         <f>COUNTIF(tblLines[Verdict],"SKIPPED")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>183</v>
-      </c>
-      <c r="B16" s="9">
+        <v>190</v>
+      </c>
+      <c r="B16" s="10">
         <f>SUM(tblLines[Exposed])</f>
         <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>184</v>
-      </c>
-      <c r="B17" s="10">
+        <v>191</v>
+      </c>
+      <c r="B17" s="11">
         <f>ROUND(SUM(tblLines[Shortfall_r]),2)</f>
         <v>780</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>185</v>
-      </c>
-      <c r="B18" s="10">
+        <v>192</v>
+      </c>
+      <c r="B18" s="11">
         <f>ROUND(SUM(tblLines[NEC_r]),2)</f>
         <v>8.07</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>186</v>
-      </c>
-      <c r="B19" s="10">
+        <v>193</v>
+      </c>
+      <c r="B19" s="11">
         <f>ROUND(SUM(tblLines[SGC_low]),2)</f>
         <v>788.07</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>187</v>
-      </c>
-      <c r="B20" s="10">
+        <v>194</v>
+      </c>
+      <c r="B20" s="11">
         <f>ROUND(SUM(tblLines[SGC_high]),2)</f>
         <v>1260.92</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>188</v>
-      </c>
-      <c r="B21" s="9">
+        <v>195</v>
+      </c>
+      <c r="B21" s="10">
         <f>SUMPRODUCT(--(tblLines[Unassessable_between]&lt;&gt;""))</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>189</v>
-      </c>
-      <c r="B22" s="9" t="str">
+        <v>196</v>
+      </c>
+      <c r="B22" s="10" t="str">
         <f>IF(AND(SUM(tblLines[Assessable])&gt;0,SUMPRODUCT(tblLines[Assessable]*tblLines[Receipt_established])=0),"YES","NO")</f>
         <v>NO</v>
       </c>
@@ -5325,229 +8650,229 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>194</v>
-      </c>
-      <c r="B2" s="9" t="str">
+        <v>201</v>
+      </c>
+      <c r="B2" s="10" t="str">
         <f>IF(C2=0,"PASS","BLOCKED")</f>
         <v>PASS</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="10">
         <f>SUMPRODUCT(--(tblLines[Row_problem]&lt;&gt;""))</f>
         <v>0</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="10" t="str">
         <f t="array" ref="D2">IF(C2=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[Row_problem]&lt;&gt;"")*(ROW(tblLines[employee_id])-1)))))</f>
         <v/>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B3" s="9" t="str">
+        <v>202</v>
+      </c>
+      <c r="B3" s="10" t="str">
         <f>IF(C3=0,"PASS","BLOCKED")</f>
         <v>PASS</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="10">
         <f>SUM(tblLines[Guard])</f>
         <v>0</v>
       </c>
-      <c r="D3" s="9" t="str">
+      <c r="D3" s="10" t="str">
         <f t="array" ref="D3">IF(C3=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[Guard]=1)*(ROW(tblLines[employee_id])-1)))))</f>
         <v/>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>196</v>
-      </c>
-      <c r="B4" s="9" t="str">
+        <v>203</v>
+      </c>
+      <c r="B4" s="10" t="str">
         <f>IF(OR(C4=0,Summary!$B$4="Y"),"PASS","BLOCKED")</f>
         <v>BLOCKED</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="10">
         <f>SUM(tblLines[Transition_row])</f>
         <v>2</v>
       </c>
-      <c r="D4" s="9" t="str">
+      <c r="D4" s="10" t="str">
         <f t="array" ref="D4">IF(C4=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[Transition_row]=1)*(ROW(tblLines[employee_id])-1)))))</f>
         <v>EMP003</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>197</v>
-      </c>
-      <c r="B5" s="9" t="str">
+        <v>204</v>
+      </c>
+      <c r="B5" s="10" t="str">
         <f>IF(C5=0,"PASS","REVIEW")</f>
         <v>REVIEW</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="10">
         <f>SUM(tblLines[Exposed])</f>
         <v>3</v>
       </c>
-      <c r="D5" s="9" t="str">
+      <c r="D5" s="10" t="str">
         <f t="array" ref="D5">IF(C5=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[Exposed]=1)*(ROW(tblLines[employee_id])-1)))))</f>
         <v>EMP001</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>198</v>
-      </c>
-      <c r="B6" s="9" t="str">
+        <v>205</v>
+      </c>
+      <c r="B6" s="10" t="str">
         <f>IF(C6=0,"PASS","REVIEW")</f>
         <v>PASS</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="10">
         <f>SUMPRODUCT(--(tblLines[Unassessable_between]&lt;&gt;""))</f>
         <v>0</v>
       </c>
-      <c r="D6" s="9" t="str">
+      <c r="D6" s="10" t="str">
         <f t="array" ref="D6">IF(C6=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[Unassessable_between]&lt;&gt;"")*(ROW(tblLines[employee_id])-1)))))</f>
         <v/>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>199</v>
-      </c>
-      <c r="B7" s="9" t="str">
+        <v>206</v>
+      </c>
+      <c r="B7" s="10" t="str">
         <f>IF(OR(Summary!B22="NO",Summary!$B$5="Y"),"PASS","REVIEW")</f>
         <v>PASS</v>
       </c>
-      <c r="C7" s="9" t="str">
+      <c r="C7" s="10" t="str">
         <f>Summary!B22</f>
         <v>NO</v>
       </c>
-      <c r="D7" s="9"/>
+      <c r="D7" s="10"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>200</v>
-      </c>
-      <c r="B8" s="9" t="str">
+        <v>207</v>
+      </c>
+      <c r="B8" s="10" t="str">
         <f>IF(C8=0,"PASS","NOTE")</f>
         <v>PASS</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="10">
         <f>SUM(tblLines[Past_horizon])</f>
         <v>0</v>
       </c>
-      <c r="D8" s="9" t="str">
+      <c r="D8" s="10" t="str">
         <f t="array" ref="D8">IF(C8=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[Past_horizon]=1)*(ROW(tblLines[employee_id])-1)))))</f>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B9" s="9" t="str">
+        <v>208</v>
+      </c>
+      <c r="B9" s="10" t="str">
         <f>IF(C9=0,"PASS","NOTE")</f>
         <v>PASS</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="10">
         <f>SUM(tblLines[GIC_estimated])</f>
         <v>0</v>
       </c>
-      <c r="D9" s="9" t="str">
+      <c r="D9" s="10" t="str">
         <f t="array" ref="D9">IF(C9=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[GIC_estimated]=1)*(ROW(tblLines[employee_id])-1)))))</f>
         <v/>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>202</v>
-      </c>
-      <c r="B10" s="9" t="str">
+        <v>209</v>
+      </c>
+      <c r="B10" s="10" t="str">
         <f>IF(C10=0,"PASS","NOTE")</f>
         <v>PASS</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="10">
         <f>SUM(tblLines[Duplicate])</f>
         <v>0</v>
       </c>
-      <c r="D10" s="9" t="str">
+      <c r="D10" s="10" t="str">
         <f t="array" ref="D10">IF(C10=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[Duplicate]=1)*(ROW(tblLines[employee_id])-1)))))</f>
         <v/>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>203</v>
-      </c>
-      <c r="B11" s="9" t="str">
+        <v>210</v>
+      </c>
+      <c r="B11" s="10" t="str">
         <f>IF(C11=0,"PASS","NOTE")</f>
         <v>PASS</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="10">
         <f>COUNTIF(tblLines[Branch],"NIL")</f>
         <v>0</v>
       </c>
-      <c r="D11" s="9" t="str">
+      <c r="D11" s="10" t="str">
         <f t="array" ref="D11">IF(C11=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[Branch]="NIL")*(ROW(tblLines[employee_id])-1)))))</f>
         <v/>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>204</v>
-      </c>
-      <c r="B12" s="9" t="str">
-        <f>IF(AND(ISNUMBER(Summary!$B$2),OR(Summary!$B$3="",ISNUMBER(Summary!$B$3)),ISNUMBER(Summary!$B$6)),"PASS","BLOCKED")</f>
+        <v>211</v>
+      </c>
+      <c r="B12" s="10" t="str">
+        <f>IF(AND(ISNUMBER(Summary!$D$2),Summary!$D$2&lt;=DATE(2200,12,31),OR(Summary!$D$3="",AND(ISNUMBER(Summary!$D$3),Summary!$D$3&lt;=DATE(2200,12,31))),ISNUMBER(Summary!$B$6)),"PASS","BLOCKED")</f>
         <v>PASS</v>
       </c>
-      <c r="C12" s="9">
-        <f>Summary!$B$2</f>
+      <c r="C12" s="10">
+        <f>Summary!$D$2</f>
         <v>46244</v>
       </c>
-      <c r="D12" s="9"/>
+      <c r="D12" s="10"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>205</v>
-      </c>
-      <c r="B13" s="9" t="str">
+        <v>212</v>
+      </c>
+      <c r="B13" s="10" t="str">
         <f>IF(C13=0,"PASS","REVIEW")</f>
         <v>REVIEW</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="10">
         <f>SUM(tblLines[Sample_row])</f>
         <v>10</v>
       </c>
-      <c r="D13" s="9" t="str">
+      <c r="D13" s="10" t="str">
         <f t="array" ref="D13">IF(C13=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[Sample_row]=1)*(ROW(tblLines[employee_id])-1)))))</f>
         <v>EMP005</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>206</v>
-      </c>
-      <c r="B14" s="9" t="str">
+        <v>213</v>
+      </c>
+      <c r="B14" s="10" t="str">
         <f>IF(C14=0,"PASS","NOTE")</f>
         <v>PASS</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="10">
         <f>SUM(tblLines[Case_variant])</f>
         <v>0</v>
       </c>
-      <c r="D14" s="9" t="str">
+      <c r="D14" s="10" t="str">
         <f t="array" ref="D14">IF(C14=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[Case_variant]=1)*(ROW(tblLines[employee_id])-1)))))</f>
         <v/>
       </c>
@@ -5563,37 +8888,37 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -5624,74 +8949,74 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B2" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B3" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B4" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B5" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B6" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B7" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B8" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B9" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>

--- a/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
+++ b/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02CA20E-20D9-4C1C-95C7-226F380FE415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D44E127-64F6-4BE1-8D3C-D03DBAEF4F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3510" yWindow="3510" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8834,7 +8834,7 @@
         <v>211</v>
       </c>
       <c r="B12" s="10" t="str">
-        <f>IF(AND(ISNUMBER(Summary!$D$2),Summary!$D$2&lt;=DATE(2200,12,31),OR(Summary!$D$3="",AND(ISNUMBER(Summary!$D$3),Summary!$D$3&lt;=DATE(2200,12,31))),ISNUMBER(Summary!$B$6)),"PASS","BLOCKED")</f>
+        <f>IF(AND(ISNUMBER(Summary!$D$2),Summary!$D$2&lt;=DATE(2200,12,31),OR(Summary!$D$3="",AND(ISNUMBER(Summary!$D$3),Summary!$D$3&lt;=DATE(2200,12,31))),AND(ISNUMBER(Summary!$B$6),Summary!$B$6&lt;=DATE(2200,12,31))),"PASS","BLOCKED")</f>
         <v>PASS</v>
       </c>
       <c r="C12" s="10">

--- a/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
+++ b/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D803C876-E965-4529-8BED-7102C166DD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D44E127-64F6-4BE1-8D3C-D03DBAEF4F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3510" yWindow="3510" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="239">
   <si>
     <t>Payday Super review: s 18C deadlines and the SG charge estimate</t>
   </si>
@@ -100,6 +100,18 @@
     <t>defined_benefit</t>
   </si>
   <si>
+    <t>Pay_day</t>
+  </si>
+  <si>
+    <t>Remit_day</t>
+  </si>
+  <si>
+    <t>Recv_day</t>
+  </si>
+  <si>
+    <t>Next_day</t>
+  </si>
+  <si>
     <t>Flag_db</t>
   </si>
   <si>
@@ -199,6 +211,9 @@
     <t>Outstanding_to</t>
   </si>
   <si>
+    <t>Accrual_to</t>
+  </si>
+  <si>
     <t>NEC_end</t>
   </si>
   <si>
@@ -568,9 +583,15 @@
     <t>As-at date (notional earnings on unpaid lines run to it)</t>
   </si>
   <si>
+    <t>As-at date used by the register (whole day)</t>
+  </si>
+  <si>
     <t>ATO assessment date (blank if none has issued)</t>
   </si>
   <si>
+    <t>Assessment date used by the register (whole day)</t>
+  </si>
+  <si>
     <t>LCR 2026/1 transition allocation reconciled and confirmed (Y/N)</t>
   </si>
   <si>
@@ -652,7 +673,7 @@
     <t>Lines assessed at a nil SG amount (nothing to assess)</t>
   </si>
   <si>
-    <t>As-at, assessment and coverage dates on Summary are dates</t>
+    <t>As-at, assessment and coverage dates on Summary are real dates</t>
   </si>
   <si>
     <t>No fabricated example line from the shipped sample remains in the register</t>
@@ -827,9 +848,9 @@
     <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
@@ -923,8 +944,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblLines" displayName="tblLines" ref="A1:BH11">
-  <tableColumns count="60">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblLines" displayName="tblLines" ref="A1:BM11">
+  <tableColumns count="65">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="employee_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="payment_date"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="sg_amount"/>
@@ -936,152 +957,167 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="out_of_cycle"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="next_standard_payday"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="defined_benefit"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Flag_db">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Pay_day">
+      <calculatedColumnFormula>IF(tblLines[[#This Row],[payment_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),INT(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Remit_day">
+      <calculatedColumnFormula>IF(tblLines[[#This Row],[remitted_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[remitted_date]]),INT(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Recv_day">
+      <calculatedColumnFormula>IF(tblLines[[#This Row],[fund_received_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),INT(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Next_day">
+      <calculatedColumnFormula>IF(tblLines[[#This Row],[next_standard_payday]]="","",IF(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),INT(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Flag_db">
       <calculatedColumnFormula>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Flag_ooc">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Flag_ooc">
       <calculatedColumnFormula>IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"","0","f","false","n","no"}),0,""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Flag_ftf">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Flag_ftf">
       <calculatedColumnFormula>IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"","0","f","false","n","no"}),0,""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Row_problem">
-      <calculatedColumnFormula>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</calculatedColumnFormula>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Row_problem">
+      <calculatedColumnFormula>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]&gt;DATE(2200,12,31))),"date-not-real ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Pay_day]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[sg_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[remitted_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[matched_amount]],2)=0)),"amount-under-half-a-cent ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[Remit_day]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[matched_amount]],2)),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&lt;ROUND(tblLines[[#This Row],[sg_amount]],2),ISNUMBER(tblLines[[#This Row],[Remit_day]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Remit_day]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Next_day]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]]),ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Next_day]]&lt;=tblLines[[#This Row],[Pay_day]]),"next_standard_payday-not-after-payday ",""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Guard">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Guard">
       <calculatedColumnFormula>IF(OR(_xlfn.ISFORMULA(tblLines[[#This Row],[employee_id]]),_xlfn.ISFORMULA(tblLines[[#This Row],[payment_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[sg_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[matched_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[fund_received_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[first_contribution_to_fund]]),_xlfn.ISFORMULA(tblLines[[#This Row],[out_of_cycle]]),_xlfn.ISFORMULA(tblLines[[#This Row],[next_standard_payday]]),_xlfn.ISFORMULA(tblLines[[#This Row],[defined_benefit]])),1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Cap">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Cap">
       <calculatedColumnFormula>IF(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]],IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]],tblLines[[#This Row],[sg_amount]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Due_ooc">
-      <calculatedColumnFormula>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]])),WORKDAY.INTL(tblLines[[#This Row],[next_standard_payday]],7,1,tblHolidays[date]),"")</calculatedColumnFormula>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Due_ooc">
+      <calculatedColumnFormula>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]])),WORKDAY.INTL(tblLines[[#This Row],[Next_day]],7,1,tblHolidays[date]),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Due_ftf">
-      <calculatedColumnFormula>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</calculatedColumnFormula>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Due_ftf">
+      <calculatedColumnFormula>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],20,1,tblHolidays[date]),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Own_due">
-      <calculatedColumnFormula>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</calculatedColumnFormula>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Own_due">
+      <calculatedColumnFormula>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],7,1,tblHolidays[date])))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Own_pathway">
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Own_pathway">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Earliest_prepay">
-      <calculatedColumnFormula>IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),EDATE(tblLines[[#This Row],[payment_date]]-1,-12)+1,"")</calculatedColumnFormula>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Earliest_prepay">
+      <calculatedColumnFormula>IF(ISNUMBER(tblLines[[#This Row],[Pay_day]]),EDATE(tblLines[[#This Row],[Pay_day]]-1,-12)+1,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Settled">
-      <calculatedColumnFormula>IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[fund_received_date]],"")</calculatedColumnFormula>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Settled">
+      <calculatedColumnFormula>IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Recv_day]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Remit">
-      <calculatedColumnFormula>IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[remitted_date]],"")</calculatedColumnFormula>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Remit">
+      <calculatedColumnFormula>IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Remit_day]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Receipt_credit">
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="Receipt_credit">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[Cap]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Credit">
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Credit">
       <calculatedColumnFormula>IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[remitted_amount]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",ROUND(tblLines[[#This Row],[sg_amount]],2),0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Evidence_own">
-      <calculatedColumnFormula>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</calculatedColumnFormula>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="Evidence_own">
+      <calculatedColumnFormula>IF(OR(tblLines[[#This Row],[Own_due]]=0,ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,tblLines[[#This Row],[Flag_db]]=1,ROUND(tblLines[[#This Row],[Cap]],2)&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),IF(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2,IF(OR(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[Recv_day]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Confirmed_latest">
-      <calculatedColumnFormula array="1">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</calculatedColumnFormula>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="Confirmed_latest">
+      <calculatedColumnFormula array="1">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="Possible_latest">
-      <calculatedColumnFormula array="1">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</calculatedColumnFormula>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="Possible_latest">
+      <calculatedColumnFormula array="1">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Final_due">
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="Final_due">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="Pathway">
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="Pathway">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="Possible_item4">
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="Possible_item4">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Final_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Possible_latest]]),tblLines[[#This Row],[Possible_latest]]&gt;tblLines[[#This Row],[Final_due]]),tblLines[[#This Row],[Possible_latest]],""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="Past_horizon">
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="Past_horizon">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Final_due]]="","",IF((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),1,0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="Branch">
-      <calculatedColumnFormula>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(tblLines[[#This Row],[sg_amount]]&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[payment_date]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"B1",IF(Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</calculatedColumnFormula>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="Branch">
+      <calculatedColumnFormula>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="Verdict">
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="Verdict">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Branch]]="","",INDEX(tblCodes[verdict],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="Unassessable_between">
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="Unassessable_between">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Branch]]="","",T(INDEX(tblCodes[unassessable],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="Exposed">
+    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="Exposed">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[exposed],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="Stale_prepay">
+    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="Stale_prepay">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[stale],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="OTRC">
+    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="OTRC">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[otrc],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))*tblLines[[#This Row],[Receipt_credit]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="Base_shortfall">
+    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="Base_shortfall">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),MAX(ROUND(tblLines[[#This Row],[sg_amount]],2)-tblLines[[#This Row],[OTRC]],0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="Offset_s18D">
-      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$B$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$B$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</calculatedColumnFormula>
+    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="Offset_s18D">
+      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="Final_shortfall">
+    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="Final_shortfall">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),MAX(tblLines[[#This Row],[Base_shortfall]]-tblLines[[#This Row],[Offset_s18D]],0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="Lateness_basis">
-      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</calculatedColumnFormula>
+    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="Lateness_basis">
+      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="Outstanding_to">
-      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[Settled]],Summary!$B$2),"")</calculatedColumnFormula>
+    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="Outstanding_to">
+      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="NEC_end">
-      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),MIN(IF(Summary!$B$3="",DATE(2030,12,31),Summary!$B$3-1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$B$2)),"")</calculatedColumnFormula>
+    <tableColumn id="49" xr3:uid="{00000000-0010-0000-0000-000031000000}" name="Accrual_to">
+      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="Days_late">
+    <tableColumn id="50" xr3:uid="{00000000-0010-0000-0000-000032000000}" name="NEC_end">
+      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(Summary!$D$3="",tblLines[[#This Row],[Accrual_to]],MIN(Summary!$D$3-1,tblLines[[#This Row],[Accrual_to]])),"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="51" xr3:uid="{00000000-0010-0000-0000-000033000000}" name="Days_late">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="NEC">
+    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" name="NEC">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="GIC_estimated">
+    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" name="GIC_estimated">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="49" xr3:uid="{00000000-0010-0000-0000-000031000000}" name="Shortfall_r">
+    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" name="Shortfall_r">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="50" xr3:uid="{00000000-0010-0000-0000-000032000000}" name="NEC_r">
+    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" name="NEC_r">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="51" xr3:uid="{00000000-0010-0000-0000-000033000000}" name="Uplift_best">
+    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" name="Uplift_best">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" name="Uplift_worst">
+    <tableColumn id="57" xr3:uid="{00000000-0010-0000-0000-000039000000}" name="Uplift_worst">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" name="SGC_low">
+    <tableColumn id="58" xr3:uid="{00000000-0010-0000-0000-00003A000000}" name="SGC_low">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" name="SGC_high">
+    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0000-00003B000000}" name="SGC_high">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" name="Transition_row">
-      <calculatedColumnFormula>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0,tblLines[[#This Row],[Cap]]&gt;0,OR(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]])),IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]],tblLines[[#This Row],[remitted_date]])&lt;=DATE(2026,7,28)),1,0)</calculatedColumnFormula>
+    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0000-00003C000000}" name="Transition_row">
+      <calculatedColumnFormula>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0,ROUND(tblLines[[#This Row],[Cap]],2)&gt;0,OR(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]])),IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]],tblLines[[#This Row],[Remit_day]])&lt;=DATE(2026,7,28)),1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" name="Receipt_established">
+    <tableColumn id="61" xr3:uid="{00000000-0010-0000-0000-00003D000000}" name="Receipt_established">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="57" xr3:uid="{00000000-0010-0000-0000-000039000000}" name="Assessable">
-      <calculatedColumnFormula>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0),1,0)</calculatedColumnFormula>
+    <tableColumn id="62" xr3:uid="{00000000-0010-0000-0000-00003E000000}" name="Assessable">
+      <calculatedColumnFormula>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0),1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="58" xr3:uid="{00000000-0010-0000-0000-00003A000000}" name="Duplicate">
-      <calculatedColumnFormula>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</calculatedColumnFormula>
+    <tableColumn id="63" xr3:uid="{00000000-0010-0000-0000-00003F000000}" name="Duplicate">
+      <calculatedColumnFormula>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[Pay_day]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[Remit_day]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[Recv_day]]&amp;"")&gt;1,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0000-00003B000000}" name="Case_variant">
+    <tableColumn id="64" xr3:uid="{00000000-0010-0000-0000-000040000000}" name="Case_variant">
       <calculatedColumnFormula array="1">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0000-00003C000000}" name="Sample_row">
-      <calculatedColumnFormula>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</calculatedColumnFormula>
+    <tableColumn id="65" xr3:uid="{00000000-0010-0000-0000-000041000000}" name="Sample_row">
+      <calculatedColumnFormula>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[Pay_day]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1114,7 +1150,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tblGic" displayName="tblGic" ref="A1:F8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tblGic" displayName="tblGic" ref="A1:F178">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="from"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="to"/>
@@ -1487,19 +1523,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BH11"/>
+  <dimension ref="A1:BM11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="30" customWidth="1"/>
-    <col min="16" max="35" width="13" customWidth="1"/>
-    <col min="36" max="36" width="22" customWidth="1"/>
-    <col min="37" max="42" width="13" customWidth="1"/>
-    <col min="43" max="43" width="34" customWidth="1"/>
-    <col min="44" max="60" width="13" customWidth="1"/>
+    <col min="1" max="18" width="13" customWidth="1"/>
+    <col min="19" max="19" width="30" customWidth="1"/>
+    <col min="20" max="39" width="13" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="34" customWidth="1"/>
+    <col min="48" max="65" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
@@ -1680,10 +1716,25 @@
       <c r="BH1" s="5" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="2" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="BI1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="BK1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="BL1" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="BM1" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B2" s="7">
         <v>46212</v>
@@ -1700,215 +1751,235 @@
         <v>46219</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J2" s="7"/>
       <c r="K2" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L2" s="9">
+        <f>IF(tblLines[[#This Row],[payment_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),INT(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]))</f>
+        <v>46212</v>
+      </c>
+      <c r="M2" s="9">
+        <f>IF(tblLines[[#This Row],[remitted_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[remitted_date]]),INT(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]))</f>
+        <v>46217</v>
+      </c>
+      <c r="N2" s="9">
+        <f>IF(tblLines[[#This Row],[fund_received_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),INT(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]))</f>
+        <v>46219</v>
+      </c>
+      <c r="O2" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[next_standard_payday]]="","",IF(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),INT(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]))</f>
+        <v/>
+      </c>
+      <c r="P2" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="M2" s="9">
+      <c r="Q2" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="N2" s="9">
+      <c r="R2" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="O2" s="9" t="str">
-        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
-        <v/>
-      </c>
-      <c r="P2" s="9">
+      <c r="S2" s="10" t="str">
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]&gt;DATE(2200,12,31))),"date-not-real ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Pay_day]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[sg_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[remitted_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[matched_amount]],2)=0)),"amount-under-half-a-cent ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[Remit_day]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[matched_amount]],2)),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&lt;ROUND(tblLines[[#This Row],[sg_amount]],2),ISNUMBER(tblLines[[#This Row],[Remit_day]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Remit_day]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Next_day]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]]),ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Next_day]]&lt;=tblLines[[#This Row],[Pay_day]]),"next_standard_payday-not-after-payday ",""))</f>
+        <v/>
+      </c>
+      <c r="T2" s="10">
         <f>IF(OR(_xlfn.ISFORMULA(tblLines[[#This Row],[employee_id]]),_xlfn.ISFORMULA(tblLines[[#This Row],[payment_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[sg_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[matched_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[fund_received_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[first_contribution_to_fund]]),_xlfn.ISFORMULA(tblLines[[#This Row],[out_of_cycle]]),_xlfn.ISFORMULA(tblLines[[#This Row],[next_standard_payday]]),_xlfn.ISFORMULA(tblLines[[#This Row],[defined_benefit]])),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="U2" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]],IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]],tblLines[[#This Row],[sg_amount]]))</f>
         <v>612</v>
       </c>
-      <c r="R2" s="11" t="str">
-        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]])),WORKDAY.INTL(tblLines[[#This Row],[next_standard_payday]],7,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="S2" s="11" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="T2" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+      <c r="V2" s="9" t="str">
+        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]])),WORKDAY.INTL(tblLines[[#This Row],[Next_day]],7,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="W2" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],20,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="X2" s="9">
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],7,1,tblHolidays[date])))</f>
         <v>46223</v>
       </c>
-      <c r="U2" s="9" t="str">
+      <c r="Y2" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="V2" s="11">
-        <f>IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),EDATE(tblLines[[#This Row],[payment_date]]-1,-12)+1,"")</f>
+      <c r="Z2" s="9">
+        <f>IF(ISNUMBER(tblLines[[#This Row],[Pay_day]]),EDATE(tblLines[[#This Row],[Pay_day]]-1,-12)+1,"")</f>
         <v>45847</v>
       </c>
-      <c r="W2" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[fund_received_date]],"")</f>
+      <c r="AA2" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Recv_day]],"")</f>
         <v>46219</v>
       </c>
-      <c r="X2" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[remitted_date]],"")</f>
+      <c r="AB2" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Remit_day]],"")</f>
         <v>46217</v>
       </c>
-      <c r="Y2" s="10">
+      <c r="AC2" s="11">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[Cap]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0)</f>
         <v>612</v>
       </c>
-      <c r="Z2" s="10">
+      <c r="AD2" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[remitted_amount]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",ROUND(tblLines[[#This Row],[sg_amount]],2),0))</f>
         <v>612</v>
       </c>
-      <c r="AA2" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+      <c r="AE2" s="10" t="str">
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,tblLines[[#This Row],[Flag_db]]=1,ROUND(tblLines[[#This Row],[Cap]],2)&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),IF(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2,IF(OR(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[Recv_day]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>confirmed</v>
       </c>
-      <c r="AB2" s="11">
-        <f t="array" ref="AB2">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AC2" s="11">
-        <f t="array" ref="AC2">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AD2" s="11">
+      <c r="AF2" s="9">
+        <f t="array" ref="AF2">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AG2" s="9">
+        <f t="array" ref="AG2">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AH2" s="9">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46223</v>
       </c>
-      <c r="AE2" s="9" t="str">
+      <c r="AI2" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="AF2" s="11" t="str">
+      <c r="AJ2" s="9" t="str">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Possible_latest]]),tblLines[[#This Row],[Possible_latest]]&gt;tblLines[[#This Row],[Final_due]]),tblLines[[#This Row],[Possible_latest]],""))</f>
         <v/>
       </c>
-      <c r="AG2" s="9">
+      <c r="AK2" s="10">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),1,0))</f>
         <v>0</v>
       </c>
-      <c r="AH2" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(tblLines[[#This Row],[sg_amount]]&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[payment_date]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"B1",IF(Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+      <c r="AL2" s="10" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>D1</v>
       </c>
-      <c r="AI2" s="9" t="str">
+      <c r="AM2" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",INDEX(tblCodes[verdict],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>ON_TIME</v>
       </c>
-      <c r="AJ2" s="9" t="str">
+      <c r="AN2" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",T(INDEX(tblCodes[unassessable],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))))</f>
         <v/>
       </c>
-      <c r="AK2" s="9">
+      <c r="AO2" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[exposed],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AL2" s="9">
+      <c r="AP2" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[stale],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AM2" s="10">
+      <c r="AQ2" s="11">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[otrc],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))*tblLines[[#This Row],[Receipt_credit]])</f>
         <v>612</v>
       </c>
-      <c r="AN2" s="10" t="str">
+      <c r="AR2" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(ROUND(tblLines[[#This Row],[sg_amount]],2)-tblLines[[#This Row],[OTRC]],0),"")</f>
         <v/>
       </c>
-      <c r="AO2" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$B$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$B$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
-        <v/>
-      </c>
-      <c r="AP2" s="10" t="str">
+      <c r="AS2" s="11" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="AT2" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(tblLines[[#This Row],[Base_shortfall]]-tblLines[[#This Row],[Offset_s18D]],0),"")</f>
         <v/>
       </c>
-      <c r="AQ2" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
-        <v/>
-      </c>
-      <c r="AR2" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[Settled]],Summary!$B$2),"")</f>
-        <v/>
-      </c>
-      <c r="AS2" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),MIN(IF(Summary!$B$3="",DATE(2030,12,31),Summary!$B$3-1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$B$2)),"")</f>
-        <v/>
-      </c>
-      <c r="AT2" s="9" t="str">
+      <c r="AU2" s="10" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <v/>
+      </c>
+      <c r="AV2" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AW2" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AX2" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(Summary!$D$3="",tblLines[[#This Row],[Accrual_to]],MIN(Summary!$D$3-1,tblLines[[#This Row],[Accrual_to]])),"")</f>
+        <v/>
+      </c>
+      <c r="AY2" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v/>
       </c>
-      <c r="AU2" s="10" t="str">
+      <c r="AZ2" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
         <v/>
       </c>
-      <c r="AV2" s="9" t="str">
+      <c r="BA2" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
         <v/>
       </c>
-      <c r="AW2" s="10" t="str">
+      <c r="BB2" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</f>
         <v/>
       </c>
-      <c r="AX2" s="10" t="str">
+      <c r="BC2" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
         <v/>
       </c>
-      <c r="AY2" s="10" t="str">
+      <c r="BD2" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
         <v/>
       </c>
-      <c r="AZ2" s="10" t="str">
+      <c r="BE2" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
         <v/>
       </c>
-      <c r="BA2" s="10" t="str">
+      <c r="BF2" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
         <v/>
       </c>
-      <c r="BB2" s="10" t="str">
+      <c r="BG2" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
         <v/>
       </c>
-      <c r="BC2" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0,tblLines[[#This Row],[Cap]]&gt;0,OR(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]])),IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]],tblLines[[#This Row],[remitted_date]])&lt;=DATE(2026,7,28)),1,0)</f>
+      <c r="BH2" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0,ROUND(tblLines[[#This Row],[Cap]],2)&gt;0,OR(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]])),IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]],tblLines[[#This Row],[Remit_day]])&lt;=DATE(2026,7,28)),1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD2" s="9">
+      <c r="BI2" s="10">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE2" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0),1,0)</f>
+      <c r="BJ2" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF2" s="9">
-        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BG2" s="9">
-        <f t="array" ref="BG2">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH2" s="9">
-        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+      <c r="BK2" s="10">
+        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[Pay_day]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[Remit_day]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[Recv_day]]&amp;"")&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL2" s="10">
+        <f t="array" ref="BL2">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM2" s="10">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[Pay_day]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B3" s="7">
         <v>46212</v>
@@ -1925,215 +1996,235 @@
         <v>46238</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J3" s="7"/>
       <c r="K3" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L3" s="9">
+        <f>IF(tblLines[[#This Row],[payment_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),INT(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]))</f>
+        <v>46212</v>
+      </c>
+      <c r="M3" s="9">
+        <f>IF(tblLines[[#This Row],[remitted_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[remitted_date]]),INT(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]))</f>
+        <v>46233</v>
+      </c>
+      <c r="N3" s="9">
+        <f>IF(tblLines[[#This Row],[fund_received_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),INT(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]))</f>
+        <v>46238</v>
+      </c>
+      <c r="O3" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[next_standard_payday]]="","",IF(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),INT(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]))</f>
+        <v/>
+      </c>
+      <c r="P3" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="M3" s="9">
+      <c r="Q3" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="N3" s="9">
+      <c r="R3" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="O3" s="9" t="str">
-        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
-        <v/>
-      </c>
-      <c r="P3" s="9">
+      <c r="S3" s="10" t="str">
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]&gt;DATE(2200,12,31))),"date-not-real ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Pay_day]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[sg_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[remitted_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[matched_amount]],2)=0)),"amount-under-half-a-cent ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[Remit_day]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[matched_amount]],2)),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&lt;ROUND(tblLines[[#This Row],[sg_amount]],2),ISNUMBER(tblLines[[#This Row],[Remit_day]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Remit_day]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Next_day]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]]),ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Next_day]]&lt;=tblLines[[#This Row],[Pay_day]]),"next_standard_payday-not-after-payday ",""))</f>
+        <v/>
+      </c>
+      <c r="T3" s="10">
         <f>IF(OR(_xlfn.ISFORMULA(tblLines[[#This Row],[employee_id]]),_xlfn.ISFORMULA(tblLines[[#This Row],[payment_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[sg_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[matched_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[fund_received_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[first_contribution_to_fund]]),_xlfn.ISFORMULA(tblLines[[#This Row],[out_of_cycle]]),_xlfn.ISFORMULA(tblLines[[#This Row],[next_standard_payday]]),_xlfn.ISFORMULA(tblLines[[#This Row],[defined_benefit]])),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="10">
+      <c r="U3" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]],IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]],tblLines[[#This Row],[sg_amount]]))</f>
         <v>540</v>
       </c>
-      <c r="R3" s="11" t="str">
-        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]])),WORKDAY.INTL(tblLines[[#This Row],[next_standard_payday]],7,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="S3" s="11" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="T3" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+      <c r="V3" s="9" t="str">
+        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]])),WORKDAY.INTL(tblLines[[#This Row],[Next_day]],7,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="W3" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],20,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="X3" s="9">
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],7,1,tblHolidays[date])))</f>
         <v>46223</v>
       </c>
-      <c r="U3" s="9" t="str">
+      <c r="Y3" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="V3" s="11">
-        <f>IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),EDATE(tblLines[[#This Row],[payment_date]]-1,-12)+1,"")</f>
+      <c r="Z3" s="9">
+        <f>IF(ISNUMBER(tblLines[[#This Row],[Pay_day]]),EDATE(tblLines[[#This Row],[Pay_day]]-1,-12)+1,"")</f>
         <v>45847</v>
       </c>
-      <c r="W3" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[fund_received_date]],"")</f>
+      <c r="AA3" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Recv_day]],"")</f>
         <v>46238</v>
       </c>
-      <c r="X3" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[remitted_date]],"")</f>
+      <c r="AB3" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Remit_day]],"")</f>
         <v>46233</v>
       </c>
-      <c r="Y3" s="10">
+      <c r="AC3" s="11">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[Cap]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0)</f>
         <v>540</v>
       </c>
-      <c r="Z3" s="10">
+      <c r="AD3" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[remitted_amount]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",ROUND(tblLines[[#This Row],[sg_amount]],2),0))</f>
         <v>540</v>
       </c>
-      <c r="AA3" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+      <c r="AE3" s="10" t="str">
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,tblLines[[#This Row],[Flag_db]]=1,ROUND(tblLines[[#This Row],[Cap]],2)&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),IF(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2,IF(OR(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[Recv_day]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>impossible</v>
       </c>
-      <c r="AB3" s="11">
-        <f t="array" ref="AB3">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AC3" s="11">
-        <f t="array" ref="AC3">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AD3" s="11">
+      <c r="AF3" s="9">
+        <f t="array" ref="AF3">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AG3" s="9">
+        <f t="array" ref="AG3">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AH3" s="9">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46223</v>
       </c>
-      <c r="AE3" s="9" t="str">
+      <c r="AI3" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="AF3" s="11" t="str">
+      <c r="AJ3" s="9" t="str">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Possible_latest]]),tblLines[[#This Row],[Possible_latest]]&gt;tblLines[[#This Row],[Final_due]]),tblLines[[#This Row],[Possible_latest]],""))</f>
         <v/>
       </c>
-      <c r="AG3" s="9">
+      <c r="AK3" s="10">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),1,0))</f>
         <v>0</v>
       </c>
-      <c r="AH3" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(tblLines[[#This Row],[sg_amount]]&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[payment_date]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"B1",IF(Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+      <c r="AL3" s="10" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>E</v>
       </c>
-      <c r="AI3" s="9" t="str">
+      <c r="AM3" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",INDEX(tblCodes[verdict],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>LATE</v>
       </c>
-      <c r="AJ3" s="9" t="str">
+      <c r="AN3" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",T(INDEX(tblCodes[unassessable],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))))</f>
         <v/>
       </c>
-      <c r="AK3" s="9">
+      <c r="AO3" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[exposed],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>1</v>
       </c>
-      <c r="AL3" s="9">
+      <c r="AP3" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[stale],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AM3" s="10">
+      <c r="AQ3" s="11">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[otrc],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))*tblLines[[#This Row],[Receipt_credit]])</f>
         <v>0</v>
       </c>
-      <c r="AN3" s="10">
+      <c r="AR3" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(ROUND(tblLines[[#This Row],[sg_amount]],2)-tblLines[[#This Row],[OTRC]],0),"")</f>
         <v>540</v>
       </c>
-      <c r="AO3" s="10">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$B$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$B$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+      <c r="AS3" s="11">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
         <v>540</v>
       </c>
-      <c r="AP3" s="10">
+      <c r="AT3" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(tblLines[[#This Row],[Base_shortfall]]-tblLines[[#This Row],[Offset_s18D]],0),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ3" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+      <c r="AU3" s="10" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
         <v>fund receipt</v>
       </c>
-      <c r="AR3" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[Settled]],Summary!$B$2),"")</f>
+      <c r="AV3" s="9">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v>46238</v>
       </c>
-      <c r="AS3" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),MIN(IF(Summary!$B$3="",DATE(2030,12,31),Summary!$B$3-1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$B$2)),"")</f>
+      <c r="AW3" s="9">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v>46238</v>
       </c>
-      <c r="AT3" s="9">
+      <c r="AX3" s="9">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(Summary!$D$3="",tblLines[[#This Row],[Accrual_to]],MIN(Summary!$D$3-1,tblLines[[#This Row],[Accrual_to]])),"")</f>
+        <v>46238</v>
+      </c>
+      <c r="AY3" s="10">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v>15</v>
       </c>
-      <c r="AU3" s="10">
+      <c r="AZ3" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
         <v>2.5420882921707211</v>
       </c>
-      <c r="AV3" s="9">
+      <c r="BA3" s="10">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
         <v>0</v>
       </c>
-      <c r="AW3" s="10">
+      <c r="BB3" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</f>
         <v>0</v>
       </c>
-      <c r="AX3" s="10">
+      <c r="BC3" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
         <v>2.54</v>
       </c>
-      <c r="AY3" s="10">
+      <c r="BD3" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
         <v>0</v>
       </c>
-      <c r="AZ3" s="10">
+      <c r="BE3" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
         <v>1.53</v>
       </c>
-      <c r="BA3" s="10">
+      <c r="BF3" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
         <v>2.54</v>
       </c>
-      <c r="BB3" s="10">
+      <c r="BG3" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
         <v>4.07</v>
       </c>
-      <c r="BC3" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0,tblLines[[#This Row],[Cap]]&gt;0,OR(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]])),IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]],tblLines[[#This Row],[remitted_date]])&lt;=DATE(2026,7,28)),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BD3" s="9">
+      <c r="BH3" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0,ROUND(tblLines[[#This Row],[Cap]],2)&gt;0,OR(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]])),IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]],tblLines[[#This Row],[Remit_day]])&lt;=DATE(2026,7,28)),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI3" s="10">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE3" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0),1,0)</f>
+      <c r="BJ3" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF3" s="9">
-        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BG3" s="9">
-        <f t="array" ref="BG3">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH3" s="9">
-        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+      <c r="BK3" s="10">
+        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[Pay_day]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[Remit_day]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[Recv_day]]&amp;"")&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL3" s="10">
+        <f t="array" ref="BL3">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM3" s="10">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[Pay_day]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B4" s="7">
         <v>46212</v>
@@ -2148,215 +2239,235 @@
       <c r="F4" s="8"/>
       <c r="G4" s="7"/>
       <c r="H4" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J4" s="7"/>
       <c r="K4" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L4" s="9">
+        <f>IF(tblLines[[#This Row],[payment_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),INT(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]))</f>
+        <v>46212</v>
+      </c>
+      <c r="M4" s="9">
+        <f>IF(tblLines[[#This Row],[remitted_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[remitted_date]]),INT(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]))</f>
+        <v>46218</v>
+      </c>
+      <c r="N4" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[fund_received_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),INT(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]))</f>
+        <v/>
+      </c>
+      <c r="O4" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[next_standard_payday]]="","",IF(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),INT(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]))</f>
+        <v/>
+      </c>
+      <c r="P4" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="M4" s="9">
+      <c r="Q4" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="N4" s="9">
+      <c r="R4" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="O4" s="9" t="str">
-        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
-        <v/>
-      </c>
-      <c r="P4" s="9">
+      <c r="S4" s="10" t="str">
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]&gt;DATE(2200,12,31))),"date-not-real ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Pay_day]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[sg_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[remitted_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[matched_amount]],2)=0)),"amount-under-half-a-cent ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[Remit_day]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[matched_amount]],2)),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&lt;ROUND(tblLines[[#This Row],[sg_amount]],2),ISNUMBER(tblLines[[#This Row],[Remit_day]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Remit_day]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Next_day]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]]),ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Next_day]]&lt;=tblLines[[#This Row],[Pay_day]]),"next_standard_payday-not-after-payday ",""))</f>
+        <v/>
+      </c>
+      <c r="T4" s="10">
         <f>IF(OR(_xlfn.ISFORMULA(tblLines[[#This Row],[employee_id]]),_xlfn.ISFORMULA(tblLines[[#This Row],[payment_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[sg_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[matched_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[fund_received_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[first_contribution_to_fund]]),_xlfn.ISFORMULA(tblLines[[#This Row],[out_of_cycle]]),_xlfn.ISFORMULA(tblLines[[#This Row],[next_standard_payday]]),_xlfn.ISFORMULA(tblLines[[#This Row],[defined_benefit]])),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="10">
+      <c r="U4" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]],IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]],tblLines[[#This Row],[sg_amount]]))</f>
         <v>318</v>
       </c>
-      <c r="R4" s="11" t="str">
-        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]])),WORKDAY.INTL(tblLines[[#This Row],[next_standard_payday]],7,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="S4" s="11" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="T4" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+      <c r="V4" s="9" t="str">
+        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]])),WORKDAY.INTL(tblLines[[#This Row],[Next_day]],7,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="W4" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],20,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="X4" s="9">
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],7,1,tblHolidays[date])))</f>
         <v>46223</v>
       </c>
-      <c r="U4" s="9" t="str">
+      <c r="Y4" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="V4" s="11">
-        <f>IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),EDATE(tblLines[[#This Row],[payment_date]]-1,-12)+1,"")</f>
+      <c r="Z4" s="9">
+        <f>IF(ISNUMBER(tblLines[[#This Row],[Pay_day]]),EDATE(tblLines[[#This Row],[Pay_day]]-1,-12)+1,"")</f>
         <v>45847</v>
       </c>
-      <c r="W4" s="11" t="str">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[fund_received_date]],"")</f>
-        <v/>
-      </c>
-      <c r="X4" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[remitted_date]],"")</f>
+      <c r="AA4" s="9" t="str">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Recv_day]],"")</f>
+        <v/>
+      </c>
+      <c r="AB4" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Remit_day]],"")</f>
         <v>46218</v>
       </c>
-      <c r="Y4" s="10">
+      <c r="AC4" s="11">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[Cap]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0)</f>
         <v>0</v>
       </c>
-      <c r="Z4" s="10">
+      <c r="AD4" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[remitted_amount]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",ROUND(tblLines[[#This Row],[sg_amount]],2),0))</f>
         <v>318</v>
       </c>
-      <c r="AA4" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+      <c r="AE4" s="10" t="str">
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,tblLines[[#This Row],[Flag_db]]=1,ROUND(tblLines[[#This Row],[Cap]],2)&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),IF(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2,IF(OR(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[Recv_day]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>possible</v>
       </c>
-      <c r="AB4" s="11">
-        <f t="array" ref="AB4">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AC4" s="11">
-        <f t="array" ref="AC4">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AD4" s="11">
+      <c r="AF4" s="9">
+        <f t="array" ref="AF4">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AG4" s="9">
+        <f t="array" ref="AG4">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AH4" s="9">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46223</v>
       </c>
-      <c r="AE4" s="9" t="str">
+      <c r="AI4" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="AF4" s="11" t="str">
+      <c r="AJ4" s="9" t="str">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Possible_latest]]),tblLines[[#This Row],[Possible_latest]]&gt;tblLines[[#This Row],[Final_due]]),tblLines[[#This Row],[Possible_latest]],""))</f>
         <v/>
       </c>
-      <c r="AG4" s="9">
+      <c r="AK4" s="10">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),1,0))</f>
         <v>0</v>
       </c>
-      <c r="AH4" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(tblLines[[#This Row],[sg_amount]]&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[payment_date]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"B1",IF(Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+      <c r="AL4" s="10" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>R3</v>
       </c>
-      <c r="AI4" s="9" t="str">
+      <c r="AM4" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",INDEX(tblCodes[verdict],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>AT_RISK</v>
       </c>
-      <c r="AJ4" s="9" t="str">
+      <c r="AN4" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",T(INDEX(tblCodes[unassessable],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))))</f>
         <v/>
       </c>
-      <c r="AK4" s="9">
+      <c r="AO4" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[exposed],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AL4" s="9">
+      <c r="AP4" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[stale],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AM4" s="10">
+      <c r="AQ4" s="11">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[otrc],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))*tblLines[[#This Row],[Receipt_credit]])</f>
         <v>0</v>
       </c>
-      <c r="AN4" s="10" t="str">
+      <c r="AR4" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(ROUND(tblLines[[#This Row],[sg_amount]],2)-tblLines[[#This Row],[OTRC]],0),"")</f>
         <v/>
       </c>
-      <c r="AO4" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$B$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$B$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
-        <v/>
-      </c>
-      <c r="AP4" s="10" t="str">
+      <c r="AS4" s="11" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="AT4" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(tblLines[[#This Row],[Base_shortfall]]-tblLines[[#This Row],[Offset_s18D]],0),"")</f>
         <v/>
       </c>
-      <c r="AQ4" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
-        <v/>
-      </c>
-      <c r="AR4" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[Settled]],Summary!$B$2),"")</f>
-        <v/>
-      </c>
-      <c r="AS4" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),MIN(IF(Summary!$B$3="",DATE(2030,12,31),Summary!$B$3-1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$B$2)),"")</f>
-        <v/>
-      </c>
-      <c r="AT4" s="9" t="str">
+      <c r="AU4" s="10" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <v/>
+      </c>
+      <c r="AV4" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AW4" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AX4" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(Summary!$D$3="",tblLines[[#This Row],[Accrual_to]],MIN(Summary!$D$3-1,tblLines[[#This Row],[Accrual_to]])),"")</f>
+        <v/>
+      </c>
+      <c r="AY4" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v/>
       </c>
-      <c r="AU4" s="10" t="str">
+      <c r="AZ4" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
         <v/>
       </c>
-      <c r="AV4" s="9" t="str">
+      <c r="BA4" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
         <v/>
       </c>
-      <c r="AW4" s="10" t="str">
+      <c r="BB4" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</f>
         <v/>
       </c>
-      <c r="AX4" s="10" t="str">
+      <c r="BC4" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
         <v/>
       </c>
-      <c r="AY4" s="10" t="str">
+      <c r="BD4" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
         <v/>
       </c>
-      <c r="AZ4" s="10" t="str">
+      <c r="BE4" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
         <v/>
       </c>
-      <c r="BA4" s="10" t="str">
+      <c r="BF4" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
         <v/>
       </c>
-      <c r="BB4" s="10" t="str">
+      <c r="BG4" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
         <v/>
       </c>
-      <c r="BC4" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0,tblLines[[#This Row],[Cap]]&gt;0,OR(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]])),IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]],tblLines[[#This Row],[remitted_date]])&lt;=DATE(2026,7,28)),1,0)</f>
+      <c r="BH4" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0,ROUND(tblLines[[#This Row],[Cap]],2)&gt;0,OR(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]])),IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]],tblLines[[#This Row],[Remit_day]])&lt;=DATE(2026,7,28)),1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD4" s="9">
+      <c r="BI4" s="10">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",1,0)</f>
         <v>0</v>
       </c>
-      <c r="BE4" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0),1,0)</f>
+      <c r="BJ4" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF4" s="9">
-        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BG4" s="9">
-        <f t="array" ref="BG4">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH4" s="9">
-        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+      <c r="BK4" s="10">
+        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[Pay_day]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[Remit_day]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[Recv_day]]&amp;"")&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL4" s="10">
+        <f t="array" ref="BL4">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM4" s="10">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[Pay_day]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B5" s="7">
         <v>46212</v>
@@ -2369,215 +2480,235 @@
       <c r="F5" s="8"/>
       <c r="G5" s="7"/>
       <c r="H5" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J5" s="7"/>
       <c r="K5" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L5" s="9">
+        <f>IF(tblLines[[#This Row],[payment_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),INT(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]))</f>
+        <v>46212</v>
+      </c>
+      <c r="M5" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[remitted_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[remitted_date]]),INT(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]))</f>
+        <v/>
+      </c>
+      <c r="N5" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[fund_received_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),INT(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]))</f>
+        <v/>
+      </c>
+      <c r="O5" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[next_standard_payday]]="","",IF(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),INT(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]))</f>
+        <v/>
+      </c>
+      <c r="P5" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="M5" s="9">
+      <c r="Q5" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="N5" s="9">
+      <c r="R5" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="O5" s="9" t="str">
-        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
-        <v/>
-      </c>
-      <c r="P5" s="9">
+      <c r="S5" s="10" t="str">
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]&gt;DATE(2200,12,31))),"date-not-real ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Pay_day]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[sg_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[remitted_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[matched_amount]],2)=0)),"amount-under-half-a-cent ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[Remit_day]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[matched_amount]],2)),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&lt;ROUND(tblLines[[#This Row],[sg_amount]],2),ISNUMBER(tblLines[[#This Row],[Remit_day]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Remit_day]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Next_day]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]]),ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Next_day]]&lt;=tblLines[[#This Row],[Pay_day]]),"next_standard_payday-not-after-payday ",""))</f>
+        <v/>
+      </c>
+      <c r="T5" s="10">
         <f>IF(OR(_xlfn.ISFORMULA(tblLines[[#This Row],[employee_id]]),_xlfn.ISFORMULA(tblLines[[#This Row],[payment_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[sg_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[matched_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[fund_received_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[first_contribution_to_fund]]),_xlfn.ISFORMULA(tblLines[[#This Row],[out_of_cycle]]),_xlfn.ISFORMULA(tblLines[[#This Row],[next_standard_payday]]),_xlfn.ISFORMULA(tblLines[[#This Row],[defined_benefit]])),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="10">
+      <c r="U5" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]],IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]],tblLines[[#This Row],[sg_amount]]))</f>
         <v>780</v>
       </c>
-      <c r="R5" s="11" t="str">
-        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]])),WORKDAY.INTL(tblLines[[#This Row],[next_standard_payday]],7,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="S5" s="11" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="T5" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+      <c r="V5" s="9" t="str">
+        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]])),WORKDAY.INTL(tblLines[[#This Row],[Next_day]],7,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="W5" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],20,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="X5" s="9">
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],7,1,tblHolidays[date])))</f>
         <v>46223</v>
       </c>
-      <c r="U5" s="9" t="str">
+      <c r="Y5" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="V5" s="11">
-        <f>IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),EDATE(tblLines[[#This Row],[payment_date]]-1,-12)+1,"")</f>
+      <c r="Z5" s="9">
+        <f>IF(ISNUMBER(tblLines[[#This Row],[Pay_day]]),EDATE(tblLines[[#This Row],[Pay_day]]-1,-12)+1,"")</f>
         <v>45847</v>
       </c>
-      <c r="W5" s="11" t="str">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[fund_received_date]],"")</f>
-        <v/>
-      </c>
-      <c r="X5" s="11" t="str">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[remitted_date]],"")</f>
-        <v/>
-      </c>
-      <c r="Y5" s="10">
+      <c r="AA5" s="9" t="str">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Recv_day]],"")</f>
+        <v/>
+      </c>
+      <c r="AB5" s="9" t="str">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Remit_day]],"")</f>
+        <v/>
+      </c>
+      <c r="AC5" s="11">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[Cap]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0)</f>
         <v>0</v>
       </c>
-      <c r="Z5" s="10">
+      <c r="AD5" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[remitted_amount]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",ROUND(tblLines[[#This Row],[sg_amount]],2),0))</f>
         <v>0</v>
       </c>
-      <c r="AA5" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+      <c r="AE5" s="10" t="str">
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,tblLines[[#This Row],[Flag_db]]=1,ROUND(tblLines[[#This Row],[Cap]],2)&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),IF(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2,IF(OR(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[Recv_day]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>possible</v>
       </c>
-      <c r="AB5" s="11">
-        <f t="array" ref="AB5">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AC5" s="11">
-        <f t="array" ref="AC5">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AD5" s="11">
+      <c r="AF5" s="9">
+        <f t="array" ref="AF5">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AG5" s="9">
+        <f t="array" ref="AG5">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AH5" s="9">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46223</v>
       </c>
-      <c r="AE5" s="9" t="str">
+      <c r="AI5" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="AF5" s="11" t="str">
+      <c r="AJ5" s="9" t="str">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Possible_latest]]),tblLines[[#This Row],[Possible_latest]]&gt;tblLines[[#This Row],[Final_due]]),tblLines[[#This Row],[Possible_latest]],""))</f>
         <v/>
       </c>
-      <c r="AG5" s="9">
+      <c r="AK5" s="10">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),1,0))</f>
         <v>0</v>
       </c>
-      <c r="AH5" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(tblLines[[#This Row],[sg_amount]]&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[payment_date]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"B1",IF(Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+      <c r="AL5" s="10" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>N2</v>
       </c>
-      <c r="AI5" s="9" t="str">
+      <c r="AM5" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",INDEX(tblCodes[verdict],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>UNPAID</v>
       </c>
-      <c r="AJ5" s="9" t="str">
+      <c r="AN5" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",T(INDEX(tblCodes[unassessable],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))))</f>
         <v/>
       </c>
-      <c r="AK5" s="9">
+      <c r="AO5" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[exposed],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>1</v>
       </c>
-      <c r="AL5" s="9">
+      <c r="AP5" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[stale],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AM5" s="10">
+      <c r="AQ5" s="11">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[otrc],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))*tblLines[[#This Row],[Receipt_credit]])</f>
         <v>0</v>
       </c>
-      <c r="AN5" s="10">
+      <c r="AR5" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(ROUND(tblLines[[#This Row],[sg_amount]],2)-tblLines[[#This Row],[OTRC]],0),"")</f>
         <v>780</v>
       </c>
-      <c r="AO5" s="10">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$B$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$B$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
-        <v>0</v>
-      </c>
-      <c r="AP5" s="10">
+      <c r="AS5" s="11">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="AT5" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(tblLines[[#This Row],[Base_shortfall]]-tblLines[[#This Row],[Offset_s18D]],0),"")</f>
         <v>780</v>
       </c>
-      <c r="AQ5" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+      <c r="AU5" s="10" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
         <v>as-at date (nothing applied to this payday)</v>
       </c>
-      <c r="AR5" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[Settled]],Summary!$B$2),"")</f>
+      <c r="AV5" s="9">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v>46244</v>
       </c>
-      <c r="AS5" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),MIN(IF(Summary!$B$3="",DATE(2030,12,31),Summary!$B$3-1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$B$2)),"")</f>
+      <c r="AW5" s="9">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v>46244</v>
       </c>
-      <c r="AT5" s="9">
+      <c r="AX5" s="9">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(Summary!$D$3="",tblLines[[#This Row],[Accrual_to]],MIN(Summary!$D$3-1,tblLines[[#This Row],[Accrual_to]])),"")</f>
+        <v>46244</v>
+      </c>
+      <c r="AY5" s="10">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v>21</v>
       </c>
-      <c r="AU5" s="10">
+      <c r="AZ5" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
         <v>5.1455028981957529</v>
       </c>
-      <c r="AV5" s="9">
+      <c r="BA5" s="10">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
         <v>0</v>
       </c>
-      <c r="AW5" s="10">
+      <c r="BB5" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</f>
         <v>780</v>
       </c>
-      <c r="AX5" s="10">
+      <c r="BC5" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
         <v>5.15</v>
       </c>
-      <c r="AY5" s="10">
+      <c r="BD5" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
         <v>0</v>
       </c>
-      <c r="AZ5" s="10">
+      <c r="BE5" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
         <v>471.09</v>
       </c>
-      <c r="BA5" s="10">
+      <c r="BF5" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
         <v>785.15</v>
       </c>
-      <c r="BB5" s="10">
+      <c r="BG5" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
         <v>1256.24</v>
       </c>
-      <c r="BC5" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0,tblLines[[#This Row],[Cap]]&gt;0,OR(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]])),IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]],tblLines[[#This Row],[remitted_date]])&lt;=DATE(2026,7,28)),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BD5" s="9">
+      <c r="BH5" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0,ROUND(tblLines[[#This Row],[Cap]],2)&gt;0,OR(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]])),IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]],tblLines[[#This Row],[Remit_day]])&lt;=DATE(2026,7,28)),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI5" s="10">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",1,0)</f>
         <v>0</v>
       </c>
-      <c r="BE5" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0),1,0)</f>
+      <c r="BJ5" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF5" s="9">
-        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BG5" s="9">
-        <f t="array" ref="BG5">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH5" s="9">
-        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+      <c r="BK5" s="10">
+        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[Pay_day]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[Remit_day]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[Recv_day]]&amp;"")&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL5" s="10">
+        <f t="array" ref="BL5">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM5" s="10">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[Pay_day]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B6" s="7">
         <v>46212</v>
@@ -2594,215 +2725,235 @@
         <v>46239</v>
       </c>
       <c r="H6" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L6" s="9">
+        <f>IF(tblLines[[#This Row],[payment_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),INT(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]))</f>
+        <v>46212</v>
+      </c>
+      <c r="M6" s="9">
+        <f>IF(tblLines[[#This Row],[remitted_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[remitted_date]]),INT(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]))</f>
+        <v>46237</v>
+      </c>
+      <c r="N6" s="9">
+        <f>IF(tblLines[[#This Row],[fund_received_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),INT(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]))</f>
+        <v>46239</v>
+      </c>
+      <c r="O6" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[next_standard_payday]]="","",IF(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),INT(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]))</f>
+        <v/>
+      </c>
+      <c r="P6" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="M6" s="9">
+      <c r="Q6" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="N6" s="9">
+      <c r="R6" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>1</v>
       </c>
-      <c r="O6" s="9" t="str">
-        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
-        <v/>
-      </c>
-      <c r="P6" s="9">
+      <c r="S6" s="10" t="str">
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]&gt;DATE(2200,12,31))),"date-not-real ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Pay_day]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[sg_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[remitted_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[matched_amount]],2)=0)),"amount-under-half-a-cent ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[Remit_day]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[matched_amount]],2)),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&lt;ROUND(tblLines[[#This Row],[sg_amount]],2),ISNUMBER(tblLines[[#This Row],[Remit_day]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Remit_day]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Next_day]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]]),ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Next_day]]&lt;=tblLines[[#This Row],[Pay_day]]),"next_standard_payday-not-after-payday ",""))</f>
+        <v/>
+      </c>
+      <c r="T6" s="10">
         <f>IF(OR(_xlfn.ISFORMULA(tblLines[[#This Row],[employee_id]]),_xlfn.ISFORMULA(tblLines[[#This Row],[payment_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[sg_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[matched_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[fund_received_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[first_contribution_to_fund]]),_xlfn.ISFORMULA(tblLines[[#This Row],[out_of_cycle]]),_xlfn.ISFORMULA(tblLines[[#This Row],[next_standard_payday]]),_xlfn.ISFORMULA(tblLines[[#This Row],[defined_benefit]])),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="10">
+      <c r="U6" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]],IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]],tblLines[[#This Row],[sg_amount]]))</f>
         <v>450</v>
       </c>
-      <c r="R6" s="11" t="str">
-        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]])),WORKDAY.INTL(tblLines[[#This Row],[next_standard_payday]],7,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="S6" s="11">
-        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</f>
+      <c r="V6" s="9" t="str">
+        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]])),WORKDAY.INTL(tblLines[[#This Row],[Next_day]],7,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="W6" s="9">
+        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],20,1,tblHolidays[date]),"")</f>
         <v>46241</v>
       </c>
-      <c r="T6" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+      <c r="X6" s="9">
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],7,1,tblHolidays[date])))</f>
         <v>46241</v>
       </c>
-      <c r="U6" s="9" t="str">
+      <c r="Y6" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</f>
         <v>EXTENDED_20BD</v>
       </c>
-      <c r="V6" s="11">
-        <f>IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),EDATE(tblLines[[#This Row],[payment_date]]-1,-12)+1,"")</f>
+      <c r="Z6" s="9">
+        <f>IF(ISNUMBER(tblLines[[#This Row],[Pay_day]]),EDATE(tblLines[[#This Row],[Pay_day]]-1,-12)+1,"")</f>
         <v>45847</v>
       </c>
-      <c r="W6" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[fund_received_date]],"")</f>
+      <c r="AA6" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Recv_day]],"")</f>
         <v>46239</v>
       </c>
-      <c r="X6" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[remitted_date]],"")</f>
+      <c r="AB6" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Remit_day]],"")</f>
         <v>46237</v>
       </c>
-      <c r="Y6" s="10">
+      <c r="AC6" s="11">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[Cap]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0)</f>
         <v>450</v>
       </c>
-      <c r="Z6" s="10">
+      <c r="AD6" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[remitted_amount]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",ROUND(tblLines[[#This Row],[sg_amount]],2),0))</f>
         <v>450</v>
       </c>
-      <c r="AA6" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+      <c r="AE6" s="10" t="str">
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,tblLines[[#This Row],[Flag_db]]=1,ROUND(tblLines[[#This Row],[Cap]],2)&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),IF(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2,IF(OR(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[Recv_day]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>confirmed</v>
       </c>
-      <c r="AB6" s="11">
-        <f t="array" ref="AB6">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AC6" s="11">
-        <f t="array" ref="AC6">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AD6" s="11">
+      <c r="AF6" s="9">
+        <f t="array" ref="AF6">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AG6" s="9">
+        <f t="array" ref="AG6">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AH6" s="9">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46241</v>
       </c>
-      <c r="AE6" s="9" t="str">
+      <c r="AI6" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>EXTENDED_20BD</v>
       </c>
-      <c r="AF6" s="11" t="str">
+      <c r="AJ6" s="9" t="str">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Possible_latest]]),tblLines[[#This Row],[Possible_latest]]&gt;tblLines[[#This Row],[Final_due]]),tblLines[[#This Row],[Possible_latest]],""))</f>
         <v/>
       </c>
-      <c r="AG6" s="9">
+      <c r="AK6" s="10">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),1,0))</f>
         <v>0</v>
       </c>
-      <c r="AH6" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(tblLines[[#This Row],[sg_amount]]&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[payment_date]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"B1",IF(Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+      <c r="AL6" s="10" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>D1</v>
       </c>
-      <c r="AI6" s="9" t="str">
+      <c r="AM6" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",INDEX(tblCodes[verdict],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>ON_TIME</v>
       </c>
-      <c r="AJ6" s="9" t="str">
+      <c r="AN6" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",T(INDEX(tblCodes[unassessable],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))))</f>
         <v/>
       </c>
-      <c r="AK6" s="9">
+      <c r="AO6" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[exposed],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AL6" s="9">
+      <c r="AP6" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[stale],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AM6" s="10">
+      <c r="AQ6" s="11">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[otrc],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))*tblLines[[#This Row],[Receipt_credit]])</f>
         <v>450</v>
       </c>
-      <c r="AN6" s="10" t="str">
+      <c r="AR6" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(ROUND(tblLines[[#This Row],[sg_amount]],2)-tblLines[[#This Row],[OTRC]],0),"")</f>
         <v/>
       </c>
-      <c r="AO6" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$B$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$B$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
-        <v/>
-      </c>
-      <c r="AP6" s="10" t="str">
+      <c r="AS6" s="11" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="AT6" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(tblLines[[#This Row],[Base_shortfall]]-tblLines[[#This Row],[Offset_s18D]],0),"")</f>
         <v/>
       </c>
-      <c r="AQ6" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
-        <v/>
-      </c>
-      <c r="AR6" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[Settled]],Summary!$B$2),"")</f>
-        <v/>
-      </c>
-      <c r="AS6" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),MIN(IF(Summary!$B$3="",DATE(2030,12,31),Summary!$B$3-1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$B$2)),"")</f>
-        <v/>
-      </c>
-      <c r="AT6" s="9" t="str">
+      <c r="AU6" s="10" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <v/>
+      </c>
+      <c r="AV6" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AW6" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AX6" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(Summary!$D$3="",tblLines[[#This Row],[Accrual_to]],MIN(Summary!$D$3-1,tblLines[[#This Row],[Accrual_to]])),"")</f>
+        <v/>
+      </c>
+      <c r="AY6" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v/>
       </c>
-      <c r="AU6" s="10" t="str">
+      <c r="AZ6" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
         <v/>
       </c>
-      <c r="AV6" s="9" t="str">
+      <c r="BA6" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
         <v/>
       </c>
-      <c r="AW6" s="10" t="str">
+      <c r="BB6" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</f>
         <v/>
       </c>
-      <c r="AX6" s="10" t="str">
+      <c r="BC6" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
         <v/>
       </c>
-      <c r="AY6" s="10" t="str">
+      <c r="BD6" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
         <v/>
       </c>
-      <c r="AZ6" s="10" t="str">
+      <c r="BE6" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
         <v/>
       </c>
-      <c r="BA6" s="10" t="str">
+      <c r="BF6" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
         <v/>
       </c>
-      <c r="BB6" s="10" t="str">
+      <c r="BG6" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
         <v/>
       </c>
-      <c r="BC6" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0,tblLines[[#This Row],[Cap]]&gt;0,OR(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]])),IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]],tblLines[[#This Row],[remitted_date]])&lt;=DATE(2026,7,28)),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BD6" s="9">
+      <c r="BH6" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0,ROUND(tblLines[[#This Row],[Cap]],2)&gt;0,OR(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]])),IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]],tblLines[[#This Row],[Remit_day]])&lt;=DATE(2026,7,28)),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI6" s="10">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE6" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0),1,0)</f>
+      <c r="BJ6" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF6" s="9">
-        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BG6" s="9">
-        <f t="array" ref="BG6">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH6" s="9">
-        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+      <c r="BK6" s="10">
+        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[Pay_day]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[Remit_day]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[Recv_day]]&amp;"")&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL6" s="10">
+        <f t="array" ref="BL6">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM6" s="10">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[Pay_day]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B7" s="7">
         <v>46218</v>
@@ -2819,217 +2970,237 @@
         <v>46234</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J7" s="7">
         <v>46226</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L7" s="9">
+        <f>IF(tblLines[[#This Row],[payment_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),INT(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]))</f>
+        <v>46218</v>
+      </c>
+      <c r="M7" s="9">
+        <f>IF(tblLines[[#This Row],[remitted_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[remitted_date]]),INT(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]))</f>
+        <v>46233</v>
+      </c>
+      <c r="N7" s="9">
+        <f>IF(tblLines[[#This Row],[fund_received_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),INT(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]))</f>
+        <v>46234</v>
+      </c>
+      <c r="O7" s="9">
+        <f>IF(tblLines[[#This Row],[next_standard_payday]]="","",IF(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),INT(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]))</f>
+        <v>46226</v>
+      </c>
+      <c r="P7" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="M7" s="9">
+      <c r="Q7" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>1</v>
       </c>
-      <c r="N7" s="9">
+      <c r="R7" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="O7" s="9" t="str">
-        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
-        <v/>
-      </c>
-      <c r="P7" s="9">
+      <c r="S7" s="10" t="str">
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]&gt;DATE(2200,12,31))),"date-not-real ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Pay_day]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[sg_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[remitted_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[matched_amount]],2)=0)),"amount-under-half-a-cent ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[Remit_day]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[matched_amount]],2)),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&lt;ROUND(tblLines[[#This Row],[sg_amount]],2),ISNUMBER(tblLines[[#This Row],[Remit_day]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Remit_day]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Next_day]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]]),ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Next_day]]&lt;=tblLines[[#This Row],[Pay_day]]),"next_standard_payday-not-after-payday ",""))</f>
+        <v/>
+      </c>
+      <c r="T7" s="10">
         <f>IF(OR(_xlfn.ISFORMULA(tblLines[[#This Row],[employee_id]]),_xlfn.ISFORMULA(tblLines[[#This Row],[payment_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[sg_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[matched_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[fund_received_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[first_contribution_to_fund]]),_xlfn.ISFORMULA(tblLines[[#This Row],[out_of_cycle]]),_xlfn.ISFORMULA(tblLines[[#This Row],[next_standard_payday]]),_xlfn.ISFORMULA(tblLines[[#This Row],[defined_benefit]])),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="10">
+      <c r="U7" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]],IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]],tblLines[[#This Row],[sg_amount]]))</f>
         <v>120</v>
       </c>
-      <c r="R7" s="11">
-        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]])),WORKDAY.INTL(tblLines[[#This Row],[next_standard_payday]],7,1,tblHolidays[date]),"")</f>
+      <c r="V7" s="9">
+        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]])),WORKDAY.INTL(tblLines[[#This Row],[Next_day]],7,1,tblHolidays[date]),"")</f>
         <v>46238</v>
       </c>
-      <c r="S7" s="11" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="T7" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+      <c r="W7" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],20,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="X7" s="9">
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],7,1,tblHolidays[date])))</f>
         <v>46238</v>
       </c>
-      <c r="U7" s="9" t="str">
+      <c r="Y7" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</f>
         <v>OUT_OF_CYCLE</v>
       </c>
-      <c r="V7" s="11">
-        <f>IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),EDATE(tblLines[[#This Row],[payment_date]]-1,-12)+1,"")</f>
+      <c r="Z7" s="9">
+        <f>IF(ISNUMBER(tblLines[[#This Row],[Pay_day]]),EDATE(tblLines[[#This Row],[Pay_day]]-1,-12)+1,"")</f>
         <v>45853</v>
       </c>
-      <c r="W7" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[fund_received_date]],"")</f>
+      <c r="AA7" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Recv_day]],"")</f>
         <v>46234</v>
       </c>
-      <c r="X7" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[remitted_date]],"")</f>
+      <c r="AB7" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Remit_day]],"")</f>
         <v>46233</v>
       </c>
-      <c r="Y7" s="10">
+      <c r="AC7" s="11">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[Cap]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0)</f>
         <v>120</v>
       </c>
-      <c r="Z7" s="10">
+      <c r="AD7" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[remitted_amount]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",ROUND(tblLines[[#This Row],[sg_amount]],2),0))</f>
         <v>120</v>
       </c>
-      <c r="AA7" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+      <c r="AE7" s="10" t="str">
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,tblLines[[#This Row],[Flag_db]]=1,ROUND(tblLines[[#This Row],[Cap]],2)&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),IF(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2,IF(OR(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[Recv_day]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>confirmed</v>
       </c>
-      <c r="AB7" s="11">
-        <f t="array" ref="AB7">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AC7" s="11">
-        <f t="array" ref="AC7">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AD7" s="11">
+      <c r="AF7" s="9">
+        <f t="array" ref="AF7">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AG7" s="9">
+        <f t="array" ref="AG7">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AH7" s="9">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46238</v>
       </c>
-      <c r="AE7" s="9" t="str">
+      <c r="AI7" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>OUT_OF_CYCLE</v>
       </c>
-      <c r="AF7" s="11" t="str">
+      <c r="AJ7" s="9" t="str">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Possible_latest]]),tblLines[[#This Row],[Possible_latest]]&gt;tblLines[[#This Row],[Final_due]]),tblLines[[#This Row],[Possible_latest]],""))</f>
         <v/>
       </c>
-      <c r="AG7" s="9">
+      <c r="AK7" s="10">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),1,0))</f>
         <v>0</v>
       </c>
-      <c r="AH7" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(tblLines[[#This Row],[sg_amount]]&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[payment_date]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"B1",IF(Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+      <c r="AL7" s="10" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>D1</v>
       </c>
-      <c r="AI7" s="9" t="str">
+      <c r="AM7" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",INDEX(tblCodes[verdict],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>ON_TIME</v>
       </c>
-      <c r="AJ7" s="9" t="str">
+      <c r="AN7" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",T(INDEX(tblCodes[unassessable],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))))</f>
         <v/>
       </c>
-      <c r="AK7" s="9">
+      <c r="AO7" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[exposed],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AL7" s="9">
+      <c r="AP7" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[stale],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AM7" s="10">
+      <c r="AQ7" s="11">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[otrc],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))*tblLines[[#This Row],[Receipt_credit]])</f>
         <v>120</v>
       </c>
-      <c r="AN7" s="10" t="str">
+      <c r="AR7" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(ROUND(tblLines[[#This Row],[sg_amount]],2)-tblLines[[#This Row],[OTRC]],0),"")</f>
         <v/>
       </c>
-      <c r="AO7" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$B$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$B$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
-        <v/>
-      </c>
-      <c r="AP7" s="10" t="str">
+      <c r="AS7" s="11" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="AT7" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(tblLines[[#This Row],[Base_shortfall]]-tblLines[[#This Row],[Offset_s18D]],0),"")</f>
         <v/>
       </c>
-      <c r="AQ7" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
-        <v/>
-      </c>
-      <c r="AR7" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[Settled]],Summary!$B$2),"")</f>
-        <v/>
-      </c>
-      <c r="AS7" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),MIN(IF(Summary!$B$3="",DATE(2030,12,31),Summary!$B$3-1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$B$2)),"")</f>
-        <v/>
-      </c>
-      <c r="AT7" s="9" t="str">
+      <c r="AU7" s="10" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <v/>
+      </c>
+      <c r="AV7" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AW7" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AX7" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(Summary!$D$3="",tblLines[[#This Row],[Accrual_to]],MIN(Summary!$D$3-1,tblLines[[#This Row],[Accrual_to]])),"")</f>
+        <v/>
+      </c>
+      <c r="AY7" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v/>
       </c>
-      <c r="AU7" s="10" t="str">
+      <c r="AZ7" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
         <v/>
       </c>
-      <c r="AV7" s="9" t="str">
+      <c r="BA7" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
         <v/>
       </c>
-      <c r="AW7" s="10" t="str">
+      <c r="BB7" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</f>
         <v/>
       </c>
-      <c r="AX7" s="10" t="str">
+      <c r="BC7" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
         <v/>
       </c>
-      <c r="AY7" s="10" t="str">
+      <c r="BD7" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
         <v/>
       </c>
-      <c r="AZ7" s="10" t="str">
+      <c r="BE7" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
         <v/>
       </c>
-      <c r="BA7" s="10" t="str">
+      <c r="BF7" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
         <v/>
       </c>
-      <c r="BB7" s="10" t="str">
+      <c r="BG7" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
         <v/>
       </c>
-      <c r="BC7" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0,tblLines[[#This Row],[Cap]]&gt;0,OR(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]])),IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]],tblLines[[#This Row],[remitted_date]])&lt;=DATE(2026,7,28)),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BD7" s="9">
+      <c r="BH7" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0,ROUND(tblLines[[#This Row],[Cap]],2)&gt;0,OR(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]])),IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]],tblLines[[#This Row],[Remit_day]])&lt;=DATE(2026,7,28)),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI7" s="10">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE7" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0),1,0)</f>
+      <c r="BJ7" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF7" s="9">
-        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BG7" s="9">
-        <f t="array" ref="BG7">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH7" s="9">
-        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+      <c r="BK7" s="10">
+        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[Pay_day]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[Remit_day]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[Recv_day]]&amp;"")&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL7" s="10">
+        <f t="array" ref="BL7">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM7" s="10">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[Pay_day]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B8" s="7">
         <v>46212</v>
@@ -3046,215 +3217,235 @@
         <v>46216</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L8" s="9">
+        <f>IF(tblLines[[#This Row],[payment_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),INT(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]))</f>
+        <v>46212</v>
+      </c>
+      <c r="M8" s="9">
+        <f>IF(tblLines[[#This Row],[remitted_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[remitted_date]]),INT(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]))</f>
+        <v>46216</v>
+      </c>
+      <c r="N8" s="9">
+        <f>IF(tblLines[[#This Row],[fund_received_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),INT(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]))</f>
+        <v>46216</v>
+      </c>
+      <c r="O8" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[next_standard_payday]]="","",IF(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),INT(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]))</f>
+        <v/>
+      </c>
+      <c r="P8" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>1</v>
       </c>
-      <c r="M8" s="9">
+      <c r="Q8" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="N8" s="9">
+      <c r="R8" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="O8" s="9" t="str">
-        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
-        <v/>
-      </c>
-      <c r="P8" s="9">
+      <c r="S8" s="10" t="str">
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]&gt;DATE(2200,12,31))),"date-not-real ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Pay_day]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[sg_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[remitted_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[matched_amount]],2)=0)),"amount-under-half-a-cent ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[Remit_day]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[matched_amount]],2)),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&lt;ROUND(tblLines[[#This Row],[sg_amount]],2),ISNUMBER(tblLines[[#This Row],[Remit_day]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Remit_day]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Next_day]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]]),ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Next_day]]&lt;=tblLines[[#This Row],[Pay_day]]),"next_standard_payday-not-after-payday ",""))</f>
+        <v/>
+      </c>
+      <c r="T8" s="10">
         <f>IF(OR(_xlfn.ISFORMULA(tblLines[[#This Row],[employee_id]]),_xlfn.ISFORMULA(tblLines[[#This Row],[payment_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[sg_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[matched_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[fund_received_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[first_contribution_to_fund]]),_xlfn.ISFORMULA(tblLines[[#This Row],[out_of_cycle]]),_xlfn.ISFORMULA(tblLines[[#This Row],[next_standard_payday]]),_xlfn.ISFORMULA(tblLines[[#This Row],[defined_benefit]])),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="10">
+      <c r="U8" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]],IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]],tblLines[[#This Row],[sg_amount]]))</f>
         <v>900</v>
       </c>
-      <c r="R8" s="11" t="str">
-        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]])),WORKDAY.INTL(tblLines[[#This Row],[next_standard_payday]],7,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="S8" s="11" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="T8" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
-        <v>0</v>
-      </c>
-      <c r="U8" s="9" t="str">
+      <c r="V8" s="9" t="str">
+        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]])),WORKDAY.INTL(tblLines[[#This Row],[Next_day]],7,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="W8" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],20,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="X8" s="9">
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],7,1,tblHolidays[date])))</f>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</f>
         <v>SKIP_DB</v>
       </c>
-      <c r="V8" s="11">
-        <f>IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),EDATE(tblLines[[#This Row],[payment_date]]-1,-12)+1,"")</f>
+      <c r="Z8" s="9">
+        <f>IF(ISNUMBER(tblLines[[#This Row],[Pay_day]]),EDATE(tblLines[[#This Row],[Pay_day]]-1,-12)+1,"")</f>
         <v>45847</v>
       </c>
-      <c r="W8" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[fund_received_date]],"")</f>
+      <c r="AA8" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Recv_day]],"")</f>
         <v>46216</v>
       </c>
-      <c r="X8" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[remitted_date]],"")</f>
+      <c r="AB8" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Remit_day]],"")</f>
         <v>46216</v>
       </c>
-      <c r="Y8" s="10">
+      <c r="AC8" s="11">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[Cap]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0)</f>
         <v>900</v>
       </c>
-      <c r="Z8" s="10">
+      <c r="AD8" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[remitted_amount]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",ROUND(tblLines[[#This Row],[sg_amount]],2),0))</f>
         <v>900</v>
       </c>
-      <c r="AA8" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+      <c r="AE8" s="10" t="str">
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,tblLines[[#This Row],[Flag_db]]=1,ROUND(tblLines[[#This Row],[Cap]],2)&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),IF(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2,IF(OR(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[Recv_day]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>impossible</v>
       </c>
-      <c r="AB8" s="11" t="str">
-        <f t="array" ref="AB8">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
-        <v/>
-      </c>
-      <c r="AC8" s="11" t="str">
-        <f t="array" ref="AC8">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
-        <v/>
-      </c>
-      <c r="AD8" s="11" t="str">
+      <c r="AF8" s="9" t="str">
+        <f t="array" ref="AF8">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
+        <v/>
+      </c>
+      <c r="AG8" s="9" t="str">
+        <f t="array" ref="AG8">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
+        <v/>
+      </c>
+      <c r="AH8" s="9" t="str">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v/>
       </c>
-      <c r="AE8" s="9" t="str">
+      <c r="AI8" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>SKIP_DB</v>
       </c>
-      <c r="AF8" s="11" t="str">
+      <c r="AJ8" s="9" t="str">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Possible_latest]]),tblLines[[#This Row],[Possible_latest]]&gt;tblLines[[#This Row],[Final_due]]),tblLines[[#This Row],[Possible_latest]],""))</f>
         <v/>
       </c>
-      <c r="AG8" s="9" t="str">
+      <c r="AK8" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),1,0))</f>
         <v/>
       </c>
-      <c r="AH8" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(tblLines[[#This Row],[sg_amount]]&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[payment_date]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"B1",IF(Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+      <c r="AL8" s="10" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>DB</v>
       </c>
-      <c r="AI8" s="9" t="str">
+      <c r="AM8" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",INDEX(tblCodes[verdict],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>SKIPPED</v>
       </c>
-      <c r="AJ8" s="9" t="str">
+      <c r="AN8" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",T(INDEX(tblCodes[unassessable],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))))</f>
         <v/>
       </c>
-      <c r="AK8" s="9">
+      <c r="AO8" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[exposed],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AL8" s="9">
+      <c r="AP8" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[stale],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AM8" s="10">
+      <c r="AQ8" s="11">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[otrc],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))*tblLines[[#This Row],[Receipt_credit]])</f>
         <v>0</v>
       </c>
-      <c r="AN8" s="10" t="str">
+      <c r="AR8" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(ROUND(tblLines[[#This Row],[sg_amount]],2)-tblLines[[#This Row],[OTRC]],0),"")</f>
         <v/>
       </c>
-      <c r="AO8" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$B$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$B$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
-        <v/>
-      </c>
-      <c r="AP8" s="10" t="str">
+      <c r="AS8" s="11" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="AT8" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(tblLines[[#This Row],[Base_shortfall]]-tblLines[[#This Row],[Offset_s18D]],0),"")</f>
         <v/>
       </c>
-      <c r="AQ8" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
-        <v/>
-      </c>
-      <c r="AR8" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[Settled]],Summary!$B$2),"")</f>
-        <v/>
-      </c>
-      <c r="AS8" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),MIN(IF(Summary!$B$3="",DATE(2030,12,31),Summary!$B$3-1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$B$2)),"")</f>
-        <v/>
-      </c>
-      <c r="AT8" s="9" t="str">
+      <c r="AU8" s="10" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <v/>
+      </c>
+      <c r="AV8" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AW8" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AX8" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(Summary!$D$3="",tblLines[[#This Row],[Accrual_to]],MIN(Summary!$D$3-1,tblLines[[#This Row],[Accrual_to]])),"")</f>
+        <v/>
+      </c>
+      <c r="AY8" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v/>
       </c>
-      <c r="AU8" s="10" t="str">
+      <c r="AZ8" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
         <v/>
       </c>
-      <c r="AV8" s="9" t="str">
+      <c r="BA8" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
         <v/>
       </c>
-      <c r="AW8" s="10" t="str">
+      <c r="BB8" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</f>
         <v/>
       </c>
-      <c r="AX8" s="10" t="str">
+      <c r="BC8" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
         <v/>
       </c>
-      <c r="AY8" s="10" t="str">
+      <c r="BD8" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
         <v/>
       </c>
-      <c r="AZ8" s="10" t="str">
+      <c r="BE8" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
         <v/>
       </c>
-      <c r="BA8" s="10" t="str">
+      <c r="BF8" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
         <v/>
       </c>
-      <c r="BB8" s="10" t="str">
+      <c r="BG8" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
         <v/>
       </c>
-      <c r="BC8" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0,tblLines[[#This Row],[Cap]]&gt;0,OR(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]])),IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]],tblLines[[#This Row],[remitted_date]])&lt;=DATE(2026,7,28)),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BD8" s="9">
+      <c r="BH8" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0,ROUND(tblLines[[#This Row],[Cap]],2)&gt;0,OR(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]])),IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]],tblLines[[#This Row],[Remit_day]])&lt;=DATE(2026,7,28)),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI8" s="10">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE8" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BF8" s="9">
-        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BG8" s="9">
-        <f t="array" ref="BG8">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH8" s="9">
-        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+      <c r="BJ8" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK8" s="10">
+        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[Pay_day]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[Remit_day]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[Recv_day]]&amp;"")&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL8" s="10">
+        <f t="array" ref="BL8">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM8" s="10">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[Pay_day]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B9" s="7">
         <v>46226</v>
@@ -3271,215 +3462,235 @@
         <v>46240</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J9" s="7"/>
       <c r="K9" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L9" s="9">
+        <f>IF(tblLines[[#This Row],[payment_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),INT(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]))</f>
+        <v>46226</v>
+      </c>
+      <c r="M9" s="9">
+        <f>IF(tblLines[[#This Row],[remitted_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[remitted_date]]),INT(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]))</f>
+        <v>46239</v>
+      </c>
+      <c r="N9" s="9">
+        <f>IF(tblLines[[#This Row],[fund_received_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),INT(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]))</f>
+        <v>46240</v>
+      </c>
+      <c r="O9" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[next_standard_payday]]="","",IF(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),INT(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]))</f>
+        <v/>
+      </c>
+      <c r="P9" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="M9" s="9">
+      <c r="Q9" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="N9" s="9">
+      <c r="R9" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="O9" s="9" t="str">
-        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
-        <v/>
-      </c>
-      <c r="P9" s="9">
+      <c r="S9" s="10" t="str">
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]&gt;DATE(2200,12,31))),"date-not-real ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Pay_day]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[sg_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[remitted_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[matched_amount]],2)=0)),"amount-under-half-a-cent ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[Remit_day]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[matched_amount]],2)),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&lt;ROUND(tblLines[[#This Row],[sg_amount]],2),ISNUMBER(tblLines[[#This Row],[Remit_day]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Remit_day]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Next_day]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]]),ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Next_day]]&lt;=tblLines[[#This Row],[Pay_day]]),"next_standard_payday-not-after-payday ",""))</f>
+        <v/>
+      </c>
+      <c r="T9" s="10">
         <f>IF(OR(_xlfn.ISFORMULA(tblLines[[#This Row],[employee_id]]),_xlfn.ISFORMULA(tblLines[[#This Row],[payment_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[sg_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[matched_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[fund_received_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[first_contribution_to_fund]]),_xlfn.ISFORMULA(tblLines[[#This Row],[out_of_cycle]]),_xlfn.ISFORMULA(tblLines[[#This Row],[next_standard_payday]]),_xlfn.ISFORMULA(tblLines[[#This Row],[defined_benefit]])),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="10">
+      <c r="U9" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]],IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]],tblLines[[#This Row],[sg_amount]]))</f>
         <v>612</v>
       </c>
-      <c r="R9" s="11" t="str">
-        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]])),WORKDAY.INTL(tblLines[[#This Row],[next_standard_payday]],7,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="S9" s="11" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="T9" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+      <c r="V9" s="9" t="str">
+        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]])),WORKDAY.INTL(tblLines[[#This Row],[Next_day]],7,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="W9" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],20,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="X9" s="9">
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],7,1,tblHolidays[date])))</f>
         <v>46238</v>
       </c>
-      <c r="U9" s="9" t="str">
+      <c r="Y9" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="V9" s="11">
-        <f>IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),EDATE(tblLines[[#This Row],[payment_date]]-1,-12)+1,"")</f>
+      <c r="Z9" s="9">
+        <f>IF(ISNUMBER(tblLines[[#This Row],[Pay_day]]),EDATE(tblLines[[#This Row],[Pay_day]]-1,-12)+1,"")</f>
         <v>45861</v>
       </c>
-      <c r="W9" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[fund_received_date]],"")</f>
+      <c r="AA9" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Recv_day]],"")</f>
         <v>46240</v>
       </c>
-      <c r="X9" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[remitted_date]],"")</f>
+      <c r="AB9" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Remit_day]],"")</f>
         <v>46239</v>
       </c>
-      <c r="Y9" s="10">
+      <c r="AC9" s="11">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[Cap]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0)</f>
         <v>612</v>
       </c>
-      <c r="Z9" s="10">
+      <c r="AD9" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[remitted_amount]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",ROUND(tblLines[[#This Row],[sg_amount]],2),0))</f>
         <v>612</v>
       </c>
-      <c r="AA9" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+      <c r="AE9" s="10" t="str">
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,tblLines[[#This Row],[Flag_db]]=1,ROUND(tblLines[[#This Row],[Cap]],2)&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),IF(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2,IF(OR(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[Recv_day]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>impossible</v>
       </c>
-      <c r="AB9" s="11">
-        <f t="array" ref="AB9">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
+      <c r="AF9" s="9">
+        <f t="array" ref="AF9">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
         <v>46223</v>
       </c>
-      <c r="AC9" s="11">
-        <f t="array" ref="AC9">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
+      <c r="AG9" s="9">
+        <f t="array" ref="AG9">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
         <v>46223</v>
       </c>
-      <c r="AD9" s="11">
+      <c r="AH9" s="9">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46238</v>
       </c>
-      <c r="AE9" s="9" t="str">
+      <c r="AI9" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="AF9" s="11" t="str">
+      <c r="AJ9" s="9" t="str">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Possible_latest]]),tblLines[[#This Row],[Possible_latest]]&gt;tblLines[[#This Row],[Final_due]]),tblLines[[#This Row],[Possible_latest]],""))</f>
         <v/>
       </c>
-      <c r="AG9" s="9">
+      <c r="AK9" s="10">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),1,0))</f>
         <v>0</v>
       </c>
-      <c r="AH9" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(tblLines[[#This Row],[sg_amount]]&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[payment_date]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"B1",IF(Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+      <c r="AL9" s="10" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>E</v>
       </c>
-      <c r="AI9" s="9" t="str">
+      <c r="AM9" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",INDEX(tblCodes[verdict],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>LATE</v>
       </c>
-      <c r="AJ9" s="9" t="str">
+      <c r="AN9" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",T(INDEX(tblCodes[unassessable],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))))</f>
         <v/>
       </c>
-      <c r="AK9" s="9">
+      <c r="AO9" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[exposed],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>1</v>
       </c>
-      <c r="AL9" s="9">
+      <c r="AP9" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[stale],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AM9" s="10">
+      <c r="AQ9" s="11">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[otrc],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))*tblLines[[#This Row],[Receipt_credit]])</f>
         <v>0</v>
       </c>
-      <c r="AN9" s="10">
+      <c r="AR9" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(ROUND(tblLines[[#This Row],[sg_amount]],2)-tblLines[[#This Row],[OTRC]],0),"")</f>
         <v>612</v>
       </c>
-      <c r="AO9" s="10">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$B$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$B$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+      <c r="AS9" s="11">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
         <v>612</v>
       </c>
-      <c r="AP9" s="10">
+      <c r="AT9" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(tblLines[[#This Row],[Base_shortfall]]-tblLines[[#This Row],[Offset_s18D]],0),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ9" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+      <c r="AU9" s="10" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
         <v>fund receipt</v>
       </c>
-      <c r="AR9" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[Settled]],Summary!$B$2),"")</f>
+      <c r="AV9" s="9">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v>46240</v>
       </c>
-      <c r="AS9" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),MIN(IF(Summary!$B$3="",DATE(2030,12,31),Summary!$B$3-1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$B$2)),"")</f>
+      <c r="AW9" s="9">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v>46240</v>
       </c>
-      <c r="AT9" s="9">
+      <c r="AX9" s="9">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(Summary!$D$3="",tblLines[[#This Row],[Accrual_to]],MIN(Summary!$D$3-1,tblLines[[#This Row],[Accrual_to]])),"")</f>
+        <v>46240</v>
+      </c>
+      <c r="AY9" s="10">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v>2</v>
       </c>
-      <c r="AU9" s="10">
+      <c r="AZ9" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
         <v>0.38335645312715005</v>
       </c>
-      <c r="AV9" s="9">
+      <c r="BA9" s="10">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
         <v>0</v>
       </c>
-      <c r="AW9" s="10">
+      <c r="BB9" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</f>
         <v>0</v>
       </c>
-      <c r="AX9" s="10">
+      <c r="BC9" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
         <v>0.38</v>
       </c>
-      <c r="AY9" s="10">
+      <c r="BD9" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
         <v>0</v>
       </c>
-      <c r="AZ9" s="10">
+      <c r="BE9" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
         <v>0.23</v>
       </c>
-      <c r="BA9" s="10">
+      <c r="BF9" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
         <v>0.38</v>
       </c>
-      <c r="BB9" s="10">
+      <c r="BG9" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
         <v>0.61</v>
       </c>
-      <c r="BC9" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0,tblLines[[#This Row],[Cap]]&gt;0,OR(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]])),IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]],tblLines[[#This Row],[remitted_date]])&lt;=DATE(2026,7,28)),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BD9" s="9">
+      <c r="BH9" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0,ROUND(tblLines[[#This Row],[Cap]],2)&gt;0,OR(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]])),IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]],tblLines[[#This Row],[Remit_day]])&lt;=DATE(2026,7,28)),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI9" s="10">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE9" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0),1,0)</f>
+      <c r="BJ9" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF9" s="9">
-        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BG9" s="9">
-        <f t="array" ref="BG9">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH9" s="9">
-        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+      <c r="BK9" s="10">
+        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[Pay_day]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[Remit_day]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[Recv_day]]&amp;"")&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL9" s="10">
+        <f t="array" ref="BL9">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM9" s="10">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[Pay_day]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B10" s="7">
         <v>46226</v>
@@ -3496,215 +3707,235 @@
         <v>46233</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J10" s="7"/>
       <c r="K10" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L10" s="9">
+        <f>IF(tblLines[[#This Row],[payment_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),INT(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]))</f>
+        <v>46226</v>
+      </c>
+      <c r="M10" s="9">
+        <f>IF(tblLines[[#This Row],[remitted_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[remitted_date]]),INT(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]))</f>
+        <v>46231</v>
+      </c>
+      <c r="N10" s="9">
+        <f>IF(tblLines[[#This Row],[fund_received_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),INT(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]))</f>
+        <v>46233</v>
+      </c>
+      <c r="O10" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[next_standard_payday]]="","",IF(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),INT(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]))</f>
+        <v/>
+      </c>
+      <c r="P10" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="M10" s="9">
+      <c r="Q10" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="N10" s="9">
+      <c r="R10" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="O10" s="9" t="str">
-        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
-        <v/>
-      </c>
-      <c r="P10" s="9">
+      <c r="S10" s="10" t="str">
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]&gt;DATE(2200,12,31))),"date-not-real ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Pay_day]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[sg_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[remitted_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[matched_amount]],2)=0)),"amount-under-half-a-cent ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[Remit_day]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[matched_amount]],2)),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&lt;ROUND(tblLines[[#This Row],[sg_amount]],2),ISNUMBER(tblLines[[#This Row],[Remit_day]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Remit_day]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Next_day]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]]),ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Next_day]]&lt;=tblLines[[#This Row],[Pay_day]]),"next_standard_payday-not-after-payday ",""))</f>
+        <v/>
+      </c>
+      <c r="T10" s="10">
         <f>IF(OR(_xlfn.ISFORMULA(tblLines[[#This Row],[employee_id]]),_xlfn.ISFORMULA(tblLines[[#This Row],[payment_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[sg_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[matched_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[fund_received_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[first_contribution_to_fund]]),_xlfn.ISFORMULA(tblLines[[#This Row],[out_of_cycle]]),_xlfn.ISFORMULA(tblLines[[#This Row],[next_standard_payday]]),_xlfn.ISFORMULA(tblLines[[#This Row],[defined_benefit]])),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="10">
+      <c r="U10" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]],IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]],tblLines[[#This Row],[sg_amount]]))</f>
         <v>540</v>
       </c>
-      <c r="R10" s="11" t="str">
-        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]])),WORKDAY.INTL(tblLines[[#This Row],[next_standard_payday]],7,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="S10" s="11" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="T10" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+      <c r="V10" s="9" t="str">
+        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]])),WORKDAY.INTL(tblLines[[#This Row],[Next_day]],7,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="W10" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],20,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="X10" s="9">
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],7,1,tblHolidays[date])))</f>
         <v>46238</v>
       </c>
-      <c r="U10" s="9" t="str">
+      <c r="Y10" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="V10" s="11">
-        <f>IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),EDATE(tblLines[[#This Row],[payment_date]]-1,-12)+1,"")</f>
+      <c r="Z10" s="9">
+        <f>IF(ISNUMBER(tblLines[[#This Row],[Pay_day]]),EDATE(tblLines[[#This Row],[Pay_day]]-1,-12)+1,"")</f>
         <v>45861</v>
       </c>
-      <c r="W10" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[fund_received_date]],"")</f>
+      <c r="AA10" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Recv_day]],"")</f>
         <v>46233</v>
       </c>
-      <c r="X10" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[remitted_date]],"")</f>
+      <c r="AB10" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Remit_day]],"")</f>
         <v>46231</v>
       </c>
-      <c r="Y10" s="10">
+      <c r="AC10" s="11">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[Cap]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0)</f>
         <v>540</v>
       </c>
-      <c r="Z10" s="10">
+      <c r="AD10" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[remitted_amount]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",ROUND(tblLines[[#This Row],[sg_amount]],2),0))</f>
         <v>540</v>
       </c>
-      <c r="AA10" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+      <c r="AE10" s="10" t="str">
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,tblLines[[#This Row],[Flag_db]]=1,ROUND(tblLines[[#This Row],[Cap]],2)&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),IF(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2,IF(OR(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[Recv_day]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>confirmed</v>
       </c>
-      <c r="AB10" s="11">
-        <f t="array" ref="AB10">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AC10" s="11">
-        <f t="array" ref="AC10">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
-        <v>0</v>
-      </c>
-      <c r="AD10" s="11">
+      <c r="AF10" s="9">
+        <f t="array" ref="AF10">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AG10" s="9">
+        <f t="array" ref="AG10">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
+        <v>0</v>
+      </c>
+      <c r="AH10" s="9">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46238</v>
       </c>
-      <c r="AE10" s="9" t="str">
+      <c r="AI10" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="AF10" s="11" t="str">
+      <c r="AJ10" s="9" t="str">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Possible_latest]]),tblLines[[#This Row],[Possible_latest]]&gt;tblLines[[#This Row],[Final_due]]),tblLines[[#This Row],[Possible_latest]],""))</f>
         <v/>
       </c>
-      <c r="AG10" s="9">
+      <c r="AK10" s="10">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),1,0))</f>
         <v>0</v>
       </c>
-      <c r="AH10" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(tblLines[[#This Row],[sg_amount]]&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[payment_date]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"B1",IF(Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+      <c r="AL10" s="10" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>D1</v>
       </c>
-      <c r="AI10" s="9" t="str">
+      <c r="AM10" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",INDEX(tblCodes[verdict],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>ON_TIME</v>
       </c>
-      <c r="AJ10" s="9" t="str">
+      <c r="AN10" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",T(INDEX(tblCodes[unassessable],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))))</f>
         <v/>
       </c>
-      <c r="AK10" s="9">
+      <c r="AO10" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[exposed],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AL10" s="9">
+      <c r="AP10" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[stale],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AM10" s="10">
+      <c r="AQ10" s="11">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[otrc],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))*tblLines[[#This Row],[Receipt_credit]])</f>
         <v>540</v>
       </c>
-      <c r="AN10" s="10" t="str">
+      <c r="AR10" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(ROUND(tblLines[[#This Row],[sg_amount]],2)-tblLines[[#This Row],[OTRC]],0),"")</f>
         <v/>
       </c>
-      <c r="AO10" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$B$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$B$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
-        <v/>
-      </c>
-      <c r="AP10" s="10" t="str">
+      <c r="AS10" s="11" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="AT10" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(tblLines[[#This Row],[Base_shortfall]]-tblLines[[#This Row],[Offset_s18D]],0),"")</f>
         <v/>
       </c>
-      <c r="AQ10" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
-        <v/>
-      </c>
-      <c r="AR10" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[Settled]],Summary!$B$2),"")</f>
-        <v/>
-      </c>
-      <c r="AS10" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),MIN(IF(Summary!$B$3="",DATE(2030,12,31),Summary!$B$3-1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$B$2)),"")</f>
-        <v/>
-      </c>
-      <c r="AT10" s="9" t="str">
+      <c r="AU10" s="10" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <v/>
+      </c>
+      <c r="AV10" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AW10" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AX10" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(Summary!$D$3="",tblLines[[#This Row],[Accrual_to]],MIN(Summary!$D$3-1,tblLines[[#This Row],[Accrual_to]])),"")</f>
+        <v/>
+      </c>
+      <c r="AY10" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v/>
       </c>
-      <c r="AU10" s="10" t="str">
+      <c r="AZ10" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
         <v/>
       </c>
-      <c r="AV10" s="9" t="str">
+      <c r="BA10" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
         <v/>
       </c>
-      <c r="AW10" s="10" t="str">
+      <c r="BB10" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</f>
         <v/>
       </c>
-      <c r="AX10" s="10" t="str">
+      <c r="BC10" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
         <v/>
       </c>
-      <c r="AY10" s="10" t="str">
+      <c r="BD10" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
         <v/>
       </c>
-      <c r="AZ10" s="10" t="str">
+      <c r="BE10" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
         <v/>
       </c>
-      <c r="BA10" s="10" t="str">
+      <c r="BF10" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
         <v/>
       </c>
-      <c r="BB10" s="10" t="str">
+      <c r="BG10" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
         <v/>
       </c>
-      <c r="BC10" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0,tblLines[[#This Row],[Cap]]&gt;0,OR(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]])),IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]],tblLines[[#This Row],[remitted_date]])&lt;=DATE(2026,7,28)),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BD10" s="9">
+      <c r="BH10" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0,ROUND(tblLines[[#This Row],[Cap]],2)&gt;0,OR(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]])),IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]],tblLines[[#This Row],[Remit_day]])&lt;=DATE(2026,7,28)),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI10" s="10">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE10" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0),1,0)</f>
+      <c r="BJ10" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF10" s="9">
-        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BG10" s="9">
-        <f t="array" ref="BG10">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH10" s="9">
-        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+      <c r="BK10" s="10">
+        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[Pay_day]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[Remit_day]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[Recv_day]]&amp;"")&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL10" s="10">
+        <f t="array" ref="BL10">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM10" s="10">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[Pay_day]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B11" s="7">
         <v>46226</v>
@@ -3721,209 +3952,229 @@
         <v>46240</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L11" s="9">
+        <f>IF(tblLines[[#This Row],[payment_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),INT(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]))</f>
+        <v>46226</v>
+      </c>
+      <c r="M11" s="9">
+        <f>IF(tblLines[[#This Row],[remitted_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[remitted_date]]),INT(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]))</f>
+        <v>46239</v>
+      </c>
+      <c r="N11" s="9">
+        <f>IF(tblLines[[#This Row],[fund_received_date]]="","",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),INT(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]))</f>
+        <v>46240</v>
+      </c>
+      <c r="O11" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[next_standard_payday]]="","",IF(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),INT(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]))</f>
+        <v/>
+      </c>
+      <c r="P11" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="M11" s="9">
+      <c r="Q11" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[out_of_cycle]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="N11" s="9">
+      <c r="R11" s="10">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
         <v>0</v>
       </c>
-      <c r="O11" s="9" t="str">
-        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
-        <v/>
-      </c>
-      <c r="P11" s="9">
+      <c r="S11" s="10" t="str">
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&gt;DATE(2200,12,31)),AND(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),tblLines[[#This Row],[next_standard_payday]]&gt;DATE(2200,12,31))),"date-not-real ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Pay_day]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(OR(AND(ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[sg_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[remitted_amount]],2)=0),AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]]&lt;&gt;0,ROUND(tblLines[[#This Row],[matched_amount]],2)=0)),"amount-under-half-a-cent ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[Remit_day]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&gt;ROUND(tblLines[[#This Row],[sg_amount]],2)),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ROUND(tblLines[[#This Row],[remitted_amount]],2)&gt;ROUND(tblLines[[#This Row],[matched_amount]],2)),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[matched_amount]],2)&lt;ROUND(tblLines[[#This Row],[sg_amount]],2),ISNUMBER(tblLines[[#This Row],[Remit_day]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Remit_day]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Next_day]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]]),ISNUMBER(tblLines[[#This Row],[Pay_day]]),tblLines[[#This Row],[Next_day]]&lt;=tblLines[[#This Row],[Pay_day]]),"next_standard_payday-not-after-payday ",""))</f>
+        <v/>
+      </c>
+      <c r="T11" s="10">
         <f>IF(OR(_xlfn.ISFORMULA(tblLines[[#This Row],[employee_id]]),_xlfn.ISFORMULA(tblLines[[#This Row],[payment_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[sg_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[matched_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[fund_received_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[first_contribution_to_fund]]),_xlfn.ISFORMULA(tblLines[[#This Row],[out_of_cycle]]),_xlfn.ISFORMULA(tblLines[[#This Row],[next_standard_payday]]),_xlfn.ISFORMULA(tblLines[[#This Row],[defined_benefit]])),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="10">
+      <c r="U11" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[matched_amount]]),tblLines[[#This Row],[matched_amount]],IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]],tblLines[[#This Row],[sg_amount]]))</f>
         <v>450</v>
       </c>
-      <c r="R11" s="11" t="str">
-        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]])),WORKDAY.INTL(tblLines[[#This Row],[next_standard_payday]],7,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="S11" s="11" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</f>
-        <v/>
-      </c>
-      <c r="T11" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+      <c r="V11" s="9" t="str">
+        <f>IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[Next_day]])),WORKDAY.INTL(tblLines[[#This Row],[Next_day]],7,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="W11" s="9" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],20,1,tblHolidays[date]),"")</f>
+        <v/>
+      </c>
+      <c r="X11" s="9">
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[Pay_day]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[Pay_day]],7,1,tblHolidays[date])))</f>
         <v>46238</v>
       </c>
-      <c r="U11" s="9" t="str">
+      <c r="Y11" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</f>
         <v>USUAL_7BD</v>
       </c>
-      <c r="V11" s="11">
-        <f>IF(ISNUMBER(tblLines[[#This Row],[payment_date]]),EDATE(tblLines[[#This Row],[payment_date]]-1,-12)+1,"")</f>
+      <c r="Z11" s="9">
+        <f>IF(ISNUMBER(tblLines[[#This Row],[Pay_day]]),EDATE(tblLines[[#This Row],[Pay_day]]-1,-12)+1,"")</f>
         <v>45861</v>
       </c>
-      <c r="W11" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[fund_received_date]],"")</f>
+      <c r="AA11" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Recv_day]],"")</f>
         <v>46240</v>
       </c>
-      <c r="X11" s="11">
-        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&lt;=Summary!$B$2),tblLines[[#This Row],[remitted_date]],"")</f>
+      <c r="AB11" s="9">
+        <f>IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&lt;=Summary!$D$2),tblLines[[#This Row],[Remit_day]],"")</f>
         <v>46239</v>
       </c>
-      <c r="Y11" s="10">
+      <c r="AC11" s="11">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[Cap]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0)</f>
         <v>450</v>
       </c>
-      <c r="Z11" s="10">
+      <c r="AD11" s="11">
         <f>IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[remitted_amount]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",ROUND(tblLines[[#This Row],[sg_amount]],2),0))</f>
         <v>450</v>
       </c>
-      <c r="AA11" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+      <c r="AE11" s="10" t="str">
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,tblLines[[#This Row],[Flag_db]]=1,ROUND(tblLines[[#This Row],[Cap]],2)&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),IF(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[Recv_day]]&lt;=Summary!$D$2,IF(OR(tblLines[[#This Row],[Recv_day]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[Recv_day]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[Recv_day]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[Remit_day]]),tblLines[[#This Row],[Remit_day]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>impossible</v>
       </c>
-      <c r="AB11" s="11">
-        <f t="array" ref="AB11">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
+      <c r="AF11" s="9">
+        <f t="array" ref="AF11">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
         <v>46241</v>
       </c>
-      <c r="AC11" s="11">
-        <f t="array" ref="AC11">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
+      <c r="AG11" s="9">
+        <f t="array" ref="AG11">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[Pay_day]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
         <v>46241</v>
       </c>
-      <c r="AD11" s="11">
+      <c r="AH11" s="9">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46241</v>
       </c>
-      <c r="AE11" s="9" t="str">
+      <c r="AI11" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>ITEM4_ALIGNED</v>
       </c>
-      <c r="AF11" s="11" t="str">
+      <c r="AJ11" s="9" t="str">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Possible_latest]]),tblLines[[#This Row],[Possible_latest]]&gt;tblLines[[#This Row],[Final_due]]),tblLines[[#This Row],[Possible_latest]],""))</f>
         <v/>
       </c>
-      <c r="AG11" s="9">
+      <c r="AK11" s="10">
         <f>IF(tblLines[[#This Row],[Final_due]]="","",IF((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),1,0))</f>
         <v>0</v>
       </c>
-      <c r="AH11" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(tblLines[[#This Row],[sg_amount]]&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[payment_date]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$B$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"B1",IF(Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$B$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$B$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+      <c r="AL11" s="10" t="str">
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>D1</v>
       </c>
-      <c r="AI11" s="9" t="str">
+      <c r="AM11" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",INDEX(tblCodes[verdict],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>ON_TIME</v>
       </c>
-      <c r="AJ11" s="9" t="str">
+      <c r="AN11" s="10" t="str">
         <f>IF(tblLines[[#This Row],[Branch]]="","",T(INDEX(tblCodes[unassessable],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))))</f>
         <v/>
       </c>
-      <c r="AK11" s="9">
+      <c r="AO11" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[exposed],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AL11" s="9">
+      <c r="AP11" s="10">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[stale],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</f>
         <v>0</v>
       </c>
-      <c r="AM11" s="10">
+      <c r="AQ11" s="11">
         <f>IF(tblLines[[#This Row],[Branch]]="",0,INDEX(tblCodes[otrc],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0))*tblLines[[#This Row],[Receipt_credit]])</f>
         <v>450</v>
       </c>
-      <c r="AN11" s="10" t="str">
+      <c r="AR11" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(ROUND(tblLines[[#This Row],[sg_amount]],2)-tblLines[[#This Row],[OTRC]],0),"")</f>
         <v/>
       </c>
-      <c r="AO11" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$B$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$B$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
-        <v/>
-      </c>
-      <c r="AP11" s="10" t="str">
+      <c r="AS11" s="11" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <v/>
+      </c>
+      <c r="AT11" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),MAX(tblLines[[#This Row],[Base_shortfall]]-tblLines[[#This Row],[Offset_s18D]],0),"")</f>
         <v/>
       </c>
-      <c r="AQ11" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
-        <v/>
-      </c>
-      <c r="AR11" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[Settled]],Summary!$B$2),"")</f>
-        <v/>
-      </c>
-      <c r="AS11" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),MIN(IF(Summary!$B$3="",DATE(2030,12,31),Summary!$B$3-1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$B$2)),"")</f>
-        <v/>
-      </c>
-      <c r="AT11" s="9" t="str">
+      <c r="AU11" s="10" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <v/>
+      </c>
+      <c r="AV11" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AW11" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <v/>
+      </c>
+      <c r="AX11" s="9" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(Summary!$D$3="",tblLines[[#This Row],[Accrual_to]],MIN(Summary!$D$3-1,tblLines[[#This Row],[Accrual_to]])),"")</f>
+        <v/>
+      </c>
+      <c r="AY11" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v/>
       </c>
-      <c r="AU11" s="10" t="str">
+      <c r="AZ11" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
         <v/>
       </c>
-      <c r="AV11" s="9" t="str">
+      <c r="BA11" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
         <v/>
       </c>
-      <c r="AW11" s="10" t="str">
+      <c r="BB11" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</f>
         <v/>
       </c>
-      <c r="AX11" s="10" t="str">
+      <c r="BC11" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
         <v/>
       </c>
-      <c r="AY11" s="10" t="str">
+      <c r="BD11" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
         <v/>
       </c>
-      <c r="AZ11" s="10" t="str">
+      <c r="BE11" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
         <v/>
       </c>
-      <c r="BA11" s="10" t="str">
+      <c r="BF11" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
         <v/>
       </c>
-      <c r="BB11" s="10" t="str">
+      <c r="BG11" s="11" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
         <v/>
       </c>
-      <c r="BC11" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0,tblLines[[#This Row],[Cap]]&gt;0,OR(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]])),IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),tblLines[[#This Row],[fund_received_date]],tblLines[[#This Row],[remitted_date]])&lt;=DATE(2026,7,28)),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BD11" s="9">
+      <c r="BH11" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0,ROUND(tblLines[[#This Row],[Cap]],2)&gt;0,OR(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]])),IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]],tblLines[[#This Row],[Remit_day]])&lt;=DATE(2026,7,28)),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI11" s="10">
         <f>IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE11" s="9">
-        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[sg_amount]]&gt;0),1,0)</f>
+      <c r="BJ11" s="10">
+        <f>IF(AND(tblLines[[#This Row],[Verdict]]&lt;&gt;"",tblLines[[#This Row],[Verdict]]&lt;&gt;"SKIPPED",ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF11" s="9">
-        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BG11" s="9">
-        <f t="array" ref="BG11">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH11" s="9">
-        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+      <c r="BK11" s="10">
+        <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[Pay_day]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[Remit_day]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[Recv_day]]&amp;"")&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL11" s="10">
+        <f t="array" ref="BL11">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM11" s="10">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[Pay_day]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
         <v>1</v>
       </c>
     </row>
@@ -3950,30 +4201,30 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -3987,10 +4238,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -4004,10 +4255,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -4021,10 +4272,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -4038,13 +4289,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -4058,10 +4309,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -4075,10 +4326,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -4092,13 +4343,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -4112,10 +4363,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B10" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -4129,13 +4380,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -4149,13 +4400,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" t="s">
         <v>102</v>
-      </c>
-      <c r="B12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" t="s">
-        <v>97</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -4169,13 +4420,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -4189,13 +4440,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -4209,13 +4460,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -4229,10 +4480,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -4246,13 +4497,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -4266,10 +4517,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -4283,10 +4534,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -4300,10 +4551,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -4317,13 +4568,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -4337,13 +4588,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -4357,10 +4608,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B23" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -4374,10 +4625,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -4391,13 +4642,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -4411,10 +4662,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -4428,10 +4679,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -4463,13 +4714,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4477,10 +4728,10 @@
         <v>46023</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4488,10 +4739,10 @@
         <v>46048</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -4499,10 +4750,10 @@
         <v>46083</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4510,10 +4761,10 @@
         <v>46090</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -4521,10 +4772,10 @@
         <v>46115</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -4532,10 +4783,10 @@
         <v>46116</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -4543,10 +4794,10 @@
         <v>46117</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -4554,10 +4805,10 @@
         <v>46118</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -4565,10 +4816,10 @@
         <v>46137</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -4576,10 +4827,10 @@
         <v>46139</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -4587,10 +4838,10 @@
         <v>46146</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -4598,10 +4849,10 @@
         <v>46174</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -4609,10 +4860,10 @@
         <v>46181</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -4620,10 +4871,10 @@
         <v>46237</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -4631,10 +4882,10 @@
         <v>46290</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -4642,10 +4893,10 @@
         <v>46300</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -4653,10 +4904,10 @@
         <v>46381</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -4664,10 +4915,10 @@
         <v>46382</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -4675,10 +4926,10 @@
         <v>46384</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -4686,10 +4937,10 @@
         <v>46388</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -4697,10 +4948,10 @@
         <v>46413</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -4708,10 +4959,10 @@
         <v>46447</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -4719,10 +4970,10 @@
         <v>46454</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -4730,10 +4981,10 @@
         <v>46472</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -4741,10 +4992,10 @@
         <v>46473</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -4752,10 +5003,10 @@
         <v>46474</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -4763,10 +5014,10 @@
         <v>46475</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -4774,10 +5025,10 @@
         <v>46502</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -4785,10 +5036,10 @@
         <v>46503</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -4796,10 +5047,10 @@
         <v>46510</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -4807,10 +5058,10 @@
         <v>46538</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -4818,10 +5069,10 @@
         <v>46545</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -4829,10 +5080,10 @@
         <v>46552</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -4840,10 +5091,10 @@
         <v>46601</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -4851,10 +5102,10 @@
         <v>46664</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -4862,10 +5113,10 @@
         <v>46746</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -4873,10 +5124,10 @@
         <v>46747</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -4884,10 +5135,10 @@
         <v>46748</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -4895,20 +5146,20 @@
         <v>46749</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -4921,7 +5172,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F181"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="14" customWidth="1"/>
@@ -4929,22 +5180,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -4961,10 +5212,10 @@
         <v>365</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -4981,10 +5232,10 @@
         <v>365</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -5001,7 +5252,7 @@
         <v>365</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F4" s="12"/>
     </row>
@@ -5019,7 +5270,7 @@
         <v>365</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F5" s="12"/>
     </row>
@@ -5037,7 +5288,7 @@
         <v>366</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F6" s="12"/>
     </row>
@@ -5055,7 +5306,7 @@
         <v>365</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F7" s="12"/>
     </row>
@@ -5073,13 +5324,3073 @@
         <v>365</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F8" s="12"/>
     </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>47849</v>
+      </c>
+      <c r="B9" s="7">
+        <v>48213</v>
+      </c>
+      <c r="C9" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D9" s="12">
+        <v>365</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F9" s="12"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
+        <v>48214</v>
+      </c>
+      <c r="B10" s="7">
+        <v>48579</v>
+      </c>
+      <c r="C10" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D10" s="12">
+        <v>366</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F10" s="12"/>
+    </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>173</v>
+      <c r="A11" s="7">
+        <v>48580</v>
+      </c>
+      <c r="B11" s="7">
+        <v>48944</v>
+      </c>
+      <c r="C11" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D11" s="12">
+        <v>365</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F11" s="12"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
+        <v>48945</v>
+      </c>
+      <c r="B12" s="7">
+        <v>49309</v>
+      </c>
+      <c r="C12" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D12" s="12">
+        <v>365</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F12" s="12"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
+        <v>49310</v>
+      </c>
+      <c r="B13" s="7">
+        <v>49674</v>
+      </c>
+      <c r="C13" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D13" s="12">
+        <v>365</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F13" s="12"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="7">
+        <v>49675</v>
+      </c>
+      <c r="B14" s="7">
+        <v>50040</v>
+      </c>
+      <c r="C14" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D14" s="12">
+        <v>366</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F14" s="12"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="7">
+        <v>50041</v>
+      </c>
+      <c r="B15" s="7">
+        <v>50405</v>
+      </c>
+      <c r="C15" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D15" s="12">
+        <v>365</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F15" s="12"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
+        <v>50406</v>
+      </c>
+      <c r="B16" s="7">
+        <v>50770</v>
+      </c>
+      <c r="C16" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D16" s="12">
+        <v>365</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F16" s="12"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
+        <v>50771</v>
+      </c>
+      <c r="B17" s="7">
+        <v>51135</v>
+      </c>
+      <c r="C17" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D17" s="12">
+        <v>365</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F17" s="12"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>51136</v>
+      </c>
+      <c r="B18" s="7">
+        <v>51501</v>
+      </c>
+      <c r="C18" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D18" s="12">
+        <v>366</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F18" s="12"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
+        <v>51502</v>
+      </c>
+      <c r="B19" s="7">
+        <v>51866</v>
+      </c>
+      <c r="C19" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D19" s="12">
+        <v>365</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F19" s="12"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="7">
+        <v>51867</v>
+      </c>
+      <c r="B20" s="7">
+        <v>52231</v>
+      </c>
+      <c r="C20" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D20" s="12">
+        <v>365</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F20" s="12"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
+        <v>52232</v>
+      </c>
+      <c r="B21" s="7">
+        <v>52596</v>
+      </c>
+      <c r="C21" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D21" s="12">
+        <v>365</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F21" s="12"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
+        <v>52597</v>
+      </c>
+      <c r="B22" s="7">
+        <v>52962</v>
+      </c>
+      <c r="C22" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D22" s="12">
+        <v>366</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F22" s="12"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>52963</v>
+      </c>
+      <c r="B23" s="7">
+        <v>53327</v>
+      </c>
+      <c r="C23" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D23" s="12">
+        <v>365</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F23" s="12"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
+        <v>53328</v>
+      </c>
+      <c r="B24" s="7">
+        <v>53692</v>
+      </c>
+      <c r="C24" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D24" s="12">
+        <v>365</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F24" s="12"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
+        <v>53693</v>
+      </c>
+      <c r="B25" s="7">
+        <v>54057</v>
+      </c>
+      <c r="C25" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D25" s="12">
+        <v>365</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F25" s="12"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <v>54058</v>
+      </c>
+      <c r="B26" s="7">
+        <v>54423</v>
+      </c>
+      <c r="C26" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D26" s="12">
+        <v>366</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F26" s="12"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="7">
+        <v>54424</v>
+      </c>
+      <c r="B27" s="7">
+        <v>54788</v>
+      </c>
+      <c r="C27" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D27" s="12">
+        <v>365</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F27" s="12"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
+        <v>54789</v>
+      </c>
+      <c r="B28" s="7">
+        <v>55153</v>
+      </c>
+      <c r="C28" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D28" s="12">
+        <v>365</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F28" s="12"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>55154</v>
+      </c>
+      <c r="B29" s="7">
+        <v>55518</v>
+      </c>
+      <c r="C29" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D29" s="12">
+        <v>365</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F29" s="12"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <v>55519</v>
+      </c>
+      <c r="B30" s="7">
+        <v>55884</v>
+      </c>
+      <c r="C30" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D30" s="12">
+        <v>366</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F30" s="12"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
+        <v>55885</v>
+      </c>
+      <c r="B31" s="7">
+        <v>56249</v>
+      </c>
+      <c r="C31" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D31" s="12">
+        <v>365</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F31" s="12"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="7">
+        <v>56250</v>
+      </c>
+      <c r="B32" s="7">
+        <v>56614</v>
+      </c>
+      <c r="C32" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D32" s="12">
+        <v>365</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F32" s="12"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="7">
+        <v>56615</v>
+      </c>
+      <c r="B33" s="7">
+        <v>56979</v>
+      </c>
+      <c r="C33" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D33" s="12">
+        <v>365</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F33" s="12"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
+        <v>56980</v>
+      </c>
+      <c r="B34" s="7">
+        <v>57345</v>
+      </c>
+      <c r="C34" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D34" s="12">
+        <v>366</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F34" s="12"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="7">
+        <v>57346</v>
+      </c>
+      <c r="B35" s="7">
+        <v>57710</v>
+      </c>
+      <c r="C35" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D35" s="12">
+        <v>365</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F35" s="12"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="7">
+        <v>57711</v>
+      </c>
+      <c r="B36" s="7">
+        <v>58075</v>
+      </c>
+      <c r="C36" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D36" s="12">
+        <v>365</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F36" s="12"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="7">
+        <v>58076</v>
+      </c>
+      <c r="B37" s="7">
+        <v>58440</v>
+      </c>
+      <c r="C37" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D37" s="12">
+        <v>365</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F37" s="12"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="7">
+        <v>58441</v>
+      </c>
+      <c r="B38" s="7">
+        <v>58806</v>
+      </c>
+      <c r="C38" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D38" s="12">
+        <v>366</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F38" s="12"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="7">
+        <v>58807</v>
+      </c>
+      <c r="B39" s="7">
+        <v>59171</v>
+      </c>
+      <c r="C39" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D39" s="12">
+        <v>365</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F39" s="12"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="7">
+        <v>59172</v>
+      </c>
+      <c r="B40" s="7">
+        <v>59536</v>
+      </c>
+      <c r="C40" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D40" s="12">
+        <v>365</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F40" s="12"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="7">
+        <v>59537</v>
+      </c>
+      <c r="B41" s="7">
+        <v>59901</v>
+      </c>
+      <c r="C41" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D41" s="12">
+        <v>365</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F41" s="12"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="7">
+        <v>59902</v>
+      </c>
+      <c r="B42" s="7">
+        <v>60267</v>
+      </c>
+      <c r="C42" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D42" s="12">
+        <v>366</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F42" s="12"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="7">
+        <v>60268</v>
+      </c>
+      <c r="B43" s="7">
+        <v>60632</v>
+      </c>
+      <c r="C43" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D43" s="12">
+        <v>365</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F43" s="12"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
+        <v>60633</v>
+      </c>
+      <c r="B44" s="7">
+        <v>60997</v>
+      </c>
+      <c r="C44" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D44" s="12">
+        <v>365</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F44" s="12"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="7">
+        <v>60998</v>
+      </c>
+      <c r="B45" s="7">
+        <v>61362</v>
+      </c>
+      <c r="C45" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D45" s="12">
+        <v>365</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F45" s="12"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="7">
+        <v>61363</v>
+      </c>
+      <c r="B46" s="7">
+        <v>61728</v>
+      </c>
+      <c r="C46" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D46" s="12">
+        <v>366</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F46" s="12"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="7">
+        <v>61729</v>
+      </c>
+      <c r="B47" s="7">
+        <v>62093</v>
+      </c>
+      <c r="C47" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D47" s="12">
+        <v>365</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F47" s="12"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="7">
+        <v>62094</v>
+      </c>
+      <c r="B48" s="7">
+        <v>62458</v>
+      </c>
+      <c r="C48" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D48" s="12">
+        <v>365</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F48" s="12"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="7">
+        <v>62459</v>
+      </c>
+      <c r="B49" s="7">
+        <v>62823</v>
+      </c>
+      <c r="C49" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D49" s="12">
+        <v>365</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F49" s="12"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="7">
+        <v>62824</v>
+      </c>
+      <c r="B50" s="7">
+        <v>63189</v>
+      </c>
+      <c r="C50" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D50" s="12">
+        <v>366</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F50" s="12"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="7">
+        <v>63190</v>
+      </c>
+      <c r="B51" s="7">
+        <v>63554</v>
+      </c>
+      <c r="C51" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D51" s="12">
+        <v>365</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F51" s="12"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="7">
+        <v>63555</v>
+      </c>
+      <c r="B52" s="7">
+        <v>63919</v>
+      </c>
+      <c r="C52" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D52" s="12">
+        <v>365</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F52" s="12"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="7">
+        <v>63920</v>
+      </c>
+      <c r="B53" s="7">
+        <v>64284</v>
+      </c>
+      <c r="C53" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D53" s="12">
+        <v>365</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F53" s="12"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="7">
+        <v>64285</v>
+      </c>
+      <c r="B54" s="7">
+        <v>64650</v>
+      </c>
+      <c r="C54" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D54" s="12">
+        <v>366</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F54" s="12"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="7">
+        <v>64651</v>
+      </c>
+      <c r="B55" s="7">
+        <v>65015</v>
+      </c>
+      <c r="C55" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D55" s="12">
+        <v>365</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F55" s="12"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="7">
+        <v>65016</v>
+      </c>
+      <c r="B56" s="7">
+        <v>65380</v>
+      </c>
+      <c r="C56" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D56" s="12">
+        <v>365</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F56" s="12"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="7">
+        <v>65381</v>
+      </c>
+      <c r="B57" s="7">
+        <v>65745</v>
+      </c>
+      <c r="C57" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D57" s="12">
+        <v>365</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F57" s="12"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="7">
+        <v>65746</v>
+      </c>
+      <c r="B58" s="7">
+        <v>66111</v>
+      </c>
+      <c r="C58" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D58" s="12">
+        <v>366</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F58" s="12"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="7">
+        <v>66112</v>
+      </c>
+      <c r="B59" s="7">
+        <v>66476</v>
+      </c>
+      <c r="C59" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D59" s="12">
+        <v>365</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F59" s="12"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="7">
+        <v>66477</v>
+      </c>
+      <c r="B60" s="7">
+        <v>66841</v>
+      </c>
+      <c r="C60" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D60" s="12">
+        <v>365</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F60" s="12"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="7">
+        <v>66842</v>
+      </c>
+      <c r="B61" s="7">
+        <v>67206</v>
+      </c>
+      <c r="C61" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D61" s="12">
+        <v>365</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F61" s="12"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="7">
+        <v>67207</v>
+      </c>
+      <c r="B62" s="7">
+        <v>67572</v>
+      </c>
+      <c r="C62" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D62" s="12">
+        <v>366</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F62" s="12"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="7">
+        <v>67573</v>
+      </c>
+      <c r="B63" s="7">
+        <v>67937</v>
+      </c>
+      <c r="C63" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D63" s="12">
+        <v>365</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F63" s="12"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="7">
+        <v>67938</v>
+      </c>
+      <c r="B64" s="7">
+        <v>68302</v>
+      </c>
+      <c r="C64" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D64" s="12">
+        <v>365</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F64" s="12"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="7">
+        <v>68303</v>
+      </c>
+      <c r="B65" s="7">
+        <v>68667</v>
+      </c>
+      <c r="C65" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D65" s="12">
+        <v>365</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F65" s="12"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="7">
+        <v>68668</v>
+      </c>
+      <c r="B66" s="7">
+        <v>69033</v>
+      </c>
+      <c r="C66" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D66" s="12">
+        <v>366</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F66" s="12"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="7">
+        <v>69034</v>
+      </c>
+      <c r="B67" s="7">
+        <v>69398</v>
+      </c>
+      <c r="C67" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D67" s="12">
+        <v>365</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F67" s="12"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="7">
+        <v>69399</v>
+      </c>
+      <c r="B68" s="7">
+        <v>69763</v>
+      </c>
+      <c r="C68" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D68" s="12">
+        <v>365</v>
+      </c>
+      <c r="E68" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F68" s="12"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="7">
+        <v>69764</v>
+      </c>
+      <c r="B69" s="7">
+        <v>70128</v>
+      </c>
+      <c r="C69" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D69" s="12">
+        <v>365</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F69" s="12"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="7">
+        <v>70129</v>
+      </c>
+      <c r="B70" s="7">
+        <v>70494</v>
+      </c>
+      <c r="C70" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D70" s="12">
+        <v>366</v>
+      </c>
+      <c r="E70" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F70" s="12"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="7">
+        <v>70495</v>
+      </c>
+      <c r="B71" s="7">
+        <v>70859</v>
+      </c>
+      <c r="C71" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D71" s="12">
+        <v>365</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F71" s="12"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="7">
+        <v>70860</v>
+      </c>
+      <c r="B72" s="7">
+        <v>71224</v>
+      </c>
+      <c r="C72" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D72" s="12">
+        <v>365</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F72" s="12"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="7">
+        <v>71225</v>
+      </c>
+      <c r="B73" s="7">
+        <v>71589</v>
+      </c>
+      <c r="C73" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D73" s="12">
+        <v>365</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F73" s="12"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="7">
+        <v>71590</v>
+      </c>
+      <c r="B74" s="7">
+        <v>71955</v>
+      </c>
+      <c r="C74" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D74" s="12">
+        <v>366</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F74" s="12"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="7">
+        <v>71956</v>
+      </c>
+      <c r="B75" s="7">
+        <v>72320</v>
+      </c>
+      <c r="C75" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D75" s="12">
+        <v>365</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F75" s="12"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="7">
+        <v>72321</v>
+      </c>
+      <c r="B76" s="7">
+        <v>72685</v>
+      </c>
+      <c r="C76" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D76" s="12">
+        <v>365</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F76" s="12"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="7">
+        <v>72686</v>
+      </c>
+      <c r="B77" s="7">
+        <v>73050</v>
+      </c>
+      <c r="C77" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D77" s="12">
+        <v>365</v>
+      </c>
+      <c r="E77" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F77" s="12"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="7">
+        <v>73051</v>
+      </c>
+      <c r="B78" s="7">
+        <v>73415</v>
+      </c>
+      <c r="C78" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D78" s="12">
+        <v>365</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F78" s="12"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="7">
+        <v>73416</v>
+      </c>
+      <c r="B79" s="7">
+        <v>73780</v>
+      </c>
+      <c r="C79" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D79" s="12">
+        <v>365</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F79" s="12"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="7">
+        <v>73781</v>
+      </c>
+      <c r="B80" s="7">
+        <v>74145</v>
+      </c>
+      <c r="C80" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D80" s="12">
+        <v>365</v>
+      </c>
+      <c r="E80" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F80" s="12"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="7">
+        <v>74146</v>
+      </c>
+      <c r="B81" s="7">
+        <v>74510</v>
+      </c>
+      <c r="C81" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D81" s="12">
+        <v>365</v>
+      </c>
+      <c r="E81" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F81" s="12"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="7">
+        <v>74511</v>
+      </c>
+      <c r="B82" s="7">
+        <v>74876</v>
+      </c>
+      <c r="C82" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D82" s="12">
+        <v>366</v>
+      </c>
+      <c r="E82" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F82" s="12"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="7">
+        <v>74877</v>
+      </c>
+      <c r="B83" s="7">
+        <v>75241</v>
+      </c>
+      <c r="C83" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D83" s="12">
+        <v>365</v>
+      </c>
+      <c r="E83" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F83" s="12"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="7">
+        <v>75242</v>
+      </c>
+      <c r="B84" s="7">
+        <v>75606</v>
+      </c>
+      <c r="C84" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D84" s="12">
+        <v>365</v>
+      </c>
+      <c r="E84" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F84" s="12"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="7">
+        <v>75607</v>
+      </c>
+      <c r="B85" s="7">
+        <v>75971</v>
+      </c>
+      <c r="C85" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D85" s="12">
+        <v>365</v>
+      </c>
+      <c r="E85" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F85" s="12"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="7">
+        <v>75972</v>
+      </c>
+      <c r="B86" s="7">
+        <v>76337</v>
+      </c>
+      <c r="C86" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D86" s="12">
+        <v>366</v>
+      </c>
+      <c r="E86" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F86" s="12"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="7">
+        <v>76338</v>
+      </c>
+      <c r="B87" s="7">
+        <v>76702</v>
+      </c>
+      <c r="C87" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D87" s="12">
+        <v>365</v>
+      </c>
+      <c r="E87" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F87" s="12"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="7">
+        <v>76703</v>
+      </c>
+      <c r="B88" s="7">
+        <v>77067</v>
+      </c>
+      <c r="C88" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D88" s="12">
+        <v>365</v>
+      </c>
+      <c r="E88" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F88" s="12"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="7">
+        <v>77068</v>
+      </c>
+      <c r="B89" s="7">
+        <v>77432</v>
+      </c>
+      <c r="C89" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D89" s="12">
+        <v>365</v>
+      </c>
+      <c r="E89" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F89" s="12"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="7">
+        <v>77433</v>
+      </c>
+      <c r="B90" s="7">
+        <v>77798</v>
+      </c>
+      <c r="C90" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D90" s="12">
+        <v>366</v>
+      </c>
+      <c r="E90" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F90" s="12"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="7">
+        <v>77799</v>
+      </c>
+      <c r="B91" s="7">
+        <v>78163</v>
+      </c>
+      <c r="C91" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D91" s="12">
+        <v>365</v>
+      </c>
+      <c r="E91" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F91" s="12"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="7">
+        <v>78164</v>
+      </c>
+      <c r="B92" s="7">
+        <v>78528</v>
+      </c>
+      <c r="C92" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D92" s="12">
+        <v>365</v>
+      </c>
+      <c r="E92" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F92" s="12"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="7">
+        <v>78529</v>
+      </c>
+      <c r="B93" s="7">
+        <v>78893</v>
+      </c>
+      <c r="C93" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D93" s="12">
+        <v>365</v>
+      </c>
+      <c r="E93" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F93" s="12"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="7">
+        <v>78894</v>
+      </c>
+      <c r="B94" s="7">
+        <v>79259</v>
+      </c>
+      <c r="C94" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D94" s="12">
+        <v>366</v>
+      </c>
+      <c r="E94" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F94" s="12"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="7">
+        <v>79260</v>
+      </c>
+      <c r="B95" s="7">
+        <v>79624</v>
+      </c>
+      <c r="C95" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D95" s="12">
+        <v>365</v>
+      </c>
+      <c r="E95" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F95" s="12"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="7">
+        <v>79625</v>
+      </c>
+      <c r="B96" s="7">
+        <v>79989</v>
+      </c>
+      <c r="C96" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D96" s="12">
+        <v>365</v>
+      </c>
+      <c r="E96" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F96" s="12"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="7">
+        <v>79990</v>
+      </c>
+      <c r="B97" s="7">
+        <v>80354</v>
+      </c>
+      <c r="C97" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D97" s="12">
+        <v>365</v>
+      </c>
+      <c r="E97" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F97" s="12"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="7">
+        <v>80355</v>
+      </c>
+      <c r="B98" s="7">
+        <v>80720</v>
+      </c>
+      <c r="C98" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D98" s="12">
+        <v>366</v>
+      </c>
+      <c r="E98" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F98" s="12"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="7">
+        <v>80721</v>
+      </c>
+      <c r="B99" s="7">
+        <v>81085</v>
+      </c>
+      <c r="C99" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D99" s="12">
+        <v>365</v>
+      </c>
+      <c r="E99" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F99" s="12"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="7">
+        <v>81086</v>
+      </c>
+      <c r="B100" s="7">
+        <v>81450</v>
+      </c>
+      <c r="C100" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D100" s="12">
+        <v>365</v>
+      </c>
+      <c r="E100" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F100" s="12"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="7">
+        <v>81451</v>
+      </c>
+      <c r="B101" s="7">
+        <v>81815</v>
+      </c>
+      <c r="C101" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D101" s="12">
+        <v>365</v>
+      </c>
+      <c r="E101" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F101" s="12"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="7">
+        <v>81816</v>
+      </c>
+      <c r="B102" s="7">
+        <v>82181</v>
+      </c>
+      <c r="C102" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D102" s="12">
+        <v>366</v>
+      </c>
+      <c r="E102" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F102" s="12"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="7">
+        <v>82182</v>
+      </c>
+      <c r="B103" s="7">
+        <v>82546</v>
+      </c>
+      <c r="C103" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D103" s="12">
+        <v>365</v>
+      </c>
+      <c r="E103" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F103" s="12"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="7">
+        <v>82547</v>
+      </c>
+      <c r="B104" s="7">
+        <v>82911</v>
+      </c>
+      <c r="C104" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D104" s="12">
+        <v>365</v>
+      </c>
+      <c r="E104" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F104" s="12"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="7">
+        <v>82912</v>
+      </c>
+      <c r="B105" s="7">
+        <v>83276</v>
+      </c>
+      <c r="C105" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D105" s="12">
+        <v>365</v>
+      </c>
+      <c r="E105" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F105" s="12"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="7">
+        <v>83277</v>
+      </c>
+      <c r="B106" s="7">
+        <v>83642</v>
+      </c>
+      <c r="C106" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D106" s="12">
+        <v>366</v>
+      </c>
+      <c r="E106" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F106" s="12"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="7">
+        <v>83643</v>
+      </c>
+      <c r="B107" s="7">
+        <v>84007</v>
+      </c>
+      <c r="C107" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D107" s="12">
+        <v>365</v>
+      </c>
+      <c r="E107" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F107" s="12"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="7">
+        <v>84008</v>
+      </c>
+      <c r="B108" s="7">
+        <v>84372</v>
+      </c>
+      <c r="C108" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D108" s="12">
+        <v>365</v>
+      </c>
+      <c r="E108" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F108" s="12"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="7">
+        <v>84373</v>
+      </c>
+      <c r="B109" s="7">
+        <v>84737</v>
+      </c>
+      <c r="C109" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D109" s="12">
+        <v>365</v>
+      </c>
+      <c r="E109" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F109" s="12"/>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="7">
+        <v>84738</v>
+      </c>
+      <c r="B110" s="7">
+        <v>85103</v>
+      </c>
+      <c r="C110" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D110" s="12">
+        <v>366</v>
+      </c>
+      <c r="E110" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F110" s="12"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="7">
+        <v>85104</v>
+      </c>
+      <c r="B111" s="7">
+        <v>85468</v>
+      </c>
+      <c r="C111" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D111" s="12">
+        <v>365</v>
+      </c>
+      <c r="E111" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F111" s="12"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="7">
+        <v>85469</v>
+      </c>
+      <c r="B112" s="7">
+        <v>85833</v>
+      </c>
+      <c r="C112" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D112" s="12">
+        <v>365</v>
+      </c>
+      <c r="E112" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F112" s="12"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="7">
+        <v>85834</v>
+      </c>
+      <c r="B113" s="7">
+        <v>86198</v>
+      </c>
+      <c r="C113" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D113" s="12">
+        <v>365</v>
+      </c>
+      <c r="E113" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F113" s="12"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="7">
+        <v>86199</v>
+      </c>
+      <c r="B114" s="7">
+        <v>86564</v>
+      </c>
+      <c r="C114" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D114" s="12">
+        <v>366</v>
+      </c>
+      <c r="E114" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F114" s="12"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="7">
+        <v>86565</v>
+      </c>
+      <c r="B115" s="7">
+        <v>86929</v>
+      </c>
+      <c r="C115" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D115" s="12">
+        <v>365</v>
+      </c>
+      <c r="E115" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F115" s="12"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="7">
+        <v>86930</v>
+      </c>
+      <c r="B116" s="7">
+        <v>87294</v>
+      </c>
+      <c r="C116" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D116" s="12">
+        <v>365</v>
+      </c>
+      <c r="E116" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F116" s="12"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="7">
+        <v>87295</v>
+      </c>
+      <c r="B117" s="7">
+        <v>87659</v>
+      </c>
+      <c r="C117" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D117" s="12">
+        <v>365</v>
+      </c>
+      <c r="E117" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F117" s="12"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="7">
+        <v>87660</v>
+      </c>
+      <c r="B118" s="7">
+        <v>88025</v>
+      </c>
+      <c r="C118" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D118" s="12">
+        <v>366</v>
+      </c>
+      <c r="E118" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F118" s="12"/>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="7">
+        <v>88026</v>
+      </c>
+      <c r="B119" s="7">
+        <v>88390</v>
+      </c>
+      <c r="C119" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D119" s="12">
+        <v>365</v>
+      </c>
+      <c r="E119" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F119" s="12"/>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="7">
+        <v>88391</v>
+      </c>
+      <c r="B120" s="7">
+        <v>88755</v>
+      </c>
+      <c r="C120" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D120" s="12">
+        <v>365</v>
+      </c>
+      <c r="E120" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F120" s="12"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="7">
+        <v>88756</v>
+      </c>
+      <c r="B121" s="7">
+        <v>89120</v>
+      </c>
+      <c r="C121" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D121" s="12">
+        <v>365</v>
+      </c>
+      <c r="E121" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F121" s="12"/>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="7">
+        <v>89121</v>
+      </c>
+      <c r="B122" s="7">
+        <v>89486</v>
+      </c>
+      <c r="C122" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D122" s="12">
+        <v>366</v>
+      </c>
+      <c r="E122" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F122" s="12"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="7">
+        <v>89487</v>
+      </c>
+      <c r="B123" s="7">
+        <v>89851</v>
+      </c>
+      <c r="C123" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D123" s="12">
+        <v>365</v>
+      </c>
+      <c r="E123" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F123" s="12"/>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="7">
+        <v>89852</v>
+      </c>
+      <c r="B124" s="7">
+        <v>90216</v>
+      </c>
+      <c r="C124" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D124" s="12">
+        <v>365</v>
+      </c>
+      <c r="E124" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F124" s="12"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="7">
+        <v>90217</v>
+      </c>
+      <c r="B125" s="7">
+        <v>90581</v>
+      </c>
+      <c r="C125" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D125" s="12">
+        <v>365</v>
+      </c>
+      <c r="E125" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F125" s="12"/>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="7">
+        <v>90582</v>
+      </c>
+      <c r="B126" s="7">
+        <v>90947</v>
+      </c>
+      <c r="C126" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D126" s="12">
+        <v>366</v>
+      </c>
+      <c r="E126" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F126" s="12"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="7">
+        <v>90948</v>
+      </c>
+      <c r="B127" s="7">
+        <v>91312</v>
+      </c>
+      <c r="C127" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D127" s="12">
+        <v>365</v>
+      </c>
+      <c r="E127" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F127" s="12"/>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="7">
+        <v>91313</v>
+      </c>
+      <c r="B128" s="7">
+        <v>91677</v>
+      </c>
+      <c r="C128" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D128" s="12">
+        <v>365</v>
+      </c>
+      <c r="E128" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F128" s="12"/>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="7">
+        <v>91678</v>
+      </c>
+      <c r="B129" s="7">
+        <v>92042</v>
+      </c>
+      <c r="C129" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D129" s="12">
+        <v>365</v>
+      </c>
+      <c r="E129" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F129" s="12"/>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="7">
+        <v>92043</v>
+      </c>
+      <c r="B130" s="7">
+        <v>92408</v>
+      </c>
+      <c r="C130" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D130" s="12">
+        <v>366</v>
+      </c>
+      <c r="E130" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F130" s="12"/>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="7">
+        <v>92409</v>
+      </c>
+      <c r="B131" s="7">
+        <v>92773</v>
+      </c>
+      <c r="C131" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D131" s="12">
+        <v>365</v>
+      </c>
+      <c r="E131" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F131" s="12"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="7">
+        <v>92774</v>
+      </c>
+      <c r="B132" s="7">
+        <v>93138</v>
+      </c>
+      <c r="C132" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D132" s="12">
+        <v>365</v>
+      </c>
+      <c r="E132" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F132" s="12"/>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" s="7">
+        <v>93139</v>
+      </c>
+      <c r="B133" s="7">
+        <v>93503</v>
+      </c>
+      <c r="C133" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D133" s="12">
+        <v>365</v>
+      </c>
+      <c r="E133" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F133" s="12"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="7">
+        <v>93504</v>
+      </c>
+      <c r="B134" s="7">
+        <v>93869</v>
+      </c>
+      <c r="C134" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D134" s="12">
+        <v>366</v>
+      </c>
+      <c r="E134" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F134" s="12"/>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="7">
+        <v>93870</v>
+      </c>
+      <c r="B135" s="7">
+        <v>94234</v>
+      </c>
+      <c r="C135" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D135" s="12">
+        <v>365</v>
+      </c>
+      <c r="E135" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F135" s="12"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="7">
+        <v>94235</v>
+      </c>
+      <c r="B136" s="7">
+        <v>94599</v>
+      </c>
+      <c r="C136" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D136" s="12">
+        <v>365</v>
+      </c>
+      <c r="E136" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F136" s="12"/>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="7">
+        <v>94600</v>
+      </c>
+      <c r="B137" s="7">
+        <v>94964</v>
+      </c>
+      <c r="C137" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D137" s="12">
+        <v>365</v>
+      </c>
+      <c r="E137" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F137" s="12"/>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="7">
+        <v>94965</v>
+      </c>
+      <c r="B138" s="7">
+        <v>95330</v>
+      </c>
+      <c r="C138" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D138" s="12">
+        <v>366</v>
+      </c>
+      <c r="E138" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F138" s="12"/>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="7">
+        <v>95331</v>
+      </c>
+      <c r="B139" s="7">
+        <v>95695</v>
+      </c>
+      <c r="C139" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D139" s="12">
+        <v>365</v>
+      </c>
+      <c r="E139" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F139" s="12"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="7">
+        <v>95696</v>
+      </c>
+      <c r="B140" s="7">
+        <v>96060</v>
+      </c>
+      <c r="C140" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D140" s="12">
+        <v>365</v>
+      </c>
+      <c r="E140" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F140" s="12"/>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="7">
+        <v>96061</v>
+      </c>
+      <c r="B141" s="7">
+        <v>96425</v>
+      </c>
+      <c r="C141" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D141" s="12">
+        <v>365</v>
+      </c>
+      <c r="E141" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F141" s="12"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="7">
+        <v>96426</v>
+      </c>
+      <c r="B142" s="7">
+        <v>96791</v>
+      </c>
+      <c r="C142" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D142" s="12">
+        <v>366</v>
+      </c>
+      <c r="E142" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F142" s="12"/>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="7">
+        <v>96792</v>
+      </c>
+      <c r="B143" s="7">
+        <v>97156</v>
+      </c>
+      <c r="C143" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D143" s="12">
+        <v>365</v>
+      </c>
+      <c r="E143" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F143" s="12"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="7">
+        <v>97157</v>
+      </c>
+      <c r="B144" s="7">
+        <v>97521</v>
+      </c>
+      <c r="C144" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D144" s="12">
+        <v>365</v>
+      </c>
+      <c r="E144" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F144" s="12"/>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="7">
+        <v>97522</v>
+      </c>
+      <c r="B145" s="7">
+        <v>97886</v>
+      </c>
+      <c r="C145" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D145" s="12">
+        <v>365</v>
+      </c>
+      <c r="E145" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F145" s="12"/>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" s="7">
+        <v>97887</v>
+      </c>
+      <c r="B146" s="7">
+        <v>98252</v>
+      </c>
+      <c r="C146" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D146" s="12">
+        <v>366</v>
+      </c>
+      <c r="E146" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F146" s="12"/>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" s="7">
+        <v>98253</v>
+      </c>
+      <c r="B147" s="7">
+        <v>98617</v>
+      </c>
+      <c r="C147" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D147" s="12">
+        <v>365</v>
+      </c>
+      <c r="E147" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F147" s="12"/>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" s="7">
+        <v>98618</v>
+      </c>
+      <c r="B148" s="7">
+        <v>98982</v>
+      </c>
+      <c r="C148" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D148" s="12">
+        <v>365</v>
+      </c>
+      <c r="E148" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F148" s="12"/>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" s="7">
+        <v>98983</v>
+      </c>
+      <c r="B149" s="7">
+        <v>99347</v>
+      </c>
+      <c r="C149" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D149" s="12">
+        <v>365</v>
+      </c>
+      <c r="E149" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F149" s="12"/>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" s="7">
+        <v>99348</v>
+      </c>
+      <c r="B150" s="7">
+        <v>99713</v>
+      </c>
+      <c r="C150" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D150" s="12">
+        <v>366</v>
+      </c>
+      <c r="E150" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F150" s="12"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" s="7">
+        <v>99714</v>
+      </c>
+      <c r="B151" s="7">
+        <v>100078</v>
+      </c>
+      <c r="C151" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D151" s="12">
+        <v>365</v>
+      </c>
+      <c r="E151" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F151" s="12"/>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="7">
+        <v>100079</v>
+      </c>
+      <c r="B152" s="7">
+        <v>100443</v>
+      </c>
+      <c r="C152" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D152" s="12">
+        <v>365</v>
+      </c>
+      <c r="E152" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F152" s="12"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" s="7">
+        <v>100444</v>
+      </c>
+      <c r="B153" s="7">
+        <v>100808</v>
+      </c>
+      <c r="C153" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D153" s="12">
+        <v>365</v>
+      </c>
+      <c r="E153" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F153" s="12"/>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" s="7">
+        <v>100809</v>
+      </c>
+      <c r="B154" s="7">
+        <v>101174</v>
+      </c>
+      <c r="C154" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D154" s="12">
+        <v>366</v>
+      </c>
+      <c r="E154" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F154" s="12"/>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" s="7">
+        <v>101175</v>
+      </c>
+      <c r="B155" s="7">
+        <v>101539</v>
+      </c>
+      <c r="C155" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D155" s="12">
+        <v>365</v>
+      </c>
+      <c r="E155" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F155" s="12"/>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" s="7">
+        <v>101540</v>
+      </c>
+      <c r="B156" s="7">
+        <v>101904</v>
+      </c>
+      <c r="C156" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D156" s="12">
+        <v>365</v>
+      </c>
+      <c r="E156" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F156" s="12"/>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" s="7">
+        <v>101905</v>
+      </c>
+      <c r="B157" s="7">
+        <v>102269</v>
+      </c>
+      <c r="C157" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D157" s="12">
+        <v>365</v>
+      </c>
+      <c r="E157" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F157" s="12"/>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" s="7">
+        <v>102270</v>
+      </c>
+      <c r="B158" s="7">
+        <v>102635</v>
+      </c>
+      <c r="C158" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D158" s="12">
+        <v>366</v>
+      </c>
+      <c r="E158" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F158" s="12"/>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" s="7">
+        <v>102636</v>
+      </c>
+      <c r="B159" s="7">
+        <v>103000</v>
+      </c>
+      <c r="C159" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D159" s="12">
+        <v>365</v>
+      </c>
+      <c r="E159" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F159" s="12"/>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" s="7">
+        <v>103001</v>
+      </c>
+      <c r="B160" s="7">
+        <v>103365</v>
+      </c>
+      <c r="C160" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D160" s="12">
+        <v>365</v>
+      </c>
+      <c r="E160" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F160" s="12"/>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" s="7">
+        <v>103366</v>
+      </c>
+      <c r="B161" s="7">
+        <v>103730</v>
+      </c>
+      <c r="C161" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D161" s="12">
+        <v>365</v>
+      </c>
+      <c r="E161" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F161" s="12"/>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" s="7">
+        <v>103731</v>
+      </c>
+      <c r="B162" s="7">
+        <v>104096</v>
+      </c>
+      <c r="C162" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D162" s="12">
+        <v>366</v>
+      </c>
+      <c r="E162" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F162" s="12"/>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" s="7">
+        <v>104097</v>
+      </c>
+      <c r="B163" s="7">
+        <v>104461</v>
+      </c>
+      <c r="C163" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D163" s="12">
+        <v>365</v>
+      </c>
+      <c r="E163" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F163" s="12"/>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" s="7">
+        <v>104462</v>
+      </c>
+      <c r="B164" s="7">
+        <v>104826</v>
+      </c>
+      <c r="C164" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D164" s="12">
+        <v>365</v>
+      </c>
+      <c r="E164" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F164" s="12"/>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" s="7">
+        <v>104827</v>
+      </c>
+      <c r="B165" s="7">
+        <v>105191</v>
+      </c>
+      <c r="C165" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D165" s="12">
+        <v>365</v>
+      </c>
+      <c r="E165" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F165" s="12"/>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" s="7">
+        <v>105192</v>
+      </c>
+      <c r="B166" s="7">
+        <v>105557</v>
+      </c>
+      <c r="C166" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D166" s="12">
+        <v>366</v>
+      </c>
+      <c r="E166" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F166" s="12"/>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" s="7">
+        <v>105558</v>
+      </c>
+      <c r="B167" s="7">
+        <v>105922</v>
+      </c>
+      <c r="C167" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D167" s="12">
+        <v>365</v>
+      </c>
+      <c r="E167" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F167" s="12"/>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" s="7">
+        <v>105923</v>
+      </c>
+      <c r="B168" s="7">
+        <v>106287</v>
+      </c>
+      <c r="C168" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D168" s="12">
+        <v>365</v>
+      </c>
+      <c r="E168" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F168" s="12"/>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" s="7">
+        <v>106288</v>
+      </c>
+      <c r="B169" s="7">
+        <v>106652</v>
+      </c>
+      <c r="C169" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D169" s="12">
+        <v>365</v>
+      </c>
+      <c r="E169" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F169" s="12"/>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" s="7">
+        <v>106653</v>
+      </c>
+      <c r="B170" s="7">
+        <v>107018</v>
+      </c>
+      <c r="C170" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D170" s="12">
+        <v>366</v>
+      </c>
+      <c r="E170" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F170" s="12"/>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" s="7">
+        <v>107019</v>
+      </c>
+      <c r="B171" s="7">
+        <v>107383</v>
+      </c>
+      <c r="C171" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D171" s="12">
+        <v>365</v>
+      </c>
+      <c r="E171" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F171" s="12"/>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" s="7">
+        <v>107384</v>
+      </c>
+      <c r="B172" s="7">
+        <v>107748</v>
+      </c>
+      <c r="C172" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D172" s="12">
+        <v>365</v>
+      </c>
+      <c r="E172" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F172" s="12"/>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" s="7">
+        <v>107749</v>
+      </c>
+      <c r="B173" s="7">
+        <v>108113</v>
+      </c>
+      <c r="C173" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D173" s="12">
+        <v>365</v>
+      </c>
+      <c r="E173" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F173" s="12"/>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" s="7">
+        <v>108114</v>
+      </c>
+      <c r="B174" s="7">
+        <v>108479</v>
+      </c>
+      <c r="C174" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D174" s="12">
+        <v>366</v>
+      </c>
+      <c r="E174" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F174" s="12"/>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" s="7">
+        <v>108480</v>
+      </c>
+      <c r="B175" s="7">
+        <v>108844</v>
+      </c>
+      <c r="C175" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D175" s="12">
+        <v>365</v>
+      </c>
+      <c r="E175" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F175" s="12"/>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176" s="7">
+        <v>108845</v>
+      </c>
+      <c r="B176" s="7">
+        <v>109209</v>
+      </c>
+      <c r="C176" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D176" s="12">
+        <v>365</v>
+      </c>
+      <c r="E176" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F176" s="12"/>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" s="7">
+        <v>109210</v>
+      </c>
+      <c r="B177" s="7">
+        <v>109574</v>
+      </c>
+      <c r="C177" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D177" s="12">
+        <v>365</v>
+      </c>
+      <c r="E177" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F177" s="12"/>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" s="7">
+        <v>109575</v>
+      </c>
+      <c r="B178" s="7">
+        <v>109939</v>
+      </c>
+      <c r="C178" s="12">
+        <v>11.43</v>
+      </c>
+      <c r="D178" s="12">
+        <v>365</v>
+      </c>
+      <c r="E178" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F178" s="12"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -5092,185 +8403,199 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="64" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B1" s="5"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B2" s="13">
         <v>46244</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2" s="9">
+        <f>IF(Summary!$B$2="","",IF(ISNUMBER(Summary!$B$2),INT(Summary!$B$2),Summary!$B$2))</f>
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B3" s="13"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D3" s="9" t="str">
+        <f>IF(Summary!$B$3="","",IF(ISNUMBER(Summary!$B$3),INT(Summary!$B$3),Summary!$B$3))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="B6" s="13">
         <v>46630</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>181</v>
-      </c>
-      <c r="B7" s="11">
+        <v>188</v>
+      </c>
+      <c r="B7" s="9">
         <f>_xlfn.MAXIFS(tblGic[to],tblGic[basis],"known")</f>
         <v>46295</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B9" s="5"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>89</v>
-      </c>
-      <c r="B10" s="9">
+        <v>94</v>
+      </c>
+      <c r="B10" s="10">
         <f>COUNTIF(tblLines[Verdict],"ON_TIME")</f>
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B11" s="9">
+        <v>121</v>
+      </c>
+      <c r="B11" s="10">
         <f>COUNTIF(tblLines[Verdict],"AT_RISK")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>99</v>
-      </c>
-      <c r="B12" s="9">
+        <v>104</v>
+      </c>
+      <c r="B12" s="10">
         <f>COUNTIF(tblLines[Verdict],"LATE")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>94</v>
-      </c>
-      <c r="B13" s="9">
+        <v>99</v>
+      </c>
+      <c r="B13" s="10">
         <f>COUNTIF(tblLines[Verdict],"UNPAID")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>87</v>
-      </c>
-      <c r="B14" s="9">
+        <v>92</v>
+      </c>
+      <c r="B14" s="10">
         <f>COUNTIF(tblLines[Verdict],"UNKNOWN")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>85</v>
-      </c>
-      <c r="B15" s="9">
+        <v>90</v>
+      </c>
+      <c r="B15" s="10">
         <f>COUNTIF(tblLines[Verdict],"SKIPPED")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>183</v>
-      </c>
-      <c r="B16" s="9">
+        <v>190</v>
+      </c>
+      <c r="B16" s="10">
         <f>SUM(tblLines[Exposed])</f>
         <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>184</v>
-      </c>
-      <c r="B17" s="10">
+        <v>191</v>
+      </c>
+      <c r="B17" s="11">
         <f>ROUND(SUM(tblLines[Shortfall_r]),2)</f>
         <v>780</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>185</v>
-      </c>
-      <c r="B18" s="10">
+        <v>192</v>
+      </c>
+      <c r="B18" s="11">
         <f>ROUND(SUM(tblLines[NEC_r]),2)</f>
         <v>8.07</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>186</v>
-      </c>
-      <c r="B19" s="10">
+        <v>193</v>
+      </c>
+      <c r="B19" s="11">
         <f>ROUND(SUM(tblLines[SGC_low]),2)</f>
         <v>788.07</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>187</v>
-      </c>
-      <c r="B20" s="10">
+        <v>194</v>
+      </c>
+      <c r="B20" s="11">
         <f>ROUND(SUM(tblLines[SGC_high]),2)</f>
         <v>1260.92</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>188</v>
-      </c>
-      <c r="B21" s="9">
+        <v>195</v>
+      </c>
+      <c r="B21" s="10">
         <f>SUMPRODUCT(--(tblLines[Unassessable_between]&lt;&gt;""))</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>189</v>
-      </c>
-      <c r="B22" s="9" t="str">
+        <v>196</v>
+      </c>
+      <c r="B22" s="10" t="str">
         <f>IF(AND(SUM(tblLines[Assessable])&gt;0,SUMPRODUCT(tblLines[Assessable]*tblLines[Receipt_established])=0),"YES","NO")</f>
         <v>NO</v>
       </c>
@@ -5325,229 +8650,229 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>194</v>
-      </c>
-      <c r="B2" s="9" t="str">
+        <v>201</v>
+      </c>
+      <c r="B2" s="10" t="str">
         <f>IF(C2=0,"PASS","BLOCKED")</f>
         <v>PASS</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="10">
         <f>SUMPRODUCT(--(tblLines[Row_problem]&lt;&gt;""))</f>
         <v>0</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="10" t="str">
         <f t="array" ref="D2">IF(C2=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[Row_problem]&lt;&gt;"")*(ROW(tblLines[employee_id])-1)))))</f>
         <v/>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B3" s="9" t="str">
+        <v>202</v>
+      </c>
+      <c r="B3" s="10" t="str">
         <f>IF(C3=0,"PASS","BLOCKED")</f>
         <v>PASS</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="10">
         <f>SUM(tblLines[Guard])</f>
         <v>0</v>
       </c>
-      <c r="D3" s="9" t="str">
+      <c r="D3" s="10" t="str">
         <f t="array" ref="D3">IF(C3=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[Guard]=1)*(ROW(tblLines[employee_id])-1)))))</f>
         <v/>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>196</v>
-      </c>
-      <c r="B4" s="9" t="str">
+        <v>203</v>
+      </c>
+      <c r="B4" s="10" t="str">
         <f>IF(OR(C4=0,Summary!$B$4="Y"),"PASS","BLOCKED")</f>
         <v>BLOCKED</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="10">
         <f>SUM(tblLines[Transition_row])</f>
         <v>2</v>
       </c>
-      <c r="D4" s="9" t="str">
+      <c r="D4" s="10" t="str">
         <f t="array" ref="D4">IF(C4=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[Transition_row]=1)*(ROW(tblLines[employee_id])-1)))))</f>
         <v>EMP003</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>197</v>
-      </c>
-      <c r="B5" s="9" t="str">
+        <v>204</v>
+      </c>
+      <c r="B5" s="10" t="str">
         <f>IF(C5=0,"PASS","REVIEW")</f>
         <v>REVIEW</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="10">
         <f>SUM(tblLines[Exposed])</f>
         <v>3</v>
       </c>
-      <c r="D5" s="9" t="str">
+      <c r="D5" s="10" t="str">
         <f t="array" ref="D5">IF(C5=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[Exposed]=1)*(ROW(tblLines[employee_id])-1)))))</f>
         <v>EMP001</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>198</v>
-      </c>
-      <c r="B6" s="9" t="str">
+        <v>205</v>
+      </c>
+      <c r="B6" s="10" t="str">
         <f>IF(C6=0,"PASS","REVIEW")</f>
         <v>PASS</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="10">
         <f>SUMPRODUCT(--(tblLines[Unassessable_between]&lt;&gt;""))</f>
         <v>0</v>
       </c>
-      <c r="D6" s="9" t="str">
+      <c r="D6" s="10" t="str">
         <f t="array" ref="D6">IF(C6=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[Unassessable_between]&lt;&gt;"")*(ROW(tblLines[employee_id])-1)))))</f>
         <v/>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>199</v>
-      </c>
-      <c r="B7" s="9" t="str">
+        <v>206</v>
+      </c>
+      <c r="B7" s="10" t="str">
         <f>IF(OR(Summary!B22="NO",Summary!$B$5="Y"),"PASS","REVIEW")</f>
         <v>PASS</v>
       </c>
-      <c r="C7" s="9" t="str">
+      <c r="C7" s="10" t="str">
         <f>Summary!B22</f>
         <v>NO</v>
       </c>
-      <c r="D7" s="9"/>
+      <c r="D7" s="10"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>200</v>
-      </c>
-      <c r="B8" s="9" t="str">
+        <v>207</v>
+      </c>
+      <c r="B8" s="10" t="str">
         <f>IF(C8=0,"PASS","NOTE")</f>
         <v>PASS</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="10">
         <f>SUM(tblLines[Past_horizon])</f>
         <v>0</v>
       </c>
-      <c r="D8" s="9" t="str">
+      <c r="D8" s="10" t="str">
         <f t="array" ref="D8">IF(C8=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[Past_horizon]=1)*(ROW(tblLines[employee_id])-1)))))</f>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B9" s="9" t="str">
+        <v>208</v>
+      </c>
+      <c r="B9" s="10" t="str">
         <f>IF(C9=0,"PASS","NOTE")</f>
         <v>PASS</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="10">
         <f>SUM(tblLines[GIC_estimated])</f>
         <v>0</v>
       </c>
-      <c r="D9" s="9" t="str">
+      <c r="D9" s="10" t="str">
         <f t="array" ref="D9">IF(C9=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[GIC_estimated]=1)*(ROW(tblLines[employee_id])-1)))))</f>
         <v/>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>202</v>
-      </c>
-      <c r="B10" s="9" t="str">
+        <v>209</v>
+      </c>
+      <c r="B10" s="10" t="str">
         <f>IF(C10=0,"PASS","NOTE")</f>
         <v>PASS</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="10">
         <f>SUM(tblLines[Duplicate])</f>
         <v>0</v>
       </c>
-      <c r="D10" s="9" t="str">
+      <c r="D10" s="10" t="str">
         <f t="array" ref="D10">IF(C10=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[Duplicate]=1)*(ROW(tblLines[employee_id])-1)))))</f>
         <v/>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>203</v>
-      </c>
-      <c r="B11" s="9" t="str">
+        <v>210</v>
+      </c>
+      <c r="B11" s="10" t="str">
         <f>IF(C11=0,"PASS","NOTE")</f>
         <v>PASS</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="10">
         <f>COUNTIF(tblLines[Branch],"NIL")</f>
         <v>0</v>
       </c>
-      <c r="D11" s="9" t="str">
+      <c r="D11" s="10" t="str">
         <f t="array" ref="D11">IF(C11=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[Branch]="NIL")*(ROW(tblLines[employee_id])-1)))))</f>
         <v/>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>204</v>
-      </c>
-      <c r="B12" s="9" t="str">
-        <f>IF(AND(ISNUMBER(Summary!$B$2),OR(Summary!$B$3="",ISNUMBER(Summary!$B$3)),ISNUMBER(Summary!$B$6)),"PASS","BLOCKED")</f>
+        <v>211</v>
+      </c>
+      <c r="B12" s="10" t="str">
+        <f>IF(AND(ISNUMBER(Summary!$D$2),Summary!$D$2&lt;=DATE(2200,12,31),OR(Summary!$D$3="",AND(ISNUMBER(Summary!$D$3),Summary!$D$3&lt;=DATE(2200,12,31))),AND(ISNUMBER(Summary!$B$6),Summary!$B$6&lt;=DATE(2200,12,31))),"PASS","BLOCKED")</f>
         <v>PASS</v>
       </c>
-      <c r="C12" s="9">
-        <f>Summary!$B$2</f>
+      <c r="C12" s="10">
+        <f>Summary!$D$2</f>
         <v>46244</v>
       </c>
-      <c r="D12" s="9"/>
+      <c r="D12" s="10"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>205</v>
-      </c>
-      <c r="B13" s="9" t="str">
+        <v>212</v>
+      </c>
+      <c r="B13" s="10" t="str">
         <f>IF(C13=0,"PASS","REVIEW")</f>
         <v>REVIEW</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="10">
         <f>SUM(tblLines[Sample_row])</f>
         <v>10</v>
       </c>
-      <c r="D13" s="9" t="str">
+      <c r="D13" s="10" t="str">
         <f t="array" ref="D13">IF(C13=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[Sample_row]=1)*(ROW(tblLines[employee_id])-1)))))</f>
         <v>EMP005</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>206</v>
-      </c>
-      <c r="B14" s="9" t="str">
+        <v>213</v>
+      </c>
+      <c r="B14" s="10" t="str">
         <f>IF(C14=0,"PASS","NOTE")</f>
         <v>PASS</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="10">
         <f>SUM(tblLines[Case_variant])</f>
         <v>0</v>
       </c>
-      <c r="D14" s="9" t="str">
+      <c r="D14" s="10" t="str">
         <f t="array" ref="D14">IF(C14=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[Case_variant]=1)*(ROW(tblLines[employee_id])-1)))))</f>
         <v/>
       </c>
@@ -5563,37 +8888,37 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -5624,74 +8949,74 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B2" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B3" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B4" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B5" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B6" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B7" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B8" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B9" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>

--- a/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
+++ b/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D44E127-64F6-4BE1-8D3C-D03DBAEF4F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A9EF8C-9F6F-4941-9B04-905DEBCA7433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3510" yWindow="3510" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="240">
   <si>
     <t>Payday Super review: s 18C deadlines and the SG charge estimate</t>
   </si>
@@ -571,6 +571,9 @@
     <t>2026-08-14</t>
   </si>
   <si>
+    <t>2026-09-14</t>
+  </si>
+  <si>
     <t>estimate</t>
   </si>
   <si>
@@ -739,7 +742,7 @@
     <t>GIC rates</t>
   </si>
   <si>
-    <t>ATO general interest charge rates, known through 2026-09-30; later days carry the last known rate as an estimate</t>
+    <t>ATO general interest charge rates, known through 2026-12-31; later days carry the last known rate as an estimate</t>
   </si>
   <si>
     <t>No-install explainer</t>
@@ -5175,6 +5178,7 @@
   <dimension ref="A1:F181"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="3" width="14" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5246,15 +5250,17 @@
         <v>46387</v>
       </c>
       <c r="C4" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D4" s="12">
         <v>365</v>
       </c>
       <c r="E4" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="F4" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="F4" s="12"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
@@ -5264,13 +5270,13 @@
         <v>46752</v>
       </c>
       <c r="C5" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D5" s="12">
         <v>365</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F5" s="12"/>
     </row>
@@ -5282,13 +5288,13 @@
         <v>47118</v>
       </c>
       <c r="C6" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D6" s="12">
         <v>366</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F6" s="12"/>
     </row>
@@ -5300,13 +5306,13 @@
         <v>47483</v>
       </c>
       <c r="C7" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D7" s="12">
         <v>365</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F7" s="12"/>
     </row>
@@ -5318,13 +5324,13 @@
         <v>47848</v>
       </c>
       <c r="C8" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D8" s="12">
         <v>365</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F8" s="12"/>
     </row>
@@ -5336,13 +5342,13 @@
         <v>48213</v>
       </c>
       <c r="C9" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D9" s="12">
         <v>365</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F9" s="12"/>
     </row>
@@ -5354,13 +5360,13 @@
         <v>48579</v>
       </c>
       <c r="C10" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D10" s="12">
         <v>366</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F10" s="12"/>
     </row>
@@ -5372,13 +5378,13 @@
         <v>48944</v>
       </c>
       <c r="C11" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D11" s="12">
         <v>365</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F11" s="12"/>
     </row>
@@ -5390,13 +5396,13 @@
         <v>49309</v>
       </c>
       <c r="C12" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D12" s="12">
         <v>365</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F12" s="12"/>
     </row>
@@ -5408,13 +5414,13 @@
         <v>49674</v>
       </c>
       <c r="C13" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D13" s="12">
         <v>365</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F13" s="12"/>
     </row>
@@ -5426,13 +5432,13 @@
         <v>50040</v>
       </c>
       <c r="C14" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D14" s="12">
         <v>366</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F14" s="12"/>
     </row>
@@ -5444,13 +5450,13 @@
         <v>50405</v>
       </c>
       <c r="C15" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D15" s="12">
         <v>365</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F15" s="12"/>
     </row>
@@ -5462,13 +5468,13 @@
         <v>50770</v>
       </c>
       <c r="C16" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D16" s="12">
         <v>365</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F16" s="12"/>
     </row>
@@ -5480,13 +5486,13 @@
         <v>51135</v>
       </c>
       <c r="C17" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D17" s="12">
         <v>365</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F17" s="12"/>
     </row>
@@ -5498,13 +5504,13 @@
         <v>51501</v>
       </c>
       <c r="C18" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D18" s="12">
         <v>366</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F18" s="12"/>
     </row>
@@ -5516,13 +5522,13 @@
         <v>51866</v>
       </c>
       <c r="C19" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D19" s="12">
         <v>365</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F19" s="12"/>
     </row>
@@ -5534,13 +5540,13 @@
         <v>52231</v>
       </c>
       <c r="C20" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D20" s="12">
         <v>365</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F20" s="12"/>
     </row>
@@ -5552,13 +5558,13 @@
         <v>52596</v>
       </c>
       <c r="C21" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D21" s="12">
         <v>365</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F21" s="12"/>
     </row>
@@ -5570,13 +5576,13 @@
         <v>52962</v>
       </c>
       <c r="C22" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D22" s="12">
         <v>366</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F22" s="12"/>
     </row>
@@ -5588,13 +5594,13 @@
         <v>53327</v>
       </c>
       <c r="C23" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D23" s="12">
         <v>365</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F23" s="12"/>
     </row>
@@ -5606,13 +5612,13 @@
         <v>53692</v>
       </c>
       <c r="C24" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D24" s="12">
         <v>365</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F24" s="12"/>
     </row>
@@ -5624,13 +5630,13 @@
         <v>54057</v>
       </c>
       <c r="C25" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D25" s="12">
         <v>365</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F25" s="12"/>
     </row>
@@ -5642,13 +5648,13 @@
         <v>54423</v>
       </c>
       <c r="C26" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D26" s="12">
         <v>366</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F26" s="12"/>
     </row>
@@ -5660,13 +5666,13 @@
         <v>54788</v>
       </c>
       <c r="C27" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D27" s="12">
         <v>365</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F27" s="12"/>
     </row>
@@ -5678,13 +5684,13 @@
         <v>55153</v>
       </c>
       <c r="C28" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D28" s="12">
         <v>365</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F28" s="12"/>
     </row>
@@ -5696,13 +5702,13 @@
         <v>55518</v>
       </c>
       <c r="C29" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D29" s="12">
         <v>365</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F29" s="12"/>
     </row>
@@ -5714,13 +5720,13 @@
         <v>55884</v>
       </c>
       <c r="C30" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D30" s="12">
         <v>366</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F30" s="12"/>
     </row>
@@ -5732,13 +5738,13 @@
         <v>56249</v>
       </c>
       <c r="C31" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D31" s="12">
         <v>365</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F31" s="12"/>
     </row>
@@ -5750,13 +5756,13 @@
         <v>56614</v>
       </c>
       <c r="C32" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D32" s="12">
         <v>365</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F32" s="12"/>
     </row>
@@ -5768,13 +5774,13 @@
         <v>56979</v>
       </c>
       <c r="C33" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D33" s="12">
         <v>365</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F33" s="12"/>
     </row>
@@ -5786,13 +5792,13 @@
         <v>57345</v>
       </c>
       <c r="C34" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D34" s="12">
         <v>366</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F34" s="12"/>
     </row>
@@ -5804,13 +5810,13 @@
         <v>57710</v>
       </c>
       <c r="C35" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D35" s="12">
         <v>365</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F35" s="12"/>
     </row>
@@ -5822,13 +5828,13 @@
         <v>58075</v>
       </c>
       <c r="C36" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D36" s="12">
         <v>365</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F36" s="12"/>
     </row>
@@ -5840,13 +5846,13 @@
         <v>58440</v>
       </c>
       <c r="C37" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D37" s="12">
         <v>365</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F37" s="12"/>
     </row>
@@ -5858,13 +5864,13 @@
         <v>58806</v>
       </c>
       <c r="C38" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D38" s="12">
         <v>366</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F38" s="12"/>
     </row>
@@ -5876,13 +5882,13 @@
         <v>59171</v>
       </c>
       <c r="C39" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D39" s="12">
         <v>365</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F39" s="12"/>
     </row>
@@ -5894,13 +5900,13 @@
         <v>59536</v>
       </c>
       <c r="C40" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D40" s="12">
         <v>365</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F40" s="12"/>
     </row>
@@ -5912,13 +5918,13 @@
         <v>59901</v>
       </c>
       <c r="C41" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D41" s="12">
         <v>365</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F41" s="12"/>
     </row>
@@ -5930,13 +5936,13 @@
         <v>60267</v>
       </c>
       <c r="C42" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D42" s="12">
         <v>366</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F42" s="12"/>
     </row>
@@ -5948,13 +5954,13 @@
         <v>60632</v>
       </c>
       <c r="C43" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D43" s="12">
         <v>365</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F43" s="12"/>
     </row>
@@ -5966,13 +5972,13 @@
         <v>60997</v>
       </c>
       <c r="C44" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D44" s="12">
         <v>365</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F44" s="12"/>
     </row>
@@ -5984,13 +5990,13 @@
         <v>61362</v>
       </c>
       <c r="C45" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D45" s="12">
         <v>365</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F45" s="12"/>
     </row>
@@ -6002,13 +6008,13 @@
         <v>61728</v>
       </c>
       <c r="C46" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D46" s="12">
         <v>366</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F46" s="12"/>
     </row>
@@ -6020,13 +6026,13 @@
         <v>62093</v>
       </c>
       <c r="C47" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D47" s="12">
         <v>365</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F47" s="12"/>
     </row>
@@ -6038,13 +6044,13 @@
         <v>62458</v>
       </c>
       <c r="C48" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D48" s="12">
         <v>365</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F48" s="12"/>
     </row>
@@ -6056,13 +6062,13 @@
         <v>62823</v>
       </c>
       <c r="C49" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D49" s="12">
         <v>365</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F49" s="12"/>
     </row>
@@ -6074,13 +6080,13 @@
         <v>63189</v>
       </c>
       <c r="C50" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D50" s="12">
         <v>366</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F50" s="12"/>
     </row>
@@ -6092,13 +6098,13 @@
         <v>63554</v>
       </c>
       <c r="C51" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D51" s="12">
         <v>365</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F51" s="12"/>
     </row>
@@ -6110,13 +6116,13 @@
         <v>63919</v>
       </c>
       <c r="C52" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D52" s="12">
         <v>365</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F52" s="12"/>
     </row>
@@ -6128,13 +6134,13 @@
         <v>64284</v>
       </c>
       <c r="C53" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D53" s="12">
         <v>365</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F53" s="12"/>
     </row>
@@ -6146,13 +6152,13 @@
         <v>64650</v>
       </c>
       <c r="C54" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D54" s="12">
         <v>366</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F54" s="12"/>
     </row>
@@ -6164,13 +6170,13 @@
         <v>65015</v>
       </c>
       <c r="C55" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D55" s="12">
         <v>365</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F55" s="12"/>
     </row>
@@ -6182,13 +6188,13 @@
         <v>65380</v>
       </c>
       <c r="C56" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D56" s="12">
         <v>365</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F56" s="12"/>
     </row>
@@ -6200,13 +6206,13 @@
         <v>65745</v>
       </c>
       <c r="C57" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D57" s="12">
         <v>365</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F57" s="12"/>
     </row>
@@ -6218,13 +6224,13 @@
         <v>66111</v>
       </c>
       <c r="C58" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D58" s="12">
         <v>366</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F58" s="12"/>
     </row>
@@ -6236,13 +6242,13 @@
         <v>66476</v>
       </c>
       <c r="C59" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D59" s="12">
         <v>365</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F59" s="12"/>
     </row>
@@ -6254,13 +6260,13 @@
         <v>66841</v>
       </c>
       <c r="C60" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D60" s="12">
         <v>365</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F60" s="12"/>
     </row>
@@ -6272,13 +6278,13 @@
         <v>67206</v>
       </c>
       <c r="C61" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D61" s="12">
         <v>365</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F61" s="12"/>
     </row>
@@ -6290,13 +6296,13 @@
         <v>67572</v>
       </c>
       <c r="C62" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D62" s="12">
         <v>366</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F62" s="12"/>
     </row>
@@ -6308,13 +6314,13 @@
         <v>67937</v>
       </c>
       <c r="C63" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D63" s="12">
         <v>365</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F63" s="12"/>
     </row>
@@ -6326,13 +6332,13 @@
         <v>68302</v>
       </c>
       <c r="C64" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D64" s="12">
         <v>365</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F64" s="12"/>
     </row>
@@ -6344,13 +6350,13 @@
         <v>68667</v>
       </c>
       <c r="C65" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D65" s="12">
         <v>365</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F65" s="12"/>
     </row>
@@ -6362,13 +6368,13 @@
         <v>69033</v>
       </c>
       <c r="C66" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D66" s="12">
         <v>366</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F66" s="12"/>
     </row>
@@ -6380,13 +6386,13 @@
         <v>69398</v>
       </c>
       <c r="C67" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D67" s="12">
         <v>365</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F67" s="12"/>
     </row>
@@ -6398,13 +6404,13 @@
         <v>69763</v>
       </c>
       <c r="C68" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D68" s="12">
         <v>365</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F68" s="12"/>
     </row>
@@ -6416,13 +6422,13 @@
         <v>70128</v>
       </c>
       <c r="C69" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D69" s="12">
         <v>365</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F69" s="12"/>
     </row>
@@ -6434,13 +6440,13 @@
         <v>70494</v>
       </c>
       <c r="C70" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D70" s="12">
         <v>366</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F70" s="12"/>
     </row>
@@ -6452,13 +6458,13 @@
         <v>70859</v>
       </c>
       <c r="C71" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D71" s="12">
         <v>365</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F71" s="12"/>
     </row>
@@ -6470,13 +6476,13 @@
         <v>71224</v>
       </c>
       <c r="C72" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D72" s="12">
         <v>365</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F72" s="12"/>
     </row>
@@ -6488,13 +6494,13 @@
         <v>71589</v>
       </c>
       <c r="C73" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D73" s="12">
         <v>365</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F73" s="12"/>
     </row>
@@ -6506,13 +6512,13 @@
         <v>71955</v>
       </c>
       <c r="C74" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D74" s="12">
         <v>366</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F74" s="12"/>
     </row>
@@ -6524,13 +6530,13 @@
         <v>72320</v>
       </c>
       <c r="C75" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D75" s="12">
         <v>365</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F75" s="12"/>
     </row>
@@ -6542,13 +6548,13 @@
         <v>72685</v>
       </c>
       <c r="C76" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D76" s="12">
         <v>365</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F76" s="12"/>
     </row>
@@ -6560,13 +6566,13 @@
         <v>73050</v>
       </c>
       <c r="C77" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D77" s="12">
         <v>365</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F77" s="12"/>
     </row>
@@ -6578,13 +6584,13 @@
         <v>73415</v>
       </c>
       <c r="C78" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D78" s="12">
         <v>365</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F78" s="12"/>
     </row>
@@ -6596,13 +6602,13 @@
         <v>73780</v>
       </c>
       <c r="C79" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D79" s="12">
         <v>365</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F79" s="12"/>
     </row>
@@ -6614,13 +6620,13 @@
         <v>74145</v>
       </c>
       <c r="C80" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D80" s="12">
         <v>365</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F80" s="12"/>
     </row>
@@ -6632,13 +6638,13 @@
         <v>74510</v>
       </c>
       <c r="C81" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D81" s="12">
         <v>365</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F81" s="12"/>
     </row>
@@ -6650,13 +6656,13 @@
         <v>74876</v>
       </c>
       <c r="C82" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D82" s="12">
         <v>366</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F82" s="12"/>
     </row>
@@ -6668,13 +6674,13 @@
         <v>75241</v>
       </c>
       <c r="C83" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D83" s="12">
         <v>365</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F83" s="12"/>
     </row>
@@ -6686,13 +6692,13 @@
         <v>75606</v>
       </c>
       <c r="C84" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D84" s="12">
         <v>365</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F84" s="12"/>
     </row>
@@ -6704,13 +6710,13 @@
         <v>75971</v>
       </c>
       <c r="C85" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D85" s="12">
         <v>365</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F85" s="12"/>
     </row>
@@ -6722,13 +6728,13 @@
         <v>76337</v>
       </c>
       <c r="C86" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D86" s="12">
         <v>366</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F86" s="12"/>
     </row>
@@ -6740,13 +6746,13 @@
         <v>76702</v>
       </c>
       <c r="C87" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D87" s="12">
         <v>365</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F87" s="12"/>
     </row>
@@ -6758,13 +6764,13 @@
         <v>77067</v>
       </c>
       <c r="C88" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D88" s="12">
         <v>365</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F88" s="12"/>
     </row>
@@ -6776,13 +6782,13 @@
         <v>77432</v>
       </c>
       <c r="C89" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D89" s="12">
         <v>365</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F89" s="12"/>
     </row>
@@ -6794,13 +6800,13 @@
         <v>77798</v>
       </c>
       <c r="C90" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D90" s="12">
         <v>366</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F90" s="12"/>
     </row>
@@ -6812,13 +6818,13 @@
         <v>78163</v>
       </c>
       <c r="C91" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D91" s="12">
         <v>365</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F91" s="12"/>
     </row>
@@ -6830,13 +6836,13 @@
         <v>78528</v>
       </c>
       <c r="C92" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D92" s="12">
         <v>365</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F92" s="12"/>
     </row>
@@ -6848,13 +6854,13 @@
         <v>78893</v>
       </c>
       <c r="C93" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D93" s="12">
         <v>365</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F93" s="12"/>
     </row>
@@ -6866,13 +6872,13 @@
         <v>79259</v>
       </c>
       <c r="C94" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D94" s="12">
         <v>366</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F94" s="12"/>
     </row>
@@ -6884,13 +6890,13 @@
         <v>79624</v>
       </c>
       <c r="C95" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D95" s="12">
         <v>365</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F95" s="12"/>
     </row>
@@ -6902,13 +6908,13 @@
         <v>79989</v>
       </c>
       <c r="C96" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D96" s="12">
         <v>365</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F96" s="12"/>
     </row>
@@ -6920,13 +6926,13 @@
         <v>80354</v>
       </c>
       <c r="C97" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D97" s="12">
         <v>365</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F97" s="12"/>
     </row>
@@ -6938,13 +6944,13 @@
         <v>80720</v>
       </c>
       <c r="C98" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D98" s="12">
         <v>366</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F98" s="12"/>
     </row>
@@ -6956,13 +6962,13 @@
         <v>81085</v>
       </c>
       <c r="C99" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D99" s="12">
         <v>365</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F99" s="12"/>
     </row>
@@ -6974,13 +6980,13 @@
         <v>81450</v>
       </c>
       <c r="C100" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D100" s="12">
         <v>365</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F100" s="12"/>
     </row>
@@ -6992,13 +6998,13 @@
         <v>81815</v>
       </c>
       <c r="C101" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D101" s="12">
         <v>365</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F101" s="12"/>
     </row>
@@ -7010,13 +7016,13 @@
         <v>82181</v>
       </c>
       <c r="C102" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D102" s="12">
         <v>366</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F102" s="12"/>
     </row>
@@ -7028,13 +7034,13 @@
         <v>82546</v>
       </c>
       <c r="C103" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D103" s="12">
         <v>365</v>
       </c>
       <c r="E103" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F103" s="12"/>
     </row>
@@ -7046,13 +7052,13 @@
         <v>82911</v>
       </c>
       <c r="C104" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D104" s="12">
         <v>365</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F104" s="12"/>
     </row>
@@ -7064,13 +7070,13 @@
         <v>83276</v>
       </c>
       <c r="C105" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D105" s="12">
         <v>365</v>
       </c>
       <c r="E105" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F105" s="12"/>
     </row>
@@ -7082,13 +7088,13 @@
         <v>83642</v>
       </c>
       <c r="C106" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D106" s="12">
         <v>366</v>
       </c>
       <c r="E106" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F106" s="12"/>
     </row>
@@ -7100,13 +7106,13 @@
         <v>84007</v>
       </c>
       <c r="C107" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D107" s="12">
         <v>365</v>
       </c>
       <c r="E107" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F107" s="12"/>
     </row>
@@ -7118,13 +7124,13 @@
         <v>84372</v>
       </c>
       <c r="C108" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D108" s="12">
         <v>365</v>
       </c>
       <c r="E108" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F108" s="12"/>
     </row>
@@ -7136,13 +7142,13 @@
         <v>84737</v>
       </c>
       <c r="C109" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D109" s="12">
         <v>365</v>
       </c>
       <c r="E109" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F109" s="12"/>
     </row>
@@ -7154,13 +7160,13 @@
         <v>85103</v>
       </c>
       <c r="C110" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D110" s="12">
         <v>366</v>
       </c>
       <c r="E110" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F110" s="12"/>
     </row>
@@ -7172,13 +7178,13 @@
         <v>85468</v>
       </c>
       <c r="C111" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D111" s="12">
         <v>365</v>
       </c>
       <c r="E111" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F111" s="12"/>
     </row>
@@ -7190,13 +7196,13 @@
         <v>85833</v>
       </c>
       <c r="C112" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D112" s="12">
         <v>365</v>
       </c>
       <c r="E112" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F112" s="12"/>
     </row>
@@ -7208,13 +7214,13 @@
         <v>86198</v>
       </c>
       <c r="C113" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D113" s="12">
         <v>365</v>
       </c>
       <c r="E113" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F113" s="12"/>
     </row>
@@ -7226,13 +7232,13 @@
         <v>86564</v>
       </c>
       <c r="C114" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D114" s="12">
         <v>366</v>
       </c>
       <c r="E114" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F114" s="12"/>
     </row>
@@ -7244,13 +7250,13 @@
         <v>86929</v>
       </c>
       <c r="C115" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D115" s="12">
         <v>365</v>
       </c>
       <c r="E115" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F115" s="12"/>
     </row>
@@ -7262,13 +7268,13 @@
         <v>87294</v>
       </c>
       <c r="C116" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D116" s="12">
         <v>365</v>
       </c>
       <c r="E116" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F116" s="12"/>
     </row>
@@ -7280,13 +7286,13 @@
         <v>87659</v>
       </c>
       <c r="C117" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D117" s="12">
         <v>365</v>
       </c>
       <c r="E117" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F117" s="12"/>
     </row>
@@ -7298,13 +7304,13 @@
         <v>88025</v>
       </c>
       <c r="C118" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D118" s="12">
         <v>366</v>
       </c>
       <c r="E118" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F118" s="12"/>
     </row>
@@ -7316,13 +7322,13 @@
         <v>88390</v>
       </c>
       <c r="C119" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D119" s="12">
         <v>365</v>
       </c>
       <c r="E119" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F119" s="12"/>
     </row>
@@ -7334,13 +7340,13 @@
         <v>88755</v>
       </c>
       <c r="C120" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D120" s="12">
         <v>365</v>
       </c>
       <c r="E120" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F120" s="12"/>
     </row>
@@ -7352,13 +7358,13 @@
         <v>89120</v>
       </c>
       <c r="C121" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D121" s="12">
         <v>365</v>
       </c>
       <c r="E121" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F121" s="12"/>
     </row>
@@ -7370,13 +7376,13 @@
         <v>89486</v>
       </c>
       <c r="C122" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D122" s="12">
         <v>366</v>
       </c>
       <c r="E122" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F122" s="12"/>
     </row>
@@ -7388,13 +7394,13 @@
         <v>89851</v>
       </c>
       <c r="C123" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D123" s="12">
         <v>365</v>
       </c>
       <c r="E123" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F123" s="12"/>
     </row>
@@ -7406,13 +7412,13 @@
         <v>90216</v>
       </c>
       <c r="C124" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D124" s="12">
         <v>365</v>
       </c>
       <c r="E124" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F124" s="12"/>
     </row>
@@ -7424,13 +7430,13 @@
         <v>90581</v>
       </c>
       <c r="C125" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D125" s="12">
         <v>365</v>
       </c>
       <c r="E125" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F125" s="12"/>
     </row>
@@ -7442,13 +7448,13 @@
         <v>90947</v>
       </c>
       <c r="C126" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D126" s="12">
         <v>366</v>
       </c>
       <c r="E126" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F126" s="12"/>
     </row>
@@ -7460,13 +7466,13 @@
         <v>91312</v>
       </c>
       <c r="C127" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D127" s="12">
         <v>365</v>
       </c>
       <c r="E127" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F127" s="12"/>
     </row>
@@ -7478,13 +7484,13 @@
         <v>91677</v>
       </c>
       <c r="C128" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D128" s="12">
         <v>365</v>
       </c>
       <c r="E128" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F128" s="12"/>
     </row>
@@ -7496,13 +7502,13 @@
         <v>92042</v>
       </c>
       <c r="C129" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D129" s="12">
         <v>365</v>
       </c>
       <c r="E129" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F129" s="12"/>
     </row>
@@ -7514,13 +7520,13 @@
         <v>92408</v>
       </c>
       <c r="C130" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D130" s="12">
         <v>366</v>
       </c>
       <c r="E130" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F130" s="12"/>
     </row>
@@ -7532,13 +7538,13 @@
         <v>92773</v>
       </c>
       <c r="C131" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D131" s="12">
         <v>365</v>
       </c>
       <c r="E131" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F131" s="12"/>
     </row>
@@ -7550,13 +7556,13 @@
         <v>93138</v>
       </c>
       <c r="C132" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D132" s="12">
         <v>365</v>
       </c>
       <c r="E132" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F132" s="12"/>
     </row>
@@ -7568,13 +7574,13 @@
         <v>93503</v>
       </c>
       <c r="C133" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D133" s="12">
         <v>365</v>
       </c>
       <c r="E133" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F133" s="12"/>
     </row>
@@ -7586,13 +7592,13 @@
         <v>93869</v>
       </c>
       <c r="C134" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D134" s="12">
         <v>366</v>
       </c>
       <c r="E134" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F134" s="12"/>
     </row>
@@ -7604,13 +7610,13 @@
         <v>94234</v>
       </c>
       <c r="C135" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D135" s="12">
         <v>365</v>
       </c>
       <c r="E135" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F135" s="12"/>
     </row>
@@ -7622,13 +7628,13 @@
         <v>94599</v>
       </c>
       <c r="C136" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D136" s="12">
         <v>365</v>
       </c>
       <c r="E136" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F136" s="12"/>
     </row>
@@ -7640,13 +7646,13 @@
         <v>94964</v>
       </c>
       <c r="C137" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D137" s="12">
         <v>365</v>
       </c>
       <c r="E137" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F137" s="12"/>
     </row>
@@ -7658,13 +7664,13 @@
         <v>95330</v>
       </c>
       <c r="C138" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D138" s="12">
         <v>366</v>
       </c>
       <c r="E138" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F138" s="12"/>
     </row>
@@ -7676,13 +7682,13 @@
         <v>95695</v>
       </c>
       <c r="C139" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D139" s="12">
         <v>365</v>
       </c>
       <c r="E139" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F139" s="12"/>
     </row>
@@ -7694,13 +7700,13 @@
         <v>96060</v>
       </c>
       <c r="C140" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D140" s="12">
         <v>365</v>
       </c>
       <c r="E140" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F140" s="12"/>
     </row>
@@ -7712,13 +7718,13 @@
         <v>96425</v>
       </c>
       <c r="C141" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D141" s="12">
         <v>365</v>
       </c>
       <c r="E141" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F141" s="12"/>
     </row>
@@ -7730,13 +7736,13 @@
         <v>96791</v>
       </c>
       <c r="C142" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D142" s="12">
         <v>366</v>
       </c>
       <c r="E142" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F142" s="12"/>
     </row>
@@ -7748,13 +7754,13 @@
         <v>97156</v>
       </c>
       <c r="C143" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D143" s="12">
         <v>365</v>
       </c>
       <c r="E143" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F143" s="12"/>
     </row>
@@ -7766,13 +7772,13 @@
         <v>97521</v>
       </c>
       <c r="C144" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D144" s="12">
         <v>365</v>
       </c>
       <c r="E144" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F144" s="12"/>
     </row>
@@ -7784,13 +7790,13 @@
         <v>97886</v>
       </c>
       <c r="C145" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D145" s="12">
         <v>365</v>
       </c>
       <c r="E145" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F145" s="12"/>
     </row>
@@ -7802,13 +7808,13 @@
         <v>98252</v>
       </c>
       <c r="C146" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D146" s="12">
         <v>366</v>
       </c>
       <c r="E146" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F146" s="12"/>
     </row>
@@ -7820,13 +7826,13 @@
         <v>98617</v>
       </c>
       <c r="C147" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D147" s="12">
         <v>365</v>
       </c>
       <c r="E147" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F147" s="12"/>
     </row>
@@ -7838,13 +7844,13 @@
         <v>98982</v>
       </c>
       <c r="C148" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D148" s="12">
         <v>365</v>
       </c>
       <c r="E148" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F148" s="12"/>
     </row>
@@ -7856,13 +7862,13 @@
         <v>99347</v>
       </c>
       <c r="C149" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D149" s="12">
         <v>365</v>
       </c>
       <c r="E149" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F149" s="12"/>
     </row>
@@ -7874,13 +7880,13 @@
         <v>99713</v>
       </c>
       <c r="C150" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D150" s="12">
         <v>366</v>
       </c>
       <c r="E150" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F150" s="12"/>
     </row>
@@ -7892,13 +7898,13 @@
         <v>100078</v>
       </c>
       <c r="C151" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D151" s="12">
         <v>365</v>
       </c>
       <c r="E151" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F151" s="12"/>
     </row>
@@ -7910,13 +7916,13 @@
         <v>100443</v>
       </c>
       <c r="C152" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D152" s="12">
         <v>365</v>
       </c>
       <c r="E152" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F152" s="12"/>
     </row>
@@ -7928,13 +7934,13 @@
         <v>100808</v>
       </c>
       <c r="C153" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D153" s="12">
         <v>365</v>
       </c>
       <c r="E153" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F153" s="12"/>
     </row>
@@ -7946,13 +7952,13 @@
         <v>101174</v>
       </c>
       <c r="C154" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D154" s="12">
         <v>366</v>
       </c>
       <c r="E154" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F154" s="12"/>
     </row>
@@ -7964,13 +7970,13 @@
         <v>101539</v>
       </c>
       <c r="C155" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D155" s="12">
         <v>365</v>
       </c>
       <c r="E155" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F155" s="12"/>
     </row>
@@ -7982,13 +7988,13 @@
         <v>101904</v>
       </c>
       <c r="C156" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D156" s="12">
         <v>365</v>
       </c>
       <c r="E156" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F156" s="12"/>
     </row>
@@ -8000,13 +8006,13 @@
         <v>102269</v>
       </c>
       <c r="C157" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D157" s="12">
         <v>365</v>
       </c>
       <c r="E157" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F157" s="12"/>
     </row>
@@ -8018,13 +8024,13 @@
         <v>102635</v>
       </c>
       <c r="C158" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D158" s="12">
         <v>366</v>
       </c>
       <c r="E158" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F158" s="12"/>
     </row>
@@ -8036,13 +8042,13 @@
         <v>103000</v>
       </c>
       <c r="C159" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D159" s="12">
         <v>365</v>
       </c>
       <c r="E159" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F159" s="12"/>
     </row>
@@ -8054,13 +8060,13 @@
         <v>103365</v>
       </c>
       <c r="C160" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D160" s="12">
         <v>365</v>
       </c>
       <c r="E160" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F160" s="12"/>
     </row>
@@ -8072,13 +8078,13 @@
         <v>103730</v>
       </c>
       <c r="C161" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D161" s="12">
         <v>365</v>
       </c>
       <c r="E161" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F161" s="12"/>
     </row>
@@ -8090,13 +8096,13 @@
         <v>104096</v>
       </c>
       <c r="C162" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D162" s="12">
         <v>366</v>
       </c>
       <c r="E162" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F162" s="12"/>
     </row>
@@ -8108,13 +8114,13 @@
         <v>104461</v>
       </c>
       <c r="C163" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D163" s="12">
         <v>365</v>
       </c>
       <c r="E163" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F163" s="12"/>
     </row>
@@ -8126,13 +8132,13 @@
         <v>104826</v>
       </c>
       <c r="C164" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D164" s="12">
         <v>365</v>
       </c>
       <c r="E164" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F164" s="12"/>
     </row>
@@ -8144,13 +8150,13 @@
         <v>105191</v>
       </c>
       <c r="C165" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D165" s="12">
         <v>365</v>
       </c>
       <c r="E165" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F165" s="12"/>
     </row>
@@ -8162,13 +8168,13 @@
         <v>105557</v>
       </c>
       <c r="C166" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D166" s="12">
         <v>366</v>
       </c>
       <c r="E166" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F166" s="12"/>
     </row>
@@ -8180,13 +8186,13 @@
         <v>105922</v>
       </c>
       <c r="C167" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D167" s="12">
         <v>365</v>
       </c>
       <c r="E167" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F167" s="12"/>
     </row>
@@ -8198,13 +8204,13 @@
         <v>106287</v>
       </c>
       <c r="C168" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D168" s="12">
         <v>365</v>
       </c>
       <c r="E168" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F168" s="12"/>
     </row>
@@ -8216,13 +8222,13 @@
         <v>106652</v>
       </c>
       <c r="C169" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D169" s="12">
         <v>365</v>
       </c>
       <c r="E169" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F169" s="12"/>
     </row>
@@ -8234,13 +8240,13 @@
         <v>107018</v>
       </c>
       <c r="C170" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D170" s="12">
         <v>366</v>
       </c>
       <c r="E170" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F170" s="12"/>
     </row>
@@ -8252,13 +8258,13 @@
         <v>107383</v>
       </c>
       <c r="C171" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D171" s="12">
         <v>365</v>
       </c>
       <c r="E171" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F171" s="12"/>
     </row>
@@ -8270,13 +8276,13 @@
         <v>107748</v>
       </c>
       <c r="C172" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D172" s="12">
         <v>365</v>
       </c>
       <c r="E172" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F172" s="12"/>
     </row>
@@ -8288,13 +8294,13 @@
         <v>108113</v>
       </c>
       <c r="C173" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D173" s="12">
         <v>365</v>
       </c>
       <c r="E173" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F173" s="12"/>
     </row>
@@ -8306,13 +8312,13 @@
         <v>108479</v>
       </c>
       <c r="C174" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D174" s="12">
         <v>366</v>
       </c>
       <c r="E174" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F174" s="12"/>
     </row>
@@ -8324,13 +8330,13 @@
         <v>108844</v>
       </c>
       <c r="C175" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D175" s="12">
         <v>365</v>
       </c>
       <c r="E175" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F175" s="12"/>
     </row>
@@ -8342,13 +8348,13 @@
         <v>109209</v>
       </c>
       <c r="C176" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D176" s="12">
         <v>365</v>
       </c>
       <c r="E176" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F176" s="12"/>
     </row>
@@ -8360,13 +8366,13 @@
         <v>109574</v>
       </c>
       <c r="C177" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D177" s="12">
         <v>365</v>
       </c>
       <c r="E177" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F177" s="12"/>
     </row>
@@ -8378,19 +8384,19 @@
         <v>109939</v>
       </c>
       <c r="C178" s="12">
-        <v>11.43</v>
+        <v>11.51</v>
       </c>
       <c r="D178" s="12">
         <v>365</v>
       </c>
       <c r="E178" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F178" s="12"/>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -8412,19 +8418,19 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B1" s="5"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B2" s="13">
         <v>46244</v>
       </c>
       <c r="C2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D2" s="9">
         <f>IF(Summary!$B$2="","",IF(ISNUMBER(Summary!$B$2),INT(Summary!$B$2),Summary!$B$2))</f>
@@ -8433,11 +8439,11 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D3" s="9" t="str">
         <f>IF(Summary!$B$3="","",IF(ISNUMBER(Summary!$B$3),INT(Summary!$B$3),Summary!$B$3))</f>
@@ -8446,23 +8452,23 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>186</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B6" s="13">
         <v>46630</v>
@@ -8470,16 +8476,16 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B7" s="9">
         <f>_xlfn.MAXIFS(tblGic[to],tblGic[basis],"known")</f>
-        <v>46295</v>
+        <v>46387</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B9" s="5"/>
     </row>
@@ -8539,7 +8545,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B16" s="10">
         <f>SUM(tblLines[Exposed])</f>
@@ -8548,7 +8554,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B17" s="11">
         <f>ROUND(SUM(tblLines[Shortfall_r]),2)</f>
@@ -8557,7 +8563,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B18" s="11">
         <f>ROUND(SUM(tblLines[NEC_r]),2)</f>
@@ -8566,7 +8572,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B19" s="11">
         <f>ROUND(SUM(tblLines[SGC_low]),2)</f>
@@ -8575,7 +8581,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B20" s="11">
         <f>ROUND(SUM(tblLines[SGC_high]),2)</f>
@@ -8584,7 +8590,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B21" s="10">
         <f>SUMPRODUCT(--(tblLines[Unassessable_between]&lt;&gt;""))</f>
@@ -8593,7 +8599,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B22" s="10" t="str">
         <f>IF(AND(SUM(tblLines[Assessable])&gt;0,SUMPRODUCT(tblLines[Assessable]*tblLines[Receipt_established])=0),"YES","NO")</f>
@@ -8650,21 +8656,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B2" s="10" t="str">
         <f>IF(C2=0,"PASS","BLOCKED")</f>
@@ -8681,7 +8687,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B3" s="10" t="str">
         <f>IF(C3=0,"PASS","BLOCKED")</f>
@@ -8698,7 +8704,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B4" s="10" t="str">
         <f>IF(OR(C4=0,Summary!$B$4="Y"),"PASS","BLOCKED")</f>
@@ -8715,7 +8721,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B5" s="10" t="str">
         <f>IF(C5=0,"PASS","REVIEW")</f>
@@ -8732,7 +8738,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B6" s="10" t="str">
         <f>IF(C6=0,"PASS","REVIEW")</f>
@@ -8749,7 +8755,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B7" s="10" t="str">
         <f>IF(OR(Summary!B22="NO",Summary!$B$5="Y"),"PASS","REVIEW")</f>
@@ -8763,7 +8769,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B8" s="10" t="str">
         <f>IF(C8=0,"PASS","NOTE")</f>
@@ -8780,7 +8786,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B9" s="10" t="str">
         <f>IF(C9=0,"PASS","NOTE")</f>
@@ -8797,7 +8803,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B10" s="10" t="str">
         <f>IF(C10=0,"PASS","NOTE")</f>
@@ -8814,7 +8820,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B11" s="10" t="str">
         <f>IF(C11=0,"PASS","NOTE")</f>
@@ -8831,7 +8837,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B12" s="10" t="str">
         <f>IF(AND(ISNUMBER(Summary!$D$2),Summary!$D$2&lt;=DATE(2200,12,31),OR(Summary!$D$3="",AND(ISNUMBER(Summary!$D$3),Summary!$D$3&lt;=DATE(2200,12,31))),AND(ISNUMBER(Summary!$B$6),Summary!$B$6&lt;=DATE(2200,12,31))),"PASS","BLOCKED")</f>
@@ -8845,7 +8851,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B13" s="10" t="str">
         <f>IF(C13=0,"PASS","REVIEW")</f>
@@ -8862,7 +8868,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B14" s="10" t="str">
         <f>IF(C14=0,"PASS","NOTE")</f>
@@ -8888,37 +8894,37 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -8949,74 +8955,74 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
+++ b/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A9EF8C-9F6F-4941-9B04-905DEBCA7433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A536C282-8A1C-4BDF-A579-1D15B0F5B64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="38700" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
     <t>Overall status</t>
   </si>
   <si>
-    <t>payday-super-checker workbook, engine 0.1.4. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
+    <t>payday-super-checker workbook, engine 0.1.5. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
   </si>
   <si>
     <t>employee_id</t>
@@ -715,7 +715,7 @@
     <t>Workbook engine version</t>
   </si>
   <si>
-    <t>0.1.4</t>
+    <t>0.1.5</t>
   </si>
   <si>
     <t>Desktop Excel build used to calculate cached values</t>

--- a/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
+++ b/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A536C282-8A1C-4BDF-A579-1D15B0F5B64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3517BF56-22D7-44B5-98FA-9DA821F84366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="1560" windowWidth="38700" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
     <t>Overall status</t>
   </si>
   <si>
-    <t>payday-super-checker workbook, engine 0.1.5. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
+    <t>payday-super-checker workbook, engine 0.1.6. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
   </si>
   <si>
     <t>employee_id</t>
@@ -715,7 +715,7 @@
     <t>Workbook engine version</t>
   </si>
   <si>
-    <t>0.1.5</t>
+    <t>0.1.6</t>
   </si>
   <si>
     <t>Desktop Excel build used to calculate cached values</t>

--- a/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
+++ b/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3517BF56-22D7-44B5-98FA-9DA821F84366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D2CF9A-EC2E-4C1D-AA9C-6FA89C09B4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="1560" windowWidth="38700" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="239">
   <si>
     <t>Payday Super review: s 18C deadlines and the SG charge estimate</t>
   </si>
@@ -220,12 +220,12 @@
     <t>Days_late</t>
   </si>
   <si>
+    <t>Past_gic_table</t>
+  </si>
+  <si>
     <t>NEC</t>
   </si>
   <si>
-    <t>GIC_estimated</t>
-  </si>
-  <si>
     <t>Shortfall_r</t>
   </si>
   <si>
@@ -574,10 +574,7 @@
     <t>2026-09-14</t>
   </si>
   <si>
-    <t>estimate</t>
-  </si>
-  <si>
-    <t>General interest charge, TAA 1953 s 8AAD: annual rate divided by the days in the calendar year. Rows marked estimate carry the last known rate forward, as the engine does, and the workbook flags any line that uses them. Update each quarter from the ATO GIC rates page and set basis to known.</t>
+    <t>General interest charge, TAA 1953 s 8AAD: annual rate divided by the days in the calendar year. Only the ATO's published quarters are listed. A line whose accrual runs past the last row keeps its verdict, days late and shortfall and shows no notional earnings or charge estimate, as the checker does without --allow-stale-gic; the workbook has no opt-in. Add each new quarter from the ATO GIC rates page.</t>
   </si>
   <si>
     <t>Inputs</t>
@@ -667,7 +664,7 @@
     <t>Deadlines inside the holiday coverage (figures past it are a maximum)</t>
   </si>
   <si>
-    <t>Notional earnings use only known GIC quarters</t>
+    <t>Accruals past the GIC table (charge estimate withheld until the rate is added)</t>
   </si>
   <si>
     <t>No identical lines (a doubled export counts a payday twice)</t>
@@ -694,7 +691,7 @@
     <t>Item 4 (s 18C(2)) aligns a later payday only to an earlier eligible contribution the register evidences as received on time; a positive amount or a remittance alone gives a possible upper bound and an attention-driving UNKNOWN where it would change the verdict.</t>
   </si>
   <si>
-    <t>Notional earnings compound daily at the general interest charge on the base shortfall from the day after the deadline while the final shortfall remains greater than nil (s 19A, LCR 2026/3). A part receipt does not slow the accrual.</t>
+    <t>Notional earnings compound daily at the general interest charge on the base shortfall from the day after the deadline while the final shortfall remains greater than nil (s 19A, LCR 2026/3). A part receipt does not slow the accrual. Past the last published GIC quarter the notional earnings and the charge estimate are withheld, as the command line withholds them without --allow-stale-gic.</t>
   </si>
   <si>
     <t>The uplift range runs from 0 per cent (clean history and a voluntary disclosure within 30 days) to 60 per cent (prior history, no disclosure). The ATO, not this workbook, decides which reductions apply.</t>
@@ -742,7 +739,7 @@
     <t>GIC rates</t>
   </si>
   <si>
-    <t>ATO general interest charge rates, known through 2026-12-31; later days carry the last known rate as an estimate</t>
+    <t>ATO general interest charge rates, known through 2026-12-31; an accrual past that day withholds the charge estimate</t>
   </si>
   <si>
     <t>No-install explainer</t>
@@ -1080,29 +1077,29 @@
     <tableColumn id="51" xr3:uid="{00000000-0010-0000-0000-000033000000}" name="Days_late">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" name="NEC">
-      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</calculatedColumnFormula>
+    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" name="Past_gic_table">
+      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" name="GIC_estimated">
-      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</calculatedColumnFormula>
+    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" name="NEC">
+      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0)),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" name="Shortfall_r">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" name="NEC_r">
-      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",ROUND(tblLines[[#This Row],[NEC]],2)),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" name="Uplift_best">
-      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",0),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="57" xr3:uid="{00000000-0010-0000-0000-000039000000}" name="Uplift_worst">
-      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2)),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="58" xr3:uid="{00000000-0010-0000-0000-00003A000000}" name="SGC_low">
-      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]]),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="59" xr3:uid="{00000000-0010-0000-0000-00003B000000}" name="SGC_high">
-      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]]),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="60" xr3:uid="{00000000-0010-0000-0000-00003C000000}" name="Transition_row">
       <calculatedColumnFormula>IF(AND(tblLines[[#This Row],[Flag_db]]&lt;&gt;1,ISNUMBER(tblLines[[#This Row],[sg_amount]]),ROUND(tblLines[[#This Row],[sg_amount]],2)&gt;0,ROUND(tblLines[[#This Row],[Cap]],2)&gt;0,OR(ISNUMBER(tblLines[[#This Row],[Recv_day]]),ISNUMBER(tblLines[[#This Row],[Remit_day]])),IF(ISNUMBER(tblLines[[#This Row],[Recv_day]]),tblLines[[#This Row],[Recv_day]],tblLines[[#This Row],[Remit_day]])&lt;=DATE(2026,7,28)),1,0)</calculatedColumnFormula>
@@ -1153,7 +1150,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tblGic" displayName="tblGic" ref="A1:F178">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tblGic" displayName="tblGic" ref="A1:F4">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="from"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="to"/>
@@ -1923,12 +1920,12 @@
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v/>
       </c>
-      <c r="AZ2" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
-        <v/>
-      </c>
-      <c r="BA2" s="10" t="str">
+      <c r="AZ2" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
+        <v/>
+      </c>
+      <c r="BA2" s="11" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0)),"")</f>
         <v/>
       </c>
       <c r="BB2" s="11" t="str">
@@ -1936,23 +1933,23 @@
         <v/>
       </c>
       <c r="BC2" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",ROUND(tblLines[[#This Row],[NEC]],2)),"")</f>
         <v/>
       </c>
       <c r="BD2" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",0),"")</f>
         <v/>
       </c>
       <c r="BE2" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2)),"")</f>
         <v/>
       </c>
       <c r="BF2" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]]),"")</f>
         <v/>
       </c>
       <c r="BG2" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]]),"")</f>
         <v/>
       </c>
       <c r="BH2" s="10">
@@ -2168,36 +2165,36 @@
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v>15</v>
       </c>
-      <c r="AZ3" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
+      <c r="AZ3" s="10">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="BA3" s="11">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0)),"")</f>
         <v>2.5420882921707211</v>
-      </c>
-      <c r="BA3" s="10">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
-        <v>0</v>
       </c>
       <c r="BB3" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</f>
         <v>0</v>
       </c>
       <c r="BC3" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",ROUND(tblLines[[#This Row],[NEC]],2)),"")</f>
         <v>2.54</v>
       </c>
       <c r="BD3" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",0),"")</f>
         <v>0</v>
       </c>
       <c r="BE3" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2)),"")</f>
         <v>1.53</v>
       </c>
       <c r="BF3" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]]),"")</f>
         <v>2.54</v>
       </c>
       <c r="BG3" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]]),"")</f>
         <v>4.07</v>
       </c>
       <c r="BH3" s="10">
@@ -2411,12 +2408,12 @@
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v/>
       </c>
-      <c r="AZ4" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
-        <v/>
-      </c>
-      <c r="BA4" s="10" t="str">
+      <c r="AZ4" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
+        <v/>
+      </c>
+      <c r="BA4" s="11" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0)),"")</f>
         <v/>
       </c>
       <c r="BB4" s="11" t="str">
@@ -2424,23 +2421,23 @@
         <v/>
       </c>
       <c r="BC4" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",ROUND(tblLines[[#This Row],[NEC]],2)),"")</f>
         <v/>
       </c>
       <c r="BD4" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",0),"")</f>
         <v/>
       </c>
       <c r="BE4" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2)),"")</f>
         <v/>
       </c>
       <c r="BF4" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]]),"")</f>
         <v/>
       </c>
       <c r="BG4" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]]),"")</f>
         <v/>
       </c>
       <c r="BH4" s="10">
@@ -2652,36 +2649,36 @@
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v>21</v>
       </c>
-      <c r="AZ5" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
+      <c r="AZ5" s="10">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="BA5" s="11">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0)),"")</f>
         <v>5.1455028981957529</v>
-      </c>
-      <c r="BA5" s="10">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
-        <v>0</v>
       </c>
       <c r="BB5" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</f>
         <v>780</v>
       </c>
       <c r="BC5" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",ROUND(tblLines[[#This Row],[NEC]],2)),"")</f>
         <v>5.15</v>
       </c>
       <c r="BD5" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",0),"")</f>
         <v>0</v>
       </c>
       <c r="BE5" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2)),"")</f>
         <v>471.09</v>
       </c>
       <c r="BF5" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]]),"")</f>
         <v>785.15</v>
       </c>
       <c r="BG5" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]]),"")</f>
         <v>1256.24</v>
       </c>
       <c r="BH5" s="10">
@@ -2897,12 +2894,12 @@
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v/>
       </c>
-      <c r="AZ6" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
-        <v/>
-      </c>
-      <c r="BA6" s="10" t="str">
+      <c r="AZ6" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
+        <v/>
+      </c>
+      <c r="BA6" s="11" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0)),"")</f>
         <v/>
       </c>
       <c r="BB6" s="11" t="str">
@@ -2910,23 +2907,23 @@
         <v/>
       </c>
       <c r="BC6" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",ROUND(tblLines[[#This Row],[NEC]],2)),"")</f>
         <v/>
       </c>
       <c r="BD6" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",0),"")</f>
         <v/>
       </c>
       <c r="BE6" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2)),"")</f>
         <v/>
       </c>
       <c r="BF6" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]]),"")</f>
         <v/>
       </c>
       <c r="BG6" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]]),"")</f>
         <v/>
       </c>
       <c r="BH6" s="10">
@@ -3144,12 +3141,12 @@
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v/>
       </c>
-      <c r="AZ7" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
-        <v/>
-      </c>
-      <c r="BA7" s="10" t="str">
+      <c r="AZ7" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
+        <v/>
+      </c>
+      <c r="BA7" s="11" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0)),"")</f>
         <v/>
       </c>
       <c r="BB7" s="11" t="str">
@@ -3157,23 +3154,23 @@
         <v/>
       </c>
       <c r="BC7" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",ROUND(tblLines[[#This Row],[NEC]],2)),"")</f>
         <v/>
       </c>
       <c r="BD7" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",0),"")</f>
         <v/>
       </c>
       <c r="BE7" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2)),"")</f>
         <v/>
       </c>
       <c r="BF7" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]]),"")</f>
         <v/>
       </c>
       <c r="BG7" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]]),"")</f>
         <v/>
       </c>
       <c r="BH7" s="10">
@@ -3389,12 +3386,12 @@
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v/>
       </c>
-      <c r="AZ8" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
-        <v/>
-      </c>
-      <c r="BA8" s="10" t="str">
+      <c r="AZ8" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
+        <v/>
+      </c>
+      <c r="BA8" s="11" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0)),"")</f>
         <v/>
       </c>
       <c r="BB8" s="11" t="str">
@@ -3402,23 +3399,23 @@
         <v/>
       </c>
       <c r="BC8" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",ROUND(tblLines[[#This Row],[NEC]],2)),"")</f>
         <v/>
       </c>
       <c r="BD8" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",0),"")</f>
         <v/>
       </c>
       <c r="BE8" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2)),"")</f>
         <v/>
       </c>
       <c r="BF8" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]]),"")</f>
         <v/>
       </c>
       <c r="BG8" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]]),"")</f>
         <v/>
       </c>
       <c r="BH8" s="10">
@@ -3634,36 +3631,36 @@
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v>2</v>
       </c>
-      <c r="AZ9" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
+      <c r="AZ9" s="10">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="BA9" s="11">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0)),"")</f>
         <v>0.38335645312715005</v>
-      </c>
-      <c r="BA9" s="10">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
-        <v>0</v>
       </c>
       <c r="BB9" s="11">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[Final_shortfall]],2),"")</f>
         <v>0</v>
       </c>
       <c r="BC9" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",ROUND(tblLines[[#This Row],[NEC]],2)),"")</f>
         <v>0.38</v>
       </c>
       <c r="BD9" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",0),"")</f>
         <v>0</v>
       </c>
       <c r="BE9" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2)),"")</f>
         <v>0.23</v>
       </c>
       <c r="BF9" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]]),"")</f>
         <v>0.38</v>
       </c>
       <c r="BG9" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]]),"")</f>
         <v>0.61</v>
       </c>
       <c r="BH9" s="10">
@@ -3879,12 +3876,12 @@
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v/>
       </c>
-      <c r="AZ10" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
-        <v/>
-      </c>
-      <c r="BA10" s="10" t="str">
+      <c r="AZ10" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
+        <v/>
+      </c>
+      <c r="BA10" s="11" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0)),"")</f>
         <v/>
       </c>
       <c r="BB10" s="11" t="str">
@@ -3892,23 +3889,23 @@
         <v/>
       </c>
       <c r="BC10" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",ROUND(tblLines[[#This Row],[NEC]],2)),"")</f>
         <v/>
       </c>
       <c r="BD10" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",0),"")</f>
         <v/>
       </c>
       <c r="BE10" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2)),"")</f>
         <v/>
       </c>
       <c r="BF10" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]]),"")</f>
         <v/>
       </c>
       <c r="BG10" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]]),"")</f>
         <v/>
       </c>
       <c r="BH10" s="10">
@@ -4124,12 +4121,12 @@
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_horizon]]=1,"",MAX(tblLines[[#This Row],[Outstanding_to]]-tblLines[[#This Row],[Final_due]],0)),"")</f>
         <v/>
       </c>
-      <c r="AZ11" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0),"")</f>
-        <v/>
-      </c>
-      <c r="BA11" s="10" t="str">
+      <c r="AZ11" s="10" t="str">
         <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[NEC_end]]&gt;Summary!$B$7,1,0),"")</f>
+        <v/>
+      </c>
+      <c r="BA11" s="11" t="str">
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",IF(tblLines[[#This Row],[NEC_end]]&gt;tblLines[[#This Row],[Final_due]],tblLines[[#This Row],[Base_shortfall]]*(EXP(SUMPRODUCT((((((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1)&gt;0)*(((tblLines[[#This Row],[NEC_end]]+tblGic[to]-ABS(tblLines[[#This Row],[NEC_end]]-tblGic[to]))/2)-(((tblLines[[#This Row],[Final_due]]+1)+tblGic[from]+ABS((tblLines[[#This Row],[Final_due]]+1)-tblGic[from]))/2)+1))*LN(1+tblGic[annual_pct]/100/tblGic[divisor])))-1),0)),"")</f>
         <v/>
       </c>
       <c r="BB11" s="11" t="str">
@@ -4137,23 +4134,23 @@
         <v/>
       </c>
       <c r="BC11" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(tblLines[[#This Row],[NEC]],2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",ROUND(tblLines[[#This Row],[NEC]],2)),"")</f>
         <v/>
       </c>
       <c r="BD11" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),0,"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",0),"")</f>
         <v/>
       </c>
       <c r="BE11" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",ROUND(0.6*(tblLines[[#This Row],[Final_shortfall]]+tblLines[[#This Row],[NEC]]),2)),"")</f>
         <v/>
       </c>
       <c r="BF11" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]],"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_best]]),"")</f>
         <v/>
       </c>
       <c r="BG11" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]],"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(tblLines[[#This Row],[Past_gic_table]]=1,"",tblLines[[#This Row],[Shortfall_r]]+tblLines[[#This Row],[NEC_r]]+tblLines[[#This Row],[Uplift_worst]]),"")</f>
         <v/>
       </c>
       <c r="BH11" s="10">
@@ -5175,7 +5172,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F181"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="14" customWidth="1"/>
@@ -5262,3141 +5259,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>46388</v>
-      </c>
-      <c r="B5" s="7">
-        <v>46752</v>
-      </c>
-      <c r="C5" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D5" s="12">
-        <v>365</v>
-      </c>
-      <c r="E5" s="12" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>178</v>
-      </c>
-      <c r="F5" s="12"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>46753</v>
-      </c>
-      <c r="B6" s="7">
-        <v>47118</v>
-      </c>
-      <c r="C6" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D6" s="12">
-        <v>366</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F6" s="12"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>47119</v>
-      </c>
-      <c r="B7" s="7">
-        <v>47483</v>
-      </c>
-      <c r="C7" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D7" s="12">
-        <v>365</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F7" s="12"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
-        <v>47484</v>
-      </c>
-      <c r="B8" s="7">
-        <v>47848</v>
-      </c>
-      <c r="C8" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D8" s="12">
-        <v>365</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F8" s="12"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
-        <v>47849</v>
-      </c>
-      <c r="B9" s="7">
-        <v>48213</v>
-      </c>
-      <c r="C9" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D9" s="12">
-        <v>365</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F9" s="12"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>48214</v>
-      </c>
-      <c r="B10" s="7">
-        <v>48579</v>
-      </c>
-      <c r="C10" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D10" s="12">
-        <v>366</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F10" s="12"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>48580</v>
-      </c>
-      <c r="B11" s="7">
-        <v>48944</v>
-      </c>
-      <c r="C11" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D11" s="12">
-        <v>365</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F11" s="12"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>48945</v>
-      </c>
-      <c r="B12" s="7">
-        <v>49309</v>
-      </c>
-      <c r="C12" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D12" s="12">
-        <v>365</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F12" s="12"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
-        <v>49310</v>
-      </c>
-      <c r="B13" s="7">
-        <v>49674</v>
-      </c>
-      <c r="C13" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D13" s="12">
-        <v>365</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F13" s="12"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
-        <v>49675</v>
-      </c>
-      <c r="B14" s="7">
-        <v>50040</v>
-      </c>
-      <c r="C14" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D14" s="12">
-        <v>366</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F14" s="12"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
-        <v>50041</v>
-      </c>
-      <c r="B15" s="7">
-        <v>50405</v>
-      </c>
-      <c r="C15" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D15" s="12">
-        <v>365</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F15" s="12"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
-        <v>50406</v>
-      </c>
-      <c r="B16" s="7">
-        <v>50770</v>
-      </c>
-      <c r="C16" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D16" s="12">
-        <v>365</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F16" s="12"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
-        <v>50771</v>
-      </c>
-      <c r="B17" s="7">
-        <v>51135</v>
-      </c>
-      <c r="C17" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D17" s="12">
-        <v>365</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F17" s="12"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
-        <v>51136</v>
-      </c>
-      <c r="B18" s="7">
-        <v>51501</v>
-      </c>
-      <c r="C18" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D18" s="12">
-        <v>366</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F18" s="12"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
-        <v>51502</v>
-      </c>
-      <c r="B19" s="7">
-        <v>51866</v>
-      </c>
-      <c r="C19" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D19" s="12">
-        <v>365</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F19" s="12"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
-        <v>51867</v>
-      </c>
-      <c r="B20" s="7">
-        <v>52231</v>
-      </c>
-      <c r="C20" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D20" s="12">
-        <v>365</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F20" s="12"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
-        <v>52232</v>
-      </c>
-      <c r="B21" s="7">
-        <v>52596</v>
-      </c>
-      <c r="C21" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D21" s="12">
-        <v>365</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F21" s="12"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
-        <v>52597</v>
-      </c>
-      <c r="B22" s="7">
-        <v>52962</v>
-      </c>
-      <c r="C22" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D22" s="12">
-        <v>366</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F22" s="12"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
-        <v>52963</v>
-      </c>
-      <c r="B23" s="7">
-        <v>53327</v>
-      </c>
-      <c r="C23" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D23" s="12">
-        <v>365</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F23" s="12"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
-        <v>53328</v>
-      </c>
-      <c r="B24" s="7">
-        <v>53692</v>
-      </c>
-      <c r="C24" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D24" s="12">
-        <v>365</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F24" s="12"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
-        <v>53693</v>
-      </c>
-      <c r="B25" s="7">
-        <v>54057</v>
-      </c>
-      <c r="C25" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D25" s="12">
-        <v>365</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F25" s="12"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
-        <v>54058</v>
-      </c>
-      <c r="B26" s="7">
-        <v>54423</v>
-      </c>
-      <c r="C26" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D26" s="12">
-        <v>366</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F26" s="12"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
-        <v>54424</v>
-      </c>
-      <c r="B27" s="7">
-        <v>54788</v>
-      </c>
-      <c r="C27" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D27" s="12">
-        <v>365</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F27" s="12"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
-        <v>54789</v>
-      </c>
-      <c r="B28" s="7">
-        <v>55153</v>
-      </c>
-      <c r="C28" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D28" s="12">
-        <v>365</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F28" s="12"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
-        <v>55154</v>
-      </c>
-      <c r="B29" s="7">
-        <v>55518</v>
-      </c>
-      <c r="C29" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D29" s="12">
-        <v>365</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F29" s="12"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
-        <v>55519</v>
-      </c>
-      <c r="B30" s="7">
-        <v>55884</v>
-      </c>
-      <c r="C30" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D30" s="12">
-        <v>366</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F30" s="12"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="7">
-        <v>55885</v>
-      </c>
-      <c r="B31" s="7">
-        <v>56249</v>
-      </c>
-      <c r="C31" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D31" s="12">
-        <v>365</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F31" s="12"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="7">
-        <v>56250</v>
-      </c>
-      <c r="B32" s="7">
-        <v>56614</v>
-      </c>
-      <c r="C32" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D32" s="12">
-        <v>365</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F32" s="12"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="7">
-        <v>56615</v>
-      </c>
-      <c r="B33" s="7">
-        <v>56979</v>
-      </c>
-      <c r="C33" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D33" s="12">
-        <v>365</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F33" s="12"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="7">
-        <v>56980</v>
-      </c>
-      <c r="B34" s="7">
-        <v>57345</v>
-      </c>
-      <c r="C34" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D34" s="12">
-        <v>366</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F34" s="12"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="7">
-        <v>57346</v>
-      </c>
-      <c r="B35" s="7">
-        <v>57710</v>
-      </c>
-      <c r="C35" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D35" s="12">
-        <v>365</v>
-      </c>
-      <c r="E35" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F35" s="12"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="7">
-        <v>57711</v>
-      </c>
-      <c r="B36" s="7">
-        <v>58075</v>
-      </c>
-      <c r="C36" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D36" s="12">
-        <v>365</v>
-      </c>
-      <c r="E36" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F36" s="12"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="7">
-        <v>58076</v>
-      </c>
-      <c r="B37" s="7">
-        <v>58440</v>
-      </c>
-      <c r="C37" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D37" s="12">
-        <v>365</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F37" s="12"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="7">
-        <v>58441</v>
-      </c>
-      <c r="B38" s="7">
-        <v>58806</v>
-      </c>
-      <c r="C38" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D38" s="12">
-        <v>366</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F38" s="12"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="7">
-        <v>58807</v>
-      </c>
-      <c r="B39" s="7">
-        <v>59171</v>
-      </c>
-      <c r="C39" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D39" s="12">
-        <v>365</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F39" s="12"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="7">
-        <v>59172</v>
-      </c>
-      <c r="B40" s="7">
-        <v>59536</v>
-      </c>
-      <c r="C40" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D40" s="12">
-        <v>365</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F40" s="12"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="7">
-        <v>59537</v>
-      </c>
-      <c r="B41" s="7">
-        <v>59901</v>
-      </c>
-      <c r="C41" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D41" s="12">
-        <v>365</v>
-      </c>
-      <c r="E41" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F41" s="12"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="7">
-        <v>59902</v>
-      </c>
-      <c r="B42" s="7">
-        <v>60267</v>
-      </c>
-      <c r="C42" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D42" s="12">
-        <v>366</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F42" s="12"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="7">
-        <v>60268</v>
-      </c>
-      <c r="B43" s="7">
-        <v>60632</v>
-      </c>
-      <c r="C43" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D43" s="12">
-        <v>365</v>
-      </c>
-      <c r="E43" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F43" s="12"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="7">
-        <v>60633</v>
-      </c>
-      <c r="B44" s="7">
-        <v>60997</v>
-      </c>
-      <c r="C44" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D44" s="12">
-        <v>365</v>
-      </c>
-      <c r="E44" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F44" s="12"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="7">
-        <v>60998</v>
-      </c>
-      <c r="B45" s="7">
-        <v>61362</v>
-      </c>
-      <c r="C45" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D45" s="12">
-        <v>365</v>
-      </c>
-      <c r="E45" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F45" s="12"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="7">
-        <v>61363</v>
-      </c>
-      <c r="B46" s="7">
-        <v>61728</v>
-      </c>
-      <c r="C46" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D46" s="12">
-        <v>366</v>
-      </c>
-      <c r="E46" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F46" s="12"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="7">
-        <v>61729</v>
-      </c>
-      <c r="B47" s="7">
-        <v>62093</v>
-      </c>
-      <c r="C47" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D47" s="12">
-        <v>365</v>
-      </c>
-      <c r="E47" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F47" s="12"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="7">
-        <v>62094</v>
-      </c>
-      <c r="B48" s="7">
-        <v>62458</v>
-      </c>
-      <c r="C48" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D48" s="12">
-        <v>365</v>
-      </c>
-      <c r="E48" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F48" s="12"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="7">
-        <v>62459</v>
-      </c>
-      <c r="B49" s="7">
-        <v>62823</v>
-      </c>
-      <c r="C49" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D49" s="12">
-        <v>365</v>
-      </c>
-      <c r="E49" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F49" s="12"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="7">
-        <v>62824</v>
-      </c>
-      <c r="B50" s="7">
-        <v>63189</v>
-      </c>
-      <c r="C50" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D50" s="12">
-        <v>366</v>
-      </c>
-      <c r="E50" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F50" s="12"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="7">
-        <v>63190</v>
-      </c>
-      <c r="B51" s="7">
-        <v>63554</v>
-      </c>
-      <c r="C51" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D51" s="12">
-        <v>365</v>
-      </c>
-      <c r="E51" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F51" s="12"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="7">
-        <v>63555</v>
-      </c>
-      <c r="B52" s="7">
-        <v>63919</v>
-      </c>
-      <c r="C52" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D52" s="12">
-        <v>365</v>
-      </c>
-      <c r="E52" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F52" s="12"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="7">
-        <v>63920</v>
-      </c>
-      <c r="B53" s="7">
-        <v>64284</v>
-      </c>
-      <c r="C53" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D53" s="12">
-        <v>365</v>
-      </c>
-      <c r="E53" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F53" s="12"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="7">
-        <v>64285</v>
-      </c>
-      <c r="B54" s="7">
-        <v>64650</v>
-      </c>
-      <c r="C54" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D54" s="12">
-        <v>366</v>
-      </c>
-      <c r="E54" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F54" s="12"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="7">
-        <v>64651</v>
-      </c>
-      <c r="B55" s="7">
-        <v>65015</v>
-      </c>
-      <c r="C55" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D55" s="12">
-        <v>365</v>
-      </c>
-      <c r="E55" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F55" s="12"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="7">
-        <v>65016</v>
-      </c>
-      <c r="B56" s="7">
-        <v>65380</v>
-      </c>
-      <c r="C56" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D56" s="12">
-        <v>365</v>
-      </c>
-      <c r="E56" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F56" s="12"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="7">
-        <v>65381</v>
-      </c>
-      <c r="B57" s="7">
-        <v>65745</v>
-      </c>
-      <c r="C57" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D57" s="12">
-        <v>365</v>
-      </c>
-      <c r="E57" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F57" s="12"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="7">
-        <v>65746</v>
-      </c>
-      <c r="B58" s="7">
-        <v>66111</v>
-      </c>
-      <c r="C58" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D58" s="12">
-        <v>366</v>
-      </c>
-      <c r="E58" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F58" s="12"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="7">
-        <v>66112</v>
-      </c>
-      <c r="B59" s="7">
-        <v>66476</v>
-      </c>
-      <c r="C59" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D59" s="12">
-        <v>365</v>
-      </c>
-      <c r="E59" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F59" s="12"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="7">
-        <v>66477</v>
-      </c>
-      <c r="B60" s="7">
-        <v>66841</v>
-      </c>
-      <c r="C60" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D60" s="12">
-        <v>365</v>
-      </c>
-      <c r="E60" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F60" s="12"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="7">
-        <v>66842</v>
-      </c>
-      <c r="B61" s="7">
-        <v>67206</v>
-      </c>
-      <c r="C61" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D61" s="12">
-        <v>365</v>
-      </c>
-      <c r="E61" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F61" s="12"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="7">
-        <v>67207</v>
-      </c>
-      <c r="B62" s="7">
-        <v>67572</v>
-      </c>
-      <c r="C62" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D62" s="12">
-        <v>366</v>
-      </c>
-      <c r="E62" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F62" s="12"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="7">
-        <v>67573</v>
-      </c>
-      <c r="B63" s="7">
-        <v>67937</v>
-      </c>
-      <c r="C63" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D63" s="12">
-        <v>365</v>
-      </c>
-      <c r="E63" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F63" s="12"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="7">
-        <v>67938</v>
-      </c>
-      <c r="B64" s="7">
-        <v>68302</v>
-      </c>
-      <c r="C64" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D64" s="12">
-        <v>365</v>
-      </c>
-      <c r="E64" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F64" s="12"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="7">
-        <v>68303</v>
-      </c>
-      <c r="B65" s="7">
-        <v>68667</v>
-      </c>
-      <c r="C65" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D65" s="12">
-        <v>365</v>
-      </c>
-      <c r="E65" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F65" s="12"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="7">
-        <v>68668</v>
-      </c>
-      <c r="B66" s="7">
-        <v>69033</v>
-      </c>
-      <c r="C66" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D66" s="12">
-        <v>366</v>
-      </c>
-      <c r="E66" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F66" s="12"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="7">
-        <v>69034</v>
-      </c>
-      <c r="B67" s="7">
-        <v>69398</v>
-      </c>
-      <c r="C67" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D67" s="12">
-        <v>365</v>
-      </c>
-      <c r="E67" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F67" s="12"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="7">
-        <v>69399</v>
-      </c>
-      <c r="B68" s="7">
-        <v>69763</v>
-      </c>
-      <c r="C68" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D68" s="12">
-        <v>365</v>
-      </c>
-      <c r="E68" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F68" s="12"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="7">
-        <v>69764</v>
-      </c>
-      <c r="B69" s="7">
-        <v>70128</v>
-      </c>
-      <c r="C69" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D69" s="12">
-        <v>365</v>
-      </c>
-      <c r="E69" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F69" s="12"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="7">
-        <v>70129</v>
-      </c>
-      <c r="B70" s="7">
-        <v>70494</v>
-      </c>
-      <c r="C70" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D70" s="12">
-        <v>366</v>
-      </c>
-      <c r="E70" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F70" s="12"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="7">
-        <v>70495</v>
-      </c>
-      <c r="B71" s="7">
-        <v>70859</v>
-      </c>
-      <c r="C71" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D71" s="12">
-        <v>365</v>
-      </c>
-      <c r="E71" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F71" s="12"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="7">
-        <v>70860</v>
-      </c>
-      <c r="B72" s="7">
-        <v>71224</v>
-      </c>
-      <c r="C72" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D72" s="12">
-        <v>365</v>
-      </c>
-      <c r="E72" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F72" s="12"/>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="7">
-        <v>71225</v>
-      </c>
-      <c r="B73" s="7">
-        <v>71589</v>
-      </c>
-      <c r="C73" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D73" s="12">
-        <v>365</v>
-      </c>
-      <c r="E73" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F73" s="12"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="7">
-        <v>71590</v>
-      </c>
-      <c r="B74" s="7">
-        <v>71955</v>
-      </c>
-      <c r="C74" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D74" s="12">
-        <v>366</v>
-      </c>
-      <c r="E74" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F74" s="12"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="7">
-        <v>71956</v>
-      </c>
-      <c r="B75" s="7">
-        <v>72320</v>
-      </c>
-      <c r="C75" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D75" s="12">
-        <v>365</v>
-      </c>
-      <c r="E75" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F75" s="12"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="7">
-        <v>72321</v>
-      </c>
-      <c r="B76" s="7">
-        <v>72685</v>
-      </c>
-      <c r="C76" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D76" s="12">
-        <v>365</v>
-      </c>
-      <c r="E76" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F76" s="12"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="7">
-        <v>72686</v>
-      </c>
-      <c r="B77" s="7">
-        <v>73050</v>
-      </c>
-      <c r="C77" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D77" s="12">
-        <v>365</v>
-      </c>
-      <c r="E77" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F77" s="12"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="7">
-        <v>73051</v>
-      </c>
-      <c r="B78" s="7">
-        <v>73415</v>
-      </c>
-      <c r="C78" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D78" s="12">
-        <v>365</v>
-      </c>
-      <c r="E78" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F78" s="12"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="7">
-        <v>73416</v>
-      </c>
-      <c r="B79" s="7">
-        <v>73780</v>
-      </c>
-      <c r="C79" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D79" s="12">
-        <v>365</v>
-      </c>
-      <c r="E79" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F79" s="12"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="7">
-        <v>73781</v>
-      </c>
-      <c r="B80" s="7">
-        <v>74145</v>
-      </c>
-      <c r="C80" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D80" s="12">
-        <v>365</v>
-      </c>
-      <c r="E80" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F80" s="12"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="7">
-        <v>74146</v>
-      </c>
-      <c r="B81" s="7">
-        <v>74510</v>
-      </c>
-      <c r="C81" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D81" s="12">
-        <v>365</v>
-      </c>
-      <c r="E81" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F81" s="12"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="7">
-        <v>74511</v>
-      </c>
-      <c r="B82" s="7">
-        <v>74876</v>
-      </c>
-      <c r="C82" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D82" s="12">
-        <v>366</v>
-      </c>
-      <c r="E82" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F82" s="12"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="7">
-        <v>74877</v>
-      </c>
-      <c r="B83" s="7">
-        <v>75241</v>
-      </c>
-      <c r="C83" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D83" s="12">
-        <v>365</v>
-      </c>
-      <c r="E83" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F83" s="12"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="7">
-        <v>75242</v>
-      </c>
-      <c r="B84" s="7">
-        <v>75606</v>
-      </c>
-      <c r="C84" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D84" s="12">
-        <v>365</v>
-      </c>
-      <c r="E84" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F84" s="12"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="7">
-        <v>75607</v>
-      </c>
-      <c r="B85" s="7">
-        <v>75971</v>
-      </c>
-      <c r="C85" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D85" s="12">
-        <v>365</v>
-      </c>
-      <c r="E85" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F85" s="12"/>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="7">
-        <v>75972</v>
-      </c>
-      <c r="B86" s="7">
-        <v>76337</v>
-      </c>
-      <c r="C86" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D86" s="12">
-        <v>366</v>
-      </c>
-      <c r="E86" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F86" s="12"/>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="7">
-        <v>76338</v>
-      </c>
-      <c r="B87" s="7">
-        <v>76702</v>
-      </c>
-      <c r="C87" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D87" s="12">
-        <v>365</v>
-      </c>
-      <c r="E87" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F87" s="12"/>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="7">
-        <v>76703</v>
-      </c>
-      <c r="B88" s="7">
-        <v>77067</v>
-      </c>
-      <c r="C88" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D88" s="12">
-        <v>365</v>
-      </c>
-      <c r="E88" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F88" s="12"/>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="7">
-        <v>77068</v>
-      </c>
-      <c r="B89" s="7">
-        <v>77432</v>
-      </c>
-      <c r="C89" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D89" s="12">
-        <v>365</v>
-      </c>
-      <c r="E89" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F89" s="12"/>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="7">
-        <v>77433</v>
-      </c>
-      <c r="B90" s="7">
-        <v>77798</v>
-      </c>
-      <c r="C90" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D90" s="12">
-        <v>366</v>
-      </c>
-      <c r="E90" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F90" s="12"/>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="7">
-        <v>77799</v>
-      </c>
-      <c r="B91" s="7">
-        <v>78163</v>
-      </c>
-      <c r="C91" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D91" s="12">
-        <v>365</v>
-      </c>
-      <c r="E91" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F91" s="12"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="7">
-        <v>78164</v>
-      </c>
-      <c r="B92" s="7">
-        <v>78528</v>
-      </c>
-      <c r="C92" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D92" s="12">
-        <v>365</v>
-      </c>
-      <c r="E92" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F92" s="12"/>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="7">
-        <v>78529</v>
-      </c>
-      <c r="B93" s="7">
-        <v>78893</v>
-      </c>
-      <c r="C93" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D93" s="12">
-        <v>365</v>
-      </c>
-      <c r="E93" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F93" s="12"/>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="7">
-        <v>78894</v>
-      </c>
-      <c r="B94" s="7">
-        <v>79259</v>
-      </c>
-      <c r="C94" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D94" s="12">
-        <v>366</v>
-      </c>
-      <c r="E94" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F94" s="12"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="7">
-        <v>79260</v>
-      </c>
-      <c r="B95" s="7">
-        <v>79624</v>
-      </c>
-      <c r="C95" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D95" s="12">
-        <v>365</v>
-      </c>
-      <c r="E95" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F95" s="12"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="7">
-        <v>79625</v>
-      </c>
-      <c r="B96" s="7">
-        <v>79989</v>
-      </c>
-      <c r="C96" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D96" s="12">
-        <v>365</v>
-      </c>
-      <c r="E96" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F96" s="12"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="7">
-        <v>79990</v>
-      </c>
-      <c r="B97" s="7">
-        <v>80354</v>
-      </c>
-      <c r="C97" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D97" s="12">
-        <v>365</v>
-      </c>
-      <c r="E97" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F97" s="12"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="7">
-        <v>80355</v>
-      </c>
-      <c r="B98" s="7">
-        <v>80720</v>
-      </c>
-      <c r="C98" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D98" s="12">
-        <v>366</v>
-      </c>
-      <c r="E98" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F98" s="12"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="7">
-        <v>80721</v>
-      </c>
-      <c r="B99" s="7">
-        <v>81085</v>
-      </c>
-      <c r="C99" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D99" s="12">
-        <v>365</v>
-      </c>
-      <c r="E99" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F99" s="12"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="7">
-        <v>81086</v>
-      </c>
-      <c r="B100" s="7">
-        <v>81450</v>
-      </c>
-      <c r="C100" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D100" s="12">
-        <v>365</v>
-      </c>
-      <c r="E100" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F100" s="12"/>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="7">
-        <v>81451</v>
-      </c>
-      <c r="B101" s="7">
-        <v>81815</v>
-      </c>
-      <c r="C101" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D101" s="12">
-        <v>365</v>
-      </c>
-      <c r="E101" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F101" s="12"/>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="7">
-        <v>81816</v>
-      </c>
-      <c r="B102" s="7">
-        <v>82181</v>
-      </c>
-      <c r="C102" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D102" s="12">
-        <v>366</v>
-      </c>
-      <c r="E102" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F102" s="12"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="7">
-        <v>82182</v>
-      </c>
-      <c r="B103" s="7">
-        <v>82546</v>
-      </c>
-      <c r="C103" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D103" s="12">
-        <v>365</v>
-      </c>
-      <c r="E103" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F103" s="12"/>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="7">
-        <v>82547</v>
-      </c>
-      <c r="B104" s="7">
-        <v>82911</v>
-      </c>
-      <c r="C104" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D104" s="12">
-        <v>365</v>
-      </c>
-      <c r="E104" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F104" s="12"/>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="7">
-        <v>82912</v>
-      </c>
-      <c r="B105" s="7">
-        <v>83276</v>
-      </c>
-      <c r="C105" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D105" s="12">
-        <v>365</v>
-      </c>
-      <c r="E105" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F105" s="12"/>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="7">
-        <v>83277</v>
-      </c>
-      <c r="B106" s="7">
-        <v>83642</v>
-      </c>
-      <c r="C106" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D106" s="12">
-        <v>366</v>
-      </c>
-      <c r="E106" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F106" s="12"/>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="7">
-        <v>83643</v>
-      </c>
-      <c r="B107" s="7">
-        <v>84007</v>
-      </c>
-      <c r="C107" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D107" s="12">
-        <v>365</v>
-      </c>
-      <c r="E107" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F107" s="12"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" s="7">
-        <v>84008</v>
-      </c>
-      <c r="B108" s="7">
-        <v>84372</v>
-      </c>
-      <c r="C108" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D108" s="12">
-        <v>365</v>
-      </c>
-      <c r="E108" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F108" s="12"/>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" s="7">
-        <v>84373</v>
-      </c>
-      <c r="B109" s="7">
-        <v>84737</v>
-      </c>
-      <c r="C109" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D109" s="12">
-        <v>365</v>
-      </c>
-      <c r="E109" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F109" s="12"/>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" s="7">
-        <v>84738</v>
-      </c>
-      <c r="B110" s="7">
-        <v>85103</v>
-      </c>
-      <c r="C110" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D110" s="12">
-        <v>366</v>
-      </c>
-      <c r="E110" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F110" s="12"/>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" s="7">
-        <v>85104</v>
-      </c>
-      <c r="B111" s="7">
-        <v>85468</v>
-      </c>
-      <c r="C111" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D111" s="12">
-        <v>365</v>
-      </c>
-      <c r="E111" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F111" s="12"/>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="7">
-        <v>85469</v>
-      </c>
-      <c r="B112" s="7">
-        <v>85833</v>
-      </c>
-      <c r="C112" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D112" s="12">
-        <v>365</v>
-      </c>
-      <c r="E112" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F112" s="12"/>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="7">
-        <v>85834</v>
-      </c>
-      <c r="B113" s="7">
-        <v>86198</v>
-      </c>
-      <c r="C113" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D113" s="12">
-        <v>365</v>
-      </c>
-      <c r="E113" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F113" s="12"/>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="7">
-        <v>86199</v>
-      </c>
-      <c r="B114" s="7">
-        <v>86564</v>
-      </c>
-      <c r="C114" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D114" s="12">
-        <v>366</v>
-      </c>
-      <c r="E114" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F114" s="12"/>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" s="7">
-        <v>86565</v>
-      </c>
-      <c r="B115" s="7">
-        <v>86929</v>
-      </c>
-      <c r="C115" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D115" s="12">
-        <v>365</v>
-      </c>
-      <c r="E115" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F115" s="12"/>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="7">
-        <v>86930</v>
-      </c>
-      <c r="B116" s="7">
-        <v>87294</v>
-      </c>
-      <c r="C116" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D116" s="12">
-        <v>365</v>
-      </c>
-      <c r="E116" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F116" s="12"/>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" s="7">
-        <v>87295</v>
-      </c>
-      <c r="B117" s="7">
-        <v>87659</v>
-      </c>
-      <c r="C117" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D117" s="12">
-        <v>365</v>
-      </c>
-      <c r="E117" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F117" s="12"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="7">
-        <v>87660</v>
-      </c>
-      <c r="B118" s="7">
-        <v>88025</v>
-      </c>
-      <c r="C118" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D118" s="12">
-        <v>366</v>
-      </c>
-      <c r="E118" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F118" s="12"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" s="7">
-        <v>88026</v>
-      </c>
-      <c r="B119" s="7">
-        <v>88390</v>
-      </c>
-      <c r="C119" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D119" s="12">
-        <v>365</v>
-      </c>
-      <c r="E119" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F119" s="12"/>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120" s="7">
-        <v>88391</v>
-      </c>
-      <c r="B120" s="7">
-        <v>88755</v>
-      </c>
-      <c r="C120" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D120" s="12">
-        <v>365</v>
-      </c>
-      <c r="E120" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F120" s="12"/>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" s="7">
-        <v>88756</v>
-      </c>
-      <c r="B121" s="7">
-        <v>89120</v>
-      </c>
-      <c r="C121" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D121" s="12">
-        <v>365</v>
-      </c>
-      <c r="E121" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F121" s="12"/>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="7">
-        <v>89121</v>
-      </c>
-      <c r="B122" s="7">
-        <v>89486</v>
-      </c>
-      <c r="C122" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D122" s="12">
-        <v>366</v>
-      </c>
-      <c r="E122" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F122" s="12"/>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="7">
-        <v>89487</v>
-      </c>
-      <c r="B123" s="7">
-        <v>89851</v>
-      </c>
-      <c r="C123" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D123" s="12">
-        <v>365</v>
-      </c>
-      <c r="E123" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F123" s="12"/>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" s="7">
-        <v>89852</v>
-      </c>
-      <c r="B124" s="7">
-        <v>90216</v>
-      </c>
-      <c r="C124" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D124" s="12">
-        <v>365</v>
-      </c>
-      <c r="E124" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F124" s="12"/>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="7">
-        <v>90217</v>
-      </c>
-      <c r="B125" s="7">
-        <v>90581</v>
-      </c>
-      <c r="C125" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D125" s="12">
-        <v>365</v>
-      </c>
-      <c r="E125" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F125" s="12"/>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" s="7">
-        <v>90582</v>
-      </c>
-      <c r="B126" s="7">
-        <v>90947</v>
-      </c>
-      <c r="C126" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D126" s="12">
-        <v>366</v>
-      </c>
-      <c r="E126" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F126" s="12"/>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127" s="7">
-        <v>90948</v>
-      </c>
-      <c r="B127" s="7">
-        <v>91312</v>
-      </c>
-      <c r="C127" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D127" s="12">
-        <v>365</v>
-      </c>
-      <c r="E127" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F127" s="12"/>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A128" s="7">
-        <v>91313</v>
-      </c>
-      <c r="B128" s="7">
-        <v>91677</v>
-      </c>
-      <c r="C128" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D128" s="12">
-        <v>365</v>
-      </c>
-      <c r="E128" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F128" s="12"/>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" s="7">
-        <v>91678</v>
-      </c>
-      <c r="B129" s="7">
-        <v>92042</v>
-      </c>
-      <c r="C129" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D129" s="12">
-        <v>365</v>
-      </c>
-      <c r="E129" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F129" s="12"/>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" s="7">
-        <v>92043</v>
-      </c>
-      <c r="B130" s="7">
-        <v>92408</v>
-      </c>
-      <c r="C130" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D130" s="12">
-        <v>366</v>
-      </c>
-      <c r="E130" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F130" s="12"/>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" s="7">
-        <v>92409</v>
-      </c>
-      <c r="B131" s="7">
-        <v>92773</v>
-      </c>
-      <c r="C131" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D131" s="12">
-        <v>365</v>
-      </c>
-      <c r="E131" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F131" s="12"/>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" s="7">
-        <v>92774</v>
-      </c>
-      <c r="B132" s="7">
-        <v>93138</v>
-      </c>
-      <c r="C132" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D132" s="12">
-        <v>365</v>
-      </c>
-      <c r="E132" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F132" s="12"/>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" s="7">
-        <v>93139</v>
-      </c>
-      <c r="B133" s="7">
-        <v>93503</v>
-      </c>
-      <c r="C133" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D133" s="12">
-        <v>365</v>
-      </c>
-      <c r="E133" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F133" s="12"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" s="7">
-        <v>93504</v>
-      </c>
-      <c r="B134" s="7">
-        <v>93869</v>
-      </c>
-      <c r="C134" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D134" s="12">
-        <v>366</v>
-      </c>
-      <c r="E134" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F134" s="12"/>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" s="7">
-        <v>93870</v>
-      </c>
-      <c r="B135" s="7">
-        <v>94234</v>
-      </c>
-      <c r="C135" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D135" s="12">
-        <v>365</v>
-      </c>
-      <c r="E135" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F135" s="12"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="7">
-        <v>94235</v>
-      </c>
-      <c r="B136" s="7">
-        <v>94599</v>
-      </c>
-      <c r="C136" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D136" s="12">
-        <v>365</v>
-      </c>
-      <c r="E136" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F136" s="12"/>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="7">
-        <v>94600</v>
-      </c>
-      <c r="B137" s="7">
-        <v>94964</v>
-      </c>
-      <c r="C137" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D137" s="12">
-        <v>365</v>
-      </c>
-      <c r="E137" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F137" s="12"/>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="7">
-        <v>94965</v>
-      </c>
-      <c r="B138" s="7">
-        <v>95330</v>
-      </c>
-      <c r="C138" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D138" s="12">
-        <v>366</v>
-      </c>
-      <c r="E138" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F138" s="12"/>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="7">
-        <v>95331</v>
-      </c>
-      <c r="B139" s="7">
-        <v>95695</v>
-      </c>
-      <c r="C139" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D139" s="12">
-        <v>365</v>
-      </c>
-      <c r="E139" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F139" s="12"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="7">
-        <v>95696</v>
-      </c>
-      <c r="B140" s="7">
-        <v>96060</v>
-      </c>
-      <c r="C140" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D140" s="12">
-        <v>365</v>
-      </c>
-      <c r="E140" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F140" s="12"/>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" s="7">
-        <v>96061</v>
-      </c>
-      <c r="B141" s="7">
-        <v>96425</v>
-      </c>
-      <c r="C141" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D141" s="12">
-        <v>365</v>
-      </c>
-      <c r="E141" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F141" s="12"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" s="7">
-        <v>96426</v>
-      </c>
-      <c r="B142" s="7">
-        <v>96791</v>
-      </c>
-      <c r="C142" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D142" s="12">
-        <v>366</v>
-      </c>
-      <c r="E142" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F142" s="12"/>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" s="7">
-        <v>96792</v>
-      </c>
-      <c r="B143" s="7">
-        <v>97156</v>
-      </c>
-      <c r="C143" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D143" s="12">
-        <v>365</v>
-      </c>
-      <c r="E143" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F143" s="12"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" s="7">
-        <v>97157</v>
-      </c>
-      <c r="B144" s="7">
-        <v>97521</v>
-      </c>
-      <c r="C144" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D144" s="12">
-        <v>365</v>
-      </c>
-      <c r="E144" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F144" s="12"/>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A145" s="7">
-        <v>97522</v>
-      </c>
-      <c r="B145" s="7">
-        <v>97886</v>
-      </c>
-      <c r="C145" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D145" s="12">
-        <v>365</v>
-      </c>
-      <c r="E145" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F145" s="12"/>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A146" s="7">
-        <v>97887</v>
-      </c>
-      <c r="B146" s="7">
-        <v>98252</v>
-      </c>
-      <c r="C146" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D146" s="12">
-        <v>366</v>
-      </c>
-      <c r="E146" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F146" s="12"/>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A147" s="7">
-        <v>98253</v>
-      </c>
-      <c r="B147" s="7">
-        <v>98617</v>
-      </c>
-      <c r="C147" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D147" s="12">
-        <v>365</v>
-      </c>
-      <c r="E147" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F147" s="12"/>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A148" s="7">
-        <v>98618</v>
-      </c>
-      <c r="B148" s="7">
-        <v>98982</v>
-      </c>
-      <c r="C148" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D148" s="12">
-        <v>365</v>
-      </c>
-      <c r="E148" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F148" s="12"/>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A149" s="7">
-        <v>98983</v>
-      </c>
-      <c r="B149" s="7">
-        <v>99347</v>
-      </c>
-      <c r="C149" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D149" s="12">
-        <v>365</v>
-      </c>
-      <c r="E149" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F149" s="12"/>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A150" s="7">
-        <v>99348</v>
-      </c>
-      <c r="B150" s="7">
-        <v>99713</v>
-      </c>
-      <c r="C150" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D150" s="12">
-        <v>366</v>
-      </c>
-      <c r="E150" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F150" s="12"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A151" s="7">
-        <v>99714</v>
-      </c>
-      <c r="B151" s="7">
-        <v>100078</v>
-      </c>
-      <c r="C151" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D151" s="12">
-        <v>365</v>
-      </c>
-      <c r="E151" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F151" s="12"/>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A152" s="7">
-        <v>100079</v>
-      </c>
-      <c r="B152" s="7">
-        <v>100443</v>
-      </c>
-      <c r="C152" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D152" s="12">
-        <v>365</v>
-      </c>
-      <c r="E152" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F152" s="12"/>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A153" s="7">
-        <v>100444</v>
-      </c>
-      <c r="B153" s="7">
-        <v>100808</v>
-      </c>
-      <c r="C153" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D153" s="12">
-        <v>365</v>
-      </c>
-      <c r="E153" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F153" s="12"/>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A154" s="7">
-        <v>100809</v>
-      </c>
-      <c r="B154" s="7">
-        <v>101174</v>
-      </c>
-      <c r="C154" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D154" s="12">
-        <v>366</v>
-      </c>
-      <c r="E154" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F154" s="12"/>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A155" s="7">
-        <v>101175</v>
-      </c>
-      <c r="B155" s="7">
-        <v>101539</v>
-      </c>
-      <c r="C155" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D155" s="12">
-        <v>365</v>
-      </c>
-      <c r="E155" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F155" s="12"/>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A156" s="7">
-        <v>101540</v>
-      </c>
-      <c r="B156" s="7">
-        <v>101904</v>
-      </c>
-      <c r="C156" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D156" s="12">
-        <v>365</v>
-      </c>
-      <c r="E156" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F156" s="12"/>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A157" s="7">
-        <v>101905</v>
-      </c>
-      <c r="B157" s="7">
-        <v>102269</v>
-      </c>
-      <c r="C157" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D157" s="12">
-        <v>365</v>
-      </c>
-      <c r="E157" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F157" s="12"/>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A158" s="7">
-        <v>102270</v>
-      </c>
-      <c r="B158" s="7">
-        <v>102635</v>
-      </c>
-      <c r="C158" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D158" s="12">
-        <v>366</v>
-      </c>
-      <c r="E158" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F158" s="12"/>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A159" s="7">
-        <v>102636</v>
-      </c>
-      <c r="B159" s="7">
-        <v>103000</v>
-      </c>
-      <c r="C159" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D159" s="12">
-        <v>365</v>
-      </c>
-      <c r="E159" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F159" s="12"/>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A160" s="7">
-        <v>103001</v>
-      </c>
-      <c r="B160" s="7">
-        <v>103365</v>
-      </c>
-      <c r="C160" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D160" s="12">
-        <v>365</v>
-      </c>
-      <c r="E160" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F160" s="12"/>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A161" s="7">
-        <v>103366</v>
-      </c>
-      <c r="B161" s="7">
-        <v>103730</v>
-      </c>
-      <c r="C161" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D161" s="12">
-        <v>365</v>
-      </c>
-      <c r="E161" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F161" s="12"/>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A162" s="7">
-        <v>103731</v>
-      </c>
-      <c r="B162" s="7">
-        <v>104096</v>
-      </c>
-      <c r="C162" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D162" s="12">
-        <v>366</v>
-      </c>
-      <c r="E162" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F162" s="12"/>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A163" s="7">
-        <v>104097</v>
-      </c>
-      <c r="B163" s="7">
-        <v>104461</v>
-      </c>
-      <c r="C163" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D163" s="12">
-        <v>365</v>
-      </c>
-      <c r="E163" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F163" s="12"/>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A164" s="7">
-        <v>104462</v>
-      </c>
-      <c r="B164" s="7">
-        <v>104826</v>
-      </c>
-      <c r="C164" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D164" s="12">
-        <v>365</v>
-      </c>
-      <c r="E164" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F164" s="12"/>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A165" s="7">
-        <v>104827</v>
-      </c>
-      <c r="B165" s="7">
-        <v>105191</v>
-      </c>
-      <c r="C165" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D165" s="12">
-        <v>365</v>
-      </c>
-      <c r="E165" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F165" s="12"/>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A166" s="7">
-        <v>105192</v>
-      </c>
-      <c r="B166" s="7">
-        <v>105557</v>
-      </c>
-      <c r="C166" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D166" s="12">
-        <v>366</v>
-      </c>
-      <c r="E166" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F166" s="12"/>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A167" s="7">
-        <v>105558</v>
-      </c>
-      <c r="B167" s="7">
-        <v>105922</v>
-      </c>
-      <c r="C167" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D167" s="12">
-        <v>365</v>
-      </c>
-      <c r="E167" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F167" s="12"/>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A168" s="7">
-        <v>105923</v>
-      </c>
-      <c r="B168" s="7">
-        <v>106287</v>
-      </c>
-      <c r="C168" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D168" s="12">
-        <v>365</v>
-      </c>
-      <c r="E168" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F168" s="12"/>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A169" s="7">
-        <v>106288</v>
-      </c>
-      <c r="B169" s="7">
-        <v>106652</v>
-      </c>
-      <c r="C169" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D169" s="12">
-        <v>365</v>
-      </c>
-      <c r="E169" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F169" s="12"/>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A170" s="7">
-        <v>106653</v>
-      </c>
-      <c r="B170" s="7">
-        <v>107018</v>
-      </c>
-      <c r="C170" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D170" s="12">
-        <v>366</v>
-      </c>
-      <c r="E170" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F170" s="12"/>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A171" s="7">
-        <v>107019</v>
-      </c>
-      <c r="B171" s="7">
-        <v>107383</v>
-      </c>
-      <c r="C171" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D171" s="12">
-        <v>365</v>
-      </c>
-      <c r="E171" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F171" s="12"/>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A172" s="7">
-        <v>107384</v>
-      </c>
-      <c r="B172" s="7">
-        <v>107748</v>
-      </c>
-      <c r="C172" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D172" s="12">
-        <v>365</v>
-      </c>
-      <c r="E172" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F172" s="12"/>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A173" s="7">
-        <v>107749</v>
-      </c>
-      <c r="B173" s="7">
-        <v>108113</v>
-      </c>
-      <c r="C173" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D173" s="12">
-        <v>365</v>
-      </c>
-      <c r="E173" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F173" s="12"/>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A174" s="7">
-        <v>108114</v>
-      </c>
-      <c r="B174" s="7">
-        <v>108479</v>
-      </c>
-      <c r="C174" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D174" s="12">
-        <v>366</v>
-      </c>
-      <c r="E174" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F174" s="12"/>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A175" s="7">
-        <v>108480</v>
-      </c>
-      <c r="B175" s="7">
-        <v>108844</v>
-      </c>
-      <c r="C175" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D175" s="12">
-        <v>365</v>
-      </c>
-      <c r="E175" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F175" s="12"/>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A176" s="7">
-        <v>108845</v>
-      </c>
-      <c r="B176" s="7">
-        <v>109209</v>
-      </c>
-      <c r="C176" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D176" s="12">
-        <v>365</v>
-      </c>
-      <c r="E176" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F176" s="12"/>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A177" s="7">
-        <v>109210</v>
-      </c>
-      <c r="B177" s="7">
-        <v>109574</v>
-      </c>
-      <c r="C177" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D177" s="12">
-        <v>365</v>
-      </c>
-      <c r="E177" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F177" s="12"/>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A178" s="7">
-        <v>109575</v>
-      </c>
-      <c r="B178" s="7">
-        <v>109939</v>
-      </c>
-      <c r="C178" s="12">
-        <v>11.51</v>
-      </c>
-      <c r="D178" s="12">
-        <v>365</v>
-      </c>
-      <c r="E178" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F178" s="12"/>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -8418,19 +5283,19 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B1" s="5"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B2" s="13">
         <v>46244</v>
       </c>
       <c r="C2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D2" s="9">
         <f>IF(Summary!$B$2="","",IF(ISNUMBER(Summary!$B$2),INT(Summary!$B$2),Summary!$B$2))</f>
@@ -8439,11 +5304,11 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D3" s="9" t="str">
         <f>IF(Summary!$B$3="","",IF(ISNUMBER(Summary!$B$3),INT(Summary!$B$3),Summary!$B$3))</f>
@@ -8452,23 +5317,23 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>185</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B6" s="13">
         <v>46630</v>
@@ -8476,7 +5341,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B7" s="9">
         <f>_xlfn.MAXIFS(tblGic[to],tblGic[basis],"known")</f>
@@ -8485,7 +5350,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B9" s="5"/>
     </row>
@@ -8545,7 +5410,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B16" s="10">
         <f>SUM(tblLines[Exposed])</f>
@@ -8554,7 +5419,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B17" s="11">
         <f>ROUND(SUM(tblLines[Shortfall_r]),2)</f>
@@ -8563,7 +5428,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B18" s="11">
         <f>ROUND(SUM(tblLines[NEC_r]),2)</f>
@@ -8572,7 +5437,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B19" s="11">
         <f>ROUND(SUM(tblLines[SGC_low]),2)</f>
@@ -8581,7 +5446,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B20" s="11">
         <f>ROUND(SUM(tblLines[SGC_high]),2)</f>
@@ -8590,7 +5455,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B21" s="10">
         <f>SUMPRODUCT(--(tblLines[Unassessable_between]&lt;&gt;""))</f>
@@ -8599,7 +5464,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B22" s="10" t="str">
         <f>IF(AND(SUM(tblLines[Assessable])&gt;0,SUMPRODUCT(tblLines[Assessable]*tblLines[Receipt_established])=0),"YES","NO")</f>
@@ -8656,21 +5521,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>200</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B2" s="10" t="str">
         <f>IF(C2=0,"PASS","BLOCKED")</f>
@@ -8687,7 +5552,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B3" s="10" t="str">
         <f>IF(C3=0,"PASS","BLOCKED")</f>
@@ -8704,7 +5569,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B4" s="10" t="str">
         <f>IF(OR(C4=0,Summary!$B$4="Y"),"PASS","BLOCKED")</f>
@@ -8721,7 +5586,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B5" s="10" t="str">
         <f>IF(C5=0,"PASS","REVIEW")</f>
@@ -8738,7 +5603,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B6" s="10" t="str">
         <f>IF(C6=0,"PASS","REVIEW")</f>
@@ -8755,7 +5620,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B7" s="10" t="str">
         <f>IF(OR(Summary!B22="NO",Summary!$B$5="Y"),"PASS","REVIEW")</f>
@@ -8769,7 +5634,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B8" s="10" t="str">
         <f>IF(C8=0,"PASS","NOTE")</f>
@@ -8786,24 +5651,24 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B9" s="10" t="str">
         <f>IF(C9=0,"PASS","NOTE")</f>
         <v>PASS</v>
       </c>
       <c r="C9" s="10">
-        <f>SUM(tblLines[GIC_estimated])</f>
+        <f>SUM(tblLines[Past_gic_table])</f>
         <v>0</v>
       </c>
       <c r="D9" s="10" t="str">
-        <f t="array" ref="D9">IF(C9=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[GIC_estimated]=1)*(ROW(tblLines[employee_id])-1)))))</f>
+        <f t="array" ref="D9">IF(C9=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[Past_gic_table]=1)*(ROW(tblLines[employee_id])-1)))))</f>
         <v/>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B10" s="10" t="str">
         <f>IF(C10=0,"PASS","NOTE")</f>
@@ -8820,7 +5685,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B11" s="10" t="str">
         <f>IF(C11=0,"PASS","NOTE")</f>
@@ -8837,7 +5702,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B12" s="10" t="str">
         <f>IF(AND(ISNUMBER(Summary!$D$2),Summary!$D$2&lt;=DATE(2200,12,31),OR(Summary!$D$3="",AND(ISNUMBER(Summary!$D$3),Summary!$D$3&lt;=DATE(2200,12,31))),AND(ISNUMBER(Summary!$B$6),Summary!$B$6&lt;=DATE(2200,12,31))),"PASS","BLOCKED")</f>
@@ -8851,7 +5716,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B13" s="10" t="str">
         <f>IF(C13=0,"PASS","REVIEW")</f>
@@ -8868,7 +5733,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B14" s="10" t="str">
         <f>IF(C14=0,"PASS","NOTE")</f>
@@ -8894,37 +5759,37 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
         <v>217</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -8955,74 +5820,74 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>222</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2" t="s">
         <v>224</v>
-      </c>
-      <c r="B2" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B4" t="s">
         <v>227</v>
-      </c>
-      <c r="B4" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B5" t="s">
         <v>229</v>
-      </c>
-      <c r="B5" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B6" t="s">
         <v>231</v>
-      </c>
-      <c r="B6" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>232</v>
+      </c>
+      <c r="B7" t="s">
         <v>233</v>
-      </c>
-      <c r="B7" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>234</v>
+      </c>
+      <c r="B8" t="s">
         <v>235</v>
-      </c>
-      <c r="B8" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>236</v>
+      </c>
+      <c r="B9" t="s">
         <v>237</v>
-      </c>
-      <c r="B9" t="s">
-        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
+++ b/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D2CF9A-EC2E-4C1D-AA9C-6FA89C09B4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F6011A-7861-4CA8-82EF-978CC715DE7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="1560" windowWidth="38700" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="244">
   <si>
     <t>Payday Super review: s 18C deadlines and the SG charge estimate</t>
   </si>
@@ -416,6 +416,21 @@
   </si>
   <si>
     <t>N3</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>UNPAID or ON_TIME</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>NOT_YET_DUE or ON_TIME</t>
   </si>
   <si>
     <t>date</t>
@@ -1036,7 +1051,7 @@
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Final_due]]="","",IF((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),1,0))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="Branch">
-      <calculatedColumnFormula>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(AND(NOT(OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],OR(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],(tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]])))),IF(tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],"U1",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"U2","U3")),IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E"))))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="Verdict">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Branch]]="","",INDEX(tblCodes[verdict],MATCH(tblLines[[#This Row],[Branch]],tblCodes[code],0)))</calculatedColumnFormula>
@@ -1057,19 +1072,19 @@
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),MAX(ROUND(tblLines[[#This Row],[sg_amount]],2)-tblLines[[#This Row],[OTRC]],0),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="Offset_s18D">
-      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])),OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="Final_shortfall">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),MAX(tblLines[[#This Row],[Base_shortfall]]-tblLines[[#This Row],[Offset_s18D]],0),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="Lateness_basis">
-      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,NOT(OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),"as-at date (fund receipt amount not evidenced)",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)")))),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="Outstanding_to">
-      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="49" xr3:uid="{00000000-0010-0000-0000-000031000000}" name="Accrual_to">
-      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="50" xr3:uid="{00000000-0010-0000-0000-000032000000}" name="NEC_end">
       <calculatedColumnFormula>IF((tblLines[[#This Row],[Exposed]]=1),IF(Summary!$D$3="",tblLines[[#This Row],[Accrual_to]],MIN(Summary!$D$3-1,tblLines[[#This Row],[Accrual_to]])),"")</calculatedColumnFormula>
@@ -1125,7 +1140,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="tblCodes" displayName="tblCodes" ref="A1:F27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="tblCodes" displayName="tblCodes" ref="A1:F30">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="code"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="verdict"/>
@@ -1746,7 +1761,9 @@
         <v>46217</v>
       </c>
       <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
+      <c r="F2" s="8">
+        <v>612</v>
+      </c>
       <c r="G2" s="7">
         <v>46219</v>
       </c>
@@ -1865,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="AL2" s="10" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(AND(NOT(OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],OR(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],(tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]])))),IF(tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],"U1",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"U2","U3")),IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E"))))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>D1</v>
       </c>
       <c r="AM2" s="10" t="str">
@@ -1893,7 +1910,7 @@
         <v/>
       </c>
       <c r="AS2" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])),OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
         <v/>
       </c>
       <c r="AT2" s="11" t="str">
@@ -1901,15 +1918,15 @@
         <v/>
       </c>
       <c r="AU2" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,NOT(OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),"as-at date (fund receipt amount not evidenced)",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)")))),"")</f>
         <v/>
       </c>
       <c r="AV2" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v/>
       </c>
       <c r="AW2" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v/>
       </c>
       <c r="AX2" s="9" t="str">
@@ -1991,7 +2008,9 @@
         <v>46233</v>
       </c>
       <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
+      <c r="F3" s="8">
+        <v>540</v>
+      </c>
       <c r="G3" s="7">
         <v>46238</v>
       </c>
@@ -2110,7 +2129,7 @@
         <v>0</v>
       </c>
       <c r="AL3" s="10" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(AND(NOT(OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],OR(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],(tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]])))),IF(tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],"U1",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"U2","U3")),IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E"))))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>E</v>
       </c>
       <c r="AM3" s="10" t="str">
@@ -2138,7 +2157,7 @@
         <v>540</v>
       </c>
       <c r="AS3" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])),OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
         <v>540</v>
       </c>
       <c r="AT3" s="11">
@@ -2146,15 +2165,15 @@
         <v>0</v>
       </c>
       <c r="AU3" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,NOT(OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),"as-at date (fund receipt amount not evidenced)",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)")))),"")</f>
         <v>fund receipt</v>
       </c>
       <c r="AV3" s="9">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v>46238</v>
       </c>
       <c r="AW3" s="9">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v>46238</v>
       </c>
       <c r="AX3" s="9">
@@ -2353,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="AL4" s="10" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(AND(NOT(OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],OR(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],(tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]])))),IF(tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],"U1",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"U2","U3")),IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E"))))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>R3</v>
       </c>
       <c r="AM4" s="10" t="str">
@@ -2381,7 +2400,7 @@
         <v/>
       </c>
       <c r="AS4" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])),OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
         <v/>
       </c>
       <c r="AT4" s="11" t="str">
@@ -2389,15 +2408,15 @@
         <v/>
       </c>
       <c r="AU4" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,NOT(OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),"as-at date (fund receipt amount not evidenced)",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)")))),"")</f>
         <v/>
       </c>
       <c r="AV4" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v/>
       </c>
       <c r="AW4" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v/>
       </c>
       <c r="AX4" s="9" t="str">
@@ -2594,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="AL5" s="10" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(AND(NOT(OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],OR(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],(tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]])))),IF(tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],"U1",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"U2","U3")),IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E"))))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>N2</v>
       </c>
       <c r="AM5" s="10" t="str">
@@ -2622,7 +2641,7 @@
         <v>780</v>
       </c>
       <c r="AS5" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])),OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
         <v>0</v>
       </c>
       <c r="AT5" s="11">
@@ -2630,15 +2649,15 @@
         <v>780</v>
       </c>
       <c r="AU5" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,NOT(OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),"as-at date (fund receipt amount not evidenced)",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)")))),"")</f>
         <v>as-at date (nothing applied to this payday)</v>
       </c>
       <c r="AV5" s="9">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v>46244</v>
       </c>
       <c r="AW5" s="9">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v>46244</v>
       </c>
       <c r="AX5" s="9">
@@ -2720,7 +2739,9 @@
         <v>46237</v>
       </c>
       <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
+      <c r="F6" s="8">
+        <v>450</v>
+      </c>
       <c r="G6" s="7">
         <v>46239</v>
       </c>
@@ -2839,7 +2860,7 @@
         <v>0</v>
       </c>
       <c r="AL6" s="10" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(AND(NOT(OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],OR(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],(tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]])))),IF(tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],"U1",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"U2","U3")),IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E"))))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>D1</v>
       </c>
       <c r="AM6" s="10" t="str">
@@ -2867,7 +2888,7 @@
         <v/>
       </c>
       <c r="AS6" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])),OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
         <v/>
       </c>
       <c r="AT6" s="11" t="str">
@@ -2875,15 +2896,15 @@
         <v/>
       </c>
       <c r="AU6" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,NOT(OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),"as-at date (fund receipt amount not evidenced)",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)")))),"")</f>
         <v/>
       </c>
       <c r="AV6" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v/>
       </c>
       <c r="AW6" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v/>
       </c>
       <c r="AX6" s="9" t="str">
@@ -2965,7 +2986,9 @@
         <v>46233</v>
       </c>
       <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
+      <c r="F7" s="8">
+        <v>120</v>
+      </c>
       <c r="G7" s="7">
         <v>46234</v>
       </c>
@@ -3086,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="AL7" s="10" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(AND(NOT(OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],OR(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],(tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]])))),IF(tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],"U1",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"U2","U3")),IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E"))))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>D1</v>
       </c>
       <c r="AM7" s="10" t="str">
@@ -3114,7 +3137,7 @@
         <v/>
       </c>
       <c r="AS7" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])),OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
         <v/>
       </c>
       <c r="AT7" s="11" t="str">
@@ -3122,15 +3145,15 @@
         <v/>
       </c>
       <c r="AU7" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,NOT(OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),"as-at date (fund receipt amount not evidenced)",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)")))),"")</f>
         <v/>
       </c>
       <c r="AV7" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v/>
       </c>
       <c r="AW7" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v/>
       </c>
       <c r="AX7" s="9" t="str">
@@ -3212,7 +3235,9 @@
         <v>46216</v>
       </c>
       <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
+      <c r="F8" s="8">
+        <v>900</v>
+      </c>
       <c r="G8" s="7">
         <v>46216</v>
       </c>
@@ -3331,7 +3356,7 @@
         <v/>
       </c>
       <c r="AL8" s="10" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(AND(NOT(OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],OR(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],(tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]])))),IF(tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],"U1",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"U2","U3")),IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E"))))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>DB</v>
       </c>
       <c r="AM8" s="10" t="str">
@@ -3359,7 +3384,7 @@
         <v/>
       </c>
       <c r="AS8" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])),OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
         <v/>
       </c>
       <c r="AT8" s="11" t="str">
@@ -3367,15 +3392,15 @@
         <v/>
       </c>
       <c r="AU8" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,NOT(OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),"as-at date (fund receipt amount not evidenced)",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)")))),"")</f>
         <v/>
       </c>
       <c r="AV8" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v/>
       </c>
       <c r="AW8" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v/>
       </c>
       <c r="AX8" s="9" t="str">
@@ -3457,7 +3482,9 @@
         <v>46239</v>
       </c>
       <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
+      <c r="F9" s="8">
+        <v>612</v>
+      </c>
       <c r="G9" s="7">
         <v>46240</v>
       </c>
@@ -3576,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="AL9" s="10" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(AND(NOT(OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],OR(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],(tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]])))),IF(tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],"U1",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"U2","U3")),IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E"))))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>E</v>
       </c>
       <c r="AM9" s="10" t="str">
@@ -3604,7 +3631,7 @@
         <v>612</v>
       </c>
       <c r="AS9" s="11">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])),OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
         <v>612</v>
       </c>
       <c r="AT9" s="11">
@@ -3612,15 +3639,15 @@
         <v>0</v>
       </c>
       <c r="AU9" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,NOT(OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),"as-at date (fund receipt amount not evidenced)",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)")))),"")</f>
         <v>fund receipt</v>
       </c>
       <c r="AV9" s="9">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v>46240</v>
       </c>
       <c r="AW9" s="9">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v>46240</v>
       </c>
       <c r="AX9" s="9">
@@ -3702,7 +3729,9 @@
         <v>46231</v>
       </c>
       <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
+      <c r="F10" s="8">
+        <v>540</v>
+      </c>
       <c r="G10" s="7">
         <v>46233</v>
       </c>
@@ -3821,7 +3850,7 @@
         <v>0</v>
       </c>
       <c r="AL10" s="10" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(AND(NOT(OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],OR(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],(tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]])))),IF(tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],"U1",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"U2","U3")),IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E"))))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>D1</v>
       </c>
       <c r="AM10" s="10" t="str">
@@ -3849,7 +3878,7 @@
         <v/>
       </c>
       <c r="AS10" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])),OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
         <v/>
       </c>
       <c r="AT10" s="11" t="str">
@@ -3857,15 +3886,15 @@
         <v/>
       </c>
       <c r="AU10" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,NOT(OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),"as-at date (fund receipt amount not evidenced)",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)")))),"")</f>
         <v/>
       </c>
       <c r="AV10" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v/>
       </c>
       <c r="AW10" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v/>
       </c>
       <c r="AX10" s="9" t="str">
@@ -3947,7 +3976,9 @@
         <v>46239</v>
       </c>
       <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="F11" s="8">
+        <v>450</v>
+      </c>
       <c r="G11" s="7">
         <v>46240</v>
       </c>
@@ -4066,7 +4097,7 @@
         <v>0</v>
       </c>
       <c r="AL11" s="10" t="str">
-        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF((tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E")))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
+        <f>IF(tblLines[[#This Row],[Flag_db]]=1,"DB",IF(tblLines[[#This Row],[Final_due]]="","",IF(ROUND(tblLines[[#This Row],[sg_amount]],2)&lt;=0,"NIL",IF(tblLines[[#This Row],[Settled]]&lt;&gt;"",IF(AND(NOT(OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],OR(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],(tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]])))),IF(tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],"U1",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"U2","U3")),IF(tblLines[[#This Row],[Settled]]&lt;tblLines[[#This Row],[Pay_day]],IF(tblLines[[#This Row],[Settled]]&gt;=tblLines[[#This Row],[Earliest_prepay]],IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"A1",IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"A2",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"A3","A4"))),IF(tblLines[[#This Row],[Final_due]]&gt;=Summary!$D$2,"S1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"S2","S3"))),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Settled]],tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Possible_item4]]),IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"B1",IF(Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]],"B2","B3")),IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]]),IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"C1","C2"),IF(tblLines[[#This Row],[Settled]]&lt;=tblLines[[#This Row],[Final_due]],IF(AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"D1",IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"D2",IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,"D3","D4"))),"E"))))),IF(AND(tblLines[[#This Row],[Remit]]&lt;&gt;"",tblLines[[#This Row],[sg_amount]]-tblLines[[#This Row],[Credit]]&lt;=0),IF(AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),tblLines[[#This Row],[Final_due]]&lt;tblLines[[#This Row],[Remit]],tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Possible_item4]]),"R1",IF(AND((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),tblLines[[#This Row],[Remit]]&gt;tblLines[[#This Row],[Final_due]]),"R2",IF(tblLines[[#This Row],[Remit]]&lt;=tblLines[[#This Row],[Final_due]],"R3","R4"))),IF(tblLines[[#This Row],[Final_due]]&lt;Summary!$D$2,IF(OR((tblLines[[#This Row],[Final_due]]&gt;Summary!$B$6),AND((tblLines[[#This Row],[Possible_item4]]&lt;&gt;""),Summary!$D$2&lt;=tblLines[[#This Row],[Possible_item4]])),"N1","N2"),"N3"))))))</f>
         <v>D1</v>
       </c>
       <c r="AM11" s="10" t="str">
@@ -4094,7 +4125,7 @@
         <v/>
       </c>
       <c r="AS11" s="11" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,tblLines[[#This Row],[Settled]]&gt;tblLines[[#This Row],[Final_due]],OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])),OR(Summary!$D$3="",tblLines[[#This Row],[Settled]]&lt;Summary!$D$3)),MIN(tblLines[[#This Row],[Receipt_credit]],tblLines[[#This Row],[Base_shortfall]]),0),"")</f>
         <v/>
       </c>
       <c r="AT11" s="11" t="str">
@@ -4102,15 +4133,15 @@
         <v/>
       </c>
       <c r="AU11" s="10" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)"))),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),"fund receipt",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,NOT(OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),"as-at date (fund receipt amount not evidenced)",IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (shortfall remains after part receipt)",IF(AND(OR(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Remit]]&lt;&gt;""),tblLines[[#This Row],[Stale_prepay]]=0),"as-at date (no fund receipt recorded)","as-at date (nothing applied to this payday)")))),"")</f>
         <v/>
       </c>
       <c r="AV11" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]])))),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v/>
       </c>
       <c r="AW11" s="9" t="str">
-        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2)),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
+        <f>IF((tblLines[[#This Row],[Exposed]]=1),IF(AND(tblLines[[#This Row],[Settled]]&lt;&gt;"",tblLines[[#This Row],[Stale_prepay]]=0,AND(tblLines[[#This Row],[Receipt_credit]]&gt;=ROUND(tblLines[[#This Row],[sg_amount]],2),OR(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),tblLines[[#This Row],[Final_shortfall]]=0),tblLines[[#This Row],[Settled]],Summary!$D$2),"")</f>
         <v/>
       </c>
       <c r="AX11" s="9" t="str">
@@ -4193,7 +4224,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="24" customWidth="1"/>
@@ -4691,6 +4722,66 @@
         <v>0</v>
       </c>
       <c r="F27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>126</v>
+      </c>
+      <c r="B28" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>127</v>
+      </c>
+      <c r="B29" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" t="s">
+        <v>128</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>129</v>
+      </c>
+      <c r="B30" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" t="s">
+        <v>130</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
         <v>0</v>
       </c>
     </row>
@@ -4714,13 +4805,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4728,10 +4819,10 @@
         <v>46023</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4739,10 +4830,10 @@
         <v>46048</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -4750,10 +4841,10 @@
         <v>46083</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4761,10 +4852,10 @@
         <v>46090</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -4772,10 +4863,10 @@
         <v>46115</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -4783,10 +4874,10 @@
         <v>46116</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -4794,10 +4885,10 @@
         <v>46117</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -4805,10 +4896,10 @@
         <v>46118</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -4816,10 +4907,10 @@
         <v>46137</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -4827,10 +4918,10 @@
         <v>46139</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -4838,10 +4929,10 @@
         <v>46146</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -4849,10 +4940,10 @@
         <v>46174</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -4860,10 +4951,10 @@
         <v>46181</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -4871,10 +4962,10 @@
         <v>46237</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -4882,10 +4973,10 @@
         <v>46290</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -4893,10 +4984,10 @@
         <v>46300</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -4904,10 +4995,10 @@
         <v>46381</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -4915,10 +5006,10 @@
         <v>46382</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -4926,10 +5017,10 @@
         <v>46384</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -4937,10 +5028,10 @@
         <v>46388</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -4948,10 +5039,10 @@
         <v>46413</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -4959,10 +5050,10 @@
         <v>46447</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -4970,10 +5061,10 @@
         <v>46454</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -4981,10 +5072,10 @@
         <v>46472</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -4992,10 +5083,10 @@
         <v>46473</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -5003,10 +5094,10 @@
         <v>46474</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -5014,10 +5105,10 @@
         <v>46475</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -5025,10 +5116,10 @@
         <v>46502</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -5036,10 +5127,10 @@
         <v>46503</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -5047,10 +5138,10 @@
         <v>46510</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -5058,10 +5149,10 @@
         <v>46538</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -5069,10 +5160,10 @@
         <v>46545</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -5080,10 +5171,10 @@
         <v>46552</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -5091,10 +5182,10 @@
         <v>46601</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -5102,10 +5193,10 @@
         <v>46664</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -5113,10 +5204,10 @@
         <v>46746</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -5124,10 +5215,10 @@
         <v>46747</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -5135,10 +5226,10 @@
         <v>46748</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -5146,20 +5237,20 @@
         <v>46749</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -5181,22 +5272,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -5213,10 +5304,10 @@
         <v>365</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -5233,10 +5324,10 @@
         <v>365</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -5253,15 +5344,15 @@
         <v>365</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -5283,19 +5374,19 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B1" s="5"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B2" s="13">
         <v>46244</v>
       </c>
       <c r="C2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D2" s="9">
         <f>IF(Summary!$B$2="","",IF(ISNUMBER(Summary!$B$2),INT(Summary!$B$2),Summary!$B$2))</f>
@@ -5304,11 +5395,11 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D3" s="9" t="str">
         <f>IF(Summary!$B$3="","",IF(ISNUMBER(Summary!$B$3),INT(Summary!$B$3),Summary!$B$3))</f>
@@ -5317,23 +5408,23 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B6" s="13">
         <v>46630</v>
@@ -5341,7 +5432,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B7" s="9">
         <f>_xlfn.MAXIFS(tblGic[to],tblGic[basis],"known")</f>
@@ -5350,7 +5441,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B9" s="5"/>
     </row>
@@ -5410,7 +5501,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B16" s="10">
         <f>SUM(tblLines[Exposed])</f>
@@ -5419,7 +5510,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B17" s="11">
         <f>ROUND(SUM(tblLines[Shortfall_r]),2)</f>
@@ -5428,7 +5519,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B18" s="11">
         <f>ROUND(SUM(tblLines[NEC_r]),2)</f>
@@ -5437,7 +5528,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B19" s="11">
         <f>ROUND(SUM(tblLines[SGC_low]),2)</f>
@@ -5446,7 +5537,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B20" s="11">
         <f>ROUND(SUM(tblLines[SGC_high]),2)</f>
@@ -5455,7 +5546,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B21" s="10">
         <f>SUMPRODUCT(--(tblLines[Unassessable_between]&lt;&gt;""))</f>
@@ -5464,7 +5555,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B22" s="10" t="str">
         <f>IF(AND(SUM(tblLines[Assessable])&gt;0,SUMPRODUCT(tblLines[Assessable]*tblLines[Receipt_established])=0),"YES","NO")</f>
@@ -5521,21 +5612,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B2" s="10" t="str">
         <f>IF(C2=0,"PASS","BLOCKED")</f>
@@ -5552,7 +5643,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B3" s="10" t="str">
         <f>IF(C3=0,"PASS","BLOCKED")</f>
@@ -5569,7 +5660,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B4" s="10" t="str">
         <f>IF(OR(C4=0,Summary!$B$4="Y"),"PASS","BLOCKED")</f>
@@ -5586,7 +5677,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B5" s="10" t="str">
         <f>IF(C5=0,"PASS","REVIEW")</f>
@@ -5603,7 +5694,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B6" s="10" t="str">
         <f>IF(C6=0,"PASS","REVIEW")</f>
@@ -5620,7 +5711,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B7" s="10" t="str">
         <f>IF(OR(Summary!B22="NO",Summary!$B$5="Y"),"PASS","REVIEW")</f>
@@ -5634,7 +5725,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B8" s="10" t="str">
         <f>IF(C8=0,"PASS","NOTE")</f>
@@ -5651,7 +5742,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B9" s="10" t="str">
         <f>IF(C9=0,"PASS","NOTE")</f>
@@ -5668,7 +5759,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B10" s="10" t="str">
         <f>IF(C10=0,"PASS","NOTE")</f>
@@ -5685,7 +5776,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B11" s="10" t="str">
         <f>IF(C11=0,"PASS","NOTE")</f>
@@ -5702,7 +5793,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B12" s="10" t="str">
         <f>IF(AND(ISNUMBER(Summary!$D$2),Summary!$D$2&lt;=DATE(2200,12,31),OR(Summary!$D$3="",AND(ISNUMBER(Summary!$D$3),Summary!$D$3&lt;=DATE(2200,12,31))),AND(ISNUMBER(Summary!$B$6),Summary!$B$6&lt;=DATE(2200,12,31))),"PASS","BLOCKED")</f>
@@ -5716,7 +5807,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B13" s="10" t="str">
         <f>IF(C13=0,"PASS","REVIEW")</f>
@@ -5733,7 +5824,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B14" s="10" t="str">
         <f>IF(C14=0,"PASS","NOTE")</f>
@@ -5759,37 +5850,37 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -5820,74 +5911,74 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B2" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B3" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B4" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B5" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B6" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B7" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B8" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B9" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>

--- a/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
+++ b/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
@@ -64,7 +64,7 @@
     <t>Overall status</t>
   </si>
   <si>
-    <t>payday-super-checker workbook, engine 0.1.6. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
+    <t>payday-super-checker workbook, engine 0.1.7. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
   </si>
   <si>
     <t>employee_id</t>
@@ -727,7 +727,7 @@
     <t>Workbook engine version</t>
   </si>
   <si>
-    <t>0.1.6</t>
+    <t>0.1.7</t>
   </si>
   <si>
     <t>Desktop Excel build used to calculate cached values</t>

--- a/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
+++ b/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F6011A-7861-4CA8-82EF-978CC715DE7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97531ECB-8F1C-465D-AC4B-CE651390D68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="38700" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="38700" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -5522,7 +5522,7 @@
         <v>197</v>
       </c>
       <c r="B18" s="11">
-        <f>ROUND(SUM(tblLines[NEC_r]),2)</f>
+        <f>IF(SUM(tblLines[Past_gic_table])&gt;0,"Not assessed",ROUND(SUM(tblLines[NEC_r]),2))</f>
         <v>8.07</v>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
         <v>198</v>
       </c>
       <c r="B19" s="11">
-        <f>ROUND(SUM(tblLines[SGC_low]),2)</f>
+        <f>IF(SUM(tblLines[Past_gic_table])&gt;0,"Not assessed",ROUND(SUM(tblLines[SGC_low]),2))</f>
         <v>788.07</v>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
         <v>199</v>
       </c>
       <c r="B20" s="11">
-        <f>ROUND(SUM(tblLines[SGC_high]),2)</f>
+        <f>IF(SUM(tblLines[Past_gic_table])&gt;0,"Not assessed",ROUND(SUM(tblLines[SGC_high]),2))</f>
         <v>1260.92</v>
       </c>
     </row>

--- a/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
+++ b/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97531ECB-8F1C-465D-AC4B-CE651390D68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4241CEB7-3E15-411C-AA65-CBE4A4FB6F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="38700" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="26010" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
     <t>Overall status</t>
   </si>
   <si>
-    <t>payday-super-checker workbook, engine 0.1.7. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
+    <t>payday-super-checker workbook, engine 0.1.8. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
   </si>
   <si>
     <t>employee_id</t>
@@ -727,7 +727,7 @@
     <t>Workbook engine version</t>
   </si>
   <si>
-    <t>0.1.7</t>
+    <t>0.1.8</t>
   </si>
   <si>
     <t>Desktop Excel build used to calculate cached values</t>

--- a/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
+++ b/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4241CEB7-3E15-411C-AA65-CBE4A4FB6F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839199CD-7C52-46AA-A9A8-0122F3915034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-105" windowWidth="26010" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
     <t>Overall status</t>
   </si>
   <si>
-    <t>payday-super-checker workbook, engine 0.1.8. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
+    <t>payday-super-checker workbook, engine 0.1.9. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
   </si>
   <si>
     <t>employee_id</t>
@@ -727,7 +727,7 @@
     <t>Workbook engine version</t>
   </si>
   <si>
-    <t>0.1.8</t>
+    <t>0.1.9</t>
   </si>
   <si>
     <t>Desktop Excel build used to calculate cached values</t>

--- a/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
+++ b/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839199CD-7C52-46AA-A9A8-0122F3915034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4593B09-3248-44A7-A3EF-A639E9D9BAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="26010" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-210" windowWidth="26010" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
     <t>Overall status</t>
   </si>
   <si>
-    <t>payday-super-checker workbook, engine 0.1.9. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
+    <t>payday-super-checker workbook, engine 0.1.10. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
   </si>
   <si>
     <t>employee_id</t>
@@ -727,7 +727,7 @@
     <t>Workbook engine version</t>
   </si>
   <si>
-    <t>0.1.9</t>
+    <t>0.1.10</t>
   </si>
   <si>
     <t>Desktop Excel build used to calculate cached values</t>
@@ -769,7 +769,7 @@
     <t>Experimental review aid. Not a compliance determination, not an ATO assessment, and not tax, legal or financial advice.</t>
   </si>
   <si>
-    <t>Excel 16.0 build 20430</t>
+    <t>Excel 16.0 build 20527</t>
   </si>
 </sst>
 </file>

--- a/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
+++ b/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4593B09-3248-44A7-A3EF-A639E9D9BAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32F06D13-291D-43E7-B999-81F098BB3FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-210" windowWidth="26010" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
     <t>Overall status</t>
   </si>
   <si>
-    <t>payday-super-checker workbook, engine 0.1.10. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
+    <t>payday-super-checker workbook, engine 0.2.0. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
   </si>
   <si>
     <t>employee_id</t>
@@ -727,7 +727,7 @@
     <t>Workbook engine version</t>
   </si>
   <si>
-    <t>0.1.10</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Desktop Excel build used to calculate cached values</t>

--- a/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
+++ b/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32F06D13-291D-43E7-B999-81F098BB3FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760613AB-705D-4304-957A-3DC8DCE4E648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-210" windowWidth="26010" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
     <t>Overall status</t>
   </si>
   <si>
-    <t>payday-super-checker workbook, engine 0.2.0. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
+    <t>payday-super-checker workbook, engine 0.2.1. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
   </si>
   <si>
     <t>employee_id</t>
@@ -727,7 +727,7 @@
     <t>Workbook engine version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Desktop Excel build used to calculate cached values</t>

--- a/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
+++ b/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760613AB-705D-4304-957A-3DC8DCE4E648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5F2A57-E062-415A-9046-F4E04A360CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-210" windowWidth="26010" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
     <t>Overall status</t>
   </si>
   <si>
-    <t>payday-super-checker workbook, engine 0.2.1. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
+    <t>payday-super-checker workbook, engine 0.2.2. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
   </si>
   <si>
     <t>employee_id</t>
@@ -727,7 +727,7 @@
     <t>Workbook engine version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.2</t>
   </si>
   <si>
     <t>Desktop Excel build used to calculate cached values</t>

--- a/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
+++ b/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30527"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5F2A57-E062-415A-9046-F4E04A360CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F14F91-9DAD-4A81-8B71-ECFB355BE3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-210" windowWidth="26010" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
     <t>Overall status</t>
   </si>
   <si>
-    <t>payday-super-checker workbook, engine 0.2.2. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
+    <t>payday-super-checker workbook, engine 1.0.0. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
   </si>
   <si>
     <t>employee_id</t>
@@ -727,7 +727,7 @@
     <t>Workbook engine version</t>
   </si>
   <si>
-    <t>0.2.2</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Desktop Excel build used to calculate cached values</t>
@@ -793,27 +793,37 @@
       <sz val="14"/>
       <color rgb="FF5C2D91"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1F4E9E"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -826,16 +836,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF3F1F6"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5C2D91"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2E0DF"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -884,64 +897,64 @@
   <dxfs count="9">
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD4EDDA"/>
+        <patternFill>
+          <bgColor rgb="FFD4EDDA"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF3CD"/>
+        <patternFill>
+          <bgColor rgb="FFFFF3CD"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8D7DA"/>
+        <patternFill>
+          <bgColor rgb="FFF8D7DA"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD4EDDA"/>
+        <patternFill>
+          <bgColor rgb="FFD4EDDA"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF3CD"/>
+        <patternFill>
+          <bgColor rgb="FFFFF3CD"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8D7DA"/>
+        <patternFill>
+          <bgColor rgb="FFF8D7DA"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD4EDDA"/>
+        <patternFill>
+          <bgColor rgb="FFD4EDDA"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF3CD"/>
+        <patternFill>
+          <bgColor rgb="FFFFF3CD"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8D7DA"/>
+        <patternFill>
+          <bgColor rgb="FFF8D7DA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -959,7 +972,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblLines" displayName="tblLines" ref="A1:BM11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblLines" displayName="tblLines" ref="A1:BM11" totalsRowShown="0">
   <tableColumns count="65">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="employee_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="payment_date"/>
@@ -1140,7 +1153,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="tblCodes" displayName="tblCodes" ref="A1:F30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="tblCodes" displayName="tblCodes" ref="A1:F30" totalsRowShown="0">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="code"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="verdict"/>
@@ -1154,7 +1167,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="tblHolidays" displayName="tblHolidays" ref="A1:C40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="tblHolidays" displayName="tblHolidays" ref="A1:C40" totalsRowShown="0">
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="date"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="name"/>
@@ -1165,7 +1178,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tblGic" displayName="tblGic" ref="A1:F4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tblGic" displayName="tblGic" ref="A1:F4" totalsRowShown="0">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="from"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="to"/>
@@ -1179,9 +1192,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1219,7 +1232,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1253,6 +1266,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1287,9 +1301,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1533,6 +1548,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>
 
@@ -4216,6 +4232,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -4788,6 +4805,7 @@
   </sheetData>
   <sheetProtection sheet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -5255,6 +5273,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -5357,6 +5376,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -5585,17 +5605,18 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" sqref="B4:B5" xr:uid="{00000000-0002-0000-0500-000000000000}">
-      <formula1>"Y,N"</formula1>
-    </dataValidation>
-    <dataValidation type="date" operator="greaterThan" sqref="B2 B6" xr:uid="{00000000-0002-0000-0500-000002000000}">
+    <dataValidation type="date" operator="greaterThan" sqref="B2 B6" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" sqref="B3" xr:uid="{00000000-0002-0000-0500-000003000000}">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" sqref="B3" xr:uid="{00000000-0002-0000-0500-000001000000}">
       <formula1>1</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="B4:B5" xr:uid="{00000000-0002-0000-0500-000002000000}">
+      <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>
 
@@ -5897,6 +5918,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>
 
@@ -5983,5 +6005,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>
--- a/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
+++ b/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5F2A57-E062-415A-9046-F4E04A360CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2F8871-6C91-43A6-A433-0D07A0B8A09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-210" windowWidth="26010" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
     <t>Overall status</t>
   </si>
   <si>
-    <t>payday-super-checker workbook, engine 0.2.2. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
+    <t>payday-super-checker workbook, engine 0.2.3. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
   </si>
   <si>
     <t>employee_id</t>
@@ -727,7 +727,7 @@
     <t>Workbook engine version</t>
   </si>
   <si>
-    <t>0.2.2</t>
+    <t>0.2.3</t>
   </si>
   <si>
     <t>Desktop Excel build used to calculate cached values</t>
